--- a/Iteration_1/Documentation/project_tracker.xlsx
+++ b/Iteration_1/Documentation/project_tracker.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F31D70-AAAB-4E2F-AFF2-C72DCA5710BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACC9BFC-0F23-4958-999F-76FB988F79BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Project tracker" sheetId="1" r:id="rId1"/>
-    <sheet name="Task Lookup" sheetId="3" r:id="rId2"/>
+    <sheet name="Project Tracker" sheetId="1" r:id="rId1"/>
+    <sheet name="Meeting Records" sheetId="3" r:id="rId2"/>
     <sheet name="Setup" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="CategoryList">Setup!$B$5:$B$29</definedName>
     <definedName name="EmployeeList">Setup!$C$5:$C$29</definedName>
-    <definedName name="FlagPercent">'Project tracker'!$G$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Project tracker'!$4:$4</definedName>
+    <definedName name="FlagPercent">'Project Tracker'!$G$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Project Tracker'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,27 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="66">
   <si>
     <t>Category</t>
   </si>
   <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>Category 1</t>
-  </si>
-  <si>
-    <t>Category 2</t>
-  </si>
-  <si>
-    <t>Category 3</t>
-  </si>
-  <si>
-    <t>Category 4</t>
-  </si>
-  <si>
-    <t>Category 5</t>
   </si>
   <si>
     <t>Setup</t>
@@ -69,12 +54,6 @@
   </si>
   <si>
     <t>Assigned to</t>
-  </si>
-  <si>
-    <t>Estimated work (in hours)</t>
-  </si>
-  <si>
-    <t>Estimated finish</t>
   </si>
   <si>
     <t>Actual start</t>
@@ -90,74 +69,13 @@
 (in hours)</t>
   </si>
   <si>
-    <t>Estimated start</t>
-  </si>
-  <si>
     <t>Percent over/under to highlighted numbers</t>
-  </si>
-  <si>
-    <t>Estimated duration
-(in days)</t>
   </si>
   <si>
     <t>Task</t>
   </si>
   <si>
-    <t>Task 1</t>
-  </si>
-  <si>
-    <t>Task 2</t>
-  </si>
-  <si>
-    <t>Task 3</t>
-  </si>
-  <si>
-    <t>Task 4</t>
-  </si>
-  <si>
-    <t>Task 5</t>
-  </si>
-  <si>
-    <t>Task 6</t>
-  </si>
-  <si>
-    <t>Task 7</t>
-  </si>
-  <si>
-    <t>Task 8</t>
-  </si>
-  <si>
-    <t>Task 9</t>
-  </si>
-  <si>
     <t>Project Task Tracker</t>
-  </si>
-  <si>
-    <t>Student 1</t>
-  </si>
-  <si>
-    <t>Student 2</t>
-  </si>
-  <si>
-    <t>Student 3</t>
-  </si>
-  <si>
-    <t>Student 5</t>
-  </si>
-  <si>
-    <t>Student 4</t>
-  </si>
-  <si>
-    <t>Student 6</t>
-  </si>
-  <si>
-    <t>Task Number</t>
-  </si>
-  <si>
-    <t>Task Name</t>
-  </si>
-  <si>
-    <t>Task Description</t>
   </si>
   <si>
     <t>Plan</t>
@@ -252,6 +170,72 @@
   <si>
     <t>Alan Bach</t>
   </si>
+  <si>
+    <t>Start Game - use case description</t>
+  </si>
+  <si>
+    <t>Game Handler - structure diagram</t>
+  </si>
+  <si>
+    <t>Choose A Side - use case description</t>
+  </si>
+  <si>
+    <t>Resign Game - use case description</t>
+  </si>
+  <si>
+    <t>Place A Piece - use case description</t>
+  </si>
+  <si>
+    <t>Alan Bach, Anmoldeep Gill, Ethan Braum credited with the same task</t>
+  </si>
+  <si>
+    <t>Alan Bach credited with the same task</t>
+  </si>
+  <si>
+    <t>Alan Bach, Ethan Barum credited with the same task</t>
+  </si>
+  <si>
+    <t>GameBoard - structure diagram</t>
+  </si>
+  <si>
+    <t>IGameHandler - structure diagram</t>
+  </si>
+  <si>
+    <t>Meeting Purpose</t>
+  </si>
+  <si>
+    <t>Team Involved</t>
+  </si>
+  <si>
+    <t>Meeting Date</t>
+  </si>
+  <si>
+    <t>Initial Team Meeting</t>
+  </si>
+  <si>
+    <t>All Members</t>
+  </si>
+  <si>
+    <t>Meeting Duration        (hours)</t>
+  </si>
+  <si>
+    <t>Network Team</t>
+  </si>
+  <si>
+    <t>SCRUM</t>
+  </si>
+  <si>
+    <t>Backend team</t>
+  </si>
+  <si>
+    <t>Initial Subteam Meeting</t>
+  </si>
+  <si>
+    <t>Frontend Team</t>
+  </si>
+  <si>
+    <t>Backend Team</t>
+  </si>
 </sst>
 </file>
 
@@ -260,7 +244,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;Over/Under flag&quot;;&quot;&quot;;&quot;&quot;"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="3" tint="-0.499984740745262"/>
@@ -417,6 +401,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Verdana"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -601,7 +592,7 @@
       <alignment horizontal="right" vertical="center" indent="3"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -621,9 +612,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="4" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="15" fillId="4" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
@@ -686,6 +674,15 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="Actual Start" xfId="13" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -705,7 +702,7 @@
     <cellStyle name="Text" xfId="5" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
     <cellStyle name="Title" xfId="9" builtinId="15" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="23">
     <dxf>
       <font>
         <b/>
@@ -748,90 +745,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="3" tint="-0.499984740745262"/>
-        <name val="Verdana"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="6" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="3" tint="-0.499984740745262"/>
-        <name val="Verdana"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Verdana"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Verdana"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1118,17 +1031,17 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Custom Table Style" defaultPivotStyle="PivotStyleMedium2">
     <tableStyle name="Custom Table Style" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="26"/>
-      <tableStyleElement type="headerRow" dxfId="25"/>
+      <tableStyleElement type="wholeTable" dxfId="22"/>
+      <tableStyleElement type="headerRow" dxfId="21"/>
     </tableStyle>
     <tableStyle name="Custom Table Style 2" pivot="0" count="2" xr9:uid="{FFDA21C0-6F5D-4BB1-A228-A4BC4D9DA682}">
-      <tableStyleElement type="wholeTable" dxfId="24"/>
-      <tableStyleElement type="headerRow" dxfId="23"/>
+      <tableStyleElement type="wholeTable" dxfId="20"/>
+      <tableStyleElement type="headerRow" dxfId="19"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="3" xr9:uid="{5F9F0DBC-1B06-494D-8D4F-D10423CEAFF4}">
-      <tableStyleElement type="headerRow" dxfId="22"/>
-      <tableStyleElement type="firstRowStripe" dxfId="21"/>
-      <tableStyleElement type="secondRowStripe" dxfId="20"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="firstRowStripe" dxfId="17"/>
+      <tableStyleElement type="secondRowStripe" dxfId="16"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1146,14 +1059,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>952966</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>323851</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>466</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1702266</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>598171</xdr:rowOff>
     </xdr:to>
@@ -1305,8 +1218,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectTracker" displayName="ProjectTracker" ref="B4:M13" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
-  <autoFilter ref="B4:M13" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectTracker" displayName="ProjectTracker" ref="B4:I563" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="B4:I563" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1315,26 +1228,16 @@
     <filterColumn colId="5" hiddenButton="1"/>
     <filterColumn colId="6" hiddenButton="1"/>
     <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-    <filterColumn colId="9" hiddenButton="1"/>
-    <filterColumn colId="10" hiddenButton="1"/>
-    <filterColumn colId="11" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Category" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Assigned to" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Estimated start" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Estimated finish" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Estimated work (in hours)" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Estimated duration_x000a_(in days)" dataDxfId="11">
-      <calculatedColumnFormula>IF(COUNTA('Project tracker'!$E5,'Project tracker'!$F5)&lt;&gt;2,"",DAYS360('Project tracker'!$E5,'Project tracker'!$F5,FALSE))</calculatedColumnFormula>
-    </tableColumn>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Category" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Assigned to" dataDxfId="11"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Actual start" dataDxfId="10"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Actual finish" dataDxfId="9"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actual work _x000a_(in hours)" dataDxfId="8"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Actual duration (in days)" dataDxfId="7">
-      <calculatedColumnFormula>IF(COUNTA('Project tracker'!$I5,'Project tracker'!$J5)&lt;&gt;2,"",DAYS360('Project tracker'!$I5,'Project tracker'!$J5,FALSE))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(COUNTA('Project Tracker'!$E5,'Project Tracker'!$F5)&lt;&gt;2,"",DAYS360('Project Tracker'!$E5,'Project Tracker'!$F5,FALSE))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Notes" dataDxfId="6"/>
   </tableColumns>
@@ -1597,23 +1500,23 @@
     <tabColor theme="6"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:J563"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7265625" style="3" customWidth="1"/>
-    <col min="2" max="4" width="18.7265625" style="19" customWidth="1"/>
-    <col min="5" max="6" width="18.7265625" style="20" customWidth="1"/>
-    <col min="7" max="8" width="18.7265625" style="19" customWidth="1"/>
-    <col min="9" max="10" width="16.81640625" style="20" customWidth="1"/>
-    <col min="11" max="12" width="16" style="19" customWidth="1"/>
-    <col min="13" max="13" width="20.36328125" style="19" customWidth="1"/>
-    <col min="14" max="14" width="6.7265625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="4.1796875" style="2" customWidth="1"/>
-    <col min="16" max="40" width="3.26953125" style="2" customWidth="1"/>
-    <col min="41" max="16384" width="9.08984375" style="2"/>
+    <col min="2" max="2" width="53.453125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="21.1796875" style="18" customWidth="1"/>
+    <col min="4" max="4" width="23.7265625" style="18" customWidth="1"/>
+    <col min="5" max="6" width="16.81640625" style="19" customWidth="1"/>
+    <col min="7" max="8" width="16" style="18" customWidth="1"/>
+    <col min="9" max="9" width="78.54296875" style="18" customWidth="1"/>
+    <col min="10" max="10" width="6.7265625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="4.1796875" style="2" customWidth="1"/>
+    <col min="12" max="36" width="3.26953125" style="2" customWidth="1"/>
+    <col min="37" max="16384" width="9.08984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1622,532 +1525,5817 @@
       <c r="F1" s="4"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-    </row>
-    <row r="2" spans="1:14" s="5" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" s="5" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="B2" s="26" t="s">
-        <v>30</v>
+      <c r="B2" s="25" t="s">
+        <v>12</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="9">
+      <c r="E2" s="4"/>
+      <c r="F2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="8">
         <v>0</v>
       </c>
       <c r="H2" s="3"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-    </row>
-    <row r="4" spans="1:14" s="5" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="17" t="s">
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" s="5" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="17" t="s">
+      <c r="D4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="10"/>
+    </row>
+    <row r="5" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="17" t="s">
+      <c r="D5" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="24">
+        <v>45595</v>
+      </c>
+      <c r="F5" s="24">
+        <v>45595</v>
+      </c>
+      <c r="G5" s="17">
         <v>1</v>
       </c>
-      <c r="N4" s="11"/>
-    </row>
-    <row r="5" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="18" t="s">
+      <c r="H5" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E5,'Project Tracker'!$F5)&lt;&gt;2,"",DAYS360('Project Tracker'!$E5,'Project Tracker'!$F5,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="17"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="24">
+        <v>45596</v>
+      </c>
+      <c r="F6" s="24">
+        <v>45596</v>
+      </c>
+      <c r="G6" s="17">
+        <v>1</v>
+      </c>
+      <c r="H6" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E6,'Project Tracker'!$F6)&lt;&gt;2,"",DAYS360('Project Tracker'!$E6,'Project Tracker'!$F6,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="24">
+        <v>45595</v>
+      </c>
+      <c r="F7" s="24">
+        <v>45595</v>
+      </c>
+      <c r="G7" s="17">
+        <v>1</v>
+      </c>
+      <c r="H7" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E7,'Project Tracker'!$F7)&lt;&gt;2,"",DAYS360('Project Tracker'!$E7,'Project Tracker'!$F7,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="17"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="25">
-        <f ca="1">TODAY()-65</f>
-        <v>45530</v>
-      </c>
-      <c r="F5" s="25">
-        <f ca="1">TODAY()-5</f>
-        <v>45590</v>
-      </c>
-      <c r="G5" s="18">
-        <v>4</v>
-      </c>
-      <c r="H5" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$E5,'Project tracker'!$F5)&lt;&gt;2,"",DAYS360('Project tracker'!$E5,'Project tracker'!$F5,FALSE))</f>
-        <v>59</v>
-      </c>
-      <c r="I5" s="25">
-        <f ca="1">TODAY()-65</f>
-        <v>45530</v>
-      </c>
-      <c r="J5" s="25">
-        <f ca="1">TODAY()</f>
+      <c r="E8" s="24">
         <v>45595</v>
       </c>
-      <c r="K5" s="18">
-        <v>5</v>
-      </c>
-      <c r="L5" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$I5,'Project tracker'!$J5)&lt;&gt;2,"",DAYS360('Project tracker'!$I5,'Project tracker'!$J5,FALSE))</f>
-        <v>64</v>
-      </c>
-      <c r="M5" s="18"/>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="25">
-        <f ca="1">TODAY()-41</f>
-        <v>45554</v>
-      </c>
-      <c r="F6" s="25">
-        <f ca="1">TODAY()-10</f>
-        <v>45585</v>
-      </c>
-      <c r="G6" s="18">
-        <v>4</v>
-      </c>
-      <c r="H6" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$E6,'Project tracker'!$F6)&lt;&gt;2,"",DAYS360('Project tracker'!$E6,'Project tracker'!$F6,FALSE))</f>
-        <v>31</v>
-      </c>
-      <c r="I6" s="25">
-        <f ca="1">TODAY()-41</f>
-        <v>45554</v>
-      </c>
-      <c r="J6" s="25">
-        <f ca="1">TODAY()-7</f>
-        <v>45588</v>
-      </c>
-      <c r="K6" s="18">
-        <v>6</v>
-      </c>
-      <c r="L6" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$I6,'Project tracker'!$J6)&lt;&gt;2,"",DAYS360('Project tracker'!$I6,'Project tracker'!$J6,FALSE))</f>
-        <v>34</v>
-      </c>
-      <c r="M6" s="18"/>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="25">
-        <f ca="1">TODAY()-100</f>
-        <v>45495</v>
-      </c>
-      <c r="F7" s="25">
-        <f ca="1">TODAY()-40</f>
-        <v>45555</v>
-      </c>
-      <c r="G7" s="18">
-        <v>5</v>
-      </c>
-      <c r="H7" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$E7,'Project tracker'!$F7)&lt;&gt;2,"",DAYS360('Project tracker'!$E7,'Project tracker'!$F7,FALSE))</f>
-        <v>58</v>
-      </c>
-      <c r="I7" s="25">
-        <f ca="1">TODAY()-100</f>
-        <v>45495</v>
-      </c>
-      <c r="J7" s="25">
-        <f ca="1">TODAY()-27</f>
-        <v>45568</v>
-      </c>
-      <c r="K7" s="18">
-        <v>4</v>
-      </c>
-      <c r="L7" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$I7,'Project tracker'!$J7)&lt;&gt;2,"",DAYS360('Project tracker'!$I7,'Project tracker'!$J7,FALSE))</f>
-        <v>71</v>
-      </c>
-      <c r="M7" s="18"/>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="25">
-        <f ca="1">TODAY()-90</f>
-        <v>45505</v>
-      </c>
-      <c r="F8" s="25">
-        <f ca="1">TODAY()-80</f>
-        <v>45515</v>
-      </c>
-      <c r="G8" s="18">
-        <v>6</v>
-      </c>
-      <c r="H8" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$E8,'Project tracker'!$F8)&lt;&gt;2,"",DAYS360('Project tracker'!$E8,'Project tracker'!$F8,FALSE))</f>
-        <v>10</v>
-      </c>
-      <c r="I8" s="25">
-        <f ca="1">TODAY()-90</f>
-        <v>45505</v>
-      </c>
-      <c r="J8" s="25">
-        <f ca="1">TODAY()-71</f>
-        <v>45524</v>
-      </c>
-      <c r="K8" s="18">
+      <c r="F8" s="24">
+        <v>45596</v>
+      </c>
+      <c r="G8" s="17">
         <v>1</v>
       </c>
-      <c r="L8" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$I8,'Project tracker'!$J8)&lt;&gt;2,"",DAYS360('Project tracker'!$I8,'Project tracker'!$J8,FALSE))</f>
-        <v>19</v>
-      </c>
-      <c r="M8" s="18"/>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H8" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E8,'Project Tracker'!$F8)&lt;&gt;2,"",DAYS360('Project Tracker'!$E8,'Project Tracker'!$F8,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
-      <c r="B9" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="25">
-        <f ca="1">TODAY()-90</f>
-        <v>45505</v>
-      </c>
-      <c r="F9" s="25">
-        <f ca="1">TODAY()-50</f>
-        <v>45545</v>
-      </c>
-      <c r="G9" s="18">
-        <v>4</v>
-      </c>
-      <c r="H9" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$E9,'Project tracker'!$F9)&lt;&gt;2,"",DAYS360('Project tracker'!$E9,'Project tracker'!$F9,FALSE))</f>
-        <v>39</v>
-      </c>
-      <c r="I9" s="25">
-        <f ca="1">TODAY()-90</f>
-        <v>45505</v>
-      </c>
-      <c r="J9" s="25">
-        <f ca="1">TODAY()-44</f>
-        <v>45551</v>
-      </c>
-      <c r="K9" s="18">
+      <c r="B9" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="24">
+        <v>45595</v>
+      </c>
+      <c r="F9" s="24">
+        <v>45595</v>
+      </c>
+      <c r="G9" s="17">
         <v>1</v>
       </c>
-      <c r="L9" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$I9,'Project tracker'!$J9)&lt;&gt;2,"",DAYS360('Project tracker'!$I9,'Project tracker'!$J9,FALSE))</f>
-        <v>45</v>
-      </c>
-      <c r="M9" s="18"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H9" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E9,'Project Tracker'!$F9)&lt;&gt;2,"",DAYS360('Project Tracker'!$E9,'Project Tracker'!$F9,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="25">
-        <f ca="1">TODAY()-60</f>
-        <v>45535</v>
-      </c>
-      <c r="F10" s="25">
-        <f ca="1">TODAY()-50</f>
-        <v>45545</v>
-      </c>
-      <c r="G10" s="18">
-        <v>5</v>
-      </c>
-      <c r="H10" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$E10,'Project tracker'!$F10)&lt;&gt;2,"",DAYS360('Project tracker'!$E10,'Project tracker'!$F10,FALSE))</f>
-        <v>10</v>
-      </c>
-      <c r="I10" s="25">
-        <f ca="1">TODAY()-60</f>
-        <v>45535</v>
-      </c>
-      <c r="J10" s="25">
-        <f ca="1">TODAY()-45</f>
-        <v>45550</v>
-      </c>
-      <c r="K10" s="18">
-        <v>6</v>
-      </c>
-      <c r="L10" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$I10,'Project tracker'!$J10)&lt;&gt;2,"",DAYS360('Project tracker'!$I10,'Project tracker'!$J10,FALSE))</f>
-        <v>15</v>
-      </c>
-      <c r="M10" s="18"/>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="24">
+        <v>45595</v>
+      </c>
+      <c r="F10" s="24">
+        <v>45595</v>
+      </c>
+      <c r="G10" s="17">
+        <v>1</v>
+      </c>
+      <c r="H10" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E10,'Project Tracker'!$F10)&lt;&gt;2,"",DAYS360('Project Tracker'!$E10,'Project Tracker'!$F10,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
-      <c r="B11" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="25">
-        <f ca="1">TODAY()-44</f>
-        <v>45551</v>
-      </c>
-      <c r="F11" s="25">
-        <f ca="1">TODAY()-20</f>
-        <v>45575</v>
-      </c>
-      <c r="G11" s="18">
+      <c r="B11" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="24">
+        <v>45595</v>
+      </c>
+      <c r="F11" s="24">
+        <v>45595</v>
+      </c>
+      <c r="G11" s="17">
         <v>1</v>
       </c>
-      <c r="H11" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$E11,'Project tracker'!$F11)&lt;&gt;2,"",DAYS360('Project tracker'!$E11,'Project tracker'!$F11,FALSE))</f>
-        <v>24</v>
-      </c>
-      <c r="I11" s="25">
-        <f ca="1">TODAY()-44</f>
-        <v>45551</v>
-      </c>
-      <c r="J11" s="25">
-        <f ca="1">TODAY()-15</f>
-        <v>45580</v>
-      </c>
-      <c r="K11" s="18">
-        <v>5</v>
-      </c>
-      <c r="L11" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$I11,'Project tracker'!$J11)&lt;&gt;2,"",DAYS360('Project tracker'!$I11,'Project tracker'!$J11,FALSE))</f>
-        <v>29</v>
-      </c>
-      <c r="M11" s="18"/>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H11" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E11,'Project Tracker'!$F11)&lt;&gt;2,"",DAYS360('Project Tracker'!$E11,'Project Tracker'!$F11,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
-      <c r="B12" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="25">
-        <f ca="1">TODAY()-39</f>
-        <v>45556</v>
-      </c>
-      <c r="F12" s="25">
-        <f ca="1">TODAY()</f>
-        <v>45595</v>
-      </c>
-      <c r="G12" s="18">
-        <v>1</v>
-      </c>
-      <c r="H12" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$E12,'Project tracker'!$F12)&lt;&gt;2,"",DAYS360('Project tracker'!$E12,'Project tracker'!$F12,FALSE))</f>
-        <v>39</v>
-      </c>
-      <c r="I12" s="25">
-        <f ca="1">TODAY()-45</f>
-        <v>45550</v>
-      </c>
-      <c r="J12" s="25">
-        <f ca="1">TODAY()-5</f>
-        <v>45590</v>
-      </c>
-      <c r="K12" s="18">
-        <v>7</v>
-      </c>
-      <c r="L12" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$I12,'Project tracker'!$J12)&lt;&gt;2,"",DAYS360('Project tracker'!$I12,'Project tracker'!$J12,FALSE))</f>
-        <v>40</v>
-      </c>
-      <c r="M12" s="18"/>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="25">
-        <f ca="1">TODAY()-95</f>
-        <v>45500</v>
-      </c>
-      <c r="F13" s="25">
-        <f ca="1">TODAY()-75</f>
-        <v>45520</v>
-      </c>
-      <c r="G13" s="18">
-        <v>1</v>
-      </c>
-      <c r="H13" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$E13,'Project tracker'!$F13)&lt;&gt;2,"",DAYS360('Project tracker'!$E13,'Project tracker'!$F13,FALSE))</f>
-        <v>19</v>
-      </c>
-      <c r="I13" s="25">
-        <f ca="1">TODAY()-90</f>
-        <v>45505</v>
-      </c>
-      <c r="J13" s="25">
-        <f ca="1">TODAY()-80</f>
-        <v>45515</v>
-      </c>
-      <c r="K13" s="18">
-        <v>7</v>
-      </c>
-      <c r="L13" s="21">
-        <f ca="1">IF(COUNTA('Project tracker'!$I13,'Project tracker'!$J13)&lt;&gt;2,"",DAYS360('Project tracker'!$I13,'Project tracker'!$J13,FALSE))</f>
-        <v>10</v>
-      </c>
-      <c r="M13" s="18"/>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="3"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="17"/>
+    </row>
+    <row r="17" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="17"/>
+    </row>
+    <row r="18" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="17"/>
+    </row>
+    <row r="19" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="17"/>
+    </row>
+    <row r="21" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="17"/>
+    </row>
+    <row r="22" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="17"/>
+    </row>
+    <row r="23" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="17"/>
+    </row>
+    <row r="24" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="17"/>
+    </row>
+    <row r="25" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="17"/>
+    </row>
+    <row r="26" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="17"/>
+    </row>
+    <row r="27" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="17"/>
+    </row>
+    <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="17"/>
+    </row>
+    <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="17"/>
+    </row>
+    <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="17"/>
+    </row>
+    <row r="31" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="17"/>
+    </row>
+    <row r="32" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="17"/>
+    </row>
+    <row r="33" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="17"/>
+    </row>
+    <row r="34" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="17"/>
+    </row>
+    <row r="35" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="17"/>
+    </row>
+    <row r="36" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="17"/>
+    </row>
+    <row r="37" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="17"/>
+    </row>
+    <row r="38" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="17"/>
+    </row>
+    <row r="39" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="17"/>
+    </row>
+    <row r="40" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="17"/>
+    </row>
+    <row r="41" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="17"/>
+    </row>
+    <row r="42" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="17"/>
+    </row>
+    <row r="43" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="17"/>
+    </row>
+    <row r="44" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="17"/>
+    </row>
+    <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="17"/>
+    </row>
+    <row r="46" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="17"/>
+    </row>
+    <row r="47" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="17"/>
+    </row>
+    <row r="48" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="17"/>
+    </row>
+    <row r="49" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="17"/>
+    </row>
+    <row r="50" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="17"/>
+    </row>
+    <row r="51" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="17"/>
+    </row>
+    <row r="52" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="17"/>
+    </row>
+    <row r="53" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="17"/>
+    </row>
+    <row r="54" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="17"/>
+    </row>
+    <row r="55" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="17"/>
+    </row>
+    <row r="56" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="17"/>
+    </row>
+    <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="17"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="17"/>
+    </row>
+    <row r="58" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="17"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="17"/>
+    </row>
+    <row r="59" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="17"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="17"/>
+    </row>
+    <row r="60" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="17"/>
+    </row>
+    <row r="61" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="17"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="20"/>
+      <c r="I61" s="17"/>
+    </row>
+    <row r="62" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="17"/>
+    </row>
+    <row r="63" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="17"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="17"/>
+    </row>
+    <row r="64" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="17"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="17"/>
+    </row>
+    <row r="65" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="17"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="17"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="17"/>
+    </row>
+    <row r="66" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="17"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="17"/>
+      <c r="H66" s="20"/>
+      <c r="I66" s="17"/>
+    </row>
+    <row r="67" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="17"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="20"/>
+      <c r="I67" s="17"/>
+    </row>
+    <row r="68" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="20"/>
+      <c r="I68" s="17"/>
+    </row>
+    <row r="69" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="17"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="17"/>
+      <c r="H69" s="20"/>
+      <c r="I69" s="17"/>
+    </row>
+    <row r="70" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="17"/>
+      <c r="C70" s="17"/>
+      <c r="D70" s="17"/>
+      <c r="E70" s="24"/>
+      <c r="F70" s="24"/>
+      <c r="G70" s="17"/>
+      <c r="H70" s="20"/>
+      <c r="I70" s="17"/>
+    </row>
+    <row r="71" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="17"/>
+      <c r="C71" s="17"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="24"/>
+      <c r="F71" s="24"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="20"/>
+      <c r="I71" s="17"/>
+    </row>
+    <row r="72" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="17"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="24"/>
+      <c r="F72" s="24"/>
+      <c r="G72" s="17"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="17"/>
+    </row>
+    <row r="73" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="17"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="17"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="17"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="17"/>
+    </row>
+    <row r="74" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="17"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="17"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="17"/>
+      <c r="H74" s="20"/>
+      <c r="I74" s="17"/>
+    </row>
+    <row r="75" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
+      <c r="D75" s="17"/>
+      <c r="E75" s="24"/>
+      <c r="F75" s="24"/>
+      <c r="G75" s="17"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="17"/>
+    </row>
+    <row r="76" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="17"/>
+      <c r="C76" s="17"/>
+      <c r="D76" s="17"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="17"/>
+      <c r="H76" s="20"/>
+      <c r="I76" s="17"/>
+    </row>
+    <row r="77" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="17"/>
+      <c r="C77" s="17"/>
+      <c r="D77" s="17"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="17"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="17"/>
+    </row>
+    <row r="78" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="17"/>
+      <c r="C78" s="17"/>
+      <c r="D78" s="17"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="17"/>
+      <c r="H78" s="20"/>
+      <c r="I78" s="17"/>
+    </row>
+    <row r="79" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="17"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="17"/>
+      <c r="E79" s="24"/>
+      <c r="F79" s="24"/>
+      <c r="G79" s="17"/>
+      <c r="H79" s="20"/>
+      <c r="I79" s="17"/>
+    </row>
+    <row r="80" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="17"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="17"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="17"/>
+      <c r="H80" s="20"/>
+      <c r="I80" s="17"/>
+    </row>
+    <row r="81" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="17"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="24"/>
+      <c r="F81" s="24"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="20"/>
+      <c r="I81" s="17"/>
+    </row>
+    <row r="82" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="17"/>
+      <c r="C82" s="17"/>
+      <c r="D82" s="17"/>
+      <c r="E82" s="24"/>
+      <c r="F82" s="24"/>
+      <c r="G82" s="17"/>
+      <c r="H82" s="20"/>
+      <c r="I82" s="17"/>
+    </row>
+    <row r="83" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="17"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
+      <c r="E83" s="24"/>
+      <c r="F83" s="24"/>
+      <c r="G83" s="17"/>
+      <c r="H83" s="20"/>
+      <c r="I83" s="17"/>
+    </row>
+    <row r="84" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="17"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="24"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="17"/>
+      <c r="H84" s="20"/>
+      <c r="I84" s="17"/>
+    </row>
+    <row r="85" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="17"/>
+      <c r="C85" s="17"/>
+      <c r="D85" s="17"/>
+      <c r="E85" s="24"/>
+      <c r="F85" s="24"/>
+      <c r="G85" s="17"/>
+      <c r="H85" s="20"/>
+      <c r="I85" s="17"/>
+    </row>
+    <row r="86" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="17"/>
+      <c r="C86" s="17"/>
+      <c r="D86" s="17"/>
+      <c r="E86" s="24"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="17"/>
+      <c r="H86" s="20"/>
+      <c r="I86" s="17"/>
+    </row>
+    <row r="87" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="17"/>
+      <c r="C87" s="17"/>
+      <c r="D87" s="17"/>
+      <c r="E87" s="24"/>
+      <c r="F87" s="24"/>
+      <c r="G87" s="17"/>
+      <c r="H87" s="20"/>
+      <c r="I87" s="17"/>
+    </row>
+    <row r="88" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="17"/>
+      <c r="C88" s="17"/>
+      <c r="D88" s="17"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="17"/>
+      <c r="H88" s="20"/>
+      <c r="I88" s="17"/>
+    </row>
+    <row r="89" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="17"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="17"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="24"/>
+      <c r="G89" s="17"/>
+      <c r="H89" s="20"/>
+      <c r="I89" s="17"/>
+    </row>
+    <row r="90" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="17"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="17"/>
+      <c r="E90" s="24"/>
+      <c r="F90" s="24"/>
+      <c r="G90" s="17"/>
+      <c r="H90" s="20"/>
+      <c r="I90" s="17"/>
+    </row>
+    <row r="91" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="17"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="17"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="17"/>
+      <c r="H91" s="20"/>
+      <c r="I91" s="17"/>
+    </row>
+    <row r="92" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="17"/>
+      <c r="C92" s="17"/>
+      <c r="D92" s="17"/>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="17"/>
+      <c r="H92" s="20"/>
+      <c r="I92" s="17"/>
+    </row>
+    <row r="93" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="17"/>
+      <c r="C93" s="17"/>
+      <c r="D93" s="17"/>
+      <c r="E93" s="24"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="17"/>
+      <c r="H93" s="20"/>
+      <c r="I93" s="17"/>
+    </row>
+    <row r="94" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="17"/>
+      <c r="C94" s="17"/>
+      <c r="D94" s="17"/>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="17"/>
+      <c r="H94" s="20"/>
+      <c r="I94" s="17"/>
+    </row>
+    <row r="95" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="17"/>
+      <c r="C95" s="17"/>
+      <c r="D95" s="17"/>
+      <c r="E95" s="24"/>
+      <c r="F95" s="24"/>
+      <c r="G95" s="17"/>
+      <c r="H95" s="20"/>
+      <c r="I95" s="17"/>
+    </row>
+    <row r="96" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="17"/>
+      <c r="C96" s="17"/>
+      <c r="D96" s="17"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="17"/>
+      <c r="H96" s="20"/>
+      <c r="I96" s="17"/>
+    </row>
+    <row r="97" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="17"/>
+      <c r="C97" s="17"/>
+      <c r="D97" s="17"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="17"/>
+      <c r="H97" s="20"/>
+      <c r="I97" s="17"/>
+    </row>
+    <row r="98" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="17"/>
+      <c r="C98" s="17"/>
+      <c r="D98" s="17"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="17"/>
+      <c r="H98" s="20"/>
+      <c r="I98" s="17"/>
+    </row>
+    <row r="99" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="17"/>
+      <c r="C99" s="17"/>
+      <c r="D99" s="17"/>
+      <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="17"/>
+      <c r="H99" s="20"/>
+      <c r="I99" s="17"/>
+    </row>
+    <row r="100" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="17"/>
+      <c r="C100" s="17"/>
+      <c r="D100" s="17"/>
+      <c r="E100" s="24"/>
+      <c r="F100" s="24"/>
+      <c r="G100" s="17"/>
+      <c r="H100" s="20"/>
+      <c r="I100" s="17"/>
+    </row>
+    <row r="101" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="17"/>
+      <c r="C101" s="17"/>
+      <c r="D101" s="17"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="17"/>
+      <c r="H101" s="20"/>
+      <c r="I101" s="17"/>
+    </row>
+    <row r="102" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="17"/>
+      <c r="C102" s="17"/>
+      <c r="D102" s="17"/>
+      <c r="E102" s="24"/>
+      <c r="F102" s="24"/>
+      <c r="G102" s="17"/>
+      <c r="H102" s="20"/>
+      <c r="I102" s="17"/>
+    </row>
+    <row r="103" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="17"/>
+      <c r="C103" s="17"/>
+      <c r="D103" s="17"/>
+      <c r="E103" s="24"/>
+      <c r="F103" s="24"/>
+      <c r="G103" s="17"/>
+      <c r="H103" s="20"/>
+      <c r="I103" s="17"/>
+    </row>
+    <row r="104" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="17"/>
+      <c r="C104" s="17"/>
+      <c r="D104" s="17"/>
+      <c r="E104" s="24"/>
+      <c r="F104" s="24"/>
+      <c r="G104" s="17"/>
+      <c r="H104" s="20"/>
+      <c r="I104" s="17"/>
+    </row>
+    <row r="105" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="17"/>
+      <c r="C105" s="17"/>
+      <c r="D105" s="17"/>
+      <c r="E105" s="24"/>
+      <c r="F105" s="24"/>
+      <c r="G105" s="17"/>
+      <c r="H105" s="20"/>
+      <c r="I105" s="17"/>
+    </row>
+    <row r="106" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="17"/>
+      <c r="C106" s="17"/>
+      <c r="D106" s="17"/>
+      <c r="E106" s="24"/>
+      <c r="F106" s="24"/>
+      <c r="G106" s="17"/>
+      <c r="H106" s="20"/>
+      <c r="I106" s="17"/>
+    </row>
+    <row r="107" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="17"/>
+      <c r="C107" s="17"/>
+      <c r="D107" s="17"/>
+      <c r="E107" s="24"/>
+      <c r="F107" s="24"/>
+      <c r="G107" s="17"/>
+      <c r="H107" s="20"/>
+      <c r="I107" s="17"/>
+    </row>
+    <row r="108" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="17"/>
+      <c r="C108" s="17"/>
+      <c r="D108" s="17"/>
+      <c r="E108" s="24"/>
+      <c r="F108" s="24"/>
+      <c r="G108" s="17"/>
+      <c r="H108" s="20"/>
+      <c r="I108" s="17"/>
+    </row>
+    <row r="109" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="17"/>
+      <c r="C109" s="17"/>
+      <c r="D109" s="17"/>
+      <c r="E109" s="24"/>
+      <c r="F109" s="24"/>
+      <c r="G109" s="17"/>
+      <c r="H109" s="20"/>
+      <c r="I109" s="17"/>
+    </row>
+    <row r="110" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="17"/>
+      <c r="C110" s="17"/>
+      <c r="D110" s="17"/>
+      <c r="E110" s="24"/>
+      <c r="F110" s="24"/>
+      <c r="G110" s="17"/>
+      <c r="H110" s="20"/>
+      <c r="I110" s="17"/>
+    </row>
+    <row r="111" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="17"/>
+      <c r="C111" s="17"/>
+      <c r="D111" s="17"/>
+      <c r="E111" s="24"/>
+      <c r="F111" s="24"/>
+      <c r="G111" s="17"/>
+      <c r="H111" s="20"/>
+      <c r="I111" s="17"/>
+    </row>
+    <row r="112" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B112" s="17"/>
+      <c r="C112" s="17"/>
+      <c r="D112" s="17"/>
+      <c r="E112" s="24"/>
+      <c r="F112" s="24"/>
+      <c r="G112" s="17"/>
+      <c r="H112" s="20"/>
+      <c r="I112" s="17"/>
+    </row>
+    <row r="113" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B113" s="17"/>
+      <c r="C113" s="17"/>
+      <c r="D113" s="17"/>
+      <c r="E113" s="24"/>
+      <c r="F113" s="24"/>
+      <c r="G113" s="17"/>
+      <c r="H113" s="20"/>
+      <c r="I113" s="17"/>
+    </row>
+    <row r="114" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B114" s="17"/>
+      <c r="C114" s="17"/>
+      <c r="D114" s="17"/>
+      <c r="E114" s="24"/>
+      <c r="F114" s="24"/>
+      <c r="G114" s="17"/>
+      <c r="H114" s="20"/>
+      <c r="I114" s="17"/>
+    </row>
+    <row r="115" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="17"/>
+      <c r="C115" s="17"/>
+      <c r="D115" s="17"/>
+      <c r="E115" s="24"/>
+      <c r="F115" s="24"/>
+      <c r="G115" s="17"/>
+      <c r="H115" s="20"/>
+      <c r="I115" s="17"/>
+    </row>
+    <row r="116" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B116" s="17"/>
+      <c r="C116" s="17"/>
+      <c r="D116" s="17"/>
+      <c r="E116" s="24"/>
+      <c r="F116" s="24"/>
+      <c r="G116" s="17"/>
+      <c r="H116" s="20"/>
+      <c r="I116" s="17"/>
+    </row>
+    <row r="117" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="17"/>
+      <c r="C117" s="17"/>
+      <c r="D117" s="17"/>
+      <c r="E117" s="24"/>
+      <c r="F117" s="24"/>
+      <c r="G117" s="17"/>
+      <c r="H117" s="20"/>
+      <c r="I117" s="17"/>
+    </row>
+    <row r="118" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="17"/>
+      <c r="C118" s="17"/>
+      <c r="D118" s="17"/>
+      <c r="E118" s="24"/>
+      <c r="F118" s="24"/>
+      <c r="G118" s="17"/>
+      <c r="H118" s="20"/>
+      <c r="I118" s="17"/>
+    </row>
+    <row r="119" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B119" s="17"/>
+      <c r="C119" s="17"/>
+      <c r="D119" s="17"/>
+      <c r="E119" s="24"/>
+      <c r="F119" s="24"/>
+      <c r="G119" s="17"/>
+      <c r="H119" s="20"/>
+      <c r="I119" s="17"/>
+    </row>
+    <row r="120" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="17"/>
+      <c r="C120" s="17"/>
+      <c r="D120" s="17"/>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="17"/>
+      <c r="H120" s="20"/>
+      <c r="I120" s="17"/>
+    </row>
+    <row r="121" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="17"/>
+      <c r="C121" s="17"/>
+      <c r="D121" s="17"/>
+      <c r="E121" s="24"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="17"/>
+      <c r="H121" s="20"/>
+      <c r="I121" s="17"/>
+    </row>
+    <row r="122" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="17"/>
+      <c r="C122" s="17"/>
+      <c r="D122" s="17"/>
+      <c r="E122" s="24"/>
+      <c r="F122" s="24"/>
+      <c r="G122" s="17"/>
+      <c r="H122" s="20"/>
+      <c r="I122" s="17"/>
+    </row>
+    <row r="123" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="17"/>
+      <c r="C123" s="17"/>
+      <c r="D123" s="17"/>
+      <c r="E123" s="24"/>
+      <c r="F123" s="24"/>
+      <c r="G123" s="17"/>
+      <c r="H123" s="20"/>
+      <c r="I123" s="17"/>
+    </row>
+    <row r="124" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="17"/>
+      <c r="C124" s="17"/>
+      <c r="D124" s="17"/>
+      <c r="E124" s="24"/>
+      <c r="F124" s="24"/>
+      <c r="G124" s="17"/>
+      <c r="H124" s="20"/>
+      <c r="I124" s="17"/>
+    </row>
+    <row r="125" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="17"/>
+      <c r="C125" s="17"/>
+      <c r="D125" s="17"/>
+      <c r="E125" s="24"/>
+      <c r="F125" s="24"/>
+      <c r="G125" s="17"/>
+      <c r="H125" s="20"/>
+      <c r="I125" s="17"/>
+    </row>
+    <row r="126" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="17"/>
+      <c r="C126" s="17"/>
+      <c r="D126" s="17"/>
+      <c r="E126" s="24"/>
+      <c r="F126" s="24"/>
+      <c r="G126" s="17"/>
+      <c r="H126" s="20"/>
+      <c r="I126" s="17"/>
+    </row>
+    <row r="127" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="17"/>
+      <c r="C127" s="17"/>
+      <c r="D127" s="17"/>
+      <c r="E127" s="24"/>
+      <c r="F127" s="24"/>
+      <c r="G127" s="17"/>
+      <c r="H127" s="20"/>
+      <c r="I127" s="17"/>
+    </row>
+    <row r="128" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B128" s="17"/>
+      <c r="C128" s="17"/>
+      <c r="D128" s="17"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="17"/>
+      <c r="H128" s="20"/>
+      <c r="I128" s="17"/>
+    </row>
+    <row r="129" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B129" s="17"/>
+      <c r="C129" s="17"/>
+      <c r="D129" s="17"/>
+      <c r="E129" s="24"/>
+      <c r="F129" s="24"/>
+      <c r="G129" s="17"/>
+      <c r="H129" s="20"/>
+      <c r="I129" s="17"/>
+    </row>
+    <row r="130" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B130" s="17"/>
+      <c r="C130" s="17"/>
+      <c r="D130" s="17"/>
+      <c r="E130" s="24"/>
+      <c r="F130" s="24"/>
+      <c r="G130" s="17"/>
+      <c r="H130" s="20"/>
+      <c r="I130" s="17"/>
+    </row>
+    <row r="131" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B131" s="17"/>
+      <c r="C131" s="17"/>
+      <c r="D131" s="17"/>
+      <c r="E131" s="24"/>
+      <c r="F131" s="24"/>
+      <c r="G131" s="17"/>
+      <c r="H131" s="20"/>
+      <c r="I131" s="17"/>
+    </row>
+    <row r="132" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B132" s="17"/>
+      <c r="C132" s="17"/>
+      <c r="D132" s="17"/>
+      <c r="E132" s="24"/>
+      <c r="F132" s="24"/>
+      <c r="G132" s="17"/>
+      <c r="H132" s="20"/>
+      <c r="I132" s="17"/>
+    </row>
+    <row r="133" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="17"/>
+      <c r="C133" s="17"/>
+      <c r="D133" s="17"/>
+      <c r="E133" s="24"/>
+      <c r="F133" s="24"/>
+      <c r="G133" s="17"/>
+      <c r="H133" s="20"/>
+      <c r="I133" s="17"/>
+    </row>
+    <row r="134" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B134" s="17"/>
+      <c r="C134" s="17"/>
+      <c r="D134" s="17"/>
+      <c r="E134" s="24"/>
+      <c r="F134" s="24"/>
+      <c r="G134" s="17"/>
+      <c r="H134" s="20"/>
+      <c r="I134" s="17"/>
+    </row>
+    <row r="135" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B135" s="17"/>
+      <c r="C135" s="17"/>
+      <c r="D135" s="17"/>
+      <c r="E135" s="24"/>
+      <c r="F135" s="24"/>
+      <c r="G135" s="17"/>
+      <c r="H135" s="20"/>
+      <c r="I135" s="17"/>
+    </row>
+    <row r="136" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B136" s="17"/>
+      <c r="C136" s="17"/>
+      <c r="D136" s="17"/>
+      <c r="E136" s="24"/>
+      <c r="F136" s="24"/>
+      <c r="G136" s="17"/>
+      <c r="H136" s="20"/>
+      <c r="I136" s="17"/>
+    </row>
+    <row r="137" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B137" s="17"/>
+      <c r="C137" s="17"/>
+      <c r="D137" s="17"/>
+      <c r="E137" s="24"/>
+      <c r="F137" s="24"/>
+      <c r="G137" s="17"/>
+      <c r="H137" s="20"/>
+      <c r="I137" s="17"/>
+    </row>
+    <row r="138" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B138" s="17"/>
+      <c r="C138" s="17"/>
+      <c r="D138" s="17"/>
+      <c r="E138" s="24"/>
+      <c r="F138" s="24"/>
+      <c r="G138" s="17"/>
+      <c r="H138" s="20"/>
+      <c r="I138" s="17"/>
+    </row>
+    <row r="139" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B139" s="17"/>
+      <c r="C139" s="17"/>
+      <c r="D139" s="17"/>
+      <c r="E139" s="24"/>
+      <c r="F139" s="24"/>
+      <c r="G139" s="17"/>
+      <c r="H139" s="20"/>
+      <c r="I139" s="17"/>
+    </row>
+    <row r="140" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B140" s="17"/>
+      <c r="C140" s="17"/>
+      <c r="D140" s="17"/>
+      <c r="E140" s="24"/>
+      <c r="F140" s="24"/>
+      <c r="G140" s="17"/>
+      <c r="H140" s="20"/>
+      <c r="I140" s="17"/>
+    </row>
+    <row r="141" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B141" s="17"/>
+      <c r="C141" s="17"/>
+      <c r="D141" s="17"/>
+      <c r="E141" s="24"/>
+      <c r="F141" s="24"/>
+      <c r="G141" s="17"/>
+      <c r="H141" s="20"/>
+      <c r="I141" s="17"/>
+    </row>
+    <row r="142" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B142" s="17"/>
+      <c r="C142" s="17"/>
+      <c r="D142" s="17"/>
+      <c r="E142" s="24"/>
+      <c r="F142" s="24"/>
+      <c r="G142" s="17"/>
+      <c r="H142" s="20"/>
+      <c r="I142" s="17"/>
+    </row>
+    <row r="143" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B143" s="17"/>
+      <c r="C143" s="17"/>
+      <c r="D143" s="17"/>
+      <c r="E143" s="24"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="17"/>
+      <c r="H143" s="20"/>
+      <c r="I143" s="17"/>
+    </row>
+    <row r="144" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B144" s="17"/>
+      <c r="C144" s="17"/>
+      <c r="D144" s="17"/>
+      <c r="E144" s="24"/>
+      <c r="F144" s="24"/>
+      <c r="G144" s="17"/>
+      <c r="H144" s="20"/>
+      <c r="I144" s="17"/>
+    </row>
+    <row r="145" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B145" s="17"/>
+      <c r="C145" s="17"/>
+      <c r="D145" s="17"/>
+      <c r="E145" s="24"/>
+      <c r="F145" s="24"/>
+      <c r="G145" s="17"/>
+      <c r="H145" s="20"/>
+      <c r="I145" s="17"/>
+    </row>
+    <row r="146" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B146" s="17"/>
+      <c r="C146" s="17"/>
+      <c r="D146" s="17"/>
+      <c r="E146" s="24"/>
+      <c r="F146" s="24"/>
+      <c r="G146" s="17"/>
+      <c r="H146" s="20"/>
+      <c r="I146" s="17"/>
+    </row>
+    <row r="147" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B147" s="17"/>
+      <c r="C147" s="17"/>
+      <c r="D147" s="17"/>
+      <c r="E147" s="24"/>
+      <c r="F147" s="24"/>
+      <c r="G147" s="17"/>
+      <c r="H147" s="20"/>
+      <c r="I147" s="17"/>
+    </row>
+    <row r="148" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B148" s="17"/>
+      <c r="C148" s="17"/>
+      <c r="D148" s="17"/>
+      <c r="E148" s="24"/>
+      <c r="F148" s="24"/>
+      <c r="G148" s="17"/>
+      <c r="H148" s="20"/>
+      <c r="I148" s="17"/>
+    </row>
+    <row r="149" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B149" s="17"/>
+      <c r="C149" s="17"/>
+      <c r="D149" s="17"/>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="17"/>
+      <c r="H149" s="20"/>
+      <c r="I149" s="17"/>
+    </row>
+    <row r="150" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B150" s="17"/>
+      <c r="C150" s="17"/>
+      <c r="D150" s="17"/>
+      <c r="E150" s="24"/>
+      <c r="F150" s="24"/>
+      <c r="G150" s="17"/>
+      <c r="H150" s="20"/>
+      <c r="I150" s="17"/>
+    </row>
+    <row r="151" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B151" s="17"/>
+      <c r="C151" s="17"/>
+      <c r="D151" s="17"/>
+      <c r="E151" s="24"/>
+      <c r="F151" s="24"/>
+      <c r="G151" s="17"/>
+      <c r="H151" s="20"/>
+      <c r="I151" s="17"/>
+    </row>
+    <row r="152" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B152" s="17"/>
+      <c r="C152" s="17"/>
+      <c r="D152" s="17"/>
+      <c r="E152" s="24"/>
+      <c r="F152" s="24"/>
+      <c r="G152" s="17"/>
+      <c r="H152" s="20"/>
+      <c r="I152" s="17"/>
+    </row>
+    <row r="153" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B153" s="17"/>
+      <c r="C153" s="17"/>
+      <c r="D153" s="17"/>
+      <c r="E153" s="24"/>
+      <c r="F153" s="24"/>
+      <c r="G153" s="17"/>
+      <c r="H153" s="20"/>
+      <c r="I153" s="17"/>
+    </row>
+    <row r="154" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B154" s="17"/>
+      <c r="C154" s="17"/>
+      <c r="D154" s="17"/>
+      <c r="E154" s="24"/>
+      <c r="F154" s="24"/>
+      <c r="G154" s="17"/>
+      <c r="H154" s="20"/>
+      <c r="I154" s="17"/>
+    </row>
+    <row r="155" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B155" s="17"/>
+      <c r="C155" s="17"/>
+      <c r="D155" s="17"/>
+      <c r="E155" s="24"/>
+      <c r="F155" s="24"/>
+      <c r="G155" s="17"/>
+      <c r="H155" s="20"/>
+      <c r="I155" s="17"/>
+    </row>
+    <row r="156" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B156" s="17"/>
+      <c r="C156" s="17"/>
+      <c r="D156" s="17"/>
+      <c r="E156" s="24"/>
+      <c r="F156" s="24"/>
+      <c r="G156" s="17"/>
+      <c r="H156" s="20"/>
+      <c r="I156" s="17"/>
+    </row>
+    <row r="157" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B157" s="17"/>
+      <c r="C157" s="17"/>
+      <c r="D157" s="17"/>
+      <c r="E157" s="24"/>
+      <c r="F157" s="24"/>
+      <c r="G157" s="17"/>
+      <c r="H157" s="20"/>
+      <c r="I157" s="17"/>
+    </row>
+    <row r="158" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B158" s="17"/>
+      <c r="C158" s="17"/>
+      <c r="D158" s="17"/>
+      <c r="E158" s="24"/>
+      <c r="F158" s="24"/>
+      <c r="G158" s="17"/>
+      <c r="H158" s="20"/>
+      <c r="I158" s="17"/>
+    </row>
+    <row r="159" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B159" s="17"/>
+      <c r="C159" s="17"/>
+      <c r="D159" s="17"/>
+      <c r="E159" s="24"/>
+      <c r="F159" s="24"/>
+      <c r="G159" s="17"/>
+      <c r="H159" s="20"/>
+      <c r="I159" s="17"/>
+    </row>
+    <row r="160" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B160" s="17"/>
+      <c r="C160" s="17"/>
+      <c r="D160" s="17"/>
+      <c r="E160" s="24"/>
+      <c r="F160" s="24"/>
+      <c r="G160" s="17"/>
+      <c r="H160" s="20"/>
+      <c r="I160" s="17"/>
+    </row>
+    <row r="161" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B161" s="17"/>
+      <c r="C161" s="17"/>
+      <c r="D161" s="17"/>
+      <c r="E161" s="24"/>
+      <c r="F161" s="24"/>
+      <c r="G161" s="17"/>
+      <c r="H161" s="20"/>
+      <c r="I161" s="17"/>
+    </row>
+    <row r="162" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B162" s="17"/>
+      <c r="C162" s="17"/>
+      <c r="D162" s="17"/>
+      <c r="E162" s="24"/>
+      <c r="F162" s="24"/>
+      <c r="G162" s="17"/>
+      <c r="H162" s="20"/>
+      <c r="I162" s="17"/>
+    </row>
+    <row r="163" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B163" s="17"/>
+      <c r="C163" s="17"/>
+      <c r="D163" s="17"/>
+      <c r="E163" s="24"/>
+      <c r="F163" s="24"/>
+      <c r="G163" s="17"/>
+      <c r="H163" s="20"/>
+      <c r="I163" s="17"/>
+    </row>
+    <row r="164" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B164" s="17"/>
+      <c r="C164" s="17"/>
+      <c r="D164" s="17"/>
+      <c r="E164" s="24"/>
+      <c r="F164" s="24"/>
+      <c r="G164" s="17"/>
+      <c r="H164" s="20"/>
+      <c r="I164" s="17"/>
+    </row>
+    <row r="165" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B165" s="17"/>
+      <c r="C165" s="17"/>
+      <c r="D165" s="17"/>
+      <c r="E165" s="24"/>
+      <c r="F165" s="24"/>
+      <c r="G165" s="17"/>
+      <c r="H165" s="20"/>
+      <c r="I165" s="17"/>
+    </row>
+    <row r="166" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B166" s="17"/>
+      <c r="C166" s="17"/>
+      <c r="D166" s="17"/>
+      <c r="E166" s="24"/>
+      <c r="F166" s="24"/>
+      <c r="G166" s="17"/>
+      <c r="H166" s="20"/>
+      <c r="I166" s="17"/>
+    </row>
+    <row r="167" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B167" s="17"/>
+      <c r="C167" s="17"/>
+      <c r="D167" s="17"/>
+      <c r="E167" s="24"/>
+      <c r="F167" s="24"/>
+      <c r="G167" s="17"/>
+      <c r="H167" s="20"/>
+      <c r="I167" s="17"/>
+    </row>
+    <row r="168" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B168" s="17"/>
+      <c r="C168" s="17"/>
+      <c r="D168" s="17"/>
+      <c r="E168" s="24"/>
+      <c r="F168" s="24"/>
+      <c r="G168" s="17"/>
+      <c r="H168" s="20"/>
+      <c r="I168" s="17"/>
+    </row>
+    <row r="169" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B169" s="17"/>
+      <c r="C169" s="17"/>
+      <c r="D169" s="17"/>
+      <c r="E169" s="24"/>
+      <c r="F169" s="24"/>
+      <c r="G169" s="17"/>
+      <c r="H169" s="20"/>
+      <c r="I169" s="17"/>
+    </row>
+    <row r="170" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B170" s="17"/>
+      <c r="C170" s="17"/>
+      <c r="D170" s="17"/>
+      <c r="E170" s="24"/>
+      <c r="F170" s="24"/>
+      <c r="G170" s="17"/>
+      <c r="H170" s="20"/>
+      <c r="I170" s="17"/>
+    </row>
+    <row r="171" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B171" s="17"/>
+      <c r="C171" s="17"/>
+      <c r="D171" s="17"/>
+      <c r="E171" s="24"/>
+      <c r="F171" s="24"/>
+      <c r="G171" s="17"/>
+      <c r="H171" s="20"/>
+      <c r="I171" s="17"/>
+    </row>
+    <row r="172" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B172" s="17"/>
+      <c r="C172" s="17"/>
+      <c r="D172" s="17"/>
+      <c r="E172" s="24"/>
+      <c r="F172" s="24"/>
+      <c r="G172" s="17"/>
+      <c r="H172" s="20"/>
+      <c r="I172" s="17"/>
+    </row>
+    <row r="173" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B173" s="17"/>
+      <c r="C173" s="17"/>
+      <c r="D173" s="17"/>
+      <c r="E173" s="24"/>
+      <c r="F173" s="24"/>
+      <c r="G173" s="17"/>
+      <c r="H173" s="20"/>
+      <c r="I173" s="17"/>
+    </row>
+    <row r="174" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B174" s="17"/>
+      <c r="C174" s="17"/>
+      <c r="D174" s="17"/>
+      <c r="E174" s="24"/>
+      <c r="F174" s="24"/>
+      <c r="G174" s="17"/>
+      <c r="H174" s="20"/>
+      <c r="I174" s="17"/>
+    </row>
+    <row r="175" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B175" s="17"/>
+      <c r="C175" s="17"/>
+      <c r="D175" s="17"/>
+      <c r="E175" s="24"/>
+      <c r="F175" s="24"/>
+      <c r="G175" s="17"/>
+      <c r="H175" s="20"/>
+      <c r="I175" s="17"/>
+    </row>
+    <row r="176" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B176" s="17"/>
+      <c r="C176" s="17"/>
+      <c r="D176" s="17"/>
+      <c r="E176" s="24"/>
+      <c r="F176" s="24"/>
+      <c r="G176" s="17"/>
+      <c r="H176" s="20"/>
+      <c r="I176" s="17"/>
+    </row>
+    <row r="177" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B177" s="17"/>
+      <c r="C177" s="17"/>
+      <c r="D177" s="17"/>
+      <c r="E177" s="24"/>
+      <c r="F177" s="24"/>
+      <c r="G177" s="17"/>
+      <c r="H177" s="20"/>
+      <c r="I177" s="17"/>
+    </row>
+    <row r="178" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B178" s="17"/>
+      <c r="C178" s="17"/>
+      <c r="D178" s="17"/>
+      <c r="E178" s="24"/>
+      <c r="F178" s="24"/>
+      <c r="G178" s="17"/>
+      <c r="H178" s="20"/>
+      <c r="I178" s="17"/>
+    </row>
+    <row r="179" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B179" s="17"/>
+      <c r="C179" s="17"/>
+      <c r="D179" s="17"/>
+      <c r="E179" s="24"/>
+      <c r="F179" s="24"/>
+      <c r="G179" s="17"/>
+      <c r="H179" s="20"/>
+      <c r="I179" s="17"/>
+    </row>
+    <row r="180" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B180" s="17"/>
+      <c r="C180" s="17"/>
+      <c r="D180" s="17"/>
+      <c r="E180" s="24"/>
+      <c r="F180" s="24"/>
+      <c r="G180" s="17"/>
+      <c r="H180" s="20"/>
+      <c r="I180" s="17"/>
+    </row>
+    <row r="181" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B181" s="17"/>
+      <c r="C181" s="17"/>
+      <c r="D181" s="17"/>
+      <c r="E181" s="24"/>
+      <c r="F181" s="24"/>
+      <c r="G181" s="17"/>
+      <c r="H181" s="20"/>
+      <c r="I181" s="17"/>
+    </row>
+    <row r="182" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B182" s="17"/>
+      <c r="C182" s="17"/>
+      <c r="D182" s="17"/>
+      <c r="E182" s="24"/>
+      <c r="F182" s="24"/>
+      <c r="G182" s="17"/>
+      <c r="H182" s="20"/>
+      <c r="I182" s="17"/>
+    </row>
+    <row r="183" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B183" s="17"/>
+      <c r="C183" s="17"/>
+      <c r="D183" s="17"/>
+      <c r="E183" s="24"/>
+      <c r="F183" s="24"/>
+      <c r="G183" s="17"/>
+      <c r="H183" s="20"/>
+      <c r="I183" s="17"/>
+    </row>
+    <row r="184" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B184" s="17"/>
+      <c r="C184" s="17"/>
+      <c r="D184" s="17"/>
+      <c r="E184" s="24"/>
+      <c r="F184" s="24"/>
+      <c r="G184" s="17"/>
+      <c r="H184" s="20"/>
+      <c r="I184" s="17"/>
+    </row>
+    <row r="185" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B185" s="17"/>
+      <c r="C185" s="17"/>
+      <c r="D185" s="17"/>
+      <c r="E185" s="24"/>
+      <c r="F185" s="24"/>
+      <c r="G185" s="17"/>
+      <c r="H185" s="20"/>
+      <c r="I185" s="17"/>
+    </row>
+    <row r="186" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B186" s="17"/>
+      <c r="C186" s="17"/>
+      <c r="D186" s="17"/>
+      <c r="E186" s="24"/>
+      <c r="F186" s="24"/>
+      <c r="G186" s="17"/>
+      <c r="H186" s="20"/>
+      <c r="I186" s="17"/>
+    </row>
+    <row r="187" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B187" s="17"/>
+      <c r="C187" s="17"/>
+      <c r="D187" s="17"/>
+      <c r="E187" s="24"/>
+      <c r="F187" s="24"/>
+      <c r="G187" s="17"/>
+      <c r="H187" s="20"/>
+      <c r="I187" s="17"/>
+    </row>
+    <row r="188" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B188" s="17"/>
+      <c r="C188" s="17"/>
+      <c r="D188" s="17"/>
+      <c r="E188" s="24"/>
+      <c r="F188" s="24"/>
+      <c r="G188" s="17"/>
+      <c r="H188" s="20"/>
+      <c r="I188" s="17"/>
+    </row>
+    <row r="189" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B189" s="17"/>
+      <c r="C189" s="17"/>
+      <c r="D189" s="17"/>
+      <c r="E189" s="24"/>
+      <c r="F189" s="24"/>
+      <c r="G189" s="17"/>
+      <c r="H189" s="20"/>
+      <c r="I189" s="17"/>
+    </row>
+    <row r="190" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B190" s="17"/>
+      <c r="C190" s="17"/>
+      <c r="D190" s="17"/>
+      <c r="E190" s="24"/>
+      <c r="F190" s="24"/>
+      <c r="G190" s="17"/>
+      <c r="H190" s="20"/>
+      <c r="I190" s="17"/>
+    </row>
+    <row r="191" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B191" s="17"/>
+      <c r="C191" s="17"/>
+      <c r="D191" s="17"/>
+      <c r="E191" s="24"/>
+      <c r="F191" s="24"/>
+      <c r="G191" s="17"/>
+      <c r="H191" s="20"/>
+      <c r="I191" s="17"/>
+    </row>
+    <row r="192" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B192" s="17"/>
+      <c r="C192" s="17"/>
+      <c r="D192" s="17"/>
+      <c r="E192" s="24"/>
+      <c r="F192" s="24"/>
+      <c r="G192" s="17"/>
+      <c r="H192" s="20"/>
+      <c r="I192" s="17"/>
+    </row>
+    <row r="193" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B193" s="17"/>
+      <c r="C193" s="17"/>
+      <c r="D193" s="17"/>
+      <c r="E193" s="24"/>
+      <c r="F193" s="24"/>
+      <c r="G193" s="17"/>
+      <c r="H193" s="20"/>
+      <c r="I193" s="17"/>
+    </row>
+    <row r="194" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B194" s="17"/>
+      <c r="C194" s="17"/>
+      <c r="D194" s="17"/>
+      <c r="E194" s="24"/>
+      <c r="F194" s="24"/>
+      <c r="G194" s="17"/>
+      <c r="H194" s="20"/>
+      <c r="I194" s="17"/>
+    </row>
+    <row r="195" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B195" s="17"/>
+      <c r="C195" s="17"/>
+      <c r="D195" s="17"/>
+      <c r="E195" s="24"/>
+      <c r="F195" s="24"/>
+      <c r="G195" s="17"/>
+      <c r="H195" s="20"/>
+      <c r="I195" s="17"/>
+    </row>
+    <row r="196" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B196" s="17"/>
+      <c r="C196" s="17"/>
+      <c r="D196" s="17"/>
+      <c r="E196" s="24"/>
+      <c r="F196" s="24"/>
+      <c r="G196" s="17"/>
+      <c r="H196" s="20"/>
+      <c r="I196" s="17"/>
+    </row>
+    <row r="197" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B197" s="17"/>
+      <c r="C197" s="17"/>
+      <c r="D197" s="17"/>
+      <c r="E197" s="24"/>
+      <c r="F197" s="24"/>
+      <c r="G197" s="17"/>
+      <c r="H197" s="20"/>
+      <c r="I197" s="17"/>
+    </row>
+    <row r="198" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B198" s="17"/>
+      <c r="C198" s="17"/>
+      <c r="D198" s="17"/>
+      <c r="E198" s="24"/>
+      <c r="F198" s="24"/>
+      <c r="G198" s="17"/>
+      <c r="H198" s="20"/>
+      <c r="I198" s="17"/>
+    </row>
+    <row r="199" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B199" s="17"/>
+      <c r="C199" s="17"/>
+      <c r="D199" s="17"/>
+      <c r="E199" s="24"/>
+      <c r="F199" s="24"/>
+      <c r="G199" s="17"/>
+      <c r="H199" s="20"/>
+      <c r="I199" s="17"/>
+    </row>
+    <row r="200" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B200" s="17"/>
+      <c r="C200" s="17"/>
+      <c r="D200" s="17"/>
+      <c r="E200" s="24"/>
+      <c r="F200" s="24"/>
+      <c r="G200" s="17"/>
+      <c r="H200" s="20"/>
+      <c r="I200" s="17"/>
+    </row>
+    <row r="201" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B201" s="17"/>
+      <c r="C201" s="17"/>
+      <c r="D201" s="17"/>
+      <c r="E201" s="24"/>
+      <c r="F201" s="24"/>
+      <c r="G201" s="17"/>
+      <c r="H201" s="20"/>
+      <c r="I201" s="17"/>
+    </row>
+    <row r="202" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B202" s="17"/>
+      <c r="C202" s="17"/>
+      <c r="D202" s="17"/>
+      <c r="E202" s="24"/>
+      <c r="F202" s="24"/>
+      <c r="G202" s="17"/>
+      <c r="H202" s="20"/>
+      <c r="I202" s="17"/>
+    </row>
+    <row r="203" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B203" s="17"/>
+      <c r="C203" s="17"/>
+      <c r="D203" s="17"/>
+      <c r="E203" s="24"/>
+      <c r="F203" s="24"/>
+      <c r="G203" s="17"/>
+      <c r="H203" s="20"/>
+      <c r="I203" s="17"/>
+    </row>
+    <row r="204" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B204" s="17"/>
+      <c r="C204" s="17"/>
+      <c r="D204" s="17"/>
+      <c r="E204" s="24"/>
+      <c r="F204" s="24"/>
+      <c r="G204" s="17"/>
+      <c r="H204" s="20"/>
+      <c r="I204" s="17"/>
+    </row>
+    <row r="205" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B205" s="17"/>
+      <c r="C205" s="17"/>
+      <c r="D205" s="17"/>
+      <c r="E205" s="24"/>
+      <c r="F205" s="24"/>
+      <c r="G205" s="17"/>
+      <c r="H205" s="20"/>
+      <c r="I205" s="17"/>
+    </row>
+    <row r="206" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B206" s="17"/>
+      <c r="C206" s="17"/>
+      <c r="D206" s="17"/>
+      <c r="E206" s="24"/>
+      <c r="F206" s="24"/>
+      <c r="G206" s="17"/>
+      <c r="H206" s="20"/>
+      <c r="I206" s="17"/>
+    </row>
+    <row r="207" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B207" s="17"/>
+      <c r="C207" s="17"/>
+      <c r="D207" s="17"/>
+      <c r="E207" s="24"/>
+      <c r="F207" s="24"/>
+      <c r="G207" s="17"/>
+      <c r="H207" s="20"/>
+      <c r="I207" s="17"/>
+    </row>
+    <row r="208" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B208" s="17"/>
+      <c r="C208" s="17"/>
+      <c r="D208" s="17"/>
+      <c r="E208" s="24"/>
+      <c r="F208" s="24"/>
+      <c r="G208" s="17"/>
+      <c r="H208" s="20"/>
+      <c r="I208" s="17"/>
+    </row>
+    <row r="209" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B209" s="17"/>
+      <c r="C209" s="17"/>
+      <c r="D209" s="17"/>
+      <c r="E209" s="24"/>
+      <c r="F209" s="24"/>
+      <c r="G209" s="17"/>
+      <c r="H209" s="20"/>
+      <c r="I209" s="17"/>
+    </row>
+    <row r="210" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B210" s="17"/>
+      <c r="C210" s="17"/>
+      <c r="D210" s="17"/>
+      <c r="E210" s="24"/>
+      <c r="F210" s="24"/>
+      <c r="G210" s="17"/>
+      <c r="H210" s="20"/>
+      <c r="I210" s="17"/>
+    </row>
+    <row r="211" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B211" s="17"/>
+      <c r="C211" s="17"/>
+      <c r="D211" s="17"/>
+      <c r="E211" s="24"/>
+      <c r="F211" s="24"/>
+      <c r="G211" s="17"/>
+      <c r="H211" s="20"/>
+      <c r="I211" s="17"/>
+    </row>
+    <row r="212" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B212" s="17"/>
+      <c r="C212" s="17"/>
+      <c r="D212" s="17"/>
+      <c r="E212" s="24"/>
+      <c r="F212" s="24"/>
+      <c r="G212" s="17"/>
+      <c r="H212" s="20"/>
+      <c r="I212" s="17"/>
+    </row>
+    <row r="213" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B213" s="17"/>
+      <c r="C213" s="17"/>
+      <c r="D213" s="17"/>
+      <c r="E213" s="24"/>
+      <c r="F213" s="24"/>
+      <c r="G213" s="17"/>
+      <c r="H213" s="20"/>
+      <c r="I213" s="17"/>
+    </row>
+    <row r="214" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B214" s="17"/>
+      <c r="C214" s="17"/>
+      <c r="D214" s="17"/>
+      <c r="E214" s="24"/>
+      <c r="F214" s="24"/>
+      <c r="G214" s="17"/>
+      <c r="H214" s="20"/>
+      <c r="I214" s="17"/>
+    </row>
+    <row r="215" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B215" s="17"/>
+      <c r="C215" s="17"/>
+      <c r="D215" s="17"/>
+      <c r="E215" s="24"/>
+      <c r="F215" s="24"/>
+      <c r="G215" s="17"/>
+      <c r="H215" s="20"/>
+      <c r="I215" s="17"/>
+    </row>
+    <row r="216" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B216" s="17"/>
+      <c r="C216" s="17"/>
+      <c r="D216" s="17"/>
+      <c r="E216" s="24"/>
+      <c r="F216" s="24"/>
+      <c r="G216" s="17"/>
+      <c r="H216" s="20"/>
+      <c r="I216" s="17"/>
+    </row>
+    <row r="217" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B217" s="17"/>
+      <c r="C217" s="17"/>
+      <c r="D217" s="17"/>
+      <c r="E217" s="24"/>
+      <c r="F217" s="24"/>
+      <c r="G217" s="17"/>
+      <c r="H217" s="20"/>
+      <c r="I217" s="17"/>
+    </row>
+    <row r="218" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B218" s="17"/>
+      <c r="C218" s="17"/>
+      <c r="D218" s="17"/>
+      <c r="E218" s="24"/>
+      <c r="F218" s="24"/>
+      <c r="G218" s="17"/>
+      <c r="H218" s="20"/>
+      <c r="I218" s="17"/>
+    </row>
+    <row r="219" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B219" s="17"/>
+      <c r="C219" s="17"/>
+      <c r="D219" s="17"/>
+      <c r="E219" s="24"/>
+      <c r="F219" s="24"/>
+      <c r="G219" s="17"/>
+      <c r="H219" s="20"/>
+      <c r="I219" s="17"/>
+    </row>
+    <row r="220" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B220" s="17"/>
+      <c r="C220" s="17"/>
+      <c r="D220" s="17"/>
+      <c r="E220" s="24"/>
+      <c r="F220" s="24"/>
+      <c r="G220" s="17"/>
+      <c r="H220" s="20"/>
+      <c r="I220" s="17"/>
+    </row>
+    <row r="221" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B221" s="17"/>
+      <c r="C221" s="17"/>
+      <c r="D221" s="17"/>
+      <c r="E221" s="24"/>
+      <c r="F221" s="24"/>
+      <c r="G221" s="17"/>
+      <c r="H221" s="20"/>
+      <c r="I221" s="17"/>
+    </row>
+    <row r="222" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B222" s="17"/>
+      <c r="C222" s="17"/>
+      <c r="D222" s="17"/>
+      <c r="E222" s="24"/>
+      <c r="F222" s="24"/>
+      <c r="G222" s="17"/>
+      <c r="H222" s="20"/>
+      <c r="I222" s="17"/>
+    </row>
+    <row r="223" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B223" s="17"/>
+      <c r="C223" s="17"/>
+      <c r="D223" s="17"/>
+      <c r="E223" s="24"/>
+      <c r="F223" s="24"/>
+      <c r="G223" s="17"/>
+      <c r="H223" s="20"/>
+      <c r="I223" s="17"/>
+    </row>
+    <row r="224" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B224" s="17"/>
+      <c r="C224" s="17"/>
+      <c r="D224" s="17"/>
+      <c r="E224" s="24"/>
+      <c r="F224" s="24"/>
+      <c r="G224" s="17"/>
+      <c r="H224" s="20"/>
+      <c r="I224" s="17"/>
+    </row>
+    <row r="225" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B225" s="17"/>
+      <c r="C225" s="17"/>
+      <c r="D225" s="17"/>
+      <c r="E225" s="24"/>
+      <c r="F225" s="24"/>
+      <c r="G225" s="17"/>
+      <c r="H225" s="20"/>
+      <c r="I225" s="17"/>
+    </row>
+    <row r="226" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B226" s="17"/>
+      <c r="C226" s="17"/>
+      <c r="D226" s="17"/>
+      <c r="E226" s="24"/>
+      <c r="F226" s="24"/>
+      <c r="G226" s="17"/>
+      <c r="H226" s="20"/>
+      <c r="I226" s="17"/>
+    </row>
+    <row r="227" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B227" s="17"/>
+      <c r="C227" s="17"/>
+      <c r="D227" s="17"/>
+      <c r="E227" s="24"/>
+      <c r="F227" s="24"/>
+      <c r="G227" s="17"/>
+      <c r="H227" s="20"/>
+      <c r="I227" s="17"/>
+    </row>
+    <row r="228" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B228" s="17"/>
+      <c r="C228" s="17"/>
+      <c r="D228" s="17"/>
+      <c r="E228" s="24"/>
+      <c r="F228" s="24"/>
+      <c r="G228" s="17"/>
+      <c r="H228" s="20"/>
+      <c r="I228" s="17"/>
+    </row>
+    <row r="229" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B229" s="17"/>
+      <c r="C229" s="17"/>
+      <c r="D229" s="17"/>
+      <c r="E229" s="24"/>
+      <c r="F229" s="24"/>
+      <c r="G229" s="17"/>
+      <c r="H229" s="20"/>
+      <c r="I229" s="17"/>
+    </row>
+    <row r="230" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B230" s="17"/>
+      <c r="C230" s="17"/>
+      <c r="D230" s="17"/>
+      <c r="E230" s="24"/>
+      <c r="F230" s="24"/>
+      <c r="G230" s="17"/>
+      <c r="H230" s="20"/>
+      <c r="I230" s="17"/>
+    </row>
+    <row r="231" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B231" s="17"/>
+      <c r="C231" s="17"/>
+      <c r="D231" s="17"/>
+      <c r="E231" s="24"/>
+      <c r="F231" s="24"/>
+      <c r="G231" s="17"/>
+      <c r="H231" s="20"/>
+      <c r="I231" s="17"/>
+    </row>
+    <row r="232" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B232" s="17"/>
+      <c r="C232" s="17"/>
+      <c r="D232" s="17"/>
+      <c r="E232" s="24"/>
+      <c r="F232" s="24"/>
+      <c r="G232" s="17"/>
+      <c r="H232" s="20"/>
+      <c r="I232" s="17"/>
+    </row>
+    <row r="233" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B233" s="17"/>
+      <c r="C233" s="17"/>
+      <c r="D233" s="17"/>
+      <c r="E233" s="24"/>
+      <c r="F233" s="24"/>
+      <c r="G233" s="17"/>
+      <c r="H233" s="20"/>
+      <c r="I233" s="17"/>
+    </row>
+    <row r="234" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B234" s="17"/>
+      <c r="C234" s="17"/>
+      <c r="D234" s="17"/>
+      <c r="E234" s="24"/>
+      <c r="F234" s="24"/>
+      <c r="G234" s="17"/>
+      <c r="H234" s="20"/>
+      <c r="I234" s="17"/>
+    </row>
+    <row r="235" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B235" s="17"/>
+      <c r="C235" s="17"/>
+      <c r="D235" s="17"/>
+      <c r="E235" s="24"/>
+      <c r="F235" s="24"/>
+      <c r="G235" s="17"/>
+      <c r="H235" s="20"/>
+      <c r="I235" s="17"/>
+    </row>
+    <row r="236" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B236" s="17"/>
+      <c r="C236" s="17"/>
+      <c r="D236" s="17"/>
+      <c r="E236" s="24"/>
+      <c r="F236" s="24"/>
+      <c r="G236" s="17"/>
+      <c r="H236" s="20"/>
+      <c r="I236" s="17"/>
+    </row>
+    <row r="237" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B237" s="17"/>
+      <c r="C237" s="17"/>
+      <c r="D237" s="17"/>
+      <c r="E237" s="24"/>
+      <c r="F237" s="24"/>
+      <c r="G237" s="17"/>
+      <c r="H237" s="20"/>
+      <c r="I237" s="17"/>
+    </row>
+    <row r="238" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B238" s="17"/>
+      <c r="C238" s="17"/>
+      <c r="D238" s="17"/>
+      <c r="E238" s="24"/>
+      <c r="F238" s="24"/>
+      <c r="G238" s="17"/>
+      <c r="H238" s="20"/>
+      <c r="I238" s="17"/>
+    </row>
+    <row r="239" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B239" s="17"/>
+      <c r="C239" s="17"/>
+      <c r="D239" s="17"/>
+      <c r="E239" s="24"/>
+      <c r="F239" s="24"/>
+      <c r="G239" s="17"/>
+      <c r="H239" s="20"/>
+      <c r="I239" s="17"/>
+    </row>
+    <row r="240" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B240" s="17"/>
+      <c r="C240" s="17"/>
+      <c r="D240" s="17"/>
+      <c r="E240" s="24"/>
+      <c r="F240" s="24"/>
+      <c r="G240" s="17"/>
+      <c r="H240" s="20"/>
+      <c r="I240" s="17"/>
+    </row>
+    <row r="241" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B241" s="17"/>
+      <c r="C241" s="17"/>
+      <c r="D241" s="17"/>
+      <c r="E241" s="24"/>
+      <c r="F241" s="24"/>
+      <c r="G241" s="17"/>
+      <c r="H241" s="20"/>
+      <c r="I241" s="17"/>
+    </row>
+    <row r="242" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B242" s="17"/>
+      <c r="C242" s="17"/>
+      <c r="D242" s="17"/>
+      <c r="E242" s="24"/>
+      <c r="F242" s="24"/>
+      <c r="G242" s="17"/>
+      <c r="H242" s="20"/>
+      <c r="I242" s="17"/>
+    </row>
+    <row r="243" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B243" s="17"/>
+      <c r="C243" s="17"/>
+      <c r="D243" s="17"/>
+      <c r="E243" s="24"/>
+      <c r="F243" s="24"/>
+      <c r="G243" s="17"/>
+      <c r="H243" s="20"/>
+      <c r="I243" s="17"/>
+    </row>
+    <row r="244" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B244" s="17"/>
+      <c r="C244" s="17"/>
+      <c r="D244" s="17"/>
+      <c r="E244" s="24"/>
+      <c r="F244" s="24"/>
+      <c r="G244" s="17"/>
+      <c r="H244" s="20"/>
+      <c r="I244" s="17"/>
+    </row>
+    <row r="245" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B245" s="17"/>
+      <c r="C245" s="17"/>
+      <c r="D245" s="17"/>
+      <c r="E245" s="24"/>
+      <c r="F245" s="24"/>
+      <c r="G245" s="17"/>
+      <c r="H245" s="20"/>
+      <c r="I245" s="17"/>
+    </row>
+    <row r="246" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B246" s="17"/>
+      <c r="C246" s="17"/>
+      <c r="D246" s="17"/>
+      <c r="E246" s="24"/>
+      <c r="F246" s="24"/>
+      <c r="G246" s="17"/>
+      <c r="H246" s="20"/>
+      <c r="I246" s="17"/>
+    </row>
+    <row r="247" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B247" s="17"/>
+      <c r="C247" s="17"/>
+      <c r="D247" s="17"/>
+      <c r="E247" s="24"/>
+      <c r="F247" s="24"/>
+      <c r="G247" s="17"/>
+      <c r="H247" s="20"/>
+      <c r="I247" s="17"/>
+    </row>
+    <row r="248" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B248" s="17"/>
+      <c r="C248" s="17"/>
+      <c r="D248" s="17"/>
+      <c r="E248" s="24"/>
+      <c r="F248" s="24"/>
+      <c r="G248" s="17"/>
+      <c r="H248" s="20"/>
+      <c r="I248" s="17"/>
+    </row>
+    <row r="249" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B249" s="17"/>
+      <c r="C249" s="17"/>
+      <c r="D249" s="17"/>
+      <c r="E249" s="24"/>
+      <c r="F249" s="24"/>
+      <c r="G249" s="17"/>
+      <c r="H249" s="20"/>
+      <c r="I249" s="17"/>
+    </row>
+    <row r="250" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B250" s="17"/>
+      <c r="C250" s="17"/>
+      <c r="D250" s="17"/>
+      <c r="E250" s="24"/>
+      <c r="F250" s="24"/>
+      <c r="G250" s="17"/>
+      <c r="H250" s="20"/>
+      <c r="I250" s="17"/>
+    </row>
+    <row r="251" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B251" s="17"/>
+      <c r="C251" s="17"/>
+      <c r="D251" s="17"/>
+      <c r="E251" s="24"/>
+      <c r="F251" s="24"/>
+      <c r="G251" s="17"/>
+      <c r="H251" s="20"/>
+      <c r="I251" s="17"/>
+    </row>
+    <row r="252" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B252" s="17"/>
+      <c r="C252" s="17"/>
+      <c r="D252" s="17"/>
+      <c r="E252" s="24"/>
+      <c r="F252" s="24"/>
+      <c r="G252" s="17"/>
+      <c r="H252" s="20"/>
+      <c r="I252" s="17"/>
+    </row>
+    <row r="253" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B253" s="17"/>
+      <c r="C253" s="17"/>
+      <c r="D253" s="17"/>
+      <c r="E253" s="24"/>
+      <c r="F253" s="24"/>
+      <c r="G253" s="17"/>
+      <c r="H253" s="20"/>
+      <c r="I253" s="17"/>
+    </row>
+    <row r="254" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B254" s="17"/>
+      <c r="C254" s="17"/>
+      <c r="D254" s="17"/>
+      <c r="E254" s="24"/>
+      <c r="F254" s="24"/>
+      <c r="G254" s="17"/>
+      <c r="H254" s="20"/>
+      <c r="I254" s="17"/>
+    </row>
+    <row r="255" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B255" s="17"/>
+      <c r="C255" s="17"/>
+      <c r="D255" s="17"/>
+      <c r="E255" s="24"/>
+      <c r="F255" s="24"/>
+      <c r="G255" s="17"/>
+      <c r="H255" s="20"/>
+      <c r="I255" s="17"/>
+    </row>
+    <row r="256" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B256" s="17"/>
+      <c r="C256" s="17"/>
+      <c r="D256" s="17"/>
+      <c r="E256" s="24"/>
+      <c r="F256" s="24"/>
+      <c r="G256" s="17"/>
+      <c r="H256" s="20"/>
+      <c r="I256" s="17"/>
+    </row>
+    <row r="257" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B257" s="17"/>
+      <c r="C257" s="17"/>
+      <c r="D257" s="17"/>
+      <c r="E257" s="24"/>
+      <c r="F257" s="24"/>
+      <c r="G257" s="17"/>
+      <c r="H257" s="20"/>
+      <c r="I257" s="17"/>
+    </row>
+    <row r="258" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B258" s="17"/>
+      <c r="C258" s="17"/>
+      <c r="D258" s="17"/>
+      <c r="E258" s="24"/>
+      <c r="F258" s="24"/>
+      <c r="G258" s="17"/>
+      <c r="H258" s="20"/>
+      <c r="I258" s="17"/>
+    </row>
+    <row r="259" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B259" s="17"/>
+      <c r="C259" s="17"/>
+      <c r="D259" s="17"/>
+      <c r="E259" s="24"/>
+      <c r="F259" s="24"/>
+      <c r="G259" s="17"/>
+      <c r="H259" s="20"/>
+      <c r="I259" s="17"/>
+    </row>
+    <row r="260" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B260" s="17"/>
+      <c r="C260" s="17"/>
+      <c r="D260" s="17"/>
+      <c r="E260" s="24"/>
+      <c r="F260" s="24"/>
+      <c r="G260" s="17"/>
+      <c r="H260" s="20"/>
+      <c r="I260" s="17"/>
+    </row>
+    <row r="261" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B261" s="17"/>
+      <c r="C261" s="17"/>
+      <c r="D261" s="17"/>
+      <c r="E261" s="24"/>
+      <c r="F261" s="24"/>
+      <c r="G261" s="17"/>
+      <c r="H261" s="20"/>
+      <c r="I261" s="17"/>
+    </row>
+    <row r="262" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B262" s="17"/>
+      <c r="C262" s="17"/>
+      <c r="D262" s="17"/>
+      <c r="E262" s="24"/>
+      <c r="F262" s="24"/>
+      <c r="G262" s="17"/>
+      <c r="H262" s="20"/>
+      <c r="I262" s="17"/>
+    </row>
+    <row r="263" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B263" s="17"/>
+      <c r="C263" s="17"/>
+      <c r="D263" s="17"/>
+      <c r="E263" s="24"/>
+      <c r="F263" s="24"/>
+      <c r="G263" s="17"/>
+      <c r="H263" s="20"/>
+      <c r="I263" s="17"/>
+    </row>
+    <row r="264" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B264" s="17"/>
+      <c r="C264" s="17"/>
+      <c r="D264" s="17"/>
+      <c r="E264" s="24"/>
+      <c r="F264" s="24"/>
+      <c r="G264" s="17"/>
+      <c r="H264" s="20"/>
+      <c r="I264" s="17"/>
+    </row>
+    <row r="265" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B265" s="17"/>
+      <c r="C265" s="17"/>
+      <c r="D265" s="17"/>
+      <c r="E265" s="24"/>
+      <c r="F265" s="24"/>
+      <c r="G265" s="17"/>
+      <c r="H265" s="20"/>
+      <c r="I265" s="17"/>
+    </row>
+    <row r="266" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B266" s="17"/>
+      <c r="C266" s="17"/>
+      <c r="D266" s="17"/>
+      <c r="E266" s="24"/>
+      <c r="F266" s="24"/>
+      <c r="G266" s="17"/>
+      <c r="H266" s="20"/>
+      <c r="I266" s="17"/>
+    </row>
+    <row r="267" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B267" s="17"/>
+      <c r="C267" s="17"/>
+      <c r="D267" s="17"/>
+      <c r="E267" s="24"/>
+      <c r="F267" s="24"/>
+      <c r="G267" s="17"/>
+      <c r="H267" s="20"/>
+      <c r="I267" s="17"/>
+    </row>
+    <row r="268" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B268" s="17"/>
+      <c r="C268" s="17"/>
+      <c r="D268" s="17"/>
+      <c r="E268" s="24"/>
+      <c r="F268" s="24"/>
+      <c r="G268" s="17"/>
+      <c r="H268" s="20"/>
+      <c r="I268" s="17"/>
+    </row>
+    <row r="269" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B269" s="17"/>
+      <c r="C269" s="17"/>
+      <c r="D269" s="17"/>
+      <c r="E269" s="24"/>
+      <c r="F269" s="24"/>
+      <c r="G269" s="17"/>
+      <c r="H269" s="20"/>
+      <c r="I269" s="17"/>
+    </row>
+    <row r="270" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B270" s="17"/>
+      <c r="C270" s="17"/>
+      <c r="D270" s="17"/>
+      <c r="E270" s="24"/>
+      <c r="F270" s="24"/>
+      <c r="G270" s="17"/>
+      <c r="H270" s="20"/>
+      <c r="I270" s="17"/>
+    </row>
+    <row r="271" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B271" s="17"/>
+      <c r="C271" s="17"/>
+      <c r="D271" s="17"/>
+      <c r="E271" s="24"/>
+      <c r="F271" s="24"/>
+      <c r="G271" s="17"/>
+      <c r="H271" s="20"/>
+      <c r="I271" s="17"/>
+    </row>
+    <row r="272" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B272" s="17"/>
+      <c r="C272" s="17"/>
+      <c r="D272" s="17"/>
+      <c r="E272" s="24"/>
+      <c r="F272" s="24"/>
+      <c r="G272" s="17"/>
+      <c r="H272" s="20"/>
+      <c r="I272" s="17"/>
+    </row>
+    <row r="273" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B273" s="17"/>
+      <c r="C273" s="17"/>
+      <c r="D273" s="17"/>
+      <c r="E273" s="24"/>
+      <c r="F273" s="24"/>
+      <c r="G273" s="17"/>
+      <c r="H273" s="20"/>
+      <c r="I273" s="17"/>
+    </row>
+    <row r="274" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B274" s="17"/>
+      <c r="C274" s="17"/>
+      <c r="D274" s="17"/>
+      <c r="E274" s="24"/>
+      <c r="F274" s="24"/>
+      <c r="G274" s="17"/>
+      <c r="H274" s="20"/>
+      <c r="I274" s="17"/>
+    </row>
+    <row r="275" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B275" s="17"/>
+      <c r="C275" s="17"/>
+      <c r="D275" s="17"/>
+      <c r="E275" s="24"/>
+      <c r="F275" s="24"/>
+      <c r="G275" s="17"/>
+      <c r="H275" s="20"/>
+      <c r="I275" s="17"/>
+    </row>
+    <row r="276" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B276" s="17"/>
+      <c r="C276" s="17"/>
+      <c r="D276" s="17"/>
+      <c r="E276" s="24"/>
+      <c r="F276" s="24"/>
+      <c r="G276" s="17"/>
+      <c r="H276" s="20"/>
+      <c r="I276" s="17"/>
+    </row>
+    <row r="277" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B277" s="17"/>
+      <c r="C277" s="17"/>
+      <c r="D277" s="17"/>
+      <c r="E277" s="24"/>
+      <c r="F277" s="24"/>
+      <c r="G277" s="17"/>
+      <c r="H277" s="20"/>
+      <c r="I277" s="17"/>
+    </row>
+    <row r="278" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B278" s="17"/>
+      <c r="C278" s="17"/>
+      <c r="D278" s="17"/>
+      <c r="E278" s="24"/>
+      <c r="F278" s="24"/>
+      <c r="G278" s="17"/>
+      <c r="H278" s="20"/>
+      <c r="I278" s="17"/>
+    </row>
+    <row r="279" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B279" s="17"/>
+      <c r="C279" s="17"/>
+      <c r="D279" s="17"/>
+      <c r="E279" s="24"/>
+      <c r="F279" s="24"/>
+      <c r="G279" s="17"/>
+      <c r="H279" s="20"/>
+      <c r="I279" s="17"/>
+    </row>
+    <row r="280" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B280" s="17"/>
+      <c r="C280" s="17"/>
+      <c r="D280" s="17"/>
+      <c r="E280" s="24"/>
+      <c r="F280" s="24"/>
+      <c r="G280" s="17"/>
+      <c r="H280" s="20"/>
+      <c r="I280" s="17"/>
+    </row>
+    <row r="281" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B281" s="17"/>
+      <c r="C281" s="17"/>
+      <c r="D281" s="17"/>
+      <c r="E281" s="24"/>
+      <c r="F281" s="24"/>
+      <c r="G281" s="17"/>
+      <c r="H281" s="20"/>
+      <c r="I281" s="17"/>
+    </row>
+    <row r="282" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B282" s="17"/>
+      <c r="C282" s="17"/>
+      <c r="D282" s="17"/>
+      <c r="E282" s="24"/>
+      <c r="F282" s="24"/>
+      <c r="G282" s="17"/>
+      <c r="H282" s="20"/>
+      <c r="I282" s="17"/>
+    </row>
+    <row r="283" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B283" s="17"/>
+      <c r="C283" s="17"/>
+      <c r="D283" s="17"/>
+      <c r="E283" s="24"/>
+      <c r="F283" s="24"/>
+      <c r="G283" s="17"/>
+      <c r="H283" s="20"/>
+      <c r="I283" s="17"/>
+    </row>
+    <row r="284" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B284" s="17"/>
+      <c r="C284" s="17"/>
+      <c r="D284" s="17"/>
+      <c r="E284" s="24"/>
+      <c r="F284" s="24"/>
+      <c r="G284" s="17"/>
+      <c r="H284" s="20"/>
+      <c r="I284" s="17"/>
+    </row>
+    <row r="285" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B285" s="17"/>
+      <c r="C285" s="17"/>
+      <c r="D285" s="17"/>
+      <c r="E285" s="24"/>
+      <c r="F285" s="24"/>
+      <c r="G285" s="17"/>
+      <c r="H285" s="20"/>
+      <c r="I285" s="17"/>
+    </row>
+    <row r="286" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B286" s="17"/>
+      <c r="C286" s="17"/>
+      <c r="D286" s="17"/>
+      <c r="E286" s="24"/>
+      <c r="F286" s="24"/>
+      <c r="G286" s="17"/>
+      <c r="H286" s="20"/>
+      <c r="I286" s="17"/>
+    </row>
+    <row r="287" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B287" s="17"/>
+      <c r="C287" s="17"/>
+      <c r="D287" s="17"/>
+      <c r="E287" s="24"/>
+      <c r="F287" s="24"/>
+      <c r="G287" s="17"/>
+      <c r="H287" s="20"/>
+      <c r="I287" s="17"/>
+    </row>
+    <row r="288" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B288" s="17"/>
+      <c r="C288" s="17"/>
+      <c r="D288" s="17"/>
+      <c r="E288" s="24"/>
+      <c r="F288" s="24"/>
+      <c r="G288" s="17"/>
+      <c r="H288" s="20"/>
+      <c r="I288" s="17"/>
+    </row>
+    <row r="289" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B289" s="17"/>
+      <c r="C289" s="17"/>
+      <c r="D289" s="17"/>
+      <c r="E289" s="24"/>
+      <c r="F289" s="24"/>
+      <c r="G289" s="17"/>
+      <c r="H289" s="20"/>
+      <c r="I289" s="17"/>
+    </row>
+    <row r="290" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B290" s="17"/>
+      <c r="C290" s="17"/>
+      <c r="D290" s="17"/>
+      <c r="E290" s="24"/>
+      <c r="F290" s="24"/>
+      <c r="G290" s="17"/>
+      <c r="H290" s="20"/>
+      <c r="I290" s="17"/>
+    </row>
+    <row r="291" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B291" s="17"/>
+      <c r="C291" s="17"/>
+      <c r="D291" s="17"/>
+      <c r="E291" s="24"/>
+      <c r="F291" s="24"/>
+      <c r="G291" s="17"/>
+      <c r="H291" s="20"/>
+      <c r="I291" s="17"/>
+    </row>
+    <row r="292" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B292" s="17"/>
+      <c r="C292" s="17"/>
+      <c r="D292" s="17"/>
+      <c r="E292" s="24"/>
+      <c r="F292" s="24"/>
+      <c r="G292" s="17"/>
+      <c r="H292" s="20"/>
+      <c r="I292" s="17"/>
+    </row>
+    <row r="293" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B293" s="17"/>
+      <c r="C293" s="17"/>
+      <c r="D293" s="17"/>
+      <c r="E293" s="24"/>
+      <c r="F293" s="24"/>
+      <c r="G293" s="17"/>
+      <c r="H293" s="20"/>
+      <c r="I293" s="17"/>
+    </row>
+    <row r="294" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B294" s="17"/>
+      <c r="C294" s="17"/>
+      <c r="D294" s="17"/>
+      <c r="E294" s="24"/>
+      <c r="F294" s="24"/>
+      <c r="G294" s="17"/>
+      <c r="H294" s="20"/>
+      <c r="I294" s="17"/>
+    </row>
+    <row r="295" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B295" s="17"/>
+      <c r="C295" s="17"/>
+      <c r="D295" s="17"/>
+      <c r="E295" s="24"/>
+      <c r="F295" s="24"/>
+      <c r="G295" s="17"/>
+      <c r="H295" s="20"/>
+      <c r="I295" s="17"/>
+    </row>
+    <row r="296" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B296" s="17"/>
+      <c r="C296" s="17"/>
+      <c r="D296" s="17"/>
+      <c r="E296" s="24"/>
+      <c r="F296" s="24"/>
+      <c r="G296" s="17"/>
+      <c r="H296" s="20"/>
+      <c r="I296" s="17"/>
+    </row>
+    <row r="297" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B297" s="17"/>
+      <c r="C297" s="17"/>
+      <c r="D297" s="17"/>
+      <c r="E297" s="24"/>
+      <c r="F297" s="24"/>
+      <c r="G297" s="17"/>
+      <c r="H297" s="20"/>
+      <c r="I297" s="17"/>
+    </row>
+    <row r="298" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B298" s="17"/>
+      <c r="C298" s="17"/>
+      <c r="D298" s="17"/>
+      <c r="E298" s="24"/>
+      <c r="F298" s="24"/>
+      <c r="G298" s="17"/>
+      <c r="H298" s="20"/>
+      <c r="I298" s="17"/>
+    </row>
+    <row r="299" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B299" s="17"/>
+      <c r="C299" s="17"/>
+      <c r="D299" s="17"/>
+      <c r="E299" s="24"/>
+      <c r="F299" s="24"/>
+      <c r="G299" s="17"/>
+      <c r="H299" s="20"/>
+      <c r="I299" s="17"/>
+    </row>
+    <row r="300" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B300" s="17"/>
+      <c r="C300" s="17"/>
+      <c r="D300" s="17"/>
+      <c r="E300" s="24"/>
+      <c r="F300" s="24"/>
+      <c r="G300" s="17"/>
+      <c r="H300" s="20"/>
+      <c r="I300" s="17"/>
+    </row>
+    <row r="301" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B301" s="17"/>
+      <c r="C301" s="17"/>
+      <c r="D301" s="17"/>
+      <c r="E301" s="24"/>
+      <c r="F301" s="24"/>
+      <c r="G301" s="17"/>
+      <c r="H301" s="20"/>
+      <c r="I301" s="17"/>
+    </row>
+    <row r="302" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B302" s="17"/>
+      <c r="C302" s="17"/>
+      <c r="D302" s="17"/>
+      <c r="E302" s="24"/>
+      <c r="F302" s="24"/>
+      <c r="G302" s="17"/>
+      <c r="H302" s="20"/>
+      <c r="I302" s="17"/>
+    </row>
+    <row r="303" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B303" s="17"/>
+      <c r="C303" s="17"/>
+      <c r="D303" s="17"/>
+      <c r="E303" s="24"/>
+      <c r="F303" s="24"/>
+      <c r="G303" s="17"/>
+      <c r="H303" s="20"/>
+      <c r="I303" s="17"/>
+    </row>
+    <row r="304" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B304" s="17"/>
+      <c r="C304" s="17"/>
+      <c r="D304" s="17"/>
+      <c r="E304" s="24"/>
+      <c r="F304" s="24"/>
+      <c r="G304" s="17"/>
+      <c r="H304" s="20"/>
+      <c r="I304" s="17"/>
+    </row>
+    <row r="305" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B305" s="17"/>
+      <c r="C305" s="17"/>
+      <c r="D305" s="17"/>
+      <c r="E305" s="24"/>
+      <c r="F305" s="24"/>
+      <c r="G305" s="17"/>
+      <c r="H305" s="20"/>
+      <c r="I305" s="17"/>
+    </row>
+    <row r="306" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B306" s="17"/>
+      <c r="C306" s="17"/>
+      <c r="D306" s="17"/>
+      <c r="E306" s="24"/>
+      <c r="F306" s="24"/>
+      <c r="G306" s="17"/>
+      <c r="H306" s="20"/>
+      <c r="I306" s="17"/>
+    </row>
+    <row r="307" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B307" s="17"/>
+      <c r="C307" s="17"/>
+      <c r="D307" s="17"/>
+      <c r="E307" s="24"/>
+      <c r="F307" s="24"/>
+      <c r="G307" s="17"/>
+      <c r="H307" s="20"/>
+      <c r="I307" s="17"/>
+    </row>
+    <row r="308" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B308" s="17"/>
+      <c r="C308" s="17"/>
+      <c r="D308" s="17"/>
+      <c r="E308" s="24"/>
+      <c r="F308" s="24"/>
+      <c r="G308" s="17"/>
+      <c r="H308" s="20"/>
+      <c r="I308" s="17"/>
+    </row>
+    <row r="309" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B309" s="17"/>
+      <c r="C309" s="17"/>
+      <c r="D309" s="17"/>
+      <c r="E309" s="24"/>
+      <c r="F309" s="24"/>
+      <c r="G309" s="17"/>
+      <c r="H309" s="20"/>
+      <c r="I309" s="17"/>
+    </row>
+    <row r="310" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B310" s="17"/>
+      <c r="C310" s="17"/>
+      <c r="D310" s="17"/>
+      <c r="E310" s="24"/>
+      <c r="F310" s="24"/>
+      <c r="G310" s="17"/>
+      <c r="H310" s="20"/>
+      <c r="I310" s="17"/>
+    </row>
+    <row r="311" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B311" s="17"/>
+      <c r="C311" s="17"/>
+      <c r="D311" s="17"/>
+      <c r="E311" s="24"/>
+      <c r="F311" s="24"/>
+      <c r="G311" s="17"/>
+      <c r="H311" s="20"/>
+      <c r="I311" s="17"/>
+    </row>
+    <row r="312" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B312" s="17"/>
+      <c r="C312" s="17"/>
+      <c r="D312" s="17"/>
+      <c r="E312" s="24"/>
+      <c r="F312" s="24"/>
+      <c r="G312" s="17"/>
+      <c r="H312" s="20"/>
+      <c r="I312" s="17"/>
+    </row>
+    <row r="313" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B313" s="17"/>
+      <c r="C313" s="17"/>
+      <c r="D313" s="17"/>
+      <c r="E313" s="24"/>
+      <c r="F313" s="24"/>
+      <c r="G313" s="17"/>
+      <c r="H313" s="20"/>
+      <c r="I313" s="17"/>
+    </row>
+    <row r="314" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B314" s="17"/>
+      <c r="C314" s="17"/>
+      <c r="D314" s="17"/>
+      <c r="E314" s="24"/>
+      <c r="F314" s="24"/>
+      <c r="G314" s="17"/>
+      <c r="H314" s="20"/>
+      <c r="I314" s="17"/>
+    </row>
+    <row r="315" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B315" s="17"/>
+      <c r="C315" s="17"/>
+      <c r="D315" s="17"/>
+      <c r="E315" s="24"/>
+      <c r="F315" s="24"/>
+      <c r="G315" s="17"/>
+      <c r="H315" s="20"/>
+      <c r="I315" s="17"/>
+    </row>
+    <row r="316" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B316" s="17"/>
+      <c r="C316" s="17"/>
+      <c r="D316" s="17"/>
+      <c r="E316" s="24"/>
+      <c r="F316" s="24"/>
+      <c r="G316" s="17"/>
+      <c r="H316" s="20"/>
+      <c r="I316" s="17"/>
+    </row>
+    <row r="317" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B317" s="17"/>
+      <c r="C317" s="17"/>
+      <c r="D317" s="17"/>
+      <c r="E317" s="24"/>
+      <c r="F317" s="24"/>
+      <c r="G317" s="17"/>
+      <c r="H317" s="20"/>
+      <c r="I317" s="17"/>
+    </row>
+    <row r="318" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B318" s="17"/>
+      <c r="C318" s="17"/>
+      <c r="D318" s="17"/>
+      <c r="E318" s="24"/>
+      <c r="F318" s="24"/>
+      <c r="G318" s="17"/>
+      <c r="H318" s="20"/>
+      <c r="I318" s="17"/>
+    </row>
+    <row r="319" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B319" s="17"/>
+      <c r="C319" s="17"/>
+      <c r="D319" s="17"/>
+      <c r="E319" s="24"/>
+      <c r="F319" s="24"/>
+      <c r="G319" s="17"/>
+      <c r="H319" s="20"/>
+      <c r="I319" s="17"/>
+    </row>
+    <row r="320" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B320" s="17"/>
+      <c r="C320" s="17"/>
+      <c r="D320" s="17"/>
+      <c r="E320" s="24"/>
+      <c r="F320" s="24"/>
+      <c r="G320" s="17"/>
+      <c r="H320" s="20"/>
+      <c r="I320" s="17"/>
+    </row>
+    <row r="321" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B321" s="17"/>
+      <c r="C321" s="17"/>
+      <c r="D321" s="17"/>
+      <c r="E321" s="24"/>
+      <c r="F321" s="24"/>
+      <c r="G321" s="17"/>
+      <c r="H321" s="20"/>
+      <c r="I321" s="17"/>
+    </row>
+    <row r="322" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B322" s="17"/>
+      <c r="C322" s="17"/>
+      <c r="D322" s="17"/>
+      <c r="E322" s="24"/>
+      <c r="F322" s="24"/>
+      <c r="G322" s="17"/>
+      <c r="H322" s="20"/>
+      <c r="I322" s="17"/>
+    </row>
+    <row r="323" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B323" s="17"/>
+      <c r="C323" s="17"/>
+      <c r="D323" s="17"/>
+      <c r="E323" s="24"/>
+      <c r="F323" s="24"/>
+      <c r="G323" s="17"/>
+      <c r="H323" s="20"/>
+      <c r="I323" s="17"/>
+    </row>
+    <row r="324" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B324" s="17"/>
+      <c r="C324" s="17"/>
+      <c r="D324" s="17"/>
+      <c r="E324" s="24"/>
+      <c r="F324" s="24"/>
+      <c r="G324" s="17"/>
+      <c r="H324" s="20"/>
+      <c r="I324" s="17"/>
+    </row>
+    <row r="325" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B325" s="17"/>
+      <c r="C325" s="17"/>
+      <c r="D325" s="17"/>
+      <c r="E325" s="24"/>
+      <c r="F325" s="24"/>
+      <c r="G325" s="17"/>
+      <c r="H325" s="20"/>
+      <c r="I325" s="17"/>
+    </row>
+    <row r="326" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B326" s="17"/>
+      <c r="C326" s="17"/>
+      <c r="D326" s="17"/>
+      <c r="E326" s="24"/>
+      <c r="F326" s="24"/>
+      <c r="G326" s="17"/>
+      <c r="H326" s="20"/>
+      <c r="I326" s="17"/>
+    </row>
+    <row r="327" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B327" s="17"/>
+      <c r="C327" s="17"/>
+      <c r="D327" s="17"/>
+      <c r="E327" s="24"/>
+      <c r="F327" s="24"/>
+      <c r="G327" s="17"/>
+      <c r="H327" s="20"/>
+      <c r="I327" s="17"/>
+    </row>
+    <row r="328" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B328" s="17"/>
+      <c r="C328" s="17"/>
+      <c r="D328" s="17"/>
+      <c r="E328" s="24"/>
+      <c r="F328" s="24"/>
+      <c r="G328" s="17"/>
+      <c r="H328" s="20"/>
+      <c r="I328" s="17"/>
+    </row>
+    <row r="329" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B329" s="17"/>
+      <c r="C329" s="17"/>
+      <c r="D329" s="17"/>
+      <c r="E329" s="24"/>
+      <c r="F329" s="24"/>
+      <c r="G329" s="17"/>
+      <c r="H329" s="20"/>
+      <c r="I329" s="17"/>
+    </row>
+    <row r="330" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B330" s="17"/>
+      <c r="C330" s="17"/>
+      <c r="D330" s="17"/>
+      <c r="E330" s="24"/>
+      <c r="F330" s="24"/>
+      <c r="G330" s="17"/>
+      <c r="H330" s="20"/>
+      <c r="I330" s="17"/>
+    </row>
+    <row r="331" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B331" s="17"/>
+      <c r="C331" s="17"/>
+      <c r="D331" s="17"/>
+      <c r="E331" s="24"/>
+      <c r="F331" s="24"/>
+      <c r="G331" s="17"/>
+      <c r="H331" s="20"/>
+      <c r="I331" s="17"/>
+    </row>
+    <row r="332" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B332" s="17"/>
+      <c r="C332" s="17"/>
+      <c r="D332" s="17"/>
+      <c r="E332" s="24"/>
+      <c r="F332" s="24"/>
+      <c r="G332" s="17"/>
+      <c r="H332" s="20"/>
+      <c r="I332" s="17"/>
+    </row>
+    <row r="333" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B333" s="17"/>
+      <c r="C333" s="17"/>
+      <c r="D333" s="17"/>
+      <c r="E333" s="24"/>
+      <c r="F333" s="24"/>
+      <c r="G333" s="17"/>
+      <c r="H333" s="20"/>
+      <c r="I333" s="17"/>
+    </row>
+    <row r="334" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B334" s="17"/>
+      <c r="C334" s="17"/>
+      <c r="D334" s="17"/>
+      <c r="E334" s="24"/>
+      <c r="F334" s="24"/>
+      <c r="G334" s="17"/>
+      <c r="H334" s="20"/>
+      <c r="I334" s="17"/>
+    </row>
+    <row r="335" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B335" s="17"/>
+      <c r="C335" s="17"/>
+      <c r="D335" s="17"/>
+      <c r="E335" s="24"/>
+      <c r="F335" s="24"/>
+      <c r="G335" s="17"/>
+      <c r="H335" s="20"/>
+      <c r="I335" s="17"/>
+    </row>
+    <row r="336" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B336" s="17"/>
+      <c r="C336" s="17"/>
+      <c r="D336" s="17"/>
+      <c r="E336" s="24"/>
+      <c r="F336" s="24"/>
+      <c r="G336" s="17"/>
+      <c r="H336" s="20"/>
+      <c r="I336" s="17"/>
+    </row>
+    <row r="337" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B337" s="17"/>
+      <c r="C337" s="17"/>
+      <c r="D337" s="17"/>
+      <c r="E337" s="24"/>
+      <c r="F337" s="24"/>
+      <c r="G337" s="17"/>
+      <c r="H337" s="20"/>
+      <c r="I337" s="17"/>
+    </row>
+    <row r="338" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B338" s="17"/>
+      <c r="C338" s="17"/>
+      <c r="D338" s="17"/>
+      <c r="E338" s="24"/>
+      <c r="F338" s="24"/>
+      <c r="G338" s="17"/>
+      <c r="H338" s="20"/>
+      <c r="I338" s="17"/>
+    </row>
+    <row r="339" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B339" s="17"/>
+      <c r="C339" s="17"/>
+      <c r="D339" s="17"/>
+      <c r="E339" s="24"/>
+      <c r="F339" s="24"/>
+      <c r="G339" s="17"/>
+      <c r="H339" s="20"/>
+      <c r="I339" s="17"/>
+    </row>
+    <row r="340" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B340" s="17"/>
+      <c r="C340" s="17"/>
+      <c r="D340" s="17"/>
+      <c r="E340" s="24"/>
+      <c r="F340" s="24"/>
+      <c r="G340" s="17"/>
+      <c r="H340" s="20"/>
+      <c r="I340" s="17"/>
+    </row>
+    <row r="341" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B341" s="17"/>
+      <c r="C341" s="17"/>
+      <c r="D341" s="17"/>
+      <c r="E341" s="24"/>
+      <c r="F341" s="24"/>
+      <c r="G341" s="17"/>
+      <c r="H341" s="20"/>
+      <c r="I341" s="17"/>
+    </row>
+    <row r="342" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B342" s="17"/>
+      <c r="C342" s="17"/>
+      <c r="D342" s="17"/>
+      <c r="E342" s="24"/>
+      <c r="F342" s="24"/>
+      <c r="G342" s="17"/>
+      <c r="H342" s="20"/>
+      <c r="I342" s="17"/>
+    </row>
+    <row r="343" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B343" s="17"/>
+      <c r="C343" s="17"/>
+      <c r="D343" s="17"/>
+      <c r="E343" s="24"/>
+      <c r="F343" s="24"/>
+      <c r="G343" s="17"/>
+      <c r="H343" s="20"/>
+      <c r="I343" s="17"/>
+    </row>
+    <row r="344" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B344" s="17"/>
+      <c r="C344" s="17"/>
+      <c r="D344" s="17"/>
+      <c r="E344" s="24"/>
+      <c r="F344" s="24"/>
+      <c r="G344" s="17"/>
+      <c r="H344" s="20"/>
+      <c r="I344" s="17"/>
+    </row>
+    <row r="345" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B345" s="17"/>
+      <c r="C345" s="17"/>
+      <c r="D345" s="17"/>
+      <c r="E345" s="24"/>
+      <c r="F345" s="24"/>
+      <c r="G345" s="17"/>
+      <c r="H345" s="20"/>
+      <c r="I345" s="17"/>
+    </row>
+    <row r="346" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B346" s="17"/>
+      <c r="C346" s="17"/>
+      <c r="D346" s="17"/>
+      <c r="E346" s="24"/>
+      <c r="F346" s="24"/>
+      <c r="G346" s="17"/>
+      <c r="H346" s="20"/>
+      <c r="I346" s="17"/>
+    </row>
+    <row r="347" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B347" s="17"/>
+      <c r="C347" s="17"/>
+      <c r="D347" s="17"/>
+      <c r="E347" s="24"/>
+      <c r="F347" s="24"/>
+      <c r="G347" s="17"/>
+      <c r="H347" s="20"/>
+      <c r="I347" s="17"/>
+    </row>
+    <row r="348" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B348" s="17"/>
+      <c r="C348" s="17"/>
+      <c r="D348" s="17"/>
+      <c r="E348" s="24"/>
+      <c r="F348" s="24"/>
+      <c r="G348" s="17"/>
+      <c r="H348" s="20"/>
+      <c r="I348" s="17"/>
+    </row>
+    <row r="349" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B349" s="17"/>
+      <c r="C349" s="17"/>
+      <c r="D349" s="17"/>
+      <c r="E349" s="24"/>
+      <c r="F349" s="24"/>
+      <c r="G349" s="17"/>
+      <c r="H349" s="20"/>
+      <c r="I349" s="17"/>
+    </row>
+    <row r="350" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B350" s="17"/>
+      <c r="C350" s="17"/>
+      <c r="D350" s="17"/>
+      <c r="E350" s="24"/>
+      <c r="F350" s="24"/>
+      <c r="G350" s="17"/>
+      <c r="H350" s="20"/>
+      <c r="I350" s="17"/>
+    </row>
+    <row r="351" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B351" s="17"/>
+      <c r="C351" s="17"/>
+      <c r="D351" s="17"/>
+      <c r="E351" s="24"/>
+      <c r="F351" s="24"/>
+      <c r="G351" s="17"/>
+      <c r="H351" s="20"/>
+      <c r="I351" s="17"/>
+    </row>
+    <row r="352" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B352" s="17"/>
+      <c r="C352" s="17"/>
+      <c r="D352" s="17"/>
+      <c r="E352" s="24"/>
+      <c r="F352" s="24"/>
+      <c r="G352" s="17"/>
+      <c r="H352" s="20"/>
+      <c r="I352" s="17"/>
+    </row>
+    <row r="353" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B353" s="17"/>
+      <c r="C353" s="17"/>
+      <c r="D353" s="17"/>
+      <c r="E353" s="24"/>
+      <c r="F353" s="24"/>
+      <c r="G353" s="17"/>
+      <c r="H353" s="20"/>
+      <c r="I353" s="17"/>
+    </row>
+    <row r="354" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B354" s="17"/>
+      <c r="C354" s="17"/>
+      <c r="D354" s="17"/>
+      <c r="E354" s="24"/>
+      <c r="F354" s="24"/>
+      <c r="G354" s="17"/>
+      <c r="H354" s="20"/>
+      <c r="I354" s="17"/>
+    </row>
+    <row r="355" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B355" s="17"/>
+      <c r="C355" s="17"/>
+      <c r="D355" s="17"/>
+      <c r="E355" s="24"/>
+      <c r="F355" s="24"/>
+      <c r="G355" s="17"/>
+      <c r="H355" s="20"/>
+      <c r="I355" s="17"/>
+    </row>
+    <row r="356" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B356" s="17"/>
+      <c r="C356" s="17"/>
+      <c r="D356" s="17"/>
+      <c r="E356" s="24"/>
+      <c r="F356" s="24"/>
+      <c r="G356" s="17"/>
+      <c r="H356" s="20"/>
+      <c r="I356" s="17"/>
+    </row>
+    <row r="357" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B357" s="17"/>
+      <c r="C357" s="17"/>
+      <c r="D357" s="17"/>
+      <c r="E357" s="24"/>
+      <c r="F357" s="24"/>
+      <c r="G357" s="17"/>
+      <c r="H357" s="20"/>
+      <c r="I357" s="17"/>
+    </row>
+    <row r="358" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B358" s="17"/>
+      <c r="C358" s="17"/>
+      <c r="D358" s="17"/>
+      <c r="E358" s="24"/>
+      <c r="F358" s="24"/>
+      <c r="G358" s="17"/>
+      <c r="H358" s="20"/>
+      <c r="I358" s="17"/>
+    </row>
+    <row r="359" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B359" s="17"/>
+      <c r="C359" s="17"/>
+      <c r="D359" s="17"/>
+      <c r="E359" s="24"/>
+      <c r="F359" s="24"/>
+      <c r="G359" s="17"/>
+      <c r="H359" s="20"/>
+      <c r="I359" s="17"/>
+    </row>
+    <row r="360" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B360" s="17"/>
+      <c r="C360" s="17"/>
+      <c r="D360" s="17"/>
+      <c r="E360" s="24"/>
+      <c r="F360" s="24"/>
+      <c r="G360" s="17"/>
+      <c r="H360" s="20"/>
+      <c r="I360" s="17"/>
+    </row>
+    <row r="361" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B361" s="17"/>
+      <c r="C361" s="17"/>
+      <c r="D361" s="17"/>
+      <c r="E361" s="24"/>
+      <c r="F361" s="24"/>
+      <c r="G361" s="17"/>
+      <c r="H361" s="20"/>
+      <c r="I361" s="17"/>
+    </row>
+    <row r="362" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B362" s="17"/>
+      <c r="C362" s="17"/>
+      <c r="D362" s="17"/>
+      <c r="E362" s="24"/>
+      <c r="F362" s="24"/>
+      <c r="G362" s="17"/>
+      <c r="H362" s="20"/>
+      <c r="I362" s="17"/>
+    </row>
+    <row r="363" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B363" s="17"/>
+      <c r="C363" s="17"/>
+      <c r="D363" s="17"/>
+      <c r="E363" s="24"/>
+      <c r="F363" s="24"/>
+      <c r="G363" s="17"/>
+      <c r="H363" s="20"/>
+      <c r="I363" s="17"/>
+    </row>
+    <row r="364" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B364" s="17"/>
+      <c r="C364" s="17"/>
+      <c r="D364" s="17"/>
+      <c r="E364" s="24"/>
+      <c r="F364" s="24"/>
+      <c r="G364" s="17"/>
+      <c r="H364" s="20"/>
+      <c r="I364" s="17"/>
+    </row>
+    <row r="365" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B365" s="17"/>
+      <c r="C365" s="17"/>
+      <c r="D365" s="17"/>
+      <c r="E365" s="24"/>
+      <c r="F365" s="24"/>
+      <c r="G365" s="17"/>
+      <c r="H365" s="20"/>
+      <c r="I365" s="17"/>
+    </row>
+    <row r="366" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B366" s="17"/>
+      <c r="C366" s="17"/>
+      <c r="D366" s="17"/>
+      <c r="E366" s="24"/>
+      <c r="F366" s="24"/>
+      <c r="G366" s="17"/>
+      <c r="H366" s="20"/>
+      <c r="I366" s="17"/>
+    </row>
+    <row r="367" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B367" s="17"/>
+      <c r="C367" s="17"/>
+      <c r="D367" s="17"/>
+      <c r="E367" s="24"/>
+      <c r="F367" s="24"/>
+      <c r="G367" s="17"/>
+      <c r="H367" s="20"/>
+      <c r="I367" s="17"/>
+    </row>
+    <row r="368" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B368" s="17"/>
+      <c r="C368" s="17"/>
+      <c r="D368" s="17"/>
+      <c r="E368" s="24"/>
+      <c r="F368" s="24"/>
+      <c r="G368" s="17"/>
+      <c r="H368" s="20"/>
+      <c r="I368" s="17"/>
+    </row>
+    <row r="369" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B369" s="17"/>
+      <c r="C369" s="17"/>
+      <c r="D369" s="17"/>
+      <c r="E369" s="24"/>
+      <c r="F369" s="24"/>
+      <c r="G369" s="17"/>
+      <c r="H369" s="20"/>
+      <c r="I369" s="17"/>
+    </row>
+    <row r="370" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B370" s="17"/>
+      <c r="C370" s="17"/>
+      <c r="D370" s="17"/>
+      <c r="E370" s="24"/>
+      <c r="F370" s="24"/>
+      <c r="G370" s="17"/>
+      <c r="H370" s="20"/>
+      <c r="I370" s="17"/>
+    </row>
+    <row r="371" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B371" s="17"/>
+      <c r="C371" s="17"/>
+      <c r="D371" s="17"/>
+      <c r="E371" s="24"/>
+      <c r="F371" s="24"/>
+      <c r="G371" s="17"/>
+      <c r="H371" s="20"/>
+      <c r="I371" s="17"/>
+    </row>
+    <row r="372" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B372" s="17"/>
+      <c r="C372" s="17"/>
+      <c r="D372" s="17"/>
+      <c r="E372" s="24"/>
+      <c r="F372" s="24"/>
+      <c r="G372" s="17"/>
+      <c r="H372" s="20"/>
+      <c r="I372" s="17"/>
+    </row>
+    <row r="373" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B373" s="17"/>
+      <c r="C373" s="17"/>
+      <c r="D373" s="17"/>
+      <c r="E373" s="24"/>
+      <c r="F373" s="24"/>
+      <c r="G373" s="17"/>
+      <c r="H373" s="20"/>
+      <c r="I373" s="17"/>
+    </row>
+    <row r="374" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B374" s="17"/>
+      <c r="C374" s="17"/>
+      <c r="D374" s="17"/>
+      <c r="E374" s="24"/>
+      <c r="F374" s="24"/>
+      <c r="G374" s="17"/>
+      <c r="H374" s="20"/>
+      <c r="I374" s="17"/>
+    </row>
+    <row r="375" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B375" s="17"/>
+      <c r="C375" s="17"/>
+      <c r="D375" s="17"/>
+      <c r="E375" s="24"/>
+      <c r="F375" s="24"/>
+      <c r="G375" s="17"/>
+      <c r="H375" s="20"/>
+      <c r="I375" s="17"/>
+    </row>
+    <row r="376" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B376" s="17"/>
+      <c r="C376" s="17"/>
+      <c r="D376" s="17"/>
+      <c r="E376" s="24"/>
+      <c r="F376" s="24"/>
+      <c r="G376" s="17"/>
+      <c r="H376" s="20"/>
+      <c r="I376" s="17"/>
+    </row>
+    <row r="377" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B377" s="17"/>
+      <c r="C377" s="17"/>
+      <c r="D377" s="17"/>
+      <c r="E377" s="24"/>
+      <c r="F377" s="24"/>
+      <c r="G377" s="17"/>
+      <c r="H377" s="20"/>
+      <c r="I377" s="17"/>
+    </row>
+    <row r="378" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B378" s="17"/>
+      <c r="C378" s="17"/>
+      <c r="D378" s="17"/>
+      <c r="E378" s="24"/>
+      <c r="F378" s="24"/>
+      <c r="G378" s="17"/>
+      <c r="H378" s="20"/>
+      <c r="I378" s="17"/>
+    </row>
+    <row r="379" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B379" s="17"/>
+      <c r="C379" s="17"/>
+      <c r="D379" s="17"/>
+      <c r="E379" s="24"/>
+      <c r="F379" s="24"/>
+      <c r="G379" s="17"/>
+      <c r="H379" s="20"/>
+      <c r="I379" s="17"/>
+    </row>
+    <row r="380" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B380" s="17"/>
+      <c r="C380" s="17"/>
+      <c r="D380" s="17"/>
+      <c r="E380" s="24"/>
+      <c r="F380" s="24"/>
+      <c r="G380" s="17"/>
+      <c r="H380" s="20"/>
+      <c r="I380" s="17"/>
+    </row>
+    <row r="381" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B381" s="17"/>
+      <c r="C381" s="17"/>
+      <c r="D381" s="17"/>
+      <c r="E381" s="24"/>
+      <c r="F381" s="24"/>
+      <c r="G381" s="17"/>
+      <c r="H381" s="20"/>
+      <c r="I381" s="17"/>
+    </row>
+    <row r="382" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B382" s="17"/>
+      <c r="C382" s="17"/>
+      <c r="D382" s="17"/>
+      <c r="E382" s="24"/>
+      <c r="F382" s="24"/>
+      <c r="G382" s="17"/>
+      <c r="H382" s="20"/>
+      <c r="I382" s="17"/>
+    </row>
+    <row r="383" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B383" s="17"/>
+      <c r="C383" s="17"/>
+      <c r="D383" s="17"/>
+      <c r="E383" s="24"/>
+      <c r="F383" s="24"/>
+      <c r="G383" s="17"/>
+      <c r="H383" s="20"/>
+      <c r="I383" s="17"/>
+    </row>
+    <row r="384" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B384" s="17"/>
+      <c r="C384" s="17"/>
+      <c r="D384" s="17"/>
+      <c r="E384" s="24"/>
+      <c r="F384" s="24"/>
+      <c r="G384" s="17"/>
+      <c r="H384" s="20"/>
+      <c r="I384" s="17"/>
+    </row>
+    <row r="385" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B385" s="17"/>
+      <c r="C385" s="17"/>
+      <c r="D385" s="17"/>
+      <c r="E385" s="24"/>
+      <c r="F385" s="24"/>
+      <c r="G385" s="17"/>
+      <c r="H385" s="20"/>
+      <c r="I385" s="17"/>
+    </row>
+    <row r="386" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B386" s="17"/>
+      <c r="C386" s="17"/>
+      <c r="D386" s="17"/>
+      <c r="E386" s="24"/>
+      <c r="F386" s="24"/>
+      <c r="G386" s="17"/>
+      <c r="H386" s="20"/>
+      <c r="I386" s="17"/>
+    </row>
+    <row r="387" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B387" s="17"/>
+      <c r="C387" s="17"/>
+      <c r="D387" s="17"/>
+      <c r="E387" s="24"/>
+      <c r="F387" s="24"/>
+      <c r="G387" s="17"/>
+      <c r="H387" s="20"/>
+      <c r="I387" s="17"/>
+    </row>
+    <row r="388" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B388" s="17"/>
+      <c r="C388" s="17"/>
+      <c r="D388" s="17"/>
+      <c r="E388" s="24"/>
+      <c r="F388" s="24"/>
+      <c r="G388" s="17"/>
+      <c r="H388" s="20"/>
+      <c r="I388" s="17"/>
+    </row>
+    <row r="389" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B389" s="17"/>
+      <c r="C389" s="17"/>
+      <c r="D389" s="17"/>
+      <c r="E389" s="24"/>
+      <c r="F389" s="24"/>
+      <c r="G389" s="17"/>
+      <c r="H389" s="20"/>
+      <c r="I389" s="17"/>
+    </row>
+    <row r="390" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B390" s="17"/>
+      <c r="C390" s="17"/>
+      <c r="D390" s="17"/>
+      <c r="E390" s="24"/>
+      <c r="F390" s="24"/>
+      <c r="G390" s="17"/>
+      <c r="H390" s="20"/>
+      <c r="I390" s="17"/>
+    </row>
+    <row r="391" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B391" s="17"/>
+      <c r="C391" s="17"/>
+      <c r="D391" s="17"/>
+      <c r="E391" s="24"/>
+      <c r="F391" s="24"/>
+      <c r="G391" s="17"/>
+      <c r="H391" s="20"/>
+      <c r="I391" s="17"/>
+    </row>
+    <row r="392" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B392" s="17"/>
+      <c r="C392" s="17"/>
+      <c r="D392" s="17"/>
+      <c r="E392" s="24"/>
+      <c r="F392" s="24"/>
+      <c r="G392" s="17"/>
+      <c r="H392" s="20"/>
+      <c r="I392" s="17"/>
+    </row>
+    <row r="393" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B393" s="17"/>
+      <c r="C393" s="17"/>
+      <c r="D393" s="17"/>
+      <c r="E393" s="24"/>
+      <c r="F393" s="24"/>
+      <c r="G393" s="17"/>
+      <c r="H393" s="20"/>
+      <c r="I393" s="17"/>
+    </row>
+    <row r="394" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B394" s="17"/>
+      <c r="C394" s="17"/>
+      <c r="D394" s="17"/>
+      <c r="E394" s="24"/>
+      <c r="F394" s="24"/>
+      <c r="G394" s="17"/>
+      <c r="H394" s="20"/>
+      <c r="I394" s="17"/>
+    </row>
+    <row r="395" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B395" s="17"/>
+      <c r="C395" s="17"/>
+      <c r="D395" s="17"/>
+      <c r="E395" s="24"/>
+      <c r="F395" s="24"/>
+      <c r="G395" s="17"/>
+      <c r="H395" s="20"/>
+      <c r="I395" s="17"/>
+    </row>
+    <row r="396" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B396" s="17"/>
+      <c r="C396" s="17"/>
+      <c r="D396" s="17"/>
+      <c r="E396" s="24"/>
+      <c r="F396" s="24"/>
+      <c r="G396" s="17"/>
+      <c r="H396" s="20"/>
+      <c r="I396" s="17"/>
+    </row>
+    <row r="397" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B397" s="17"/>
+      <c r="C397" s="17"/>
+      <c r="D397" s="17"/>
+      <c r="E397" s="24"/>
+      <c r="F397" s="24"/>
+      <c r="G397" s="17"/>
+      <c r="H397" s="20"/>
+      <c r="I397" s="17"/>
+    </row>
+    <row r="398" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B398" s="17"/>
+      <c r="C398" s="17"/>
+      <c r="D398" s="17"/>
+      <c r="E398" s="24"/>
+      <c r="F398" s="24"/>
+      <c r="G398" s="17"/>
+      <c r="H398" s="20"/>
+      <c r="I398" s="17"/>
+    </row>
+    <row r="399" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B399" s="17"/>
+      <c r="C399" s="17"/>
+      <c r="D399" s="17"/>
+      <c r="E399" s="24"/>
+      <c r="F399" s="24"/>
+      <c r="G399" s="17"/>
+      <c r="H399" s="20"/>
+      <c r="I399" s="17"/>
+    </row>
+    <row r="400" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B400" s="17"/>
+      <c r="C400" s="17"/>
+      <c r="D400" s="17"/>
+      <c r="E400" s="24"/>
+      <c r="F400" s="24"/>
+      <c r="G400" s="17"/>
+      <c r="H400" s="20"/>
+      <c r="I400" s="17"/>
+    </row>
+    <row r="401" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B401" s="17"/>
+      <c r="C401" s="17"/>
+      <c r="D401" s="17"/>
+      <c r="E401" s="24"/>
+      <c r="F401" s="24"/>
+      <c r="G401" s="17"/>
+      <c r="H401" s="20"/>
+      <c r="I401" s="17"/>
+    </row>
+    <row r="402" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B402" s="17"/>
+      <c r="C402" s="17"/>
+      <c r="D402" s="17"/>
+      <c r="E402" s="24"/>
+      <c r="F402" s="24"/>
+      <c r="G402" s="17"/>
+      <c r="H402" s="20"/>
+      <c r="I402" s="17"/>
+    </row>
+    <row r="403" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B403" s="17"/>
+      <c r="C403" s="17"/>
+      <c r="D403" s="17"/>
+      <c r="E403" s="24"/>
+      <c r="F403" s="24"/>
+      <c r="G403" s="17"/>
+      <c r="H403" s="20"/>
+      <c r="I403" s="17"/>
+    </row>
+    <row r="404" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B404" s="17"/>
+      <c r="C404" s="17"/>
+      <c r="D404" s="17"/>
+      <c r="E404" s="24"/>
+      <c r="F404" s="24"/>
+      <c r="G404" s="17"/>
+      <c r="H404" s="20"/>
+      <c r="I404" s="17"/>
+    </row>
+    <row r="405" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B405" s="17"/>
+      <c r="C405" s="17"/>
+      <c r="D405" s="17"/>
+      <c r="E405" s="24"/>
+      <c r="F405" s="24"/>
+      <c r="G405" s="17"/>
+      <c r="H405" s="20"/>
+      <c r="I405" s="17"/>
+    </row>
+    <row r="406" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B406" s="17"/>
+      <c r="C406" s="17"/>
+      <c r="D406" s="17"/>
+      <c r="E406" s="24"/>
+      <c r="F406" s="24"/>
+      <c r="G406" s="17"/>
+      <c r="H406" s="20"/>
+      <c r="I406" s="17"/>
+    </row>
+    <row r="407" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B407" s="17"/>
+      <c r="C407" s="17"/>
+      <c r="D407" s="17"/>
+      <c r="E407" s="24"/>
+      <c r="F407" s="24"/>
+      <c r="G407" s="17"/>
+      <c r="H407" s="20"/>
+      <c r="I407" s="17"/>
+    </row>
+    <row r="408" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B408" s="17"/>
+      <c r="C408" s="17"/>
+      <c r="D408" s="17"/>
+      <c r="E408" s="24"/>
+      <c r="F408" s="24"/>
+      <c r="G408" s="17"/>
+      <c r="H408" s="20"/>
+      <c r="I408" s="17"/>
+    </row>
+    <row r="409" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B409" s="17"/>
+      <c r="C409" s="17"/>
+      <c r="D409" s="17"/>
+      <c r="E409" s="24"/>
+      <c r="F409" s="24"/>
+      <c r="G409" s="17"/>
+      <c r="H409" s="20"/>
+      <c r="I409" s="17"/>
+    </row>
+    <row r="410" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B410" s="17"/>
+      <c r="C410" s="17"/>
+      <c r="D410" s="17"/>
+      <c r="E410" s="24"/>
+      <c r="F410" s="24"/>
+      <c r="G410" s="17"/>
+      <c r="H410" s="20"/>
+      <c r="I410" s="17"/>
+    </row>
+    <row r="411" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B411" s="17"/>
+      <c r="C411" s="17"/>
+      <c r="D411" s="17"/>
+      <c r="E411" s="24"/>
+      <c r="F411" s="24"/>
+      <c r="G411" s="17"/>
+      <c r="H411" s="20"/>
+      <c r="I411" s="17"/>
+    </row>
+    <row r="412" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B412" s="17"/>
+      <c r="C412" s="17"/>
+      <c r="D412" s="17"/>
+      <c r="E412" s="24"/>
+      <c r="F412" s="24"/>
+      <c r="G412" s="17"/>
+      <c r="H412" s="20"/>
+      <c r="I412" s="17"/>
+    </row>
+    <row r="413" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B413" s="17"/>
+      <c r="C413" s="17"/>
+      <c r="D413" s="17"/>
+      <c r="E413" s="24"/>
+      <c r="F413" s="24"/>
+      <c r="G413" s="17"/>
+      <c r="H413" s="20"/>
+      <c r="I413" s="17"/>
+    </row>
+    <row r="414" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B414" s="17"/>
+      <c r="C414" s="17"/>
+      <c r="D414" s="17"/>
+      <c r="E414" s="24"/>
+      <c r="F414" s="24"/>
+      <c r="G414" s="17"/>
+      <c r="H414" s="20"/>
+      <c r="I414" s="17"/>
+    </row>
+    <row r="415" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B415" s="17"/>
+      <c r="C415" s="17"/>
+      <c r="D415" s="17"/>
+      <c r="E415" s="24"/>
+      <c r="F415" s="24"/>
+      <c r="G415" s="17"/>
+      <c r="H415" s="20"/>
+      <c r="I415" s="17"/>
+    </row>
+    <row r="416" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B416" s="17"/>
+      <c r="C416" s="17"/>
+      <c r="D416" s="17"/>
+      <c r="E416" s="24"/>
+      <c r="F416" s="24"/>
+      <c r="G416" s="17"/>
+      <c r="H416" s="20"/>
+      <c r="I416" s="17"/>
+    </row>
+    <row r="417" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B417" s="17"/>
+      <c r="C417" s="17"/>
+      <c r="D417" s="17"/>
+      <c r="E417" s="24"/>
+      <c r="F417" s="24"/>
+      <c r="G417" s="17"/>
+      <c r="H417" s="20"/>
+      <c r="I417" s="17"/>
+    </row>
+    <row r="418" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B418" s="17"/>
+      <c r="C418" s="17"/>
+      <c r="D418" s="17"/>
+      <c r="E418" s="24"/>
+      <c r="F418" s="24"/>
+      <c r="G418" s="17"/>
+      <c r="H418" s="20"/>
+      <c r="I418" s="17"/>
+    </row>
+    <row r="419" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B419" s="17"/>
+      <c r="C419" s="17"/>
+      <c r="D419" s="17"/>
+      <c r="E419" s="24"/>
+      <c r="F419" s="24"/>
+      <c r="G419" s="17"/>
+      <c r="H419" s="20"/>
+      <c r="I419" s="17"/>
+    </row>
+    <row r="420" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B420" s="17"/>
+      <c r="C420" s="17"/>
+      <c r="D420" s="17"/>
+      <c r="E420" s="24"/>
+      <c r="F420" s="24"/>
+      <c r="G420" s="17"/>
+      <c r="H420" s="20"/>
+      <c r="I420" s="17"/>
+    </row>
+    <row r="421" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B421" s="17"/>
+      <c r="C421" s="17"/>
+      <c r="D421" s="17"/>
+      <c r="E421" s="24"/>
+      <c r="F421" s="24"/>
+      <c r="G421" s="17"/>
+      <c r="H421" s="20"/>
+      <c r="I421" s="17"/>
+    </row>
+    <row r="422" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B422" s="17"/>
+      <c r="C422" s="17"/>
+      <c r="D422" s="17"/>
+      <c r="E422" s="24"/>
+      <c r="F422" s="24"/>
+      <c r="G422" s="17"/>
+      <c r="H422" s="20"/>
+      <c r="I422" s="17"/>
+    </row>
+    <row r="423" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B423" s="17"/>
+      <c r="C423" s="17"/>
+      <c r="D423" s="17"/>
+      <c r="E423" s="24"/>
+      <c r="F423" s="24"/>
+      <c r="G423" s="17"/>
+      <c r="H423" s="20"/>
+      <c r="I423" s="17"/>
+    </row>
+    <row r="424" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B424" s="17"/>
+      <c r="C424" s="17"/>
+      <c r="D424" s="17"/>
+      <c r="E424" s="24"/>
+      <c r="F424" s="24"/>
+      <c r="G424" s="17"/>
+      <c r="H424" s="20"/>
+      <c r="I424" s="17"/>
+    </row>
+    <row r="425" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B425" s="17"/>
+      <c r="C425" s="17"/>
+      <c r="D425" s="17"/>
+      <c r="E425" s="24"/>
+      <c r="F425" s="24"/>
+      <c r="G425" s="17"/>
+      <c r="H425" s="20"/>
+      <c r="I425" s="17"/>
+    </row>
+    <row r="426" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B426" s="17"/>
+      <c r="C426" s="17"/>
+      <c r="D426" s="17"/>
+      <c r="E426" s="24"/>
+      <c r="F426" s="24"/>
+      <c r="G426" s="17"/>
+      <c r="H426" s="20"/>
+      <c r="I426" s="17"/>
+    </row>
+    <row r="427" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B427" s="17"/>
+      <c r="C427" s="17"/>
+      <c r="D427" s="17"/>
+      <c r="E427" s="24"/>
+      <c r="F427" s="24"/>
+      <c r="G427" s="17"/>
+      <c r="H427" s="20"/>
+      <c r="I427" s="17"/>
+    </row>
+    <row r="428" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B428" s="17"/>
+      <c r="C428" s="17"/>
+      <c r="D428" s="17"/>
+      <c r="E428" s="24"/>
+      <c r="F428" s="24"/>
+      <c r="G428" s="17"/>
+      <c r="H428" s="20"/>
+      <c r="I428" s="17"/>
+    </row>
+    <row r="429" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B429" s="17"/>
+      <c r="C429" s="17"/>
+      <c r="D429" s="17"/>
+      <c r="E429" s="24"/>
+      <c r="F429" s="24"/>
+      <c r="G429" s="17"/>
+      <c r="H429" s="20"/>
+      <c r="I429" s="17"/>
+    </row>
+    <row r="430" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B430" s="17"/>
+      <c r="C430" s="17"/>
+      <c r="D430" s="17"/>
+      <c r="E430" s="24"/>
+      <c r="F430" s="24"/>
+      <c r="G430" s="17"/>
+      <c r="H430" s="20"/>
+      <c r="I430" s="17"/>
+    </row>
+    <row r="431" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B431" s="17"/>
+      <c r="C431" s="17"/>
+      <c r="D431" s="17"/>
+      <c r="E431" s="24"/>
+      <c r="F431" s="24"/>
+      <c r="G431" s="17"/>
+      <c r="H431" s="20"/>
+      <c r="I431" s="17"/>
+    </row>
+    <row r="432" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B432" s="17"/>
+      <c r="C432" s="17"/>
+      <c r="D432" s="17"/>
+      <c r="E432" s="24"/>
+      <c r="F432" s="24"/>
+      <c r="G432" s="17"/>
+      <c r="H432" s="20"/>
+      <c r="I432" s="17"/>
+    </row>
+    <row r="433" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B433" s="17"/>
+      <c r="C433" s="17"/>
+      <c r="D433" s="17"/>
+      <c r="E433" s="24"/>
+      <c r="F433" s="24"/>
+      <c r="G433" s="17"/>
+      <c r="H433" s="20"/>
+      <c r="I433" s="17"/>
+    </row>
+    <row r="434" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B434" s="17"/>
+      <c r="C434" s="17"/>
+      <c r="D434" s="17"/>
+      <c r="E434" s="24"/>
+      <c r="F434" s="24"/>
+      <c r="G434" s="17"/>
+      <c r="H434" s="20"/>
+      <c r="I434" s="17"/>
+    </row>
+    <row r="435" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B435" s="17"/>
+      <c r="C435" s="17"/>
+      <c r="D435" s="17"/>
+      <c r="E435" s="24"/>
+      <c r="F435" s="24"/>
+      <c r="G435" s="17"/>
+      <c r="H435" s="20"/>
+      <c r="I435" s="17"/>
+    </row>
+    <row r="436" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B436" s="17"/>
+      <c r="C436" s="17"/>
+      <c r="D436" s="17"/>
+      <c r="E436" s="24"/>
+      <c r="F436" s="24"/>
+      <c r="G436" s="17"/>
+      <c r="H436" s="20"/>
+      <c r="I436" s="17"/>
+    </row>
+    <row r="437" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B437" s="17"/>
+      <c r="C437" s="17"/>
+      <c r="D437" s="17"/>
+      <c r="E437" s="24"/>
+      <c r="F437" s="24"/>
+      <c r="G437" s="17"/>
+      <c r="H437" s="20"/>
+      <c r="I437" s="17"/>
+    </row>
+    <row r="438" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B438" s="17"/>
+      <c r="C438" s="17"/>
+      <c r="D438" s="17"/>
+      <c r="E438" s="24"/>
+      <c r="F438" s="24"/>
+      <c r="G438" s="17"/>
+      <c r="H438" s="20"/>
+      <c r="I438" s="17"/>
+    </row>
+    <row r="439" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B439" s="17"/>
+      <c r="C439" s="17"/>
+      <c r="D439" s="17"/>
+      <c r="E439" s="24"/>
+      <c r="F439" s="24"/>
+      <c r="G439" s="17"/>
+      <c r="H439" s="20"/>
+      <c r="I439" s="17"/>
+    </row>
+    <row r="440" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B440" s="17"/>
+      <c r="C440" s="17"/>
+      <c r="D440" s="17"/>
+      <c r="E440" s="24"/>
+      <c r="F440" s="24"/>
+      <c r="G440" s="17"/>
+      <c r="H440" s="20"/>
+      <c r="I440" s="17"/>
+    </row>
+    <row r="441" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B441" s="17"/>
+      <c r="C441" s="17"/>
+      <c r="D441" s="17"/>
+      <c r="E441" s="24"/>
+      <c r="F441" s="24"/>
+      <c r="G441" s="17"/>
+      <c r="H441" s="20"/>
+      <c r="I441" s="17"/>
+    </row>
+    <row r="442" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B442" s="17"/>
+      <c r="C442" s="17"/>
+      <c r="D442" s="17"/>
+      <c r="E442" s="24"/>
+      <c r="F442" s="24"/>
+      <c r="G442" s="17"/>
+      <c r="H442" s="20"/>
+      <c r="I442" s="17"/>
+    </row>
+    <row r="443" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B443" s="17"/>
+      <c r="C443" s="17"/>
+      <c r="D443" s="17"/>
+      <c r="E443" s="24"/>
+      <c r="F443" s="24"/>
+      <c r="G443" s="17"/>
+      <c r="H443" s="20"/>
+      <c r="I443" s="17"/>
+    </row>
+    <row r="444" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B444" s="17"/>
+      <c r="C444" s="17"/>
+      <c r="D444" s="17"/>
+      <c r="E444" s="24"/>
+      <c r="F444" s="24"/>
+      <c r="G444" s="17"/>
+      <c r="H444" s="20"/>
+      <c r="I444" s="17"/>
+    </row>
+    <row r="445" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B445" s="17"/>
+      <c r="C445" s="17"/>
+      <c r="D445" s="17"/>
+      <c r="E445" s="24"/>
+      <c r="F445" s="24"/>
+      <c r="G445" s="17"/>
+      <c r="H445" s="20"/>
+      <c r="I445" s="17"/>
+    </row>
+    <row r="446" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B446" s="17"/>
+      <c r="C446" s="17"/>
+      <c r="D446" s="17"/>
+      <c r="E446" s="24"/>
+      <c r="F446" s="24"/>
+      <c r="G446" s="17"/>
+      <c r="H446" s="20"/>
+      <c r="I446" s="17"/>
+    </row>
+    <row r="447" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B447" s="17"/>
+      <c r="C447" s="17"/>
+      <c r="D447" s="17"/>
+      <c r="E447" s="24"/>
+      <c r="F447" s="24"/>
+      <c r="G447" s="17"/>
+      <c r="H447" s="20"/>
+      <c r="I447" s="17"/>
+    </row>
+    <row r="448" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B448" s="17"/>
+      <c r="C448" s="17"/>
+      <c r="D448" s="17"/>
+      <c r="E448" s="24"/>
+      <c r="F448" s="24"/>
+      <c r="G448" s="17"/>
+      <c r="H448" s="20"/>
+      <c r="I448" s="17"/>
+    </row>
+    <row r="449" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B449" s="17"/>
+      <c r="C449" s="17"/>
+      <c r="D449" s="17"/>
+      <c r="E449" s="24"/>
+      <c r="F449" s="24"/>
+      <c r="G449" s="17"/>
+      <c r="H449" s="20"/>
+      <c r="I449" s="17"/>
+    </row>
+    <row r="450" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B450" s="17"/>
+      <c r="C450" s="17"/>
+      <c r="D450" s="17"/>
+      <c r="E450" s="24"/>
+      <c r="F450" s="24"/>
+      <c r="G450" s="17"/>
+      <c r="H450" s="20"/>
+      <c r="I450" s="17"/>
+    </row>
+    <row r="451" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B451" s="17"/>
+      <c r="C451" s="17"/>
+      <c r="D451" s="17"/>
+      <c r="E451" s="24"/>
+      <c r="F451" s="24"/>
+      <c r="G451" s="17"/>
+      <c r="H451" s="20"/>
+      <c r="I451" s="17"/>
+    </row>
+    <row r="452" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B452" s="17"/>
+      <c r="C452" s="17"/>
+      <c r="D452" s="17"/>
+      <c r="E452" s="24"/>
+      <c r="F452" s="24"/>
+      <c r="G452" s="17"/>
+      <c r="H452" s="20"/>
+      <c r="I452" s="17"/>
+    </row>
+    <row r="453" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B453" s="17"/>
+      <c r="C453" s="17"/>
+      <c r="D453" s="17"/>
+      <c r="E453" s="24"/>
+      <c r="F453" s="24"/>
+      <c r="G453" s="17"/>
+      <c r="H453" s="20"/>
+      <c r="I453" s="17"/>
+    </row>
+    <row r="454" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B454" s="17"/>
+      <c r="C454" s="17"/>
+      <c r="D454" s="17"/>
+      <c r="E454" s="24"/>
+      <c r="F454" s="24"/>
+      <c r="G454" s="17"/>
+      <c r="H454" s="20"/>
+      <c r="I454" s="17"/>
+    </row>
+    <row r="455" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B455" s="17"/>
+      <c r="C455" s="17"/>
+      <c r="D455" s="17"/>
+      <c r="E455" s="24"/>
+      <c r="F455" s="24"/>
+      <c r="G455" s="17"/>
+      <c r="H455" s="20"/>
+      <c r="I455" s="17"/>
+    </row>
+    <row r="456" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B456" s="17"/>
+      <c r="C456" s="17"/>
+      <c r="D456" s="17"/>
+      <c r="E456" s="24"/>
+      <c r="F456" s="24"/>
+      <c r="G456" s="17"/>
+      <c r="H456" s="20"/>
+      <c r="I456" s="17"/>
+    </row>
+    <row r="457" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B457" s="17"/>
+      <c r="C457" s="17"/>
+      <c r="D457" s="17"/>
+      <c r="E457" s="24"/>
+      <c r="F457" s="24"/>
+      <c r="G457" s="17"/>
+      <c r="H457" s="20"/>
+      <c r="I457" s="17"/>
+    </row>
+    <row r="458" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B458" s="17"/>
+      <c r="C458" s="17"/>
+      <c r="D458" s="17"/>
+      <c r="E458" s="24"/>
+      <c r="F458" s="24"/>
+      <c r="G458" s="17"/>
+      <c r="H458" s="20"/>
+      <c r="I458" s="17"/>
+    </row>
+    <row r="459" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B459" s="17"/>
+      <c r="C459" s="17"/>
+      <c r="D459" s="17"/>
+      <c r="E459" s="24"/>
+      <c r="F459" s="24"/>
+      <c r="G459" s="17"/>
+      <c r="H459" s="20"/>
+      <c r="I459" s="17"/>
+    </row>
+    <row r="460" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B460" s="17"/>
+      <c r="C460" s="17"/>
+      <c r="D460" s="17"/>
+      <c r="E460" s="24"/>
+      <c r="F460" s="24"/>
+      <c r="G460" s="17"/>
+      <c r="H460" s="20"/>
+      <c r="I460" s="17"/>
+    </row>
+    <row r="461" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B461" s="17"/>
+      <c r="C461" s="17"/>
+      <c r="D461" s="17"/>
+      <c r="E461" s="24"/>
+      <c r="F461" s="24"/>
+      <c r="G461" s="17"/>
+      <c r="H461" s="20"/>
+      <c r="I461" s="17"/>
+    </row>
+    <row r="462" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B462" s="17"/>
+      <c r="C462" s="17"/>
+      <c r="D462" s="17"/>
+      <c r="E462" s="24"/>
+      <c r="F462" s="24"/>
+      <c r="G462" s="17"/>
+      <c r="H462" s="20"/>
+      <c r="I462" s="17"/>
+    </row>
+    <row r="463" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B463" s="17"/>
+      <c r="C463" s="17"/>
+      <c r="D463" s="17"/>
+      <c r="E463" s="24"/>
+      <c r="F463" s="24"/>
+      <c r="G463" s="17"/>
+      <c r="H463" s="20"/>
+      <c r="I463" s="17"/>
+    </row>
+    <row r="464" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B464" s="17"/>
+      <c r="C464" s="17"/>
+      <c r="D464" s="17"/>
+      <c r="E464" s="24"/>
+      <c r="F464" s="24"/>
+      <c r="G464" s="17"/>
+      <c r="H464" s="20"/>
+      <c r="I464" s="17"/>
+    </row>
+    <row r="465" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B465" s="17"/>
+      <c r="C465" s="17"/>
+      <c r="D465" s="17"/>
+      <c r="E465" s="24"/>
+      <c r="F465" s="24"/>
+      <c r="G465" s="17"/>
+      <c r="H465" s="20"/>
+      <c r="I465" s="17"/>
+    </row>
+    <row r="466" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B466" s="17"/>
+      <c r="C466" s="17"/>
+      <c r="D466" s="17"/>
+      <c r="E466" s="24"/>
+      <c r="F466" s="24"/>
+      <c r="G466" s="17"/>
+      <c r="H466" s="20"/>
+      <c r="I466" s="17"/>
+    </row>
+    <row r="467" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B467" s="17"/>
+      <c r="C467" s="17"/>
+      <c r="D467" s="17"/>
+      <c r="E467" s="24"/>
+      <c r="F467" s="24"/>
+      <c r="G467" s="17"/>
+      <c r="H467" s="20"/>
+      <c r="I467" s="17"/>
+    </row>
+    <row r="468" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B468" s="17"/>
+      <c r="C468" s="17"/>
+      <c r="D468" s="17"/>
+      <c r="E468" s="24"/>
+      <c r="F468" s="24"/>
+      <c r="G468" s="17"/>
+      <c r="H468" s="20"/>
+      <c r="I468" s="17"/>
+    </row>
+    <row r="469" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B469" s="17"/>
+      <c r="C469" s="17"/>
+      <c r="D469" s="17"/>
+      <c r="E469" s="24"/>
+      <c r="F469" s="24"/>
+      <c r="G469" s="17"/>
+      <c r="H469" s="20"/>
+      <c r="I469" s="17"/>
+    </row>
+    <row r="470" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B470" s="17"/>
+      <c r="C470" s="17"/>
+      <c r="D470" s="17"/>
+      <c r="E470" s="24"/>
+      <c r="F470" s="24"/>
+      <c r="G470" s="17"/>
+      <c r="H470" s="20"/>
+      <c r="I470" s="17"/>
+    </row>
+    <row r="471" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B471" s="17"/>
+      <c r="C471" s="17"/>
+      <c r="D471" s="17"/>
+      <c r="E471" s="24"/>
+      <c r="F471" s="24"/>
+      <c r="G471" s="17"/>
+      <c r="H471" s="20"/>
+      <c r="I471" s="17"/>
+    </row>
+    <row r="472" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B472" s="17"/>
+      <c r="C472" s="17"/>
+      <c r="D472" s="17"/>
+      <c r="E472" s="24"/>
+      <c r="F472" s="24"/>
+      <c r="G472" s="17"/>
+      <c r="H472" s="20"/>
+      <c r="I472" s="17"/>
+    </row>
+    <row r="473" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B473" s="17"/>
+      <c r="C473" s="17"/>
+      <c r="D473" s="17"/>
+      <c r="E473" s="24"/>
+      <c r="F473" s="24"/>
+      <c r="G473" s="17"/>
+      <c r="H473" s="20"/>
+      <c r="I473" s="17"/>
+    </row>
+    <row r="474" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B474" s="17"/>
+      <c r="C474" s="17"/>
+      <c r="D474" s="17"/>
+      <c r="E474" s="24"/>
+      <c r="F474" s="24"/>
+      <c r="G474" s="17"/>
+      <c r="H474" s="20"/>
+      <c r="I474" s="17"/>
+    </row>
+    <row r="475" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B475" s="17"/>
+      <c r="C475" s="17"/>
+      <c r="D475" s="17"/>
+      <c r="E475" s="24"/>
+      <c r="F475" s="24"/>
+      <c r="G475" s="17"/>
+      <c r="H475" s="20"/>
+      <c r="I475" s="17"/>
+    </row>
+    <row r="476" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B476" s="17"/>
+      <c r="C476" s="17"/>
+      <c r="D476" s="17"/>
+      <c r="E476" s="24"/>
+      <c r="F476" s="24"/>
+      <c r="G476" s="17"/>
+      <c r="H476" s="20"/>
+      <c r="I476" s="17"/>
+    </row>
+    <row r="477" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B477" s="17"/>
+      <c r="C477" s="17"/>
+      <c r="D477" s="17"/>
+      <c r="E477" s="24"/>
+      <c r="F477" s="24"/>
+      <c r="G477" s="17"/>
+      <c r="H477" s="20"/>
+      <c r="I477" s="17"/>
+    </row>
+    <row r="478" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B478" s="17"/>
+      <c r="C478" s="17"/>
+      <c r="D478" s="17"/>
+      <c r="E478" s="24"/>
+      <c r="F478" s="24"/>
+      <c r="G478" s="17"/>
+      <c r="H478" s="20"/>
+      <c r="I478" s="17"/>
+    </row>
+    <row r="479" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B479" s="17"/>
+      <c r="C479" s="17"/>
+      <c r="D479" s="17"/>
+      <c r="E479" s="24"/>
+      <c r="F479" s="24"/>
+      <c r="G479" s="17"/>
+      <c r="H479" s="20"/>
+      <c r="I479" s="17"/>
+    </row>
+    <row r="480" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B480" s="17"/>
+      <c r="C480" s="17"/>
+      <c r="D480" s="17"/>
+      <c r="E480" s="24"/>
+      <c r="F480" s="24"/>
+      <c r="G480" s="17"/>
+      <c r="H480" s="20"/>
+      <c r="I480" s="17"/>
+    </row>
+    <row r="481" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B481" s="17"/>
+      <c r="C481" s="17"/>
+      <c r="D481" s="17"/>
+      <c r="E481" s="24"/>
+      <c r="F481" s="24"/>
+      <c r="G481" s="17"/>
+      <c r="H481" s="20"/>
+      <c r="I481" s="17"/>
+    </row>
+    <row r="482" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B482" s="17"/>
+      <c r="C482" s="17"/>
+      <c r="D482" s="17"/>
+      <c r="E482" s="24"/>
+      <c r="F482" s="24"/>
+      <c r="G482" s="17"/>
+      <c r="H482" s="20"/>
+      <c r="I482" s="17"/>
+    </row>
+    <row r="483" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B483" s="17"/>
+      <c r="C483" s="17"/>
+      <c r="D483" s="17"/>
+      <c r="E483" s="24"/>
+      <c r="F483" s="24"/>
+      <c r="G483" s="17"/>
+      <c r="H483" s="20"/>
+      <c r="I483" s="17"/>
+    </row>
+    <row r="484" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B484" s="17"/>
+      <c r="C484" s="17"/>
+      <c r="D484" s="17"/>
+      <c r="E484" s="24"/>
+      <c r="F484" s="24"/>
+      <c r="G484" s="17"/>
+      <c r="H484" s="20"/>
+      <c r="I484" s="17"/>
+    </row>
+    <row r="485" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B485" s="17"/>
+      <c r="C485" s="17"/>
+      <c r="D485" s="17"/>
+      <c r="E485" s="24"/>
+      <c r="F485" s="24"/>
+      <c r="G485" s="17"/>
+      <c r="H485" s="20"/>
+      <c r="I485" s="17"/>
+    </row>
+    <row r="486" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B486" s="17"/>
+      <c r="C486" s="17"/>
+      <c r="D486" s="17"/>
+      <c r="E486" s="24"/>
+      <c r="F486" s="24"/>
+      <c r="G486" s="17"/>
+      <c r="H486" s="20"/>
+      <c r="I486" s="17"/>
+    </row>
+    <row r="487" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B487" s="17"/>
+      <c r="C487" s="17"/>
+      <c r="D487" s="17"/>
+      <c r="E487" s="24"/>
+      <c r="F487" s="24"/>
+      <c r="G487" s="17"/>
+      <c r="H487" s="20"/>
+      <c r="I487" s="17"/>
+    </row>
+    <row r="488" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B488" s="17"/>
+      <c r="C488" s="17"/>
+      <c r="D488" s="17"/>
+      <c r="E488" s="24"/>
+      <c r="F488" s="24"/>
+      <c r="G488" s="17"/>
+      <c r="H488" s="20"/>
+      <c r="I488" s="17"/>
+    </row>
+    <row r="489" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B489" s="17"/>
+      <c r="C489" s="17"/>
+      <c r="D489" s="17"/>
+      <c r="E489" s="24"/>
+      <c r="F489" s="24"/>
+      <c r="G489" s="17"/>
+      <c r="H489" s="20"/>
+      <c r="I489" s="17"/>
+    </row>
+    <row r="490" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B490" s="17"/>
+      <c r="C490" s="17"/>
+      <c r="D490" s="17"/>
+      <c r="E490" s="24"/>
+      <c r="F490" s="24"/>
+      <c r="G490" s="17"/>
+      <c r="H490" s="20"/>
+      <c r="I490" s="17"/>
+    </row>
+    <row r="491" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B491" s="17"/>
+      <c r="C491" s="17"/>
+      <c r="D491" s="17"/>
+      <c r="E491" s="24"/>
+      <c r="F491" s="24"/>
+      <c r="G491" s="17"/>
+      <c r="H491" s="20"/>
+      <c r="I491" s="17"/>
+    </row>
+    <row r="492" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B492" s="17"/>
+      <c r="C492" s="17"/>
+      <c r="D492" s="17"/>
+      <c r="E492" s="24"/>
+      <c r="F492" s="24"/>
+      <c r="G492" s="17"/>
+      <c r="H492" s="20"/>
+      <c r="I492" s="17"/>
+    </row>
+    <row r="493" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B493" s="17"/>
+      <c r="C493" s="17"/>
+      <c r="D493" s="17"/>
+      <c r="E493" s="24"/>
+      <c r="F493" s="24"/>
+      <c r="G493" s="17"/>
+      <c r="H493" s="20"/>
+      <c r="I493" s="17"/>
+    </row>
+    <row r="494" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B494" s="17"/>
+      <c r="C494" s="17"/>
+      <c r="D494" s="17"/>
+      <c r="E494" s="24"/>
+      <c r="F494" s="24"/>
+      <c r="G494" s="17"/>
+      <c r="H494" s="20"/>
+      <c r="I494" s="17"/>
+    </row>
+    <row r="495" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B495" s="17"/>
+      <c r="C495" s="17"/>
+      <c r="D495" s="17"/>
+      <c r="E495" s="24"/>
+      <c r="F495" s="24"/>
+      <c r="G495" s="17"/>
+      <c r="H495" s="20"/>
+      <c r="I495" s="17"/>
+    </row>
+    <row r="496" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B496" s="17"/>
+      <c r="C496" s="17"/>
+      <c r="D496" s="17"/>
+      <c r="E496" s="24"/>
+      <c r="F496" s="24"/>
+      <c r="G496" s="17"/>
+      <c r="H496" s="20"/>
+      <c r="I496" s="17"/>
+    </row>
+    <row r="497" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B497" s="17"/>
+      <c r="C497" s="17"/>
+      <c r="D497" s="17"/>
+      <c r="E497" s="24"/>
+      <c r="F497" s="24"/>
+      <c r="G497" s="17"/>
+      <c r="H497" s="20"/>
+      <c r="I497" s="17"/>
+    </row>
+    <row r="498" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B498" s="17"/>
+      <c r="C498" s="17"/>
+      <c r="D498" s="17"/>
+      <c r="E498" s="24"/>
+      <c r="F498" s="24"/>
+      <c r="G498" s="17"/>
+      <c r="H498" s="20"/>
+      <c r="I498" s="17"/>
+    </row>
+    <row r="499" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B499" s="17"/>
+      <c r="C499" s="17"/>
+      <c r="D499" s="17"/>
+      <c r="E499" s="24"/>
+      <c r="F499" s="24"/>
+      <c r="G499" s="17"/>
+      <c r="H499" s="20"/>
+      <c r="I499" s="17"/>
+    </row>
+    <row r="500" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B500" s="17"/>
+      <c r="C500" s="17"/>
+      <c r="D500" s="17"/>
+      <c r="E500" s="24"/>
+      <c r="F500" s="24"/>
+      <c r="G500" s="17"/>
+      <c r="H500" s="20"/>
+      <c r="I500" s="17"/>
+    </row>
+    <row r="501" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B501" s="17"/>
+      <c r="C501" s="17"/>
+      <c r="D501" s="17"/>
+      <c r="E501" s="24"/>
+      <c r="F501" s="24"/>
+      <c r="G501" s="17"/>
+      <c r="H501" s="20"/>
+      <c r="I501" s="17"/>
+    </row>
+    <row r="502" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B502" s="17"/>
+      <c r="C502" s="17"/>
+      <c r="D502" s="17"/>
+      <c r="E502" s="24"/>
+      <c r="F502" s="24"/>
+      <c r="G502" s="17"/>
+      <c r="H502" s="20"/>
+      <c r="I502" s="17"/>
+    </row>
+    <row r="503" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B503" s="17"/>
+      <c r="C503" s="17"/>
+      <c r="D503" s="17"/>
+      <c r="E503" s="24"/>
+      <c r="F503" s="24"/>
+      <c r="G503" s="17"/>
+      <c r="H503" s="20"/>
+      <c r="I503" s="17"/>
+    </row>
+    <row r="504" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B504" s="17"/>
+      <c r="C504" s="17"/>
+      <c r="D504" s="17"/>
+      <c r="E504" s="24"/>
+      <c r="F504" s="24"/>
+      <c r="G504" s="17"/>
+      <c r="H504" s="20"/>
+      <c r="I504" s="17"/>
+    </row>
+    <row r="505" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B505" s="17"/>
+      <c r="C505" s="17"/>
+      <c r="D505" s="17"/>
+      <c r="E505" s="24"/>
+      <c r="F505" s="24"/>
+      <c r="G505" s="17"/>
+      <c r="H505" s="20"/>
+      <c r="I505" s="17"/>
+    </row>
+    <row r="506" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B506" s="17"/>
+      <c r="C506" s="17"/>
+      <c r="D506" s="17"/>
+      <c r="E506" s="24"/>
+      <c r="F506" s="24"/>
+      <c r="G506" s="17"/>
+      <c r="H506" s="20"/>
+      <c r="I506" s="17"/>
+    </row>
+    <row r="507" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B507" s="17"/>
+      <c r="C507" s="17"/>
+      <c r="D507" s="17"/>
+      <c r="E507" s="24"/>
+      <c r="F507" s="24"/>
+      <c r="G507" s="17"/>
+      <c r="H507" s="20"/>
+      <c r="I507" s="17"/>
+    </row>
+    <row r="508" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B508" s="17"/>
+      <c r="C508" s="17"/>
+      <c r="D508" s="17"/>
+      <c r="E508" s="24"/>
+      <c r="F508" s="24"/>
+      <c r="G508" s="17"/>
+      <c r="H508" s="20"/>
+      <c r="I508" s="17"/>
+    </row>
+    <row r="509" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B509" s="17"/>
+      <c r="C509" s="17"/>
+      <c r="D509" s="17"/>
+      <c r="E509" s="24"/>
+      <c r="F509" s="24"/>
+      <c r="G509" s="17"/>
+      <c r="H509" s="20"/>
+      <c r="I509" s="17"/>
+    </row>
+    <row r="510" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B510" s="17"/>
+      <c r="C510" s="17"/>
+      <c r="D510" s="17"/>
+      <c r="E510" s="24"/>
+      <c r="F510" s="24"/>
+      <c r="G510" s="17"/>
+      <c r="H510" s="20"/>
+      <c r="I510" s="17"/>
+    </row>
+    <row r="511" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B511" s="17"/>
+      <c r="C511" s="17"/>
+      <c r="D511" s="17"/>
+      <c r="E511" s="24"/>
+      <c r="F511" s="24"/>
+      <c r="G511" s="17"/>
+      <c r="H511" s="20"/>
+      <c r="I511" s="17"/>
+    </row>
+    <row r="512" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B512" s="17"/>
+      <c r="C512" s="17"/>
+      <c r="D512" s="17"/>
+      <c r="E512" s="24"/>
+      <c r="F512" s="24"/>
+      <c r="G512" s="17"/>
+      <c r="H512" s="20"/>
+      <c r="I512" s="17"/>
+    </row>
+    <row r="513" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B513" s="17"/>
+      <c r="C513" s="17"/>
+      <c r="D513" s="17"/>
+      <c r="E513" s="24"/>
+      <c r="F513" s="24"/>
+      <c r="G513" s="17"/>
+      <c r="H513" s="20"/>
+      <c r="I513" s="17"/>
+    </row>
+    <row r="514" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B514" s="17"/>
+      <c r="C514" s="17"/>
+      <c r="D514" s="17"/>
+      <c r="E514" s="24"/>
+      <c r="F514" s="24"/>
+      <c r="G514" s="17"/>
+      <c r="H514" s="20"/>
+      <c r="I514" s="17"/>
+    </row>
+    <row r="515" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B515" s="17"/>
+      <c r="C515" s="17"/>
+      <c r="D515" s="17"/>
+      <c r="E515" s="24"/>
+      <c r="F515" s="24"/>
+      <c r="G515" s="17"/>
+      <c r="H515" s="20"/>
+      <c r="I515" s="17"/>
+    </row>
+    <row r="516" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B516" s="17"/>
+      <c r="C516" s="17"/>
+      <c r="D516" s="17"/>
+      <c r="E516" s="24"/>
+      <c r="F516" s="24"/>
+      <c r="G516" s="17"/>
+      <c r="H516" s="20"/>
+      <c r="I516" s="17"/>
+    </row>
+    <row r="517" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B517" s="17"/>
+      <c r="C517" s="17"/>
+      <c r="D517" s="17"/>
+      <c r="E517" s="24"/>
+      <c r="F517" s="24"/>
+      <c r="G517" s="17"/>
+      <c r="H517" s="20"/>
+      <c r="I517" s="17"/>
+    </row>
+    <row r="518" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B518" s="17"/>
+      <c r="C518" s="17"/>
+      <c r="D518" s="17"/>
+      <c r="E518" s="24"/>
+      <c r="F518" s="24"/>
+      <c r="G518" s="17"/>
+      <c r="H518" s="20"/>
+      <c r="I518" s="17"/>
+    </row>
+    <row r="519" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B519" s="17"/>
+      <c r="C519" s="17"/>
+      <c r="D519" s="17"/>
+      <c r="E519" s="24"/>
+      <c r="F519" s="24"/>
+      <c r="G519" s="17"/>
+      <c r="H519" s="20"/>
+      <c r="I519" s="17"/>
+    </row>
+    <row r="520" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B520" s="17"/>
+      <c r="C520" s="17"/>
+      <c r="D520" s="17"/>
+      <c r="E520" s="24"/>
+      <c r="F520" s="24"/>
+      <c r="G520" s="17"/>
+      <c r="H520" s="20"/>
+      <c r="I520" s="17"/>
+    </row>
+    <row r="521" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B521" s="17"/>
+      <c r="C521" s="17"/>
+      <c r="D521" s="17"/>
+      <c r="E521" s="24"/>
+      <c r="F521" s="24"/>
+      <c r="G521" s="17"/>
+      <c r="H521" s="20"/>
+      <c r="I521" s="17"/>
+    </row>
+    <row r="522" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B522" s="17"/>
+      <c r="C522" s="17"/>
+      <c r="D522" s="17"/>
+      <c r="E522" s="24"/>
+      <c r="F522" s="24"/>
+      <c r="G522" s="17"/>
+      <c r="H522" s="20"/>
+      <c r="I522" s="17"/>
+    </row>
+    <row r="523" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B523" s="17"/>
+      <c r="C523" s="17"/>
+      <c r="D523" s="17"/>
+      <c r="E523" s="24"/>
+      <c r="F523" s="24"/>
+      <c r="G523" s="17"/>
+      <c r="H523" s="20"/>
+      <c r="I523" s="17"/>
+    </row>
+    <row r="524" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B524" s="17"/>
+      <c r="C524" s="17"/>
+      <c r="D524" s="17"/>
+      <c r="E524" s="24"/>
+      <c r="F524" s="24"/>
+      <c r="G524" s="17"/>
+      <c r="H524" s="20"/>
+      <c r="I524" s="17"/>
+    </row>
+    <row r="525" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B525" s="17"/>
+      <c r="C525" s="17"/>
+      <c r="D525" s="17"/>
+      <c r="E525" s="24"/>
+      <c r="F525" s="24"/>
+      <c r="G525" s="17"/>
+      <c r="H525" s="20"/>
+      <c r="I525" s="17"/>
+    </row>
+    <row r="526" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B526" s="17"/>
+      <c r="C526" s="17"/>
+      <c r="D526" s="17"/>
+      <c r="E526" s="24"/>
+      <c r="F526" s="24"/>
+      <c r="G526" s="17"/>
+      <c r="H526" s="20"/>
+      <c r="I526" s="17"/>
+    </row>
+    <row r="527" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B527" s="17"/>
+      <c r="C527" s="17"/>
+      <c r="D527" s="17"/>
+      <c r="E527" s="24"/>
+      <c r="F527" s="24"/>
+      <c r="G527" s="17"/>
+      <c r="H527" s="20"/>
+      <c r="I527" s="17"/>
+    </row>
+    <row r="528" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B528" s="17"/>
+      <c r="C528" s="17"/>
+      <c r="D528" s="17"/>
+      <c r="E528" s="24"/>
+      <c r="F528" s="24"/>
+      <c r="G528" s="17"/>
+      <c r="H528" s="20"/>
+      <c r="I528" s="17"/>
+    </row>
+    <row r="529" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B529" s="17"/>
+      <c r="C529" s="17"/>
+      <c r="D529" s="17"/>
+      <c r="E529" s="24"/>
+      <c r="F529" s="24"/>
+      <c r="G529" s="17"/>
+      <c r="H529" s="20"/>
+      <c r="I529" s="17"/>
+    </row>
+    <row r="530" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B530" s="17"/>
+      <c r="C530" s="17"/>
+      <c r="D530" s="17"/>
+      <c r="E530" s="24"/>
+      <c r="F530" s="24"/>
+      <c r="G530" s="17"/>
+      <c r="H530" s="20"/>
+      <c r="I530" s="17"/>
+    </row>
+    <row r="531" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B531" s="17"/>
+      <c r="C531" s="17"/>
+      <c r="D531" s="17"/>
+      <c r="E531" s="24"/>
+      <c r="F531" s="24"/>
+      <c r="G531" s="17"/>
+      <c r="H531" s="20"/>
+      <c r="I531" s="17"/>
+    </row>
+    <row r="532" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B532" s="17"/>
+      <c r="C532" s="17"/>
+      <c r="D532" s="17"/>
+      <c r="E532" s="24"/>
+      <c r="F532" s="24"/>
+      <c r="G532" s="17"/>
+      <c r="H532" s="20"/>
+      <c r="I532" s="17"/>
+    </row>
+    <row r="533" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B533" s="17"/>
+      <c r="C533" s="17"/>
+      <c r="D533" s="17"/>
+      <c r="E533" s="24"/>
+      <c r="F533" s="24"/>
+      <c r="G533" s="17"/>
+      <c r="H533" s="20"/>
+      <c r="I533" s="17"/>
+    </row>
+    <row r="534" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B534" s="17"/>
+      <c r="C534" s="17"/>
+      <c r="D534" s="17"/>
+      <c r="E534" s="24"/>
+      <c r="F534" s="24"/>
+      <c r="G534" s="17"/>
+      <c r="H534" s="20"/>
+      <c r="I534" s="17"/>
+    </row>
+    <row r="535" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B535" s="17"/>
+      <c r="C535" s="17"/>
+      <c r="D535" s="17"/>
+      <c r="E535" s="24"/>
+      <c r="F535" s="24"/>
+      <c r="G535" s="17"/>
+      <c r="H535" s="20"/>
+      <c r="I535" s="17"/>
+    </row>
+    <row r="536" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B536" s="17"/>
+      <c r="C536" s="17"/>
+      <c r="D536" s="17"/>
+      <c r="E536" s="24"/>
+      <c r="F536" s="24"/>
+      <c r="G536" s="17"/>
+      <c r="H536" s="20"/>
+      <c r="I536" s="17"/>
+    </row>
+    <row r="537" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B537" s="17"/>
+      <c r="C537" s="17"/>
+      <c r="D537" s="17"/>
+      <c r="E537" s="24"/>
+      <c r="F537" s="24"/>
+      <c r="G537" s="17"/>
+      <c r="H537" s="20"/>
+      <c r="I537" s="17"/>
+    </row>
+    <row r="538" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B538" s="17"/>
+      <c r="C538" s="17"/>
+      <c r="D538" s="17"/>
+      <c r="E538" s="24"/>
+      <c r="F538" s="24"/>
+      <c r="G538" s="17"/>
+      <c r="H538" s="20"/>
+      <c r="I538" s="17"/>
+    </row>
+    <row r="539" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B539" s="17"/>
+      <c r="C539" s="17"/>
+      <c r="D539" s="17"/>
+      <c r="E539" s="24"/>
+      <c r="F539" s="24"/>
+      <c r="G539" s="17"/>
+      <c r="H539" s="20"/>
+      <c r="I539" s="17"/>
+    </row>
+    <row r="540" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B540" s="17"/>
+      <c r="C540" s="17"/>
+      <c r="D540" s="17"/>
+      <c r="E540" s="24"/>
+      <c r="F540" s="24"/>
+      <c r="G540" s="17"/>
+      <c r="H540" s="20"/>
+      <c r="I540" s="17"/>
+    </row>
+    <row r="541" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B541" s="17"/>
+      <c r="C541" s="17"/>
+      <c r="D541" s="17"/>
+      <c r="E541" s="24"/>
+      <c r="F541" s="24"/>
+      <c r="G541" s="17"/>
+      <c r="H541" s="20"/>
+      <c r="I541" s="17"/>
+    </row>
+    <row r="542" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B542" s="17"/>
+      <c r="C542" s="17"/>
+      <c r="D542" s="17"/>
+      <c r="E542" s="24"/>
+      <c r="F542" s="24"/>
+      <c r="G542" s="17"/>
+      <c r="H542" s="20"/>
+      <c r="I542" s="17"/>
+    </row>
+    <row r="543" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B543" s="17"/>
+      <c r="C543" s="17"/>
+      <c r="D543" s="17"/>
+      <c r="E543" s="24"/>
+      <c r="F543" s="24"/>
+      <c r="G543" s="17"/>
+      <c r="H543" s="20"/>
+      <c r="I543" s="17"/>
+    </row>
+    <row r="544" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B544" s="17"/>
+      <c r="C544" s="17"/>
+      <c r="D544" s="17"/>
+      <c r="E544" s="24"/>
+      <c r="F544" s="24"/>
+      <c r="G544" s="17"/>
+      <c r="H544" s="20"/>
+      <c r="I544" s="17"/>
+    </row>
+    <row r="545" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B545" s="17"/>
+      <c r="C545" s="17"/>
+      <c r="D545" s="17"/>
+      <c r="E545" s="24"/>
+      <c r="F545" s="24"/>
+      <c r="G545" s="17"/>
+      <c r="H545" s="20"/>
+      <c r="I545" s="17"/>
+    </row>
+    <row r="546" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B546" s="17"/>
+      <c r="C546" s="17"/>
+      <c r="D546" s="17"/>
+      <c r="E546" s="24"/>
+      <c r="F546" s="24"/>
+      <c r="G546" s="17"/>
+      <c r="H546" s="20"/>
+      <c r="I546" s="17"/>
+    </row>
+    <row r="547" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B547" s="17"/>
+      <c r="C547" s="17"/>
+      <c r="D547" s="17"/>
+      <c r="E547" s="24"/>
+      <c r="F547" s="24"/>
+      <c r="G547" s="17"/>
+      <c r="H547" s="20"/>
+      <c r="I547" s="17"/>
+    </row>
+    <row r="548" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B548" s="17"/>
+      <c r="C548" s="17"/>
+      <c r="D548" s="17"/>
+      <c r="E548" s="24"/>
+      <c r="F548" s="24"/>
+      <c r="G548" s="17"/>
+      <c r="H548" s="20"/>
+      <c r="I548" s="17"/>
+    </row>
+    <row r="549" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B549" s="17"/>
+      <c r="C549" s="17"/>
+      <c r="D549" s="17"/>
+      <c r="E549" s="24"/>
+      <c r="F549" s="24"/>
+      <c r="G549" s="17"/>
+      <c r="H549" s="20"/>
+      <c r="I549" s="17"/>
+    </row>
+    <row r="550" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B550" s="17"/>
+      <c r="C550" s="17"/>
+      <c r="D550" s="17"/>
+      <c r="E550" s="24"/>
+      <c r="F550" s="24"/>
+      <c r="G550" s="17"/>
+      <c r="H550" s="20"/>
+      <c r="I550" s="17"/>
+    </row>
+    <row r="551" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B551" s="17"/>
+      <c r="C551" s="17"/>
+      <c r="D551" s="17"/>
+      <c r="E551" s="24"/>
+      <c r="F551" s="24"/>
+      <c r="G551" s="17"/>
+      <c r="H551" s="20"/>
+      <c r="I551" s="17"/>
+    </row>
+    <row r="552" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B552" s="17"/>
+      <c r="C552" s="17"/>
+      <c r="D552" s="17"/>
+      <c r="E552" s="24"/>
+      <c r="F552" s="24"/>
+      <c r="G552" s="17"/>
+      <c r="H552" s="20"/>
+      <c r="I552" s="17"/>
+    </row>
+    <row r="553" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B553" s="17"/>
+      <c r="C553" s="17"/>
+      <c r="D553" s="17"/>
+      <c r="E553" s="24"/>
+      <c r="F553" s="24"/>
+      <c r="G553" s="17"/>
+      <c r="H553" s="20"/>
+      <c r="I553" s="17"/>
+    </row>
+    <row r="554" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B554" s="17"/>
+      <c r="C554" s="17"/>
+      <c r="D554" s="17"/>
+      <c r="E554" s="24"/>
+      <c r="F554" s="24"/>
+      <c r="G554" s="17"/>
+      <c r="H554" s="20"/>
+      <c r="I554" s="17"/>
+    </row>
+    <row r="555" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B555" s="17"/>
+      <c r="C555" s="17"/>
+      <c r="D555" s="17"/>
+      <c r="E555" s="24"/>
+      <c r="F555" s="24"/>
+      <c r="G555" s="17"/>
+      <c r="H555" s="20"/>
+      <c r="I555" s="17"/>
+    </row>
+    <row r="556" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B556" s="17"/>
+      <c r="C556" s="17"/>
+      <c r="D556" s="17"/>
+      <c r="E556" s="24"/>
+      <c r="F556" s="24"/>
+      <c r="G556" s="17"/>
+      <c r="H556" s="20"/>
+      <c r="I556" s="17"/>
+    </row>
+    <row r="557" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B557" s="17"/>
+      <c r="C557" s="17"/>
+      <c r="D557" s="17"/>
+      <c r="E557" s="24"/>
+      <c r="F557" s="24"/>
+      <c r="G557" s="17"/>
+      <c r="H557" s="20"/>
+      <c r="I557" s="17"/>
+    </row>
+    <row r="558" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B558" s="17"/>
+      <c r="C558" s="17"/>
+      <c r="D558" s="17"/>
+      <c r="E558" s="24"/>
+      <c r="F558" s="24"/>
+      <c r="G558" s="17"/>
+      <c r="H558" s="20"/>
+      <c r="I558" s="17"/>
+    </row>
+    <row r="559" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B559" s="17"/>
+      <c r="C559" s="17"/>
+      <c r="D559" s="17"/>
+      <c r="E559" s="24"/>
+      <c r="F559" s="24"/>
+      <c r="G559" s="17"/>
+      <c r="H559" s="20"/>
+      <c r="I559" s="17"/>
+    </row>
+    <row r="560" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B560" s="17"/>
+      <c r="C560" s="17"/>
+      <c r="D560" s="17"/>
+      <c r="E560" s="24"/>
+      <c r="F560" s="24"/>
+      <c r="G560" s="17"/>
+      <c r="H560" s="20"/>
+      <c r="I560" s="17"/>
+    </row>
+    <row r="561" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B561" s="17"/>
+      <c r="C561" s="17"/>
+      <c r="D561" s="17"/>
+      <c r="E561" s="24"/>
+      <c r="F561" s="24"/>
+      <c r="G561" s="17"/>
+      <c r="H561" s="20"/>
+      <c r="I561" s="17"/>
+    </row>
+    <row r="562" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B562" s="17"/>
+      <c r="C562" s="17"/>
+      <c r="D562" s="17"/>
+      <c r="E562" s="24"/>
+      <c r="F562" s="24"/>
+      <c r="G562" s="17"/>
+      <c r="H562" s="20"/>
+      <c r="I562" s="17"/>
+    </row>
+    <row r="563" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B563" s="17"/>
+      <c r="C563" s="17"/>
+      <c r="D563" s="17"/>
+      <c r="E563" s="24"/>
+      <c r="F563" s="24"/>
+      <c r="G563" s="17"/>
+      <c r="H563" s="20"/>
+      <c r="I563" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K5:K13">
+  <conditionalFormatting sqref="G5:G563">
     <cfRule type="expression" dxfId="1" priority="1">
-      <formula>(ABS((K5-G5))/G5)&gt;FlagPercent</formula>
+      <formula>(ABS((G5-#REF!))/#REF!)&gt;FlagPercent</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L5:L13">
+  <conditionalFormatting sqref="H5:H563">
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>(ABS((L5-H5))/H5)&gt;FlagPercent</formula>
+      <formula>(ABS((H5-#REF!))/#REF!)&gt;FlagPercent</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
+  <dataValidations count="11">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter project names in this column" sqref="B4" xr:uid="{00000000-0002-0000-0000-000006000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select Category name from the dropdown list in each cell in this column. Options in this list are defined in the Setup worksheet. Press ALT+DOWN ARROW to navigate the list, then ENTER to make a selection" sqref="C4" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select the Employee name from the dropdown list in each cell in this column. Options are defined in the Setup worksheet. Press ALT+DOWN ARROW to navigate the list, then ENTER to make a selection" sqref="D4" xr:uid="{00000000-0002-0000-0000-000008000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter the estimated project start date in this column" sqref="E4" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter the estimated project finish date in this column" sqref="F4" xr:uid="{00000000-0002-0000-0000-00000A000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter estimated project work in hours" sqref="G4" xr:uid="{00000000-0002-0000-0000-00000B000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Estimated duration in days is auto calculated in this column" sqref="H4" xr:uid="{00000000-0002-0000-0000-00000C000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter the actual project start date in this column" sqref="I4" xr:uid="{00000000-0002-0000-0000-00000D000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter the actual project finish date in this column" sqref="J4" xr:uid="{00000000-0002-0000-0000-00000E000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter the actual project work in hours. Values that meet the Over/Under criteria are highlighted bold font styling." sqref="K4" xr:uid="{00000000-0002-0000-0000-000011000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Actual number of days is auto calculated in this column. Values that meet the Over/Under criteria are highlighted bold font styling." sqref="L4" xr:uid="{00000000-0002-0000-0000-000012000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter notes for projects in this column" sqref="M4" xr:uid="{00000000-0002-0000-0000-000013000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter the actual project start date in this column" sqref="E4" xr:uid="{00000000-0002-0000-0000-00000D000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter the actual project finish date in this column" sqref="F4" xr:uid="{00000000-0002-0000-0000-00000E000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter the actual project work in hours. Values that meet the Over/Under criteria are highlighted bold font styling." sqref="G4" xr:uid="{00000000-0002-0000-0000-000011000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Actual number of days is auto calculated in this column. Values that meet the Over/Under criteria are highlighted bold font styling." sqref="H4" xr:uid="{00000000-0002-0000-0000-000012000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter notes for projects in this column" sqref="I4" xr:uid="{00000000-0002-0000-0000-000013000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter projects in this project tracker worksheet. Set the percent over/under to flag in G2. Actual work in hours and actual duration in days will highlight over/under values with bold font styling in columns K and L." sqref="A1" xr:uid="{3A6D0288-E989-47CF-AA20-17E7D5BC6A0A}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select a category from the list or create a new category to display in this list from the Setup worksheet." sqref="C5:C13" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select a category from the list or create a new category to display in this list from the Setup worksheet." sqref="C5:C563" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>CategoryList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select an employee from the list or create a new employee to display in this list from the Setup worksheet." sqref="D5:D13" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select an employee from the list or create a new employee to display in this list from the Setup worksheet." sqref="D5:D563" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>EmployeeList</formula1>
     </dataValidation>
   </dataValidations>
@@ -2164,40 +7352,112 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C52F64F2-A0CB-432E-B537-8AB164D6506B}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" style="27" customWidth="1"/>
-    <col min="2" max="2" width="22.81640625" style="27" customWidth="1"/>
-    <col min="3" max="3" width="30.6328125" style="27" customWidth="1"/>
-    <col min="4" max="4" width="42.81640625" style="27" customWidth="1"/>
-    <col min="5" max="16384" width="8.7265625" style="27"/>
+    <col min="1" max="1" width="32.81640625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" style="26" customWidth="1"/>
+    <col min="3" max="3" width="18.54296875" style="26" customWidth="1"/>
+    <col min="4" max="4" width="27.54296875" style="26" customWidth="1"/>
+    <col min="5" max="16384" width="8.7265625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
-        <v>23</v>
+        <v>56</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45593</v>
+      </c>
+      <c r="D2" s="29">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45594</v>
+      </c>
+      <c r="D3" s="29">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45594</v>
+      </c>
+      <c r="D4" s="29">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45594</v>
+      </c>
+      <c r="D5" s="29">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45596</v>
+      </c>
+      <c r="D6" s="29">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45596</v>
+      </c>
+      <c r="D7" s="29">
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2215,216 +7475,216 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" style="12" customWidth="1"/>
-    <col min="2" max="3" width="18.453125" style="23" customWidth="1"/>
-    <col min="4" max="4" width="6.7265625" style="13" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="11" customWidth="1"/>
+    <col min="2" max="3" width="18.453125" style="22" customWidth="1"/>
+    <col min="4" max="4" width="6.7265625" style="12" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12"/>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
+      <c r="A1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
     </row>
     <row r="2" spans="1:4" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
     </row>
     <row r="3" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="15"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="22" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="12"/>
+    </row>
+    <row r="6" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11"/>
+      <c r="B6" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="12"/>
+    </row>
+    <row r="7" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11"/>
+      <c r="B7" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="12"/>
+    </row>
+    <row r="8" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="12"/>
+    </row>
+    <row r="9" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+      <c r="B9" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="12"/>
+    </row>
+    <row r="10" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11"/>
+      <c r="B10" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="12"/>
+    </row>
+    <row r="11" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="12"/>
+    </row>
+    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="21"/>
+      <c r="C12" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="21"/>
+      <c r="C13" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="21"/>
+      <c r="C14" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="21"/>
+      <c r="C15" s="21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="21"/>
+      <c r="C16" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="21"/>
+      <c r="C17" s="21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="21"/>
+      <c r="C18" s="21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="21"/>
+      <c r="C19" s="21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="21"/>
+      <c r="C20" s="21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="21"/>
+      <c r="C21" s="21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="21"/>
+      <c r="C22" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="21"/>
+      <c r="C23" s="21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="21"/>
+      <c r="C24" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="21"/>
+      <c r="C25" s="21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="21"/>
+      <c r="C26" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="13"/>
-    </row>
-    <row r="6" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="22" t="s">
+    </row>
+    <row r="27" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="21"/>
+      <c r="C27" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="13"/>
-    </row>
-    <row r="7" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="22" t="s">
+    </row>
+    <row r="28" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="21"/>
+      <c r="C28" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="13"/>
-    </row>
-    <row r="8" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="22" t="s">
+    </row>
+    <row r="29" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="21"/>
+      <c r="C29" s="21" t="s">
         <v>43</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="13"/>
-    </row>
-    <row r="9" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="B9" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="13"/>
-    </row>
-    <row r="10" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="13"/>
-    </row>
-    <row r="11" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="13"/>
-    </row>
-    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="22"/>
-      <c r="C12" s="22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="22"/>
-      <c r="C13" s="22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="22"/>
-      <c r="C14" s="22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="22"/>
-      <c r="C15" s="22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="22"/>
-      <c r="C16" s="22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="22"/>
-      <c r="C17" s="22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="22"/>
-      <c r="C18" s="22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="22"/>
-      <c r="C19" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="22"/>
-      <c r="C20" s="22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="22"/>
-      <c r="C21" s="22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="22"/>
-      <c r="C22" s="22" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="22"/>
-      <c r="C23" s="22" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="22"/>
-      <c r="C24" s="22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="22"/>
-      <c r="C25" s="22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="22"/>
-      <c r="C26" s="22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="22"/>
-      <c r="C27" s="22" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="22"/>
-      <c r="C28" s="22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="22"/>
-      <c r="C29" s="22" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Iteration_1/Documentation/project_tracker.xlsx
+++ b/Iteration_1/Documentation/project_tracker.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACC9BFC-0F23-4958-999F-76FB988F79BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5320FAAF-258A-4259-B004-449536AC8D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Tracker" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="94">
   <si>
     <t>Category</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Setup</t>
@@ -186,15 +183,6 @@
     <t>Place A Piece - use case description</t>
   </si>
   <si>
-    <t>Alan Bach, Anmoldeep Gill, Ethan Braum credited with the same task</t>
-  </si>
-  <si>
-    <t>Alan Bach credited with the same task</t>
-  </si>
-  <si>
-    <t>Alan Bach, Ethan Barum credited with the same task</t>
-  </si>
-  <si>
     <t>GameBoard - structure diagram</t>
   </si>
   <si>
@@ -216,9 +204,6 @@
     <t>All Members</t>
   </si>
   <si>
-    <t>Meeting Duration        (hours)</t>
-  </si>
-  <si>
     <t>Network Team</t>
   </si>
   <si>
@@ -235,6 +220,105 @@
   </si>
   <si>
     <t>Backend Team</t>
+  </si>
+  <si>
+    <t>Lead Team</t>
+  </si>
+  <si>
+    <t>Meeting Duration (hours)</t>
+  </si>
+  <si>
+    <t>Compilation Meeting</t>
+  </si>
+  <si>
+    <t>Tic Tac Toe - use case description</t>
+  </si>
+  <si>
+    <t>Notes (credit also applies to:)</t>
+  </si>
+  <si>
+    <t>Alan Bach, Anmoldeep Gill, Ethan Braum</t>
+  </si>
+  <si>
+    <t>Alan Bach, Ethan Barum</t>
+  </si>
+  <si>
+    <t>Player Profile - use case description</t>
+  </si>
+  <si>
+    <t>Checkers Piece - structure diagram</t>
+  </si>
+  <si>
+    <t>Frontend - structure diagram</t>
+  </si>
+  <si>
+    <t>Frontend - use case diagram</t>
+  </si>
+  <si>
+    <t>Michelle Yoon, Amir Khan</t>
+  </si>
+  <si>
+    <t>Connect 4 - use case description</t>
+  </si>
+  <si>
+    <t>Tic Tac Toe Piece - structure diagram</t>
+  </si>
+  <si>
+    <t>Connect 4 Piece - structure diagram</t>
+  </si>
+  <si>
+    <t>Gabriel Moises, Alan Bach</t>
+  </si>
+  <si>
+    <t>Checkers Check for Capture - use case description</t>
+  </si>
+  <si>
+    <t>Check Game End - sequence diagram</t>
+  </si>
+  <si>
+    <t>Backend - use case diagram</t>
+  </si>
+  <si>
+    <t>Aftermath - use case description</t>
+  </si>
+  <si>
+    <t>Checkers - use case description</t>
+  </si>
+  <si>
+    <t>Leaderboard - use case description</t>
+  </si>
+  <si>
+    <t>Login/Sign Out - use case diagram</t>
+  </si>
+  <si>
+    <t>Update Player Timer - use case description</t>
+  </si>
+  <si>
+    <t>Alan Bach, Gabriel Moises</t>
+  </si>
+  <si>
+    <t>Check Game End - use case description</t>
+  </si>
+  <si>
+    <t>Connect 4 Handler - structure diagram</t>
+  </si>
+  <si>
+    <t>Validate Move - use case description</t>
+  </si>
+  <si>
+    <t>Tic Tac Toe Handler - structure diagram</t>
+  </si>
+  <si>
+    <t>Risharbh Agarwal, Richard Nguyen, Mohammad Moustaqim</t>
+  </si>
+  <si>
+    <t>Connect 4 Queue - use case diagram</t>
+  </si>
+  <si>
+    <t>Checkers Handler - structure diagram</t>
+  </si>
+  <si>
+    <t>Game Piece - structure diagram</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1323,7 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Actual duration (in days)" dataDxfId="7">
       <calculatedColumnFormula>IF(COUNTA('Project Tracker'!$E5,'Project Tracker'!$F5)&lt;&gt;2,"",DAYS360('Project Tracker'!$E5,'Project Tracker'!$F5,FALSE))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Notes" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Notes (credit also applies to:)" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="Custom Table Style" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -1504,12 +1588,12 @@
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7265625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="53.453125" style="18" customWidth="1"/>
+    <col min="2" max="2" width="56.36328125" style="18" customWidth="1"/>
     <col min="3" max="3" width="21.1796875" style="18" customWidth="1"/>
-    <col min="4" max="4" width="23.7265625" style="18" customWidth="1"/>
+    <col min="4" max="4" width="27.81640625" style="18" customWidth="1"/>
     <col min="5" max="6" width="16.81640625" style="19" customWidth="1"/>
     <col min="7" max="8" width="16" style="18" customWidth="1"/>
-    <col min="9" max="9" width="78.54296875" style="18" customWidth="1"/>
+    <col min="9" max="9" width="85.6328125" style="18" customWidth="1"/>
     <col min="10" max="10" width="6.7265625" style="3" customWidth="1"/>
     <col min="11" max="11" width="4.1796875" style="2" customWidth="1"/>
     <col min="12" max="36" width="3.26953125" style="2" customWidth="1"/>
@@ -1531,13 +1615,13 @@
     <row r="2" spans="1:10" s="5" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="4"/>
       <c r="F2" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="8">
         <v>0</v>
@@ -1561,41 +1645,41 @@
     <row r="4" spans="1:10" s="5" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="F4" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="G4" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>8</v>
-      </c>
       <c r="I4" s="16" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="J4" s="10"/>
     </row>
     <row r="5" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="17" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" s="24">
         <v>45595</v>
@@ -1616,13 +1700,13 @@
     <row r="6" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" s="24">
         <v>45596</v>
@@ -1638,20 +1722,20 @@
         <v>0</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" s="24">
         <v>45595</v>
@@ -1672,13 +1756,13 @@
     <row r="8" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="24">
         <v>45595</v>
@@ -1694,20 +1778,20 @@
         <v>0</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="24">
         <v>45595</v>
@@ -1723,20 +1807,20 @@
         <v>0</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" s="24">
         <v>45595</v>
@@ -1752,20 +1836,20 @@
         <v>0</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="17" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11" s="24">
         <v>45595</v>
@@ -1781,244 +1865,619 @@
         <v>0</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="17"/>
+      <c r="B12" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="24">
+        <v>45598</v>
+      </c>
+      <c r="F12" s="24">
+        <v>45599</v>
+      </c>
+      <c r="G12" s="17">
+        <v>1</v>
+      </c>
+      <c r="H12" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E12,'Project Tracker'!$F12)&lt;&gt;2,"",DAYS360('Project Tracker'!$E12,'Project Tracker'!$F12,FALSE))</f>
+        <v>1</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>24</v>
+      </c>
       <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="17"/>
+      <c r="B13" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="24">
+        <v>45599</v>
+      </c>
+      <c r="F13" s="24">
+        <v>45599</v>
+      </c>
+      <c r="G13" s="17">
+        <v>1</v>
+      </c>
+      <c r="H13" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E13,'Project Tracker'!$F13)&lt;&gt;2,"",DAYS360('Project Tracker'!$E13,'Project Tracker'!$F13,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>24</v>
+      </c>
       <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:10" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="17"/>
+      <c r="B14" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="24">
+        <v>45599</v>
+      </c>
+      <c r="F14" s="24">
+        <v>45599</v>
+      </c>
+      <c r="G14" s="17">
+        <v>1</v>
+      </c>
+      <c r="H14" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E14,'Project Tracker'!$F14)&lt;&gt;2,"",DAYS360('Project Tracker'!$E14,'Project Tracker'!$F14,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>42</v>
+      </c>
       <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="20"/>
+      <c r="B15" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="24">
+        <v>45599</v>
+      </c>
+      <c r="F15" s="24">
+        <v>45599</v>
+      </c>
+      <c r="G15" s="17">
+        <v>1</v>
+      </c>
+      <c r="H15" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E15,'Project Tracker'!$F15)&lt;&gt;2,"",DAYS360('Project Tracker'!$E15,'Project Tracker'!$F15,FALSE))</f>
+        <v>0</v>
+      </c>
       <c r="I15" s="17"/>
     </row>
     <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="17"/>
+      <c r="B16" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="24">
+        <v>45599</v>
+      </c>
+      <c r="F16" s="24">
+        <v>45599</v>
+      </c>
+      <c r="G16" s="17">
+        <v>1</v>
+      </c>
+      <c r="H16" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E16,'Project Tracker'!$F16)&lt;&gt;2,"",DAYS360('Project Tracker'!$E16,'Project Tracker'!$F16,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="17" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="20"/>
+      <c r="B17" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="24">
+        <v>45599</v>
+      </c>
+      <c r="F17" s="24">
+        <v>45599</v>
+      </c>
+      <c r="G17" s="17">
+        <v>1</v>
+      </c>
+      <c r="H17" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E17,'Project Tracker'!$F17)&lt;&gt;2,"",DAYS360('Project Tracker'!$E17,'Project Tracker'!$F17,FALSE))</f>
+        <v>0</v>
+      </c>
       <c r="I17" s="17"/>
     </row>
     <row r="18" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="17"/>
+      <c r="B18" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="24">
+        <v>45599</v>
+      </c>
+      <c r="F18" s="24">
+        <v>45599</v>
+      </c>
+      <c r="G18" s="17">
+        <v>1</v>
+      </c>
+      <c r="H18" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E18,'Project Tracker'!$F18)&lt;&gt;2,"",DAYS360('Project Tracker'!$E18,'Project Tracker'!$F18,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="19" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="17"/>
+      <c r="B19" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="24">
+        <v>45599</v>
+      </c>
+      <c r="F19" s="24">
+        <v>45599</v>
+      </c>
+      <c r="G19" s="17">
+        <v>1</v>
+      </c>
+      <c r="H19" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E19,'Project Tracker'!$F19)&lt;&gt;2,"",DAYS360('Project Tracker'!$E19,'Project Tracker'!$F19,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="20" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="17"/>
+      <c r="B20" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="24">
+        <v>45598</v>
+      </c>
+      <c r="F20" s="24">
+        <v>45599</v>
+      </c>
+      <c r="G20" s="17">
+        <v>1</v>
+      </c>
+      <c r="H20" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E20,'Project Tracker'!$F20)&lt;&gt;2,"",DAYS360('Project Tracker'!$E20,'Project Tracker'!$F20,FALSE))</f>
+        <v>1</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="21" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="20"/>
+      <c r="B21" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="24">
+        <v>45596</v>
+      </c>
+      <c r="F21" s="24">
+        <v>45599</v>
+      </c>
+      <c r="G21" s="17">
+        <v>1</v>
+      </c>
+      <c r="H21" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E21,'Project Tracker'!$F21)&lt;&gt;2,"",DAYS360('Project Tracker'!$E21,'Project Tracker'!$F21,FALSE))</f>
+        <v>3</v>
+      </c>
       <c r="I21" s="17"/>
     </row>
     <row r="22" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="17"/>
+      <c r="B22" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="24">
+        <v>45596</v>
+      </c>
+      <c r="F22" s="24">
+        <v>45599</v>
+      </c>
+      <c r="G22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E22,'Project Tracker'!$F22)&lt;&gt;2,"",DAYS360('Project Tracker'!$E22,'Project Tracker'!$F22,FALSE))</f>
+        <v>3</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="23" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="17"/>
+      <c r="B23" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="24">
+        <v>45597</v>
+      </c>
+      <c r="F23" s="24">
+        <v>45597</v>
+      </c>
+      <c r="G23" s="17">
+        <v>1</v>
+      </c>
+      <c r="H23" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E23,'Project Tracker'!$F23)&lt;&gt;2,"",DAYS360('Project Tracker'!$E23,'Project Tracker'!$F23,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="17" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="24" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="17"/>
+      <c r="B24" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="24">
+        <v>45595</v>
+      </c>
+      <c r="F24" s="24">
+        <v>45599</v>
+      </c>
+      <c r="G24" s="17">
+        <v>1</v>
+      </c>
+      <c r="H24" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E24,'Project Tracker'!$F24)&lt;&gt;2,"",DAYS360('Project Tracker'!$E24,'Project Tracker'!$F24,FALSE))</f>
+        <v>3</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="25" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="17"/>
+      <c r="B25" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="24">
+        <v>45594</v>
+      </c>
+      <c r="F25" s="24">
+        <v>45599</v>
+      </c>
+      <c r="G25" s="17">
+        <v>2</v>
+      </c>
+      <c r="H25" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E25,'Project Tracker'!$F25)&lt;&gt;2,"",DAYS360('Project Tracker'!$E25,'Project Tracker'!$F25,FALSE))</f>
+        <v>4</v>
+      </c>
+      <c r="I25" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="26" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="17"/>
+      <c r="B26" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="24">
+        <v>45594</v>
+      </c>
+      <c r="F26" s="24">
+        <v>45598</v>
+      </c>
+      <c r="G26" s="17">
+        <v>1</v>
+      </c>
+      <c r="H26" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E26,'Project Tracker'!$F26)&lt;&gt;2,"",DAYS360('Project Tracker'!$E26,'Project Tracker'!$F26,FALSE))</f>
+        <v>3</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="27" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="17"/>
+      <c r="B27" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="24">
+        <v>45597</v>
+      </c>
+      <c r="F27" s="24">
+        <v>45598</v>
+      </c>
+      <c r="G27" s="17">
+        <v>1</v>
+      </c>
+      <c r="H27" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E27,'Project Tracker'!$F27)&lt;&gt;2,"",DAYS360('Project Tracker'!$E27,'Project Tracker'!$F27,FALSE))</f>
+        <v>1</v>
+      </c>
+      <c r="I27" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="17"/>
+      <c r="B28" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="24">
+        <v>45596</v>
+      </c>
+      <c r="F28" s="24">
+        <v>45598</v>
+      </c>
+      <c r="G28" s="17">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E28,'Project Tracker'!$F28)&lt;&gt;2,"",DAYS360('Project Tracker'!$E28,'Project Tracker'!$F28,FALSE))</f>
+        <v>2</v>
+      </c>
+      <c r="I28" s="17" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="20"/>
+      <c r="B29" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="24">
+        <v>45596</v>
+      </c>
+      <c r="F29" s="24">
+        <v>45597</v>
+      </c>
+      <c r="G29" s="17">
+        <v>1</v>
+      </c>
+      <c r="H29" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E29,'Project Tracker'!$F29)&lt;&gt;2,"",DAYS360('Project Tracker'!$E29,'Project Tracker'!$F29,FALSE))</f>
+        <v>1</v>
+      </c>
       <c r="I29" s="17"/>
     </row>
     <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="17"/>
+      <c r="B30" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="24">
+        <v>45596</v>
+      </c>
+      <c r="F30" s="24">
+        <v>45598</v>
+      </c>
+      <c r="G30" s="17">
+        <v>1</v>
+      </c>
+      <c r="H30" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E30,'Project Tracker'!$F30)&lt;&gt;2,"",DAYS360('Project Tracker'!$E30,'Project Tracker'!$F30,FALSE))</f>
+        <v>2</v>
+      </c>
+      <c r="I30" s="17" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="31" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="20"/>
+      <c r="B31" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" s="24">
+        <v>45596</v>
+      </c>
+      <c r="F31" s="24">
+        <v>45597</v>
+      </c>
+      <c r="G31" s="17">
+        <v>1</v>
+      </c>
+      <c r="H31" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E31,'Project Tracker'!$F31)&lt;&gt;2,"",DAYS360('Project Tracker'!$E31,'Project Tracker'!$F31,FALSE))</f>
+        <v>1</v>
+      </c>
       <c r="I31" s="17"/>
     </row>
     <row r="32" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="20"/>
+      <c r="B32" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="24">
+        <v>45597</v>
+      </c>
+      <c r="F32" s="24">
+        <v>45599</v>
+      </c>
+      <c r="G32" s="17">
+        <v>4</v>
+      </c>
+      <c r="H32" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E32,'Project Tracker'!$F32)&lt;&gt;2,"",DAYS360('Project Tracker'!$E32,'Project Tracker'!$F32,FALSE))</f>
+        <v>2</v>
+      </c>
       <c r="I32" s="17"/>
     </row>
     <row r="33" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="20"/>
+      <c r="B33" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="24">
+        <v>45596</v>
+      </c>
+      <c r="F33" s="24">
+        <v>45597</v>
+      </c>
+      <c r="G33" s="17">
+        <v>1</v>
+      </c>
+      <c r="H33" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E33,'Project Tracker'!$F33)&lt;&gt;2,"",DAYS360('Project Tracker'!$E33,'Project Tracker'!$F33,FALSE))</f>
+        <v>1</v>
+      </c>
       <c r="I33" s="17"/>
     </row>
     <row r="34" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="20"/>
+      <c r="B34" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" s="24">
+        <v>45596</v>
+      </c>
+      <c r="F34" s="24">
+        <v>45597</v>
+      </c>
+      <c r="G34" s="17">
+        <v>1</v>
+      </c>
+      <c r="H34" s="20">
+        <f>IF(COUNTA('Project Tracker'!$E34,'Project Tracker'!$F34)&lt;&gt;2,"",DAYS360('Project Tracker'!$E34,'Project Tracker'!$F34,FALSE))</f>
+        <v>1</v>
+      </c>
       <c r="I34" s="17"/>
     </row>
     <row r="35" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2028,7 +2487,10 @@
       <c r="E35" s="24"/>
       <c r="F35" s="24"/>
       <c r="G35" s="17"/>
-      <c r="H35" s="20"/>
+      <c r="H35" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E35,'Project Tracker'!$F35)&lt;&gt;2,"",DAYS360('Project Tracker'!$E35,'Project Tracker'!$F35,FALSE))</f>
+        <v/>
+      </c>
       <c r="I35" s="17"/>
     </row>
     <row r="36" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2038,7 +2500,10 @@
       <c r="E36" s="24"/>
       <c r="F36" s="24"/>
       <c r="G36" s="17"/>
-      <c r="H36" s="20"/>
+      <c r="H36" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E36,'Project Tracker'!$F36)&lt;&gt;2,"",DAYS360('Project Tracker'!$E36,'Project Tracker'!$F36,FALSE))</f>
+        <v/>
+      </c>
       <c r="I36" s="17"/>
     </row>
     <row r="37" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2048,7 +2513,10 @@
       <c r="E37" s="24"/>
       <c r="F37" s="24"/>
       <c r="G37" s="17"/>
-      <c r="H37" s="20"/>
+      <c r="H37" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E37,'Project Tracker'!$F37)&lt;&gt;2,"",DAYS360('Project Tracker'!$E37,'Project Tracker'!$F37,FALSE))</f>
+        <v/>
+      </c>
       <c r="I37" s="17"/>
     </row>
     <row r="38" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2058,7 +2526,10 @@
       <c r="E38" s="24"/>
       <c r="F38" s="24"/>
       <c r="G38" s="17"/>
-      <c r="H38" s="20"/>
+      <c r="H38" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E38,'Project Tracker'!$F38)&lt;&gt;2,"",DAYS360('Project Tracker'!$E38,'Project Tracker'!$F38,FALSE))</f>
+        <v/>
+      </c>
       <c r="I38" s="17"/>
     </row>
     <row r="39" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2068,7 +2539,10 @@
       <c r="E39" s="24"/>
       <c r="F39" s="24"/>
       <c r="G39" s="17"/>
-      <c r="H39" s="20"/>
+      <c r="H39" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E39,'Project Tracker'!$F39)&lt;&gt;2,"",DAYS360('Project Tracker'!$E39,'Project Tracker'!$F39,FALSE))</f>
+        <v/>
+      </c>
       <c r="I39" s="17"/>
     </row>
     <row r="40" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2078,7 +2552,10 @@
       <c r="E40" s="24"/>
       <c r="F40" s="24"/>
       <c r="G40" s="17"/>
-      <c r="H40" s="20"/>
+      <c r="H40" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E40,'Project Tracker'!$F40)&lt;&gt;2,"",DAYS360('Project Tracker'!$E40,'Project Tracker'!$F40,FALSE))</f>
+        <v/>
+      </c>
       <c r="I40" s="17"/>
     </row>
     <row r="41" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2088,7 +2565,10 @@
       <c r="E41" s="24"/>
       <c r="F41" s="24"/>
       <c r="G41" s="17"/>
-      <c r="H41" s="20"/>
+      <c r="H41" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E41,'Project Tracker'!$F41)&lt;&gt;2,"",DAYS360('Project Tracker'!$E41,'Project Tracker'!$F41,FALSE))</f>
+        <v/>
+      </c>
       <c r="I41" s="17"/>
     </row>
     <row r="42" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2098,7 +2578,10 @@
       <c r="E42" s="24"/>
       <c r="F42" s="24"/>
       <c r="G42" s="17"/>
-      <c r="H42" s="20"/>
+      <c r="H42" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E42,'Project Tracker'!$F42)&lt;&gt;2,"",DAYS360('Project Tracker'!$E42,'Project Tracker'!$F42,FALSE))</f>
+        <v/>
+      </c>
       <c r="I42" s="17"/>
     </row>
     <row r="43" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2108,7 +2591,10 @@
       <c r="E43" s="24"/>
       <c r="F43" s="24"/>
       <c r="G43" s="17"/>
-      <c r="H43" s="20"/>
+      <c r="H43" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E43,'Project Tracker'!$F43)&lt;&gt;2,"",DAYS360('Project Tracker'!$E43,'Project Tracker'!$F43,FALSE))</f>
+        <v/>
+      </c>
       <c r="I43" s="17"/>
     </row>
     <row r="44" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2118,7 +2604,10 @@
       <c r="E44" s="24"/>
       <c r="F44" s="24"/>
       <c r="G44" s="17"/>
-      <c r="H44" s="20"/>
+      <c r="H44" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E44,'Project Tracker'!$F44)&lt;&gt;2,"",DAYS360('Project Tracker'!$E44,'Project Tracker'!$F44,FALSE))</f>
+        <v/>
+      </c>
       <c r="I44" s="17"/>
     </row>
     <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2128,7 +2617,10 @@
       <c r="E45" s="24"/>
       <c r="F45" s="24"/>
       <c r="G45" s="17"/>
-      <c r="H45" s="20"/>
+      <c r="H45" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E45,'Project Tracker'!$F45)&lt;&gt;2,"",DAYS360('Project Tracker'!$E45,'Project Tracker'!$F45,FALSE))</f>
+        <v/>
+      </c>
       <c r="I45" s="17"/>
     </row>
     <row r="46" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2138,7 +2630,10 @@
       <c r="E46" s="24"/>
       <c r="F46" s="24"/>
       <c r="G46" s="17"/>
-      <c r="H46" s="20"/>
+      <c r="H46" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E46,'Project Tracker'!$F46)&lt;&gt;2,"",DAYS360('Project Tracker'!$E46,'Project Tracker'!$F46,FALSE))</f>
+        <v/>
+      </c>
       <c r="I46" s="17"/>
     </row>
     <row r="47" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2148,7 +2643,10 @@
       <c r="E47" s="24"/>
       <c r="F47" s="24"/>
       <c r="G47" s="17"/>
-      <c r="H47" s="20"/>
+      <c r="H47" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E47,'Project Tracker'!$F47)&lt;&gt;2,"",DAYS360('Project Tracker'!$E47,'Project Tracker'!$F47,FALSE))</f>
+        <v/>
+      </c>
       <c r="I47" s="17"/>
     </row>
     <row r="48" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2158,7 +2656,10 @@
       <c r="E48" s="24"/>
       <c r="F48" s="24"/>
       <c r="G48" s="17"/>
-      <c r="H48" s="20"/>
+      <c r="H48" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E48,'Project Tracker'!$F48)&lt;&gt;2,"",DAYS360('Project Tracker'!$E48,'Project Tracker'!$F48,FALSE))</f>
+        <v/>
+      </c>
       <c r="I48" s="17"/>
     </row>
     <row r="49" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2168,7 +2669,10 @@
       <c r="E49" s="24"/>
       <c r="F49" s="24"/>
       <c r="G49" s="17"/>
-      <c r="H49" s="20"/>
+      <c r="H49" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E49,'Project Tracker'!$F49)&lt;&gt;2,"",DAYS360('Project Tracker'!$E49,'Project Tracker'!$F49,FALSE))</f>
+        <v/>
+      </c>
       <c r="I49" s="17"/>
     </row>
     <row r="50" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2178,7 +2682,10 @@
       <c r="E50" s="24"/>
       <c r="F50" s="24"/>
       <c r="G50" s="17"/>
-      <c r="H50" s="20"/>
+      <c r="H50" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E50,'Project Tracker'!$F50)&lt;&gt;2,"",DAYS360('Project Tracker'!$E50,'Project Tracker'!$F50,FALSE))</f>
+        <v/>
+      </c>
       <c r="I50" s="17"/>
     </row>
     <row r="51" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2188,7 +2695,10 @@
       <c r="E51" s="24"/>
       <c r="F51" s="24"/>
       <c r="G51" s="17"/>
-      <c r="H51" s="20"/>
+      <c r="H51" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E51,'Project Tracker'!$F51)&lt;&gt;2,"",DAYS360('Project Tracker'!$E51,'Project Tracker'!$F51,FALSE))</f>
+        <v/>
+      </c>
       <c r="I51" s="17"/>
     </row>
     <row r="52" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2198,7 +2708,10 @@
       <c r="E52" s="24"/>
       <c r="F52" s="24"/>
       <c r="G52" s="17"/>
-      <c r="H52" s="20"/>
+      <c r="H52" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E52,'Project Tracker'!$F52)&lt;&gt;2,"",DAYS360('Project Tracker'!$E52,'Project Tracker'!$F52,FALSE))</f>
+        <v/>
+      </c>
       <c r="I52" s="17"/>
     </row>
     <row r="53" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2208,7 +2721,10 @@
       <c r="E53" s="24"/>
       <c r="F53" s="24"/>
       <c r="G53" s="17"/>
-      <c r="H53" s="20"/>
+      <c r="H53" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E53,'Project Tracker'!$F53)&lt;&gt;2,"",DAYS360('Project Tracker'!$E53,'Project Tracker'!$F53,FALSE))</f>
+        <v/>
+      </c>
       <c r="I53" s="17"/>
     </row>
     <row r="54" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2218,7 +2734,10 @@
       <c r="E54" s="24"/>
       <c r="F54" s="24"/>
       <c r="G54" s="17"/>
-      <c r="H54" s="20"/>
+      <c r="H54" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E54,'Project Tracker'!$F54)&lt;&gt;2,"",DAYS360('Project Tracker'!$E54,'Project Tracker'!$F54,FALSE))</f>
+        <v/>
+      </c>
       <c r="I54" s="17"/>
     </row>
     <row r="55" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2228,7 +2747,10 @@
       <c r="E55" s="24"/>
       <c r="F55" s="24"/>
       <c r="G55" s="17"/>
-      <c r="H55" s="20"/>
+      <c r="H55" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E55,'Project Tracker'!$F55)&lt;&gt;2,"",DAYS360('Project Tracker'!$E55,'Project Tracker'!$F55,FALSE))</f>
+        <v/>
+      </c>
       <c r="I55" s="17"/>
     </row>
     <row r="56" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2238,7 +2760,10 @@
       <c r="E56" s="24"/>
       <c r="F56" s="24"/>
       <c r="G56" s="17"/>
-      <c r="H56" s="20"/>
+      <c r="H56" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E56,'Project Tracker'!$F56)&lt;&gt;2,"",DAYS360('Project Tracker'!$E56,'Project Tracker'!$F56,FALSE))</f>
+        <v/>
+      </c>
       <c r="I56" s="17"/>
     </row>
     <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2248,7 +2773,10 @@
       <c r="E57" s="24"/>
       <c r="F57" s="24"/>
       <c r="G57" s="17"/>
-      <c r="H57" s="20"/>
+      <c r="H57" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E57,'Project Tracker'!$F57)&lt;&gt;2,"",DAYS360('Project Tracker'!$E57,'Project Tracker'!$F57,FALSE))</f>
+        <v/>
+      </c>
       <c r="I57" s="17"/>
     </row>
     <row r="58" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2258,7 +2786,10 @@
       <c r="E58" s="24"/>
       <c r="F58" s="24"/>
       <c r="G58" s="17"/>
-      <c r="H58" s="20"/>
+      <c r="H58" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E58,'Project Tracker'!$F58)&lt;&gt;2,"",DAYS360('Project Tracker'!$E58,'Project Tracker'!$F58,FALSE))</f>
+        <v/>
+      </c>
       <c r="I58" s="17"/>
     </row>
     <row r="59" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2268,7 +2799,10 @@
       <c r="E59" s="24"/>
       <c r="F59" s="24"/>
       <c r="G59" s="17"/>
-      <c r="H59" s="20"/>
+      <c r="H59" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E59,'Project Tracker'!$F59)&lt;&gt;2,"",DAYS360('Project Tracker'!$E59,'Project Tracker'!$F59,FALSE))</f>
+        <v/>
+      </c>
       <c r="I59" s="17"/>
     </row>
     <row r="60" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2278,7 +2812,10 @@
       <c r="E60" s="24"/>
       <c r="F60" s="24"/>
       <c r="G60" s="17"/>
-      <c r="H60" s="20"/>
+      <c r="H60" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E60,'Project Tracker'!$F60)&lt;&gt;2,"",DAYS360('Project Tracker'!$E60,'Project Tracker'!$F60,FALSE))</f>
+        <v/>
+      </c>
       <c r="I60" s="17"/>
     </row>
     <row r="61" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2288,7 +2825,10 @@
       <c r="E61" s="24"/>
       <c r="F61" s="24"/>
       <c r="G61" s="17"/>
-      <c r="H61" s="20"/>
+      <c r="H61" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E61,'Project Tracker'!$F61)&lt;&gt;2,"",DAYS360('Project Tracker'!$E61,'Project Tracker'!$F61,FALSE))</f>
+        <v/>
+      </c>
       <c r="I61" s="17"/>
     </row>
     <row r="62" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2298,7 +2838,10 @@
       <c r="E62" s="24"/>
       <c r="F62" s="24"/>
       <c r="G62" s="17"/>
-      <c r="H62" s="20"/>
+      <c r="H62" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E62,'Project Tracker'!$F62)&lt;&gt;2,"",DAYS360('Project Tracker'!$E62,'Project Tracker'!$F62,FALSE))</f>
+        <v/>
+      </c>
       <c r="I62" s="17"/>
     </row>
     <row r="63" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2308,7 +2851,10 @@
       <c r="E63" s="24"/>
       <c r="F63" s="24"/>
       <c r="G63" s="17"/>
-      <c r="H63" s="20"/>
+      <c r="H63" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E63,'Project Tracker'!$F63)&lt;&gt;2,"",DAYS360('Project Tracker'!$E63,'Project Tracker'!$F63,FALSE))</f>
+        <v/>
+      </c>
       <c r="I63" s="17"/>
     </row>
     <row r="64" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2318,7 +2864,10 @@
       <c r="E64" s="24"/>
       <c r="F64" s="24"/>
       <c r="G64" s="17"/>
-      <c r="H64" s="20"/>
+      <c r="H64" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E64,'Project Tracker'!$F64)&lt;&gt;2,"",DAYS360('Project Tracker'!$E64,'Project Tracker'!$F64,FALSE))</f>
+        <v/>
+      </c>
       <c r="I64" s="17"/>
     </row>
     <row r="65" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2328,7 +2877,10 @@
       <c r="E65" s="24"/>
       <c r="F65" s="24"/>
       <c r="G65" s="17"/>
-      <c r="H65" s="20"/>
+      <c r="H65" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E65,'Project Tracker'!$F65)&lt;&gt;2,"",DAYS360('Project Tracker'!$E65,'Project Tracker'!$F65,FALSE))</f>
+        <v/>
+      </c>
       <c r="I65" s="17"/>
     </row>
     <row r="66" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2338,7 +2890,10 @@
       <c r="E66" s="24"/>
       <c r="F66" s="24"/>
       <c r="G66" s="17"/>
-      <c r="H66" s="20"/>
+      <c r="H66" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E66,'Project Tracker'!$F66)&lt;&gt;2,"",DAYS360('Project Tracker'!$E66,'Project Tracker'!$F66,FALSE))</f>
+        <v/>
+      </c>
       <c r="I66" s="17"/>
     </row>
     <row r="67" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2348,7 +2903,10 @@
       <c r="E67" s="24"/>
       <c r="F67" s="24"/>
       <c r="G67" s="17"/>
-      <c r="H67" s="20"/>
+      <c r="H67" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E67,'Project Tracker'!$F67)&lt;&gt;2,"",DAYS360('Project Tracker'!$E67,'Project Tracker'!$F67,FALSE))</f>
+        <v/>
+      </c>
       <c r="I67" s="17"/>
     </row>
     <row r="68" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2358,7 +2916,10 @@
       <c r="E68" s="24"/>
       <c r="F68" s="24"/>
       <c r="G68" s="17"/>
-      <c r="H68" s="20"/>
+      <c r="H68" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E68,'Project Tracker'!$F68)&lt;&gt;2,"",DAYS360('Project Tracker'!$E68,'Project Tracker'!$F68,FALSE))</f>
+        <v/>
+      </c>
       <c r="I68" s="17"/>
     </row>
     <row r="69" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2368,7 +2929,10 @@
       <c r="E69" s="24"/>
       <c r="F69" s="24"/>
       <c r="G69" s="17"/>
-      <c r="H69" s="20"/>
+      <c r="H69" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E69,'Project Tracker'!$F69)&lt;&gt;2,"",DAYS360('Project Tracker'!$E69,'Project Tracker'!$F69,FALSE))</f>
+        <v/>
+      </c>
       <c r="I69" s="17"/>
     </row>
     <row r="70" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2378,7 +2942,10 @@
       <c r="E70" s="24"/>
       <c r="F70" s="24"/>
       <c r="G70" s="17"/>
-      <c r="H70" s="20"/>
+      <c r="H70" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E70,'Project Tracker'!$F70)&lt;&gt;2,"",DAYS360('Project Tracker'!$E70,'Project Tracker'!$F70,FALSE))</f>
+        <v/>
+      </c>
       <c r="I70" s="17"/>
     </row>
     <row r="71" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2388,7 +2955,10 @@
       <c r="E71" s="24"/>
       <c r="F71" s="24"/>
       <c r="G71" s="17"/>
-      <c r="H71" s="20"/>
+      <c r="H71" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E71,'Project Tracker'!$F71)&lt;&gt;2,"",DAYS360('Project Tracker'!$E71,'Project Tracker'!$F71,FALSE))</f>
+        <v/>
+      </c>
       <c r="I71" s="17"/>
     </row>
     <row r="72" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2398,7 +2968,10 @@
       <c r="E72" s="24"/>
       <c r="F72" s="24"/>
       <c r="G72" s="17"/>
-      <c r="H72" s="20"/>
+      <c r="H72" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E72,'Project Tracker'!$F72)&lt;&gt;2,"",DAYS360('Project Tracker'!$E72,'Project Tracker'!$F72,FALSE))</f>
+        <v/>
+      </c>
       <c r="I72" s="17"/>
     </row>
     <row r="73" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2408,7 +2981,10 @@
       <c r="E73" s="24"/>
       <c r="F73" s="24"/>
       <c r="G73" s="17"/>
-      <c r="H73" s="20"/>
+      <c r="H73" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E73,'Project Tracker'!$F73)&lt;&gt;2,"",DAYS360('Project Tracker'!$E73,'Project Tracker'!$F73,FALSE))</f>
+        <v/>
+      </c>
       <c r="I73" s="17"/>
     </row>
     <row r="74" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2418,7 +2994,10 @@
       <c r="E74" s="24"/>
       <c r="F74" s="24"/>
       <c r="G74" s="17"/>
-      <c r="H74" s="20"/>
+      <c r="H74" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E74,'Project Tracker'!$F74)&lt;&gt;2,"",DAYS360('Project Tracker'!$E74,'Project Tracker'!$F74,FALSE))</f>
+        <v/>
+      </c>
       <c r="I74" s="17"/>
     </row>
     <row r="75" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2428,7 +3007,10 @@
       <c r="E75" s="24"/>
       <c r="F75" s="24"/>
       <c r="G75" s="17"/>
-      <c r="H75" s="20"/>
+      <c r="H75" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E75,'Project Tracker'!$F75)&lt;&gt;2,"",DAYS360('Project Tracker'!$E75,'Project Tracker'!$F75,FALSE))</f>
+        <v/>
+      </c>
       <c r="I75" s="17"/>
     </row>
     <row r="76" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2438,7 +3020,10 @@
       <c r="E76" s="24"/>
       <c r="F76" s="24"/>
       <c r="G76" s="17"/>
-      <c r="H76" s="20"/>
+      <c r="H76" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E76,'Project Tracker'!$F76)&lt;&gt;2,"",DAYS360('Project Tracker'!$E76,'Project Tracker'!$F76,FALSE))</f>
+        <v/>
+      </c>
       <c r="I76" s="17"/>
     </row>
     <row r="77" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2448,7 +3033,10 @@
       <c r="E77" s="24"/>
       <c r="F77" s="24"/>
       <c r="G77" s="17"/>
-      <c r="H77" s="20"/>
+      <c r="H77" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E77,'Project Tracker'!$F77)&lt;&gt;2,"",DAYS360('Project Tracker'!$E77,'Project Tracker'!$F77,FALSE))</f>
+        <v/>
+      </c>
       <c r="I77" s="17"/>
     </row>
     <row r="78" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2458,7 +3046,10 @@
       <c r="E78" s="24"/>
       <c r="F78" s="24"/>
       <c r="G78" s="17"/>
-      <c r="H78" s="20"/>
+      <c r="H78" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E78,'Project Tracker'!$F78)&lt;&gt;2,"",DAYS360('Project Tracker'!$E78,'Project Tracker'!$F78,FALSE))</f>
+        <v/>
+      </c>
       <c r="I78" s="17"/>
     </row>
     <row r="79" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2468,7 +3059,10 @@
       <c r="E79" s="24"/>
       <c r="F79" s="24"/>
       <c r="G79" s="17"/>
-      <c r="H79" s="20"/>
+      <c r="H79" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E79,'Project Tracker'!$F79)&lt;&gt;2,"",DAYS360('Project Tracker'!$E79,'Project Tracker'!$F79,FALSE))</f>
+        <v/>
+      </c>
       <c r="I79" s="17"/>
     </row>
     <row r="80" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2478,7 +3072,10 @@
       <c r="E80" s="24"/>
       <c r="F80" s="24"/>
       <c r="G80" s="17"/>
-      <c r="H80" s="20"/>
+      <c r="H80" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E80,'Project Tracker'!$F80)&lt;&gt;2,"",DAYS360('Project Tracker'!$E80,'Project Tracker'!$F80,FALSE))</f>
+        <v/>
+      </c>
       <c r="I80" s="17"/>
     </row>
     <row r="81" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2488,7 +3085,10 @@
       <c r="E81" s="24"/>
       <c r="F81" s="24"/>
       <c r="G81" s="17"/>
-      <c r="H81" s="20"/>
+      <c r="H81" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E81,'Project Tracker'!$F81)&lt;&gt;2,"",DAYS360('Project Tracker'!$E81,'Project Tracker'!$F81,FALSE))</f>
+        <v/>
+      </c>
       <c r="I81" s="17"/>
     </row>
     <row r="82" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2498,7 +3098,10 @@
       <c r="E82" s="24"/>
       <c r="F82" s="24"/>
       <c r="G82" s="17"/>
-      <c r="H82" s="20"/>
+      <c r="H82" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E82,'Project Tracker'!$F82)&lt;&gt;2,"",DAYS360('Project Tracker'!$E82,'Project Tracker'!$F82,FALSE))</f>
+        <v/>
+      </c>
       <c r="I82" s="17"/>
     </row>
     <row r="83" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2508,7 +3111,10 @@
       <c r="E83" s="24"/>
       <c r="F83" s="24"/>
       <c r="G83" s="17"/>
-      <c r="H83" s="20"/>
+      <c r="H83" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E83,'Project Tracker'!$F83)&lt;&gt;2,"",DAYS360('Project Tracker'!$E83,'Project Tracker'!$F83,FALSE))</f>
+        <v/>
+      </c>
       <c r="I83" s="17"/>
     </row>
     <row r="84" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2518,7 +3124,10 @@
       <c r="E84" s="24"/>
       <c r="F84" s="24"/>
       <c r="G84" s="17"/>
-      <c r="H84" s="20"/>
+      <c r="H84" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E84,'Project Tracker'!$F84)&lt;&gt;2,"",DAYS360('Project Tracker'!$E84,'Project Tracker'!$F84,FALSE))</f>
+        <v/>
+      </c>
       <c r="I84" s="17"/>
     </row>
     <row r="85" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2528,7 +3137,10 @@
       <c r="E85" s="24"/>
       <c r="F85" s="24"/>
       <c r="G85" s="17"/>
-      <c r="H85" s="20"/>
+      <c r="H85" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E85,'Project Tracker'!$F85)&lt;&gt;2,"",DAYS360('Project Tracker'!$E85,'Project Tracker'!$F85,FALSE))</f>
+        <v/>
+      </c>
       <c r="I85" s="17"/>
     </row>
     <row r="86" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2538,7 +3150,10 @@
       <c r="E86" s="24"/>
       <c r="F86" s="24"/>
       <c r="G86" s="17"/>
-      <c r="H86" s="20"/>
+      <c r="H86" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E86,'Project Tracker'!$F86)&lt;&gt;2,"",DAYS360('Project Tracker'!$E86,'Project Tracker'!$F86,FALSE))</f>
+        <v/>
+      </c>
       <c r="I86" s="17"/>
     </row>
     <row r="87" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2548,7 +3163,10 @@
       <c r="E87" s="24"/>
       <c r="F87" s="24"/>
       <c r="G87" s="17"/>
-      <c r="H87" s="20"/>
+      <c r="H87" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E87,'Project Tracker'!$F87)&lt;&gt;2,"",DAYS360('Project Tracker'!$E87,'Project Tracker'!$F87,FALSE))</f>
+        <v/>
+      </c>
       <c r="I87" s="17"/>
     </row>
     <row r="88" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2558,7 +3176,10 @@
       <c r="E88" s="24"/>
       <c r="F88" s="24"/>
       <c r="G88" s="17"/>
-      <c r="H88" s="20"/>
+      <c r="H88" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E88,'Project Tracker'!$F88)&lt;&gt;2,"",DAYS360('Project Tracker'!$E88,'Project Tracker'!$F88,FALSE))</f>
+        <v/>
+      </c>
       <c r="I88" s="17"/>
     </row>
     <row r="89" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2568,7 +3189,10 @@
       <c r="E89" s="24"/>
       <c r="F89" s="24"/>
       <c r="G89" s="17"/>
-      <c r="H89" s="20"/>
+      <c r="H89" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E89,'Project Tracker'!$F89)&lt;&gt;2,"",DAYS360('Project Tracker'!$E89,'Project Tracker'!$F89,FALSE))</f>
+        <v/>
+      </c>
       <c r="I89" s="17"/>
     </row>
     <row r="90" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2578,7 +3202,10 @@
       <c r="E90" s="24"/>
       <c r="F90" s="24"/>
       <c r="G90" s="17"/>
-      <c r="H90" s="20"/>
+      <c r="H90" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E90,'Project Tracker'!$F90)&lt;&gt;2,"",DAYS360('Project Tracker'!$E90,'Project Tracker'!$F90,FALSE))</f>
+        <v/>
+      </c>
       <c r="I90" s="17"/>
     </row>
     <row r="91" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2588,7 +3215,10 @@
       <c r="E91" s="24"/>
       <c r="F91" s="24"/>
       <c r="G91" s="17"/>
-      <c r="H91" s="20"/>
+      <c r="H91" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E91,'Project Tracker'!$F91)&lt;&gt;2,"",DAYS360('Project Tracker'!$E91,'Project Tracker'!$F91,FALSE))</f>
+        <v/>
+      </c>
       <c r="I91" s="17"/>
     </row>
     <row r="92" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2598,7 +3228,10 @@
       <c r="E92" s="24"/>
       <c r="F92" s="24"/>
       <c r="G92" s="17"/>
-      <c r="H92" s="20"/>
+      <c r="H92" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E92,'Project Tracker'!$F92)&lt;&gt;2,"",DAYS360('Project Tracker'!$E92,'Project Tracker'!$F92,FALSE))</f>
+        <v/>
+      </c>
       <c r="I92" s="17"/>
     </row>
     <row r="93" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2608,7 +3241,10 @@
       <c r="E93" s="24"/>
       <c r="F93" s="24"/>
       <c r="G93" s="17"/>
-      <c r="H93" s="20"/>
+      <c r="H93" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E93,'Project Tracker'!$F93)&lt;&gt;2,"",DAYS360('Project Tracker'!$E93,'Project Tracker'!$F93,FALSE))</f>
+        <v/>
+      </c>
       <c r="I93" s="17"/>
     </row>
     <row r="94" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2618,7 +3254,10 @@
       <c r="E94" s="24"/>
       <c r="F94" s="24"/>
       <c r="G94" s="17"/>
-      <c r="H94" s="20"/>
+      <c r="H94" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E94,'Project Tracker'!$F94)&lt;&gt;2,"",DAYS360('Project Tracker'!$E94,'Project Tracker'!$F94,FALSE))</f>
+        <v/>
+      </c>
       <c r="I94" s="17"/>
     </row>
     <row r="95" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2628,7 +3267,10 @@
       <c r="E95" s="24"/>
       <c r="F95" s="24"/>
       <c r="G95" s="17"/>
-      <c r="H95" s="20"/>
+      <c r="H95" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E95,'Project Tracker'!$F95)&lt;&gt;2,"",DAYS360('Project Tracker'!$E95,'Project Tracker'!$F95,FALSE))</f>
+        <v/>
+      </c>
       <c r="I95" s="17"/>
     </row>
     <row r="96" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2638,7 +3280,10 @@
       <c r="E96" s="24"/>
       <c r="F96" s="24"/>
       <c r="G96" s="17"/>
-      <c r="H96" s="20"/>
+      <c r="H96" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E96,'Project Tracker'!$F96)&lt;&gt;2,"",DAYS360('Project Tracker'!$E96,'Project Tracker'!$F96,FALSE))</f>
+        <v/>
+      </c>
       <c r="I96" s="17"/>
     </row>
     <row r="97" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2648,7 +3293,10 @@
       <c r="E97" s="24"/>
       <c r="F97" s="24"/>
       <c r="G97" s="17"/>
-      <c r="H97" s="20"/>
+      <c r="H97" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E97,'Project Tracker'!$F97)&lt;&gt;2,"",DAYS360('Project Tracker'!$E97,'Project Tracker'!$F97,FALSE))</f>
+        <v/>
+      </c>
       <c r="I97" s="17"/>
     </row>
     <row r="98" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2658,7 +3306,10 @@
       <c r="E98" s="24"/>
       <c r="F98" s="24"/>
       <c r="G98" s="17"/>
-      <c r="H98" s="20"/>
+      <c r="H98" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E98,'Project Tracker'!$F98)&lt;&gt;2,"",DAYS360('Project Tracker'!$E98,'Project Tracker'!$F98,FALSE))</f>
+        <v/>
+      </c>
       <c r="I98" s="17"/>
     </row>
     <row r="99" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2668,7 +3319,10 @@
       <c r="E99" s="24"/>
       <c r="F99" s="24"/>
       <c r="G99" s="17"/>
-      <c r="H99" s="20"/>
+      <c r="H99" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E99,'Project Tracker'!$F99)&lt;&gt;2,"",DAYS360('Project Tracker'!$E99,'Project Tracker'!$F99,FALSE))</f>
+        <v/>
+      </c>
       <c r="I99" s="17"/>
     </row>
     <row r="100" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2678,7 +3332,10 @@
       <c r="E100" s="24"/>
       <c r="F100" s="24"/>
       <c r="G100" s="17"/>
-      <c r="H100" s="20"/>
+      <c r="H100" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E100,'Project Tracker'!$F100)&lt;&gt;2,"",DAYS360('Project Tracker'!$E100,'Project Tracker'!$F100,FALSE))</f>
+        <v/>
+      </c>
       <c r="I100" s="17"/>
     </row>
     <row r="101" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2688,7 +3345,10 @@
       <c r="E101" s="24"/>
       <c r="F101" s="24"/>
       <c r="G101" s="17"/>
-      <c r="H101" s="20"/>
+      <c r="H101" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E101,'Project Tracker'!$F101)&lt;&gt;2,"",DAYS360('Project Tracker'!$E101,'Project Tracker'!$F101,FALSE))</f>
+        <v/>
+      </c>
       <c r="I101" s="17"/>
     </row>
     <row r="102" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2698,7 +3358,10 @@
       <c r="E102" s="24"/>
       <c r="F102" s="24"/>
       <c r="G102" s="17"/>
-      <c r="H102" s="20"/>
+      <c r="H102" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E102,'Project Tracker'!$F102)&lt;&gt;2,"",DAYS360('Project Tracker'!$E102,'Project Tracker'!$F102,FALSE))</f>
+        <v/>
+      </c>
       <c r="I102" s="17"/>
     </row>
     <row r="103" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2708,7 +3371,10 @@
       <c r="E103" s="24"/>
       <c r="F103" s="24"/>
       <c r="G103" s="17"/>
-      <c r="H103" s="20"/>
+      <c r="H103" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E103,'Project Tracker'!$F103)&lt;&gt;2,"",DAYS360('Project Tracker'!$E103,'Project Tracker'!$F103,FALSE))</f>
+        <v/>
+      </c>
       <c r="I103" s="17"/>
     </row>
     <row r="104" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2718,7 +3384,10 @@
       <c r="E104" s="24"/>
       <c r="F104" s="24"/>
       <c r="G104" s="17"/>
-      <c r="H104" s="20"/>
+      <c r="H104" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E104,'Project Tracker'!$F104)&lt;&gt;2,"",DAYS360('Project Tracker'!$E104,'Project Tracker'!$F104,FALSE))</f>
+        <v/>
+      </c>
       <c r="I104" s="17"/>
     </row>
     <row r="105" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2728,7 +3397,10 @@
       <c r="E105" s="24"/>
       <c r="F105" s="24"/>
       <c r="G105" s="17"/>
-      <c r="H105" s="20"/>
+      <c r="H105" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E105,'Project Tracker'!$F105)&lt;&gt;2,"",DAYS360('Project Tracker'!$E105,'Project Tracker'!$F105,FALSE))</f>
+        <v/>
+      </c>
       <c r="I105" s="17"/>
     </row>
     <row r="106" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2738,7 +3410,10 @@
       <c r="E106" s="24"/>
       <c r="F106" s="24"/>
       <c r="G106" s="17"/>
-      <c r="H106" s="20"/>
+      <c r="H106" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E106,'Project Tracker'!$F106)&lt;&gt;2,"",DAYS360('Project Tracker'!$E106,'Project Tracker'!$F106,FALSE))</f>
+        <v/>
+      </c>
       <c r="I106" s="17"/>
     </row>
     <row r="107" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2748,7 +3423,10 @@
       <c r="E107" s="24"/>
       <c r="F107" s="24"/>
       <c r="G107" s="17"/>
-      <c r="H107" s="20"/>
+      <c r="H107" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E107,'Project Tracker'!$F107)&lt;&gt;2,"",DAYS360('Project Tracker'!$E107,'Project Tracker'!$F107,FALSE))</f>
+        <v/>
+      </c>
       <c r="I107" s="17"/>
     </row>
     <row r="108" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2758,7 +3436,10 @@
       <c r="E108" s="24"/>
       <c r="F108" s="24"/>
       <c r="G108" s="17"/>
-      <c r="H108" s="20"/>
+      <c r="H108" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E108,'Project Tracker'!$F108)&lt;&gt;2,"",DAYS360('Project Tracker'!$E108,'Project Tracker'!$F108,FALSE))</f>
+        <v/>
+      </c>
       <c r="I108" s="17"/>
     </row>
     <row r="109" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2768,7 +3449,10 @@
       <c r="E109" s="24"/>
       <c r="F109" s="24"/>
       <c r="G109" s="17"/>
-      <c r="H109" s="20"/>
+      <c r="H109" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E109,'Project Tracker'!$F109)&lt;&gt;2,"",DAYS360('Project Tracker'!$E109,'Project Tracker'!$F109,FALSE))</f>
+        <v/>
+      </c>
       <c r="I109" s="17"/>
     </row>
     <row r="110" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2778,7 +3462,10 @@
       <c r="E110" s="24"/>
       <c r="F110" s="24"/>
       <c r="G110" s="17"/>
-      <c r="H110" s="20"/>
+      <c r="H110" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E110,'Project Tracker'!$F110)&lt;&gt;2,"",DAYS360('Project Tracker'!$E110,'Project Tracker'!$F110,FALSE))</f>
+        <v/>
+      </c>
       <c r="I110" s="17"/>
     </row>
     <row r="111" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2788,7 +3475,10 @@
       <c r="E111" s="24"/>
       <c r="F111" s="24"/>
       <c r="G111" s="17"/>
-      <c r="H111" s="20"/>
+      <c r="H111" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E111,'Project Tracker'!$F111)&lt;&gt;2,"",DAYS360('Project Tracker'!$E111,'Project Tracker'!$F111,FALSE))</f>
+        <v/>
+      </c>
       <c r="I111" s="17"/>
     </row>
     <row r="112" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2798,7 +3488,10 @@
       <c r="E112" s="24"/>
       <c r="F112" s="24"/>
       <c r="G112" s="17"/>
-      <c r="H112" s="20"/>
+      <c r="H112" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E112,'Project Tracker'!$F112)&lt;&gt;2,"",DAYS360('Project Tracker'!$E112,'Project Tracker'!$F112,FALSE))</f>
+        <v/>
+      </c>
       <c r="I112" s="17"/>
     </row>
     <row r="113" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2808,7 +3501,10 @@
       <c r="E113" s="24"/>
       <c r="F113" s="24"/>
       <c r="G113" s="17"/>
-      <c r="H113" s="20"/>
+      <c r="H113" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E113,'Project Tracker'!$F113)&lt;&gt;2,"",DAYS360('Project Tracker'!$E113,'Project Tracker'!$F113,FALSE))</f>
+        <v/>
+      </c>
       <c r="I113" s="17"/>
     </row>
     <row r="114" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2818,7 +3514,10 @@
       <c r="E114" s="24"/>
       <c r="F114" s="24"/>
       <c r="G114" s="17"/>
-      <c r="H114" s="20"/>
+      <c r="H114" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E114,'Project Tracker'!$F114)&lt;&gt;2,"",DAYS360('Project Tracker'!$E114,'Project Tracker'!$F114,FALSE))</f>
+        <v/>
+      </c>
       <c r="I114" s="17"/>
     </row>
     <row r="115" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2828,7 +3527,10 @@
       <c r="E115" s="24"/>
       <c r="F115" s="24"/>
       <c r="G115" s="17"/>
-      <c r="H115" s="20"/>
+      <c r="H115" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E115,'Project Tracker'!$F115)&lt;&gt;2,"",DAYS360('Project Tracker'!$E115,'Project Tracker'!$F115,FALSE))</f>
+        <v/>
+      </c>
       <c r="I115" s="17"/>
     </row>
     <row r="116" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2838,7 +3540,10 @@
       <c r="E116" s="24"/>
       <c r="F116" s="24"/>
       <c r="G116" s="17"/>
-      <c r="H116" s="20"/>
+      <c r="H116" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E116,'Project Tracker'!$F116)&lt;&gt;2,"",DAYS360('Project Tracker'!$E116,'Project Tracker'!$F116,FALSE))</f>
+        <v/>
+      </c>
       <c r="I116" s="17"/>
     </row>
     <row r="117" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2848,7 +3553,10 @@
       <c r="E117" s="24"/>
       <c r="F117" s="24"/>
       <c r="G117" s="17"/>
-      <c r="H117" s="20"/>
+      <c r="H117" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E117,'Project Tracker'!$F117)&lt;&gt;2,"",DAYS360('Project Tracker'!$E117,'Project Tracker'!$F117,FALSE))</f>
+        <v/>
+      </c>
       <c r="I117" s="17"/>
     </row>
     <row r="118" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2858,7 +3566,10 @@
       <c r="E118" s="24"/>
       <c r="F118" s="24"/>
       <c r="G118" s="17"/>
-      <c r="H118" s="20"/>
+      <c r="H118" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E118,'Project Tracker'!$F118)&lt;&gt;2,"",DAYS360('Project Tracker'!$E118,'Project Tracker'!$F118,FALSE))</f>
+        <v/>
+      </c>
       <c r="I118" s="17"/>
     </row>
     <row r="119" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2868,7 +3579,10 @@
       <c r="E119" s="24"/>
       <c r="F119" s="24"/>
       <c r="G119" s="17"/>
-      <c r="H119" s="20"/>
+      <c r="H119" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E119,'Project Tracker'!$F119)&lt;&gt;2,"",DAYS360('Project Tracker'!$E119,'Project Tracker'!$F119,FALSE))</f>
+        <v/>
+      </c>
       <c r="I119" s="17"/>
     </row>
     <row r="120" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2878,7 +3592,10 @@
       <c r="E120" s="24"/>
       <c r="F120" s="24"/>
       <c r="G120" s="17"/>
-      <c r="H120" s="20"/>
+      <c r="H120" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E120,'Project Tracker'!$F120)&lt;&gt;2,"",DAYS360('Project Tracker'!$E120,'Project Tracker'!$F120,FALSE))</f>
+        <v/>
+      </c>
       <c r="I120" s="17"/>
     </row>
     <row r="121" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2888,7 +3605,10 @@
       <c r="E121" s="24"/>
       <c r="F121" s="24"/>
       <c r="G121" s="17"/>
-      <c r="H121" s="20"/>
+      <c r="H121" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E121,'Project Tracker'!$F121)&lt;&gt;2,"",DAYS360('Project Tracker'!$E121,'Project Tracker'!$F121,FALSE))</f>
+        <v/>
+      </c>
       <c r="I121" s="17"/>
     </row>
     <row r="122" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2898,7 +3618,10 @@
       <c r="E122" s="24"/>
       <c r="F122" s="24"/>
       <c r="G122" s="17"/>
-      <c r="H122" s="20"/>
+      <c r="H122" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E122,'Project Tracker'!$F122)&lt;&gt;2,"",DAYS360('Project Tracker'!$E122,'Project Tracker'!$F122,FALSE))</f>
+        <v/>
+      </c>
       <c r="I122" s="17"/>
     </row>
     <row r="123" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2908,7 +3631,10 @@
       <c r="E123" s="24"/>
       <c r="F123" s="24"/>
       <c r="G123" s="17"/>
-      <c r="H123" s="20"/>
+      <c r="H123" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E123,'Project Tracker'!$F123)&lt;&gt;2,"",DAYS360('Project Tracker'!$E123,'Project Tracker'!$F123,FALSE))</f>
+        <v/>
+      </c>
       <c r="I123" s="17"/>
     </row>
     <row r="124" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2918,7 +3644,10 @@
       <c r="E124" s="24"/>
       <c r="F124" s="24"/>
       <c r="G124" s="17"/>
-      <c r="H124" s="20"/>
+      <c r="H124" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E124,'Project Tracker'!$F124)&lt;&gt;2,"",DAYS360('Project Tracker'!$E124,'Project Tracker'!$F124,FALSE))</f>
+        <v/>
+      </c>
       <c r="I124" s="17"/>
     </row>
     <row r="125" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2928,7 +3657,10 @@
       <c r="E125" s="24"/>
       <c r="F125" s="24"/>
       <c r="G125" s="17"/>
-      <c r="H125" s="20"/>
+      <c r="H125" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E125,'Project Tracker'!$F125)&lt;&gt;2,"",DAYS360('Project Tracker'!$E125,'Project Tracker'!$F125,FALSE))</f>
+        <v/>
+      </c>
       <c r="I125" s="17"/>
     </row>
     <row r="126" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2938,7 +3670,10 @@
       <c r="E126" s="24"/>
       <c r="F126" s="24"/>
       <c r="G126" s="17"/>
-      <c r="H126" s="20"/>
+      <c r="H126" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E126,'Project Tracker'!$F126)&lt;&gt;2,"",DAYS360('Project Tracker'!$E126,'Project Tracker'!$F126,FALSE))</f>
+        <v/>
+      </c>
       <c r="I126" s="17"/>
     </row>
     <row r="127" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2948,7 +3683,10 @@
       <c r="E127" s="24"/>
       <c r="F127" s="24"/>
       <c r="G127" s="17"/>
-      <c r="H127" s="20"/>
+      <c r="H127" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E127,'Project Tracker'!$F127)&lt;&gt;2,"",DAYS360('Project Tracker'!$E127,'Project Tracker'!$F127,FALSE))</f>
+        <v/>
+      </c>
       <c r="I127" s="17"/>
     </row>
     <row r="128" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2958,7 +3696,10 @@
       <c r="E128" s="24"/>
       <c r="F128" s="24"/>
       <c r="G128" s="17"/>
-      <c r="H128" s="20"/>
+      <c r="H128" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E128,'Project Tracker'!$F128)&lt;&gt;2,"",DAYS360('Project Tracker'!$E128,'Project Tracker'!$F128,FALSE))</f>
+        <v/>
+      </c>
       <c r="I128" s="17"/>
     </row>
     <row r="129" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2968,7 +3709,10 @@
       <c r="E129" s="24"/>
       <c r="F129" s="24"/>
       <c r="G129" s="17"/>
-      <c r="H129" s="20"/>
+      <c r="H129" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E129,'Project Tracker'!$F129)&lt;&gt;2,"",DAYS360('Project Tracker'!$E129,'Project Tracker'!$F129,FALSE))</f>
+        <v/>
+      </c>
       <c r="I129" s="17"/>
     </row>
     <row r="130" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2978,7 +3722,10 @@
       <c r="E130" s="24"/>
       <c r="F130" s="24"/>
       <c r="G130" s="17"/>
-      <c r="H130" s="20"/>
+      <c r="H130" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E130,'Project Tracker'!$F130)&lt;&gt;2,"",DAYS360('Project Tracker'!$E130,'Project Tracker'!$F130,FALSE))</f>
+        <v/>
+      </c>
       <c r="I130" s="17"/>
     </row>
     <row r="131" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2988,7 +3735,10 @@
       <c r="E131" s="24"/>
       <c r="F131" s="24"/>
       <c r="G131" s="17"/>
-      <c r="H131" s="20"/>
+      <c r="H131" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E131,'Project Tracker'!$F131)&lt;&gt;2,"",DAYS360('Project Tracker'!$E131,'Project Tracker'!$F131,FALSE))</f>
+        <v/>
+      </c>
       <c r="I131" s="17"/>
     </row>
     <row r="132" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2998,7 +3748,10 @@
       <c r="E132" s="24"/>
       <c r="F132" s="24"/>
       <c r="G132" s="17"/>
-      <c r="H132" s="20"/>
+      <c r="H132" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E132,'Project Tracker'!$F132)&lt;&gt;2,"",DAYS360('Project Tracker'!$E132,'Project Tracker'!$F132,FALSE))</f>
+        <v/>
+      </c>
       <c r="I132" s="17"/>
     </row>
     <row r="133" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3008,7 +3761,10 @@
       <c r="E133" s="24"/>
       <c r="F133" s="24"/>
       <c r="G133" s="17"/>
-      <c r="H133" s="20"/>
+      <c r="H133" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E133,'Project Tracker'!$F133)&lt;&gt;2,"",DAYS360('Project Tracker'!$E133,'Project Tracker'!$F133,FALSE))</f>
+        <v/>
+      </c>
       <c r="I133" s="17"/>
     </row>
     <row r="134" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3018,7 +3774,10 @@
       <c r="E134" s="24"/>
       <c r="F134" s="24"/>
       <c r="G134" s="17"/>
-      <c r="H134" s="20"/>
+      <c r="H134" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E134,'Project Tracker'!$F134)&lt;&gt;2,"",DAYS360('Project Tracker'!$E134,'Project Tracker'!$F134,FALSE))</f>
+        <v/>
+      </c>
       <c r="I134" s="17"/>
     </row>
     <row r="135" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3028,7 +3787,10 @@
       <c r="E135" s="24"/>
       <c r="F135" s="24"/>
       <c r="G135" s="17"/>
-      <c r="H135" s="20"/>
+      <c r="H135" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E135,'Project Tracker'!$F135)&lt;&gt;2,"",DAYS360('Project Tracker'!$E135,'Project Tracker'!$F135,FALSE))</f>
+        <v/>
+      </c>
       <c r="I135" s="17"/>
     </row>
     <row r="136" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3038,7 +3800,10 @@
       <c r="E136" s="24"/>
       <c r="F136" s="24"/>
       <c r="G136" s="17"/>
-      <c r="H136" s="20"/>
+      <c r="H136" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E136,'Project Tracker'!$F136)&lt;&gt;2,"",DAYS360('Project Tracker'!$E136,'Project Tracker'!$F136,FALSE))</f>
+        <v/>
+      </c>
       <c r="I136" s="17"/>
     </row>
     <row r="137" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3048,7 +3813,10 @@
       <c r="E137" s="24"/>
       <c r="F137" s="24"/>
       <c r="G137" s="17"/>
-      <c r="H137" s="20"/>
+      <c r="H137" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E137,'Project Tracker'!$F137)&lt;&gt;2,"",DAYS360('Project Tracker'!$E137,'Project Tracker'!$F137,FALSE))</f>
+        <v/>
+      </c>
       <c r="I137" s="17"/>
     </row>
     <row r="138" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3058,7 +3826,10 @@
       <c r="E138" s="24"/>
       <c r="F138" s="24"/>
       <c r="G138" s="17"/>
-      <c r="H138" s="20"/>
+      <c r="H138" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E138,'Project Tracker'!$F138)&lt;&gt;2,"",DAYS360('Project Tracker'!$E138,'Project Tracker'!$F138,FALSE))</f>
+        <v/>
+      </c>
       <c r="I138" s="17"/>
     </row>
     <row r="139" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3068,7 +3839,10 @@
       <c r="E139" s="24"/>
       <c r="F139" s="24"/>
       <c r="G139" s="17"/>
-      <c r="H139" s="20"/>
+      <c r="H139" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E139,'Project Tracker'!$F139)&lt;&gt;2,"",DAYS360('Project Tracker'!$E139,'Project Tracker'!$F139,FALSE))</f>
+        <v/>
+      </c>
       <c r="I139" s="17"/>
     </row>
     <row r="140" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3078,7 +3852,10 @@
       <c r="E140" s="24"/>
       <c r="F140" s="24"/>
       <c r="G140" s="17"/>
-      <c r="H140" s="20"/>
+      <c r="H140" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E140,'Project Tracker'!$F140)&lt;&gt;2,"",DAYS360('Project Tracker'!$E140,'Project Tracker'!$F140,FALSE))</f>
+        <v/>
+      </c>
       <c r="I140" s="17"/>
     </row>
     <row r="141" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3088,7 +3865,10 @@
       <c r="E141" s="24"/>
       <c r="F141" s="24"/>
       <c r="G141" s="17"/>
-      <c r="H141" s="20"/>
+      <c r="H141" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E141,'Project Tracker'!$F141)&lt;&gt;2,"",DAYS360('Project Tracker'!$E141,'Project Tracker'!$F141,FALSE))</f>
+        <v/>
+      </c>
       <c r="I141" s="17"/>
     </row>
     <row r="142" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3098,7 +3878,10 @@
       <c r="E142" s="24"/>
       <c r="F142" s="24"/>
       <c r="G142" s="17"/>
-      <c r="H142" s="20"/>
+      <c r="H142" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E142,'Project Tracker'!$F142)&lt;&gt;2,"",DAYS360('Project Tracker'!$E142,'Project Tracker'!$F142,FALSE))</f>
+        <v/>
+      </c>
       <c r="I142" s="17"/>
     </row>
     <row r="143" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3108,7 +3891,10 @@
       <c r="E143" s="24"/>
       <c r="F143" s="24"/>
       <c r="G143" s="17"/>
-      <c r="H143" s="20"/>
+      <c r="H143" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E143,'Project Tracker'!$F143)&lt;&gt;2,"",DAYS360('Project Tracker'!$E143,'Project Tracker'!$F143,FALSE))</f>
+        <v/>
+      </c>
       <c r="I143" s="17"/>
     </row>
     <row r="144" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3118,7 +3904,10 @@
       <c r="E144" s="24"/>
       <c r="F144" s="24"/>
       <c r="G144" s="17"/>
-      <c r="H144" s="20"/>
+      <c r="H144" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E144,'Project Tracker'!$F144)&lt;&gt;2,"",DAYS360('Project Tracker'!$E144,'Project Tracker'!$F144,FALSE))</f>
+        <v/>
+      </c>
       <c r="I144" s="17"/>
     </row>
     <row r="145" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3128,7 +3917,10 @@
       <c r="E145" s="24"/>
       <c r="F145" s="24"/>
       <c r="G145" s="17"/>
-      <c r="H145" s="20"/>
+      <c r="H145" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E145,'Project Tracker'!$F145)&lt;&gt;2,"",DAYS360('Project Tracker'!$E145,'Project Tracker'!$F145,FALSE))</f>
+        <v/>
+      </c>
       <c r="I145" s="17"/>
     </row>
     <row r="146" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3138,7 +3930,10 @@
       <c r="E146" s="24"/>
       <c r="F146" s="24"/>
       <c r="G146" s="17"/>
-      <c r="H146" s="20"/>
+      <c r="H146" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E146,'Project Tracker'!$F146)&lt;&gt;2,"",DAYS360('Project Tracker'!$E146,'Project Tracker'!$F146,FALSE))</f>
+        <v/>
+      </c>
       <c r="I146" s="17"/>
     </row>
     <row r="147" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3148,7 +3943,10 @@
       <c r="E147" s="24"/>
       <c r="F147" s="24"/>
       <c r="G147" s="17"/>
-      <c r="H147" s="20"/>
+      <c r="H147" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E147,'Project Tracker'!$F147)&lt;&gt;2,"",DAYS360('Project Tracker'!$E147,'Project Tracker'!$F147,FALSE))</f>
+        <v/>
+      </c>
       <c r="I147" s="17"/>
     </row>
     <row r="148" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3158,7 +3956,10 @@
       <c r="E148" s="24"/>
       <c r="F148" s="24"/>
       <c r="G148" s="17"/>
-      <c r="H148" s="20"/>
+      <c r="H148" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E148,'Project Tracker'!$F148)&lt;&gt;2,"",DAYS360('Project Tracker'!$E148,'Project Tracker'!$F148,FALSE))</f>
+        <v/>
+      </c>
       <c r="I148" s="17"/>
     </row>
     <row r="149" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3168,7 +3969,10 @@
       <c r="E149" s="24"/>
       <c r="F149" s="24"/>
       <c r="G149" s="17"/>
-      <c r="H149" s="20"/>
+      <c r="H149" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E149,'Project Tracker'!$F149)&lt;&gt;2,"",DAYS360('Project Tracker'!$E149,'Project Tracker'!$F149,FALSE))</f>
+        <v/>
+      </c>
       <c r="I149" s="17"/>
     </row>
     <row r="150" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3178,7 +3982,10 @@
       <c r="E150" s="24"/>
       <c r="F150" s="24"/>
       <c r="G150" s="17"/>
-      <c r="H150" s="20"/>
+      <c r="H150" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E150,'Project Tracker'!$F150)&lt;&gt;2,"",DAYS360('Project Tracker'!$E150,'Project Tracker'!$F150,FALSE))</f>
+        <v/>
+      </c>
       <c r="I150" s="17"/>
     </row>
     <row r="151" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3188,7 +3995,10 @@
       <c r="E151" s="24"/>
       <c r="F151" s="24"/>
       <c r="G151" s="17"/>
-      <c r="H151" s="20"/>
+      <c r="H151" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E151,'Project Tracker'!$F151)&lt;&gt;2,"",DAYS360('Project Tracker'!$E151,'Project Tracker'!$F151,FALSE))</f>
+        <v/>
+      </c>
       <c r="I151" s="17"/>
     </row>
     <row r="152" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3198,7 +4008,10 @@
       <c r="E152" s="24"/>
       <c r="F152" s="24"/>
       <c r="G152" s="17"/>
-      <c r="H152" s="20"/>
+      <c r="H152" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E152,'Project Tracker'!$F152)&lt;&gt;2,"",DAYS360('Project Tracker'!$E152,'Project Tracker'!$F152,FALSE))</f>
+        <v/>
+      </c>
       <c r="I152" s="17"/>
     </row>
     <row r="153" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3208,7 +4021,10 @@
       <c r="E153" s="24"/>
       <c r="F153" s="24"/>
       <c r="G153" s="17"/>
-      <c r="H153" s="20"/>
+      <c r="H153" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E153,'Project Tracker'!$F153)&lt;&gt;2,"",DAYS360('Project Tracker'!$E153,'Project Tracker'!$F153,FALSE))</f>
+        <v/>
+      </c>
       <c r="I153" s="17"/>
     </row>
     <row r="154" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3218,7 +4034,10 @@
       <c r="E154" s="24"/>
       <c r="F154" s="24"/>
       <c r="G154" s="17"/>
-      <c r="H154" s="20"/>
+      <c r="H154" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E154,'Project Tracker'!$F154)&lt;&gt;2,"",DAYS360('Project Tracker'!$E154,'Project Tracker'!$F154,FALSE))</f>
+        <v/>
+      </c>
       <c r="I154" s="17"/>
     </row>
     <row r="155" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3228,7 +4047,10 @@
       <c r="E155" s="24"/>
       <c r="F155" s="24"/>
       <c r="G155" s="17"/>
-      <c r="H155" s="20"/>
+      <c r="H155" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E155,'Project Tracker'!$F155)&lt;&gt;2,"",DAYS360('Project Tracker'!$E155,'Project Tracker'!$F155,FALSE))</f>
+        <v/>
+      </c>
       <c r="I155" s="17"/>
     </row>
     <row r="156" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3238,7 +4060,10 @@
       <c r="E156" s="24"/>
       <c r="F156" s="24"/>
       <c r="G156" s="17"/>
-      <c r="H156" s="20"/>
+      <c r="H156" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E156,'Project Tracker'!$F156)&lt;&gt;2,"",DAYS360('Project Tracker'!$E156,'Project Tracker'!$F156,FALSE))</f>
+        <v/>
+      </c>
       <c r="I156" s="17"/>
     </row>
     <row r="157" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3248,7 +4073,10 @@
       <c r="E157" s="24"/>
       <c r="F157" s="24"/>
       <c r="G157" s="17"/>
-      <c r="H157" s="20"/>
+      <c r="H157" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E157,'Project Tracker'!$F157)&lt;&gt;2,"",DAYS360('Project Tracker'!$E157,'Project Tracker'!$F157,FALSE))</f>
+        <v/>
+      </c>
       <c r="I157" s="17"/>
     </row>
     <row r="158" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3258,7 +4086,10 @@
       <c r="E158" s="24"/>
       <c r="F158" s="24"/>
       <c r="G158" s="17"/>
-      <c r="H158" s="20"/>
+      <c r="H158" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E158,'Project Tracker'!$F158)&lt;&gt;2,"",DAYS360('Project Tracker'!$E158,'Project Tracker'!$F158,FALSE))</f>
+        <v/>
+      </c>
       <c r="I158" s="17"/>
     </row>
     <row r="159" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3268,7 +4099,10 @@
       <c r="E159" s="24"/>
       <c r="F159" s="24"/>
       <c r="G159" s="17"/>
-      <c r="H159" s="20"/>
+      <c r="H159" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E159,'Project Tracker'!$F159)&lt;&gt;2,"",DAYS360('Project Tracker'!$E159,'Project Tracker'!$F159,FALSE))</f>
+        <v/>
+      </c>
       <c r="I159" s="17"/>
     </row>
     <row r="160" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3278,7 +4112,10 @@
       <c r="E160" s="24"/>
       <c r="F160" s="24"/>
       <c r="G160" s="17"/>
-      <c r="H160" s="20"/>
+      <c r="H160" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E160,'Project Tracker'!$F160)&lt;&gt;2,"",DAYS360('Project Tracker'!$E160,'Project Tracker'!$F160,FALSE))</f>
+        <v/>
+      </c>
       <c r="I160" s="17"/>
     </row>
     <row r="161" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3288,7 +4125,10 @@
       <c r="E161" s="24"/>
       <c r="F161" s="24"/>
       <c r="G161" s="17"/>
-      <c r="H161" s="20"/>
+      <c r="H161" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E161,'Project Tracker'!$F161)&lt;&gt;2,"",DAYS360('Project Tracker'!$E161,'Project Tracker'!$F161,FALSE))</f>
+        <v/>
+      </c>
       <c r="I161" s="17"/>
     </row>
     <row r="162" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3298,7 +4138,10 @@
       <c r="E162" s="24"/>
       <c r="F162" s="24"/>
       <c r="G162" s="17"/>
-      <c r="H162" s="20"/>
+      <c r="H162" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E162,'Project Tracker'!$F162)&lt;&gt;2,"",DAYS360('Project Tracker'!$E162,'Project Tracker'!$F162,FALSE))</f>
+        <v/>
+      </c>
       <c r="I162" s="17"/>
     </row>
     <row r="163" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3308,7 +4151,10 @@
       <c r="E163" s="24"/>
       <c r="F163" s="24"/>
       <c r="G163" s="17"/>
-      <c r="H163" s="20"/>
+      <c r="H163" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E163,'Project Tracker'!$F163)&lt;&gt;2,"",DAYS360('Project Tracker'!$E163,'Project Tracker'!$F163,FALSE))</f>
+        <v/>
+      </c>
       <c r="I163" s="17"/>
     </row>
     <row r="164" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3318,7 +4164,10 @@
       <c r="E164" s="24"/>
       <c r="F164" s="24"/>
       <c r="G164" s="17"/>
-      <c r="H164" s="20"/>
+      <c r="H164" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E164,'Project Tracker'!$F164)&lt;&gt;2,"",DAYS360('Project Tracker'!$E164,'Project Tracker'!$F164,FALSE))</f>
+        <v/>
+      </c>
       <c r="I164" s="17"/>
     </row>
     <row r="165" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3328,7 +4177,10 @@
       <c r="E165" s="24"/>
       <c r="F165" s="24"/>
       <c r="G165" s="17"/>
-      <c r="H165" s="20"/>
+      <c r="H165" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E165,'Project Tracker'!$F165)&lt;&gt;2,"",DAYS360('Project Tracker'!$E165,'Project Tracker'!$F165,FALSE))</f>
+        <v/>
+      </c>
       <c r="I165" s="17"/>
     </row>
     <row r="166" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3338,7 +4190,10 @@
       <c r="E166" s="24"/>
       <c r="F166" s="24"/>
       <c r="G166" s="17"/>
-      <c r="H166" s="20"/>
+      <c r="H166" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E166,'Project Tracker'!$F166)&lt;&gt;2,"",DAYS360('Project Tracker'!$E166,'Project Tracker'!$F166,FALSE))</f>
+        <v/>
+      </c>
       <c r="I166" s="17"/>
     </row>
     <row r="167" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3348,7 +4203,10 @@
       <c r="E167" s="24"/>
       <c r="F167" s="24"/>
       <c r="G167" s="17"/>
-      <c r="H167" s="20"/>
+      <c r="H167" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E167,'Project Tracker'!$F167)&lt;&gt;2,"",DAYS360('Project Tracker'!$E167,'Project Tracker'!$F167,FALSE))</f>
+        <v/>
+      </c>
       <c r="I167" s="17"/>
     </row>
     <row r="168" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3358,7 +4216,10 @@
       <c r="E168" s="24"/>
       <c r="F168" s="24"/>
       <c r="G168" s="17"/>
-      <c r="H168" s="20"/>
+      <c r="H168" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E168,'Project Tracker'!$F168)&lt;&gt;2,"",DAYS360('Project Tracker'!$E168,'Project Tracker'!$F168,FALSE))</f>
+        <v/>
+      </c>
       <c r="I168" s="17"/>
     </row>
     <row r="169" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3368,7 +4229,10 @@
       <c r="E169" s="24"/>
       <c r="F169" s="24"/>
       <c r="G169" s="17"/>
-      <c r="H169" s="20"/>
+      <c r="H169" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E169,'Project Tracker'!$F169)&lt;&gt;2,"",DAYS360('Project Tracker'!$E169,'Project Tracker'!$F169,FALSE))</f>
+        <v/>
+      </c>
       <c r="I169" s="17"/>
     </row>
     <row r="170" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3378,7 +4242,10 @@
       <c r="E170" s="24"/>
       <c r="F170" s="24"/>
       <c r="G170" s="17"/>
-      <c r="H170" s="20"/>
+      <c r="H170" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E170,'Project Tracker'!$F170)&lt;&gt;2,"",DAYS360('Project Tracker'!$E170,'Project Tracker'!$F170,FALSE))</f>
+        <v/>
+      </c>
       <c r="I170" s="17"/>
     </row>
     <row r="171" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3388,7 +4255,10 @@
       <c r="E171" s="24"/>
       <c r="F171" s="24"/>
       <c r="G171" s="17"/>
-      <c r="H171" s="20"/>
+      <c r="H171" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E171,'Project Tracker'!$F171)&lt;&gt;2,"",DAYS360('Project Tracker'!$E171,'Project Tracker'!$F171,FALSE))</f>
+        <v/>
+      </c>
       <c r="I171" s="17"/>
     </row>
     <row r="172" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3398,7 +4268,10 @@
       <c r="E172" s="24"/>
       <c r="F172" s="24"/>
       <c r="G172" s="17"/>
-      <c r="H172" s="20"/>
+      <c r="H172" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E172,'Project Tracker'!$F172)&lt;&gt;2,"",DAYS360('Project Tracker'!$E172,'Project Tracker'!$F172,FALSE))</f>
+        <v/>
+      </c>
       <c r="I172" s="17"/>
     </row>
     <row r="173" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3408,7 +4281,10 @@
       <c r="E173" s="24"/>
       <c r="F173" s="24"/>
       <c r="G173" s="17"/>
-      <c r="H173" s="20"/>
+      <c r="H173" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E173,'Project Tracker'!$F173)&lt;&gt;2,"",DAYS360('Project Tracker'!$E173,'Project Tracker'!$F173,FALSE))</f>
+        <v/>
+      </c>
       <c r="I173" s="17"/>
     </row>
     <row r="174" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3418,7 +4294,10 @@
       <c r="E174" s="24"/>
       <c r="F174" s="24"/>
       <c r="G174" s="17"/>
-      <c r="H174" s="20"/>
+      <c r="H174" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E174,'Project Tracker'!$F174)&lt;&gt;2,"",DAYS360('Project Tracker'!$E174,'Project Tracker'!$F174,FALSE))</f>
+        <v/>
+      </c>
       <c r="I174" s="17"/>
     </row>
     <row r="175" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3428,7 +4307,10 @@
       <c r="E175" s="24"/>
       <c r="F175" s="24"/>
       <c r="G175" s="17"/>
-      <c r="H175" s="20"/>
+      <c r="H175" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E175,'Project Tracker'!$F175)&lt;&gt;2,"",DAYS360('Project Tracker'!$E175,'Project Tracker'!$F175,FALSE))</f>
+        <v/>
+      </c>
       <c r="I175" s="17"/>
     </row>
     <row r="176" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3438,7 +4320,10 @@
       <c r="E176" s="24"/>
       <c r="F176" s="24"/>
       <c r="G176" s="17"/>
-      <c r="H176" s="20"/>
+      <c r="H176" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E176,'Project Tracker'!$F176)&lt;&gt;2,"",DAYS360('Project Tracker'!$E176,'Project Tracker'!$F176,FALSE))</f>
+        <v/>
+      </c>
       <c r="I176" s="17"/>
     </row>
     <row r="177" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3448,7 +4333,10 @@
       <c r="E177" s="24"/>
       <c r="F177" s="24"/>
       <c r="G177" s="17"/>
-      <c r="H177" s="20"/>
+      <c r="H177" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E177,'Project Tracker'!$F177)&lt;&gt;2,"",DAYS360('Project Tracker'!$E177,'Project Tracker'!$F177,FALSE))</f>
+        <v/>
+      </c>
       <c r="I177" s="17"/>
     </row>
     <row r="178" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3458,7 +4346,10 @@
       <c r="E178" s="24"/>
       <c r="F178" s="24"/>
       <c r="G178" s="17"/>
-      <c r="H178" s="20"/>
+      <c r="H178" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E178,'Project Tracker'!$F178)&lt;&gt;2,"",DAYS360('Project Tracker'!$E178,'Project Tracker'!$F178,FALSE))</f>
+        <v/>
+      </c>
       <c r="I178" s="17"/>
     </row>
     <row r="179" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3468,7 +4359,10 @@
       <c r="E179" s="24"/>
       <c r="F179" s="24"/>
       <c r="G179" s="17"/>
-      <c r="H179" s="20"/>
+      <c r="H179" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E179,'Project Tracker'!$F179)&lt;&gt;2,"",DAYS360('Project Tracker'!$E179,'Project Tracker'!$F179,FALSE))</f>
+        <v/>
+      </c>
       <c r="I179" s="17"/>
     </row>
     <row r="180" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3478,7 +4372,10 @@
       <c r="E180" s="24"/>
       <c r="F180" s="24"/>
       <c r="G180" s="17"/>
-      <c r="H180" s="20"/>
+      <c r="H180" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E180,'Project Tracker'!$F180)&lt;&gt;2,"",DAYS360('Project Tracker'!$E180,'Project Tracker'!$F180,FALSE))</f>
+        <v/>
+      </c>
       <c r="I180" s="17"/>
     </row>
     <row r="181" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3488,7 +4385,10 @@
       <c r="E181" s="24"/>
       <c r="F181" s="24"/>
       <c r="G181" s="17"/>
-      <c r="H181" s="20"/>
+      <c r="H181" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E181,'Project Tracker'!$F181)&lt;&gt;2,"",DAYS360('Project Tracker'!$E181,'Project Tracker'!$F181,FALSE))</f>
+        <v/>
+      </c>
       <c r="I181" s="17"/>
     </row>
     <row r="182" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3498,7 +4398,10 @@
       <c r="E182" s="24"/>
       <c r="F182" s="24"/>
       <c r="G182" s="17"/>
-      <c r="H182" s="20"/>
+      <c r="H182" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E182,'Project Tracker'!$F182)&lt;&gt;2,"",DAYS360('Project Tracker'!$E182,'Project Tracker'!$F182,FALSE))</f>
+        <v/>
+      </c>
       <c r="I182" s="17"/>
     </row>
     <row r="183" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3508,7 +4411,10 @@
       <c r="E183" s="24"/>
       <c r="F183" s="24"/>
       <c r="G183" s="17"/>
-      <c r="H183" s="20"/>
+      <c r="H183" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E183,'Project Tracker'!$F183)&lt;&gt;2,"",DAYS360('Project Tracker'!$E183,'Project Tracker'!$F183,FALSE))</f>
+        <v/>
+      </c>
       <c r="I183" s="17"/>
     </row>
     <row r="184" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3518,7 +4424,10 @@
       <c r="E184" s="24"/>
       <c r="F184" s="24"/>
       <c r="G184" s="17"/>
-      <c r="H184" s="20"/>
+      <c r="H184" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E184,'Project Tracker'!$F184)&lt;&gt;2,"",DAYS360('Project Tracker'!$E184,'Project Tracker'!$F184,FALSE))</f>
+        <v/>
+      </c>
       <c r="I184" s="17"/>
     </row>
     <row r="185" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3528,7 +4437,10 @@
       <c r="E185" s="24"/>
       <c r="F185" s="24"/>
       <c r="G185" s="17"/>
-      <c r="H185" s="20"/>
+      <c r="H185" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E185,'Project Tracker'!$F185)&lt;&gt;2,"",DAYS360('Project Tracker'!$E185,'Project Tracker'!$F185,FALSE))</f>
+        <v/>
+      </c>
       <c r="I185" s="17"/>
     </row>
     <row r="186" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3538,7 +4450,10 @@
       <c r="E186" s="24"/>
       <c r="F186" s="24"/>
       <c r="G186" s="17"/>
-      <c r="H186" s="20"/>
+      <c r="H186" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E186,'Project Tracker'!$F186)&lt;&gt;2,"",DAYS360('Project Tracker'!$E186,'Project Tracker'!$F186,FALSE))</f>
+        <v/>
+      </c>
       <c r="I186" s="17"/>
     </row>
     <row r="187" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3548,7 +4463,10 @@
       <c r="E187" s="24"/>
       <c r="F187" s="24"/>
       <c r="G187" s="17"/>
-      <c r="H187" s="20"/>
+      <c r="H187" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E187,'Project Tracker'!$F187)&lt;&gt;2,"",DAYS360('Project Tracker'!$E187,'Project Tracker'!$F187,FALSE))</f>
+        <v/>
+      </c>
       <c r="I187" s="17"/>
     </row>
     <row r="188" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3558,7 +4476,10 @@
       <c r="E188" s="24"/>
       <c r="F188" s="24"/>
       <c r="G188" s="17"/>
-      <c r="H188" s="20"/>
+      <c r="H188" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E188,'Project Tracker'!$F188)&lt;&gt;2,"",DAYS360('Project Tracker'!$E188,'Project Tracker'!$F188,FALSE))</f>
+        <v/>
+      </c>
       <c r="I188" s="17"/>
     </row>
     <row r="189" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3568,7 +4489,10 @@
       <c r="E189" s="24"/>
       <c r="F189" s="24"/>
       <c r="G189" s="17"/>
-      <c r="H189" s="20"/>
+      <c r="H189" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E189,'Project Tracker'!$F189)&lt;&gt;2,"",DAYS360('Project Tracker'!$E189,'Project Tracker'!$F189,FALSE))</f>
+        <v/>
+      </c>
       <c r="I189" s="17"/>
     </row>
     <row r="190" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3578,7 +4502,10 @@
       <c r="E190" s="24"/>
       <c r="F190" s="24"/>
       <c r="G190" s="17"/>
-      <c r="H190" s="20"/>
+      <c r="H190" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E190,'Project Tracker'!$F190)&lt;&gt;2,"",DAYS360('Project Tracker'!$E190,'Project Tracker'!$F190,FALSE))</f>
+        <v/>
+      </c>
       <c r="I190" s="17"/>
     </row>
     <row r="191" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3588,7 +4515,10 @@
       <c r="E191" s="24"/>
       <c r="F191" s="24"/>
       <c r="G191" s="17"/>
-      <c r="H191" s="20"/>
+      <c r="H191" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E191,'Project Tracker'!$F191)&lt;&gt;2,"",DAYS360('Project Tracker'!$E191,'Project Tracker'!$F191,FALSE))</f>
+        <v/>
+      </c>
       <c r="I191" s="17"/>
     </row>
     <row r="192" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3598,7 +4528,10 @@
       <c r="E192" s="24"/>
       <c r="F192" s="24"/>
       <c r="G192" s="17"/>
-      <c r="H192" s="20"/>
+      <c r="H192" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E192,'Project Tracker'!$F192)&lt;&gt;2,"",DAYS360('Project Tracker'!$E192,'Project Tracker'!$F192,FALSE))</f>
+        <v/>
+      </c>
       <c r="I192" s="17"/>
     </row>
     <row r="193" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3608,7 +4541,10 @@
       <c r="E193" s="24"/>
       <c r="F193" s="24"/>
       <c r="G193" s="17"/>
-      <c r="H193" s="20"/>
+      <c r="H193" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E193,'Project Tracker'!$F193)&lt;&gt;2,"",DAYS360('Project Tracker'!$E193,'Project Tracker'!$F193,FALSE))</f>
+        <v/>
+      </c>
       <c r="I193" s="17"/>
     </row>
     <row r="194" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3618,7 +4554,10 @@
       <c r="E194" s="24"/>
       <c r="F194" s="24"/>
       <c r="G194" s="17"/>
-      <c r="H194" s="20"/>
+      <c r="H194" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E194,'Project Tracker'!$F194)&lt;&gt;2,"",DAYS360('Project Tracker'!$E194,'Project Tracker'!$F194,FALSE))</f>
+        <v/>
+      </c>
       <c r="I194" s="17"/>
     </row>
     <row r="195" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3628,7 +4567,10 @@
       <c r="E195" s="24"/>
       <c r="F195" s="24"/>
       <c r="G195" s="17"/>
-      <c r="H195" s="20"/>
+      <c r="H195" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E195,'Project Tracker'!$F195)&lt;&gt;2,"",DAYS360('Project Tracker'!$E195,'Project Tracker'!$F195,FALSE))</f>
+        <v/>
+      </c>
       <c r="I195" s="17"/>
     </row>
     <row r="196" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3638,7 +4580,10 @@
       <c r="E196" s="24"/>
       <c r="F196" s="24"/>
       <c r="G196" s="17"/>
-      <c r="H196" s="20"/>
+      <c r="H196" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E196,'Project Tracker'!$F196)&lt;&gt;2,"",DAYS360('Project Tracker'!$E196,'Project Tracker'!$F196,FALSE))</f>
+        <v/>
+      </c>
       <c r="I196" s="17"/>
     </row>
     <row r="197" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3648,7 +4593,10 @@
       <c r="E197" s="24"/>
       <c r="F197" s="24"/>
       <c r="G197" s="17"/>
-      <c r="H197" s="20"/>
+      <c r="H197" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E197,'Project Tracker'!$F197)&lt;&gt;2,"",DAYS360('Project Tracker'!$E197,'Project Tracker'!$F197,FALSE))</f>
+        <v/>
+      </c>
       <c r="I197" s="17"/>
     </row>
     <row r="198" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3658,7 +4606,10 @@
       <c r="E198" s="24"/>
       <c r="F198" s="24"/>
       <c r="G198" s="17"/>
-      <c r="H198" s="20"/>
+      <c r="H198" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E198,'Project Tracker'!$F198)&lt;&gt;2,"",DAYS360('Project Tracker'!$E198,'Project Tracker'!$F198,FALSE))</f>
+        <v/>
+      </c>
       <c r="I198" s="17"/>
     </row>
     <row r="199" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3668,7 +4619,10 @@
       <c r="E199" s="24"/>
       <c r="F199" s="24"/>
       <c r="G199" s="17"/>
-      <c r="H199" s="20"/>
+      <c r="H199" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E199,'Project Tracker'!$F199)&lt;&gt;2,"",DAYS360('Project Tracker'!$E199,'Project Tracker'!$F199,FALSE))</f>
+        <v/>
+      </c>
       <c r="I199" s="17"/>
     </row>
     <row r="200" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3678,7 +4632,10 @@
       <c r="E200" s="24"/>
       <c r="F200" s="24"/>
       <c r="G200" s="17"/>
-      <c r="H200" s="20"/>
+      <c r="H200" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E200,'Project Tracker'!$F200)&lt;&gt;2,"",DAYS360('Project Tracker'!$E200,'Project Tracker'!$F200,FALSE))</f>
+        <v/>
+      </c>
       <c r="I200" s="17"/>
     </row>
     <row r="201" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3688,7 +4645,10 @@
       <c r="E201" s="24"/>
       <c r="F201" s="24"/>
       <c r="G201" s="17"/>
-      <c r="H201" s="20"/>
+      <c r="H201" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E201,'Project Tracker'!$F201)&lt;&gt;2,"",DAYS360('Project Tracker'!$E201,'Project Tracker'!$F201,FALSE))</f>
+        <v/>
+      </c>
       <c r="I201" s="17"/>
     </row>
     <row r="202" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3698,7 +4658,10 @@
       <c r="E202" s="24"/>
       <c r="F202" s="24"/>
       <c r="G202" s="17"/>
-      <c r="H202" s="20"/>
+      <c r="H202" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E202,'Project Tracker'!$F202)&lt;&gt;2,"",DAYS360('Project Tracker'!$E202,'Project Tracker'!$F202,FALSE))</f>
+        <v/>
+      </c>
       <c r="I202" s="17"/>
     </row>
     <row r="203" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3708,7 +4671,10 @@
       <c r="E203" s="24"/>
       <c r="F203" s="24"/>
       <c r="G203" s="17"/>
-      <c r="H203" s="20"/>
+      <c r="H203" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E203,'Project Tracker'!$F203)&lt;&gt;2,"",DAYS360('Project Tracker'!$E203,'Project Tracker'!$F203,FALSE))</f>
+        <v/>
+      </c>
       <c r="I203" s="17"/>
     </row>
     <row r="204" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3718,7 +4684,10 @@
       <c r="E204" s="24"/>
       <c r="F204" s="24"/>
       <c r="G204" s="17"/>
-      <c r="H204" s="20"/>
+      <c r="H204" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E204,'Project Tracker'!$F204)&lt;&gt;2,"",DAYS360('Project Tracker'!$E204,'Project Tracker'!$F204,FALSE))</f>
+        <v/>
+      </c>
       <c r="I204" s="17"/>
     </row>
     <row r="205" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3728,7 +4697,10 @@
       <c r="E205" s="24"/>
       <c r="F205" s="24"/>
       <c r="G205" s="17"/>
-      <c r="H205" s="20"/>
+      <c r="H205" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E205,'Project Tracker'!$F205)&lt;&gt;2,"",DAYS360('Project Tracker'!$E205,'Project Tracker'!$F205,FALSE))</f>
+        <v/>
+      </c>
       <c r="I205" s="17"/>
     </row>
     <row r="206" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3738,7 +4710,10 @@
       <c r="E206" s="24"/>
       <c r="F206" s="24"/>
       <c r="G206" s="17"/>
-      <c r="H206" s="20"/>
+      <c r="H206" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E206,'Project Tracker'!$F206)&lt;&gt;2,"",DAYS360('Project Tracker'!$E206,'Project Tracker'!$F206,FALSE))</f>
+        <v/>
+      </c>
       <c r="I206" s="17"/>
     </row>
     <row r="207" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3748,7 +4723,10 @@
       <c r="E207" s="24"/>
       <c r="F207" s="24"/>
       <c r="G207" s="17"/>
-      <c r="H207" s="20"/>
+      <c r="H207" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E207,'Project Tracker'!$F207)&lt;&gt;2,"",DAYS360('Project Tracker'!$E207,'Project Tracker'!$F207,FALSE))</f>
+        <v/>
+      </c>
       <c r="I207" s="17"/>
     </row>
     <row r="208" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3758,7 +4736,10 @@
       <c r="E208" s="24"/>
       <c r="F208" s="24"/>
       <c r="G208" s="17"/>
-      <c r="H208" s="20"/>
+      <c r="H208" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E208,'Project Tracker'!$F208)&lt;&gt;2,"",DAYS360('Project Tracker'!$E208,'Project Tracker'!$F208,FALSE))</f>
+        <v/>
+      </c>
       <c r="I208" s="17"/>
     </row>
     <row r="209" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3768,7 +4749,10 @@
       <c r="E209" s="24"/>
       <c r="F209" s="24"/>
       <c r="G209" s="17"/>
-      <c r="H209" s="20"/>
+      <c r="H209" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E209,'Project Tracker'!$F209)&lt;&gt;2,"",DAYS360('Project Tracker'!$E209,'Project Tracker'!$F209,FALSE))</f>
+        <v/>
+      </c>
       <c r="I209" s="17"/>
     </row>
     <row r="210" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3778,7 +4762,10 @@
       <c r="E210" s="24"/>
       <c r="F210" s="24"/>
       <c r="G210" s="17"/>
-      <c r="H210" s="20"/>
+      <c r="H210" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E210,'Project Tracker'!$F210)&lt;&gt;2,"",DAYS360('Project Tracker'!$E210,'Project Tracker'!$F210,FALSE))</f>
+        <v/>
+      </c>
       <c r="I210" s="17"/>
     </row>
     <row r="211" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3788,7 +4775,10 @@
       <c r="E211" s="24"/>
       <c r="F211" s="24"/>
       <c r="G211" s="17"/>
-      <c r="H211" s="20"/>
+      <c r="H211" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E211,'Project Tracker'!$F211)&lt;&gt;2,"",DAYS360('Project Tracker'!$E211,'Project Tracker'!$F211,FALSE))</f>
+        <v/>
+      </c>
       <c r="I211" s="17"/>
     </row>
     <row r="212" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3798,7 +4788,10 @@
       <c r="E212" s="24"/>
       <c r="F212" s="24"/>
       <c r="G212" s="17"/>
-      <c r="H212" s="20"/>
+      <c r="H212" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E212,'Project Tracker'!$F212)&lt;&gt;2,"",DAYS360('Project Tracker'!$E212,'Project Tracker'!$F212,FALSE))</f>
+        <v/>
+      </c>
       <c r="I212" s="17"/>
     </row>
     <row r="213" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3808,7 +4801,10 @@
       <c r="E213" s="24"/>
       <c r="F213" s="24"/>
       <c r="G213" s="17"/>
-      <c r="H213" s="20"/>
+      <c r="H213" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E213,'Project Tracker'!$F213)&lt;&gt;2,"",DAYS360('Project Tracker'!$E213,'Project Tracker'!$F213,FALSE))</f>
+        <v/>
+      </c>
       <c r="I213" s="17"/>
     </row>
     <row r="214" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3818,7 +4814,10 @@
       <c r="E214" s="24"/>
       <c r="F214" s="24"/>
       <c r="G214" s="17"/>
-      <c r="H214" s="20"/>
+      <c r="H214" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E214,'Project Tracker'!$F214)&lt;&gt;2,"",DAYS360('Project Tracker'!$E214,'Project Tracker'!$F214,FALSE))</f>
+        <v/>
+      </c>
       <c r="I214" s="17"/>
     </row>
     <row r="215" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3828,7 +4827,10 @@
       <c r="E215" s="24"/>
       <c r="F215" s="24"/>
       <c r="G215" s="17"/>
-      <c r="H215" s="20"/>
+      <c r="H215" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E215,'Project Tracker'!$F215)&lt;&gt;2,"",DAYS360('Project Tracker'!$E215,'Project Tracker'!$F215,FALSE))</f>
+        <v/>
+      </c>
       <c r="I215" s="17"/>
     </row>
     <row r="216" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3838,7 +4840,10 @@
       <c r="E216" s="24"/>
       <c r="F216" s="24"/>
       <c r="G216" s="17"/>
-      <c r="H216" s="20"/>
+      <c r="H216" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E216,'Project Tracker'!$F216)&lt;&gt;2,"",DAYS360('Project Tracker'!$E216,'Project Tracker'!$F216,FALSE))</f>
+        <v/>
+      </c>
       <c r="I216" s="17"/>
     </row>
     <row r="217" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3848,7 +4853,10 @@
       <c r="E217" s="24"/>
       <c r="F217" s="24"/>
       <c r="G217" s="17"/>
-      <c r="H217" s="20"/>
+      <c r="H217" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E217,'Project Tracker'!$F217)&lt;&gt;2,"",DAYS360('Project Tracker'!$E217,'Project Tracker'!$F217,FALSE))</f>
+        <v/>
+      </c>
       <c r="I217" s="17"/>
     </row>
     <row r="218" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3858,7 +4866,10 @@
       <c r="E218" s="24"/>
       <c r="F218" s="24"/>
       <c r="G218" s="17"/>
-      <c r="H218" s="20"/>
+      <c r="H218" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E218,'Project Tracker'!$F218)&lt;&gt;2,"",DAYS360('Project Tracker'!$E218,'Project Tracker'!$F218,FALSE))</f>
+        <v/>
+      </c>
       <c r="I218" s="17"/>
     </row>
     <row r="219" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3868,7 +4879,10 @@
       <c r="E219" s="24"/>
       <c r="F219" s="24"/>
       <c r="G219" s="17"/>
-      <c r="H219" s="20"/>
+      <c r="H219" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E219,'Project Tracker'!$F219)&lt;&gt;2,"",DAYS360('Project Tracker'!$E219,'Project Tracker'!$F219,FALSE))</f>
+        <v/>
+      </c>
       <c r="I219" s="17"/>
     </row>
     <row r="220" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3878,7 +4892,10 @@
       <c r="E220" s="24"/>
       <c r="F220" s="24"/>
       <c r="G220" s="17"/>
-      <c r="H220" s="20"/>
+      <c r="H220" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E220,'Project Tracker'!$F220)&lt;&gt;2,"",DAYS360('Project Tracker'!$E220,'Project Tracker'!$F220,FALSE))</f>
+        <v/>
+      </c>
       <c r="I220" s="17"/>
     </row>
     <row r="221" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3888,7 +4905,10 @@
       <c r="E221" s="24"/>
       <c r="F221" s="24"/>
       <c r="G221" s="17"/>
-      <c r="H221" s="20"/>
+      <c r="H221" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E221,'Project Tracker'!$F221)&lt;&gt;2,"",DAYS360('Project Tracker'!$E221,'Project Tracker'!$F221,FALSE))</f>
+        <v/>
+      </c>
       <c r="I221" s="17"/>
     </row>
     <row r="222" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3898,7 +4918,10 @@
       <c r="E222" s="24"/>
       <c r="F222" s="24"/>
       <c r="G222" s="17"/>
-      <c r="H222" s="20"/>
+      <c r="H222" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E222,'Project Tracker'!$F222)&lt;&gt;2,"",DAYS360('Project Tracker'!$E222,'Project Tracker'!$F222,FALSE))</f>
+        <v/>
+      </c>
       <c r="I222" s="17"/>
     </row>
     <row r="223" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3908,7 +4931,10 @@
       <c r="E223" s="24"/>
       <c r="F223" s="24"/>
       <c r="G223" s="17"/>
-      <c r="H223" s="20"/>
+      <c r="H223" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E223,'Project Tracker'!$F223)&lt;&gt;2,"",DAYS360('Project Tracker'!$E223,'Project Tracker'!$F223,FALSE))</f>
+        <v/>
+      </c>
       <c r="I223" s="17"/>
     </row>
     <row r="224" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3918,7 +4944,10 @@
       <c r="E224" s="24"/>
       <c r="F224" s="24"/>
       <c r="G224" s="17"/>
-      <c r="H224" s="20"/>
+      <c r="H224" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E224,'Project Tracker'!$F224)&lt;&gt;2,"",DAYS360('Project Tracker'!$E224,'Project Tracker'!$F224,FALSE))</f>
+        <v/>
+      </c>
       <c r="I224" s="17"/>
     </row>
     <row r="225" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3928,7 +4957,10 @@
       <c r="E225" s="24"/>
       <c r="F225" s="24"/>
       <c r="G225" s="17"/>
-      <c r="H225" s="20"/>
+      <c r="H225" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E225,'Project Tracker'!$F225)&lt;&gt;2,"",DAYS360('Project Tracker'!$E225,'Project Tracker'!$F225,FALSE))</f>
+        <v/>
+      </c>
       <c r="I225" s="17"/>
     </row>
     <row r="226" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3938,7 +4970,10 @@
       <c r="E226" s="24"/>
       <c r="F226" s="24"/>
       <c r="G226" s="17"/>
-      <c r="H226" s="20"/>
+      <c r="H226" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E226,'Project Tracker'!$F226)&lt;&gt;2,"",DAYS360('Project Tracker'!$E226,'Project Tracker'!$F226,FALSE))</f>
+        <v/>
+      </c>
       <c r="I226" s="17"/>
     </row>
     <row r="227" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3948,7 +4983,10 @@
       <c r="E227" s="24"/>
       <c r="F227" s="24"/>
       <c r="G227" s="17"/>
-      <c r="H227" s="20"/>
+      <c r="H227" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E227,'Project Tracker'!$F227)&lt;&gt;2,"",DAYS360('Project Tracker'!$E227,'Project Tracker'!$F227,FALSE))</f>
+        <v/>
+      </c>
       <c r="I227" s="17"/>
     </row>
     <row r="228" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3958,7 +4996,10 @@
       <c r="E228" s="24"/>
       <c r="F228" s="24"/>
       <c r="G228" s="17"/>
-      <c r="H228" s="20"/>
+      <c r="H228" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E228,'Project Tracker'!$F228)&lt;&gt;2,"",DAYS360('Project Tracker'!$E228,'Project Tracker'!$F228,FALSE))</f>
+        <v/>
+      </c>
       <c r="I228" s="17"/>
     </row>
     <row r="229" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3968,7 +5009,10 @@
       <c r="E229" s="24"/>
       <c r="F229" s="24"/>
       <c r="G229" s="17"/>
-      <c r="H229" s="20"/>
+      <c r="H229" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E229,'Project Tracker'!$F229)&lt;&gt;2,"",DAYS360('Project Tracker'!$E229,'Project Tracker'!$F229,FALSE))</f>
+        <v/>
+      </c>
       <c r="I229" s="17"/>
     </row>
     <row r="230" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3978,7 +5022,10 @@
       <c r="E230" s="24"/>
       <c r="F230" s="24"/>
       <c r="G230" s="17"/>
-      <c r="H230" s="20"/>
+      <c r="H230" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E230,'Project Tracker'!$F230)&lt;&gt;2,"",DAYS360('Project Tracker'!$E230,'Project Tracker'!$F230,FALSE))</f>
+        <v/>
+      </c>
       <c r="I230" s="17"/>
     </row>
     <row r="231" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3988,7 +5035,10 @@
       <c r="E231" s="24"/>
       <c r="F231" s="24"/>
       <c r="G231" s="17"/>
-      <c r="H231" s="20"/>
+      <c r="H231" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E231,'Project Tracker'!$F231)&lt;&gt;2,"",DAYS360('Project Tracker'!$E231,'Project Tracker'!$F231,FALSE))</f>
+        <v/>
+      </c>
       <c r="I231" s="17"/>
     </row>
     <row r="232" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3998,7 +5048,10 @@
       <c r="E232" s="24"/>
       <c r="F232" s="24"/>
       <c r="G232" s="17"/>
-      <c r="H232" s="20"/>
+      <c r="H232" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E232,'Project Tracker'!$F232)&lt;&gt;2,"",DAYS360('Project Tracker'!$E232,'Project Tracker'!$F232,FALSE))</f>
+        <v/>
+      </c>
       <c r="I232" s="17"/>
     </row>
     <row r="233" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4008,7 +5061,10 @@
       <c r="E233" s="24"/>
       <c r="F233" s="24"/>
       <c r="G233" s="17"/>
-      <c r="H233" s="20"/>
+      <c r="H233" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E233,'Project Tracker'!$F233)&lt;&gt;2,"",DAYS360('Project Tracker'!$E233,'Project Tracker'!$F233,FALSE))</f>
+        <v/>
+      </c>
       <c r="I233" s="17"/>
     </row>
     <row r="234" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4018,7 +5074,10 @@
       <c r="E234" s="24"/>
       <c r="F234" s="24"/>
       <c r="G234" s="17"/>
-      <c r="H234" s="20"/>
+      <c r="H234" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E234,'Project Tracker'!$F234)&lt;&gt;2,"",DAYS360('Project Tracker'!$E234,'Project Tracker'!$F234,FALSE))</f>
+        <v/>
+      </c>
       <c r="I234" s="17"/>
     </row>
     <row r="235" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4028,7 +5087,10 @@
       <c r="E235" s="24"/>
       <c r="F235" s="24"/>
       <c r="G235" s="17"/>
-      <c r="H235" s="20"/>
+      <c r="H235" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E235,'Project Tracker'!$F235)&lt;&gt;2,"",DAYS360('Project Tracker'!$E235,'Project Tracker'!$F235,FALSE))</f>
+        <v/>
+      </c>
       <c r="I235" s="17"/>
     </row>
     <row r="236" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4038,7 +5100,10 @@
       <c r="E236" s="24"/>
       <c r="F236" s="24"/>
       <c r="G236" s="17"/>
-      <c r="H236" s="20"/>
+      <c r="H236" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E236,'Project Tracker'!$F236)&lt;&gt;2,"",DAYS360('Project Tracker'!$E236,'Project Tracker'!$F236,FALSE))</f>
+        <v/>
+      </c>
       <c r="I236" s="17"/>
     </row>
     <row r="237" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4048,7 +5113,10 @@
       <c r="E237" s="24"/>
       <c r="F237" s="24"/>
       <c r="G237" s="17"/>
-      <c r="H237" s="20"/>
+      <c r="H237" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E237,'Project Tracker'!$F237)&lt;&gt;2,"",DAYS360('Project Tracker'!$E237,'Project Tracker'!$F237,FALSE))</f>
+        <v/>
+      </c>
       <c r="I237" s="17"/>
     </row>
     <row r="238" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4058,7 +5126,10 @@
       <c r="E238" s="24"/>
       <c r="F238" s="24"/>
       <c r="G238" s="17"/>
-      <c r="H238" s="20"/>
+      <c r="H238" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E238,'Project Tracker'!$F238)&lt;&gt;2,"",DAYS360('Project Tracker'!$E238,'Project Tracker'!$F238,FALSE))</f>
+        <v/>
+      </c>
       <c r="I238" s="17"/>
     </row>
     <row r="239" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4068,7 +5139,10 @@
       <c r="E239" s="24"/>
       <c r="F239" s="24"/>
       <c r="G239" s="17"/>
-      <c r="H239" s="20"/>
+      <c r="H239" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E239,'Project Tracker'!$F239)&lt;&gt;2,"",DAYS360('Project Tracker'!$E239,'Project Tracker'!$F239,FALSE))</f>
+        <v/>
+      </c>
       <c r="I239" s="17"/>
     </row>
     <row r="240" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4078,7 +5152,10 @@
       <c r="E240" s="24"/>
       <c r="F240" s="24"/>
       <c r="G240" s="17"/>
-      <c r="H240" s="20"/>
+      <c r="H240" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E240,'Project Tracker'!$F240)&lt;&gt;2,"",DAYS360('Project Tracker'!$E240,'Project Tracker'!$F240,FALSE))</f>
+        <v/>
+      </c>
       <c r="I240" s="17"/>
     </row>
     <row r="241" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4088,7 +5165,10 @@
       <c r="E241" s="24"/>
       <c r="F241" s="24"/>
       <c r="G241" s="17"/>
-      <c r="H241" s="20"/>
+      <c r="H241" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E241,'Project Tracker'!$F241)&lt;&gt;2,"",DAYS360('Project Tracker'!$E241,'Project Tracker'!$F241,FALSE))</f>
+        <v/>
+      </c>
       <c r="I241" s="17"/>
     </row>
     <row r="242" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4098,7 +5178,10 @@
       <c r="E242" s="24"/>
       <c r="F242" s="24"/>
       <c r="G242" s="17"/>
-      <c r="H242" s="20"/>
+      <c r="H242" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E242,'Project Tracker'!$F242)&lt;&gt;2,"",DAYS360('Project Tracker'!$E242,'Project Tracker'!$F242,FALSE))</f>
+        <v/>
+      </c>
       <c r="I242" s="17"/>
     </row>
     <row r="243" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4108,7 +5191,10 @@
       <c r="E243" s="24"/>
       <c r="F243" s="24"/>
       <c r="G243" s="17"/>
-      <c r="H243" s="20"/>
+      <c r="H243" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E243,'Project Tracker'!$F243)&lt;&gt;2,"",DAYS360('Project Tracker'!$E243,'Project Tracker'!$F243,FALSE))</f>
+        <v/>
+      </c>
       <c r="I243" s="17"/>
     </row>
     <row r="244" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4118,7 +5204,10 @@
       <c r="E244" s="24"/>
       <c r="F244" s="24"/>
       <c r="G244" s="17"/>
-      <c r="H244" s="20"/>
+      <c r="H244" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E244,'Project Tracker'!$F244)&lt;&gt;2,"",DAYS360('Project Tracker'!$E244,'Project Tracker'!$F244,FALSE))</f>
+        <v/>
+      </c>
       <c r="I244" s="17"/>
     </row>
     <row r="245" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4128,7 +5217,10 @@
       <c r="E245" s="24"/>
       <c r="F245" s="24"/>
       <c r="G245" s="17"/>
-      <c r="H245" s="20"/>
+      <c r="H245" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E245,'Project Tracker'!$F245)&lt;&gt;2,"",DAYS360('Project Tracker'!$E245,'Project Tracker'!$F245,FALSE))</f>
+        <v/>
+      </c>
       <c r="I245" s="17"/>
     </row>
     <row r="246" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4138,7 +5230,10 @@
       <c r="E246" s="24"/>
       <c r="F246" s="24"/>
       <c r="G246" s="17"/>
-      <c r="H246" s="20"/>
+      <c r="H246" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E246,'Project Tracker'!$F246)&lt;&gt;2,"",DAYS360('Project Tracker'!$E246,'Project Tracker'!$F246,FALSE))</f>
+        <v/>
+      </c>
       <c r="I246" s="17"/>
     </row>
     <row r="247" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4148,7 +5243,10 @@
       <c r="E247" s="24"/>
       <c r="F247" s="24"/>
       <c r="G247" s="17"/>
-      <c r="H247" s="20"/>
+      <c r="H247" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E247,'Project Tracker'!$F247)&lt;&gt;2,"",DAYS360('Project Tracker'!$E247,'Project Tracker'!$F247,FALSE))</f>
+        <v/>
+      </c>
       <c r="I247" s="17"/>
     </row>
     <row r="248" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4158,7 +5256,10 @@
       <c r="E248" s="24"/>
       <c r="F248" s="24"/>
       <c r="G248" s="17"/>
-      <c r="H248" s="20"/>
+      <c r="H248" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E248,'Project Tracker'!$F248)&lt;&gt;2,"",DAYS360('Project Tracker'!$E248,'Project Tracker'!$F248,FALSE))</f>
+        <v/>
+      </c>
       <c r="I248" s="17"/>
     </row>
     <row r="249" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4168,7 +5269,10 @@
       <c r="E249" s="24"/>
       <c r="F249" s="24"/>
       <c r="G249" s="17"/>
-      <c r="H249" s="20"/>
+      <c r="H249" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E249,'Project Tracker'!$F249)&lt;&gt;2,"",DAYS360('Project Tracker'!$E249,'Project Tracker'!$F249,FALSE))</f>
+        <v/>
+      </c>
       <c r="I249" s="17"/>
     </row>
     <row r="250" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4178,7 +5282,10 @@
       <c r="E250" s="24"/>
       <c r="F250" s="24"/>
       <c r="G250" s="17"/>
-      <c r="H250" s="20"/>
+      <c r="H250" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E250,'Project Tracker'!$F250)&lt;&gt;2,"",DAYS360('Project Tracker'!$E250,'Project Tracker'!$F250,FALSE))</f>
+        <v/>
+      </c>
       <c r="I250" s="17"/>
     </row>
     <row r="251" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4188,7 +5295,10 @@
       <c r="E251" s="24"/>
       <c r="F251" s="24"/>
       <c r="G251" s="17"/>
-      <c r="H251" s="20"/>
+      <c r="H251" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E251,'Project Tracker'!$F251)&lt;&gt;2,"",DAYS360('Project Tracker'!$E251,'Project Tracker'!$F251,FALSE))</f>
+        <v/>
+      </c>
       <c r="I251" s="17"/>
     </row>
     <row r="252" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4198,7 +5308,10 @@
       <c r="E252" s="24"/>
       <c r="F252" s="24"/>
       <c r="G252" s="17"/>
-      <c r="H252" s="20"/>
+      <c r="H252" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E252,'Project Tracker'!$F252)&lt;&gt;2,"",DAYS360('Project Tracker'!$E252,'Project Tracker'!$F252,FALSE))</f>
+        <v/>
+      </c>
       <c r="I252" s="17"/>
     </row>
     <row r="253" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4208,7 +5321,10 @@
       <c r="E253" s="24"/>
       <c r="F253" s="24"/>
       <c r="G253" s="17"/>
-      <c r="H253" s="20"/>
+      <c r="H253" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E253,'Project Tracker'!$F253)&lt;&gt;2,"",DAYS360('Project Tracker'!$E253,'Project Tracker'!$F253,FALSE))</f>
+        <v/>
+      </c>
       <c r="I253" s="17"/>
     </row>
     <row r="254" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4218,7 +5334,10 @@
       <c r="E254" s="24"/>
       <c r="F254" s="24"/>
       <c r="G254" s="17"/>
-      <c r="H254" s="20"/>
+      <c r="H254" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E254,'Project Tracker'!$F254)&lt;&gt;2,"",DAYS360('Project Tracker'!$E254,'Project Tracker'!$F254,FALSE))</f>
+        <v/>
+      </c>
       <c r="I254" s="17"/>
     </row>
     <row r="255" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4228,7 +5347,10 @@
       <c r="E255" s="24"/>
       <c r="F255" s="24"/>
       <c r="G255" s="17"/>
-      <c r="H255" s="20"/>
+      <c r="H255" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E255,'Project Tracker'!$F255)&lt;&gt;2,"",DAYS360('Project Tracker'!$E255,'Project Tracker'!$F255,FALSE))</f>
+        <v/>
+      </c>
       <c r="I255" s="17"/>
     </row>
     <row r="256" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4238,7 +5360,10 @@
       <c r="E256" s="24"/>
       <c r="F256" s="24"/>
       <c r="G256" s="17"/>
-      <c r="H256" s="20"/>
+      <c r="H256" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E256,'Project Tracker'!$F256)&lt;&gt;2,"",DAYS360('Project Tracker'!$E256,'Project Tracker'!$F256,FALSE))</f>
+        <v/>
+      </c>
       <c r="I256" s="17"/>
     </row>
     <row r="257" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4248,7 +5373,10 @@
       <c r="E257" s="24"/>
       <c r="F257" s="24"/>
       <c r="G257" s="17"/>
-      <c r="H257" s="20"/>
+      <c r="H257" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E257,'Project Tracker'!$F257)&lt;&gt;2,"",DAYS360('Project Tracker'!$E257,'Project Tracker'!$F257,FALSE))</f>
+        <v/>
+      </c>
       <c r="I257" s="17"/>
     </row>
     <row r="258" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4258,7 +5386,10 @@
       <c r="E258" s="24"/>
       <c r="F258" s="24"/>
       <c r="G258" s="17"/>
-      <c r="H258" s="20"/>
+      <c r="H258" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E258,'Project Tracker'!$F258)&lt;&gt;2,"",DAYS360('Project Tracker'!$E258,'Project Tracker'!$F258,FALSE))</f>
+        <v/>
+      </c>
       <c r="I258" s="17"/>
     </row>
     <row r="259" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4268,7 +5399,10 @@
       <c r="E259" s="24"/>
       <c r="F259" s="24"/>
       <c r="G259" s="17"/>
-      <c r="H259" s="20"/>
+      <c r="H259" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E259,'Project Tracker'!$F259)&lt;&gt;2,"",DAYS360('Project Tracker'!$E259,'Project Tracker'!$F259,FALSE))</f>
+        <v/>
+      </c>
       <c r="I259" s="17"/>
     </row>
     <row r="260" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4278,7 +5412,10 @@
       <c r="E260" s="24"/>
       <c r="F260" s="24"/>
       <c r="G260" s="17"/>
-      <c r="H260" s="20"/>
+      <c r="H260" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E260,'Project Tracker'!$F260)&lt;&gt;2,"",DAYS360('Project Tracker'!$E260,'Project Tracker'!$F260,FALSE))</f>
+        <v/>
+      </c>
       <c r="I260" s="17"/>
     </row>
     <row r="261" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4288,7 +5425,10 @@
       <c r="E261" s="24"/>
       <c r="F261" s="24"/>
       <c r="G261" s="17"/>
-      <c r="H261" s="20"/>
+      <c r="H261" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E261,'Project Tracker'!$F261)&lt;&gt;2,"",DAYS360('Project Tracker'!$E261,'Project Tracker'!$F261,FALSE))</f>
+        <v/>
+      </c>
       <c r="I261" s="17"/>
     </row>
     <row r="262" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4298,7 +5438,10 @@
       <c r="E262" s="24"/>
       <c r="F262" s="24"/>
       <c r="G262" s="17"/>
-      <c r="H262" s="20"/>
+      <c r="H262" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E262,'Project Tracker'!$F262)&lt;&gt;2,"",DAYS360('Project Tracker'!$E262,'Project Tracker'!$F262,FALSE))</f>
+        <v/>
+      </c>
       <c r="I262" s="17"/>
     </row>
     <row r="263" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4308,7 +5451,10 @@
       <c r="E263" s="24"/>
       <c r="F263" s="24"/>
       <c r="G263" s="17"/>
-      <c r="H263" s="20"/>
+      <c r="H263" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E263,'Project Tracker'!$F263)&lt;&gt;2,"",DAYS360('Project Tracker'!$E263,'Project Tracker'!$F263,FALSE))</f>
+        <v/>
+      </c>
       <c r="I263" s="17"/>
     </row>
     <row r="264" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4318,7 +5464,10 @@
       <c r="E264" s="24"/>
       <c r="F264" s="24"/>
       <c r="G264" s="17"/>
-      <c r="H264" s="20"/>
+      <c r="H264" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E264,'Project Tracker'!$F264)&lt;&gt;2,"",DAYS360('Project Tracker'!$E264,'Project Tracker'!$F264,FALSE))</f>
+        <v/>
+      </c>
       <c r="I264" s="17"/>
     </row>
     <row r="265" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4328,7 +5477,10 @@
       <c r="E265" s="24"/>
       <c r="F265" s="24"/>
       <c r="G265" s="17"/>
-      <c r="H265" s="20"/>
+      <c r="H265" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E265,'Project Tracker'!$F265)&lt;&gt;2,"",DAYS360('Project Tracker'!$E265,'Project Tracker'!$F265,FALSE))</f>
+        <v/>
+      </c>
       <c r="I265" s="17"/>
     </row>
     <row r="266" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4338,7 +5490,10 @@
       <c r="E266" s="24"/>
       <c r="F266" s="24"/>
       <c r="G266" s="17"/>
-      <c r="H266" s="20"/>
+      <c r="H266" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E266,'Project Tracker'!$F266)&lt;&gt;2,"",DAYS360('Project Tracker'!$E266,'Project Tracker'!$F266,FALSE))</f>
+        <v/>
+      </c>
       <c r="I266" s="17"/>
     </row>
     <row r="267" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4348,7 +5503,10 @@
       <c r="E267" s="24"/>
       <c r="F267" s="24"/>
       <c r="G267" s="17"/>
-      <c r="H267" s="20"/>
+      <c r="H267" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E267,'Project Tracker'!$F267)&lt;&gt;2,"",DAYS360('Project Tracker'!$E267,'Project Tracker'!$F267,FALSE))</f>
+        <v/>
+      </c>
       <c r="I267" s="17"/>
     </row>
     <row r="268" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4358,7 +5516,10 @@
       <c r="E268" s="24"/>
       <c r="F268" s="24"/>
       <c r="G268" s="17"/>
-      <c r="H268" s="20"/>
+      <c r="H268" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E268,'Project Tracker'!$F268)&lt;&gt;2,"",DAYS360('Project Tracker'!$E268,'Project Tracker'!$F268,FALSE))</f>
+        <v/>
+      </c>
       <c r="I268" s="17"/>
     </row>
     <row r="269" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4368,7 +5529,10 @@
       <c r="E269" s="24"/>
       <c r="F269" s="24"/>
       <c r="G269" s="17"/>
-      <c r="H269" s="20"/>
+      <c r="H269" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E269,'Project Tracker'!$F269)&lt;&gt;2,"",DAYS360('Project Tracker'!$E269,'Project Tracker'!$F269,FALSE))</f>
+        <v/>
+      </c>
       <c r="I269" s="17"/>
     </row>
     <row r="270" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4378,7 +5542,10 @@
       <c r="E270" s="24"/>
       <c r="F270" s="24"/>
       <c r="G270" s="17"/>
-      <c r="H270" s="20"/>
+      <c r="H270" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E270,'Project Tracker'!$F270)&lt;&gt;2,"",DAYS360('Project Tracker'!$E270,'Project Tracker'!$F270,FALSE))</f>
+        <v/>
+      </c>
       <c r="I270" s="17"/>
     </row>
     <row r="271" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4388,7 +5555,10 @@
       <c r="E271" s="24"/>
       <c r="F271" s="24"/>
       <c r="G271" s="17"/>
-      <c r="H271" s="20"/>
+      <c r="H271" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E271,'Project Tracker'!$F271)&lt;&gt;2,"",DAYS360('Project Tracker'!$E271,'Project Tracker'!$F271,FALSE))</f>
+        <v/>
+      </c>
       <c r="I271" s="17"/>
     </row>
     <row r="272" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4398,7 +5568,10 @@
       <c r="E272" s="24"/>
       <c r="F272" s="24"/>
       <c r="G272" s="17"/>
-      <c r="H272" s="20"/>
+      <c r="H272" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E272,'Project Tracker'!$F272)&lt;&gt;2,"",DAYS360('Project Tracker'!$E272,'Project Tracker'!$F272,FALSE))</f>
+        <v/>
+      </c>
       <c r="I272" s="17"/>
     </row>
     <row r="273" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4408,7 +5581,10 @@
       <c r="E273" s="24"/>
       <c r="F273" s="24"/>
       <c r="G273" s="17"/>
-      <c r="H273" s="20"/>
+      <c r="H273" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E273,'Project Tracker'!$F273)&lt;&gt;2,"",DAYS360('Project Tracker'!$E273,'Project Tracker'!$F273,FALSE))</f>
+        <v/>
+      </c>
       <c r="I273" s="17"/>
     </row>
     <row r="274" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4418,7 +5594,10 @@
       <c r="E274" s="24"/>
       <c r="F274" s="24"/>
       <c r="G274" s="17"/>
-      <c r="H274" s="20"/>
+      <c r="H274" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E274,'Project Tracker'!$F274)&lt;&gt;2,"",DAYS360('Project Tracker'!$E274,'Project Tracker'!$F274,FALSE))</f>
+        <v/>
+      </c>
       <c r="I274" s="17"/>
     </row>
     <row r="275" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4428,7 +5607,10 @@
       <c r="E275" s="24"/>
       <c r="F275" s="24"/>
       <c r="G275" s="17"/>
-      <c r="H275" s="20"/>
+      <c r="H275" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E275,'Project Tracker'!$F275)&lt;&gt;2,"",DAYS360('Project Tracker'!$E275,'Project Tracker'!$F275,FALSE))</f>
+        <v/>
+      </c>
       <c r="I275" s="17"/>
     </row>
     <row r="276" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4438,7 +5620,10 @@
       <c r="E276" s="24"/>
       <c r="F276" s="24"/>
       <c r="G276" s="17"/>
-      <c r="H276" s="20"/>
+      <c r="H276" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E276,'Project Tracker'!$F276)&lt;&gt;2,"",DAYS360('Project Tracker'!$E276,'Project Tracker'!$F276,FALSE))</f>
+        <v/>
+      </c>
       <c r="I276" s="17"/>
     </row>
     <row r="277" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4448,7 +5633,10 @@
       <c r="E277" s="24"/>
       <c r="F277" s="24"/>
       <c r="G277" s="17"/>
-      <c r="H277" s="20"/>
+      <c r="H277" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E277,'Project Tracker'!$F277)&lt;&gt;2,"",DAYS360('Project Tracker'!$E277,'Project Tracker'!$F277,FALSE))</f>
+        <v/>
+      </c>
       <c r="I277" s="17"/>
     </row>
     <row r="278" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4458,7 +5646,10 @@
       <c r="E278" s="24"/>
       <c r="F278" s="24"/>
       <c r="G278" s="17"/>
-      <c r="H278" s="20"/>
+      <c r="H278" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E278,'Project Tracker'!$F278)&lt;&gt;2,"",DAYS360('Project Tracker'!$E278,'Project Tracker'!$F278,FALSE))</f>
+        <v/>
+      </c>
       <c r="I278" s="17"/>
     </row>
     <row r="279" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4468,7 +5659,10 @@
       <c r="E279" s="24"/>
       <c r="F279" s="24"/>
       <c r="G279" s="17"/>
-      <c r="H279" s="20"/>
+      <c r="H279" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E279,'Project Tracker'!$F279)&lt;&gt;2,"",DAYS360('Project Tracker'!$E279,'Project Tracker'!$F279,FALSE))</f>
+        <v/>
+      </c>
       <c r="I279" s="17"/>
     </row>
     <row r="280" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4478,7 +5672,10 @@
       <c r="E280" s="24"/>
       <c r="F280" s="24"/>
       <c r="G280" s="17"/>
-      <c r="H280" s="20"/>
+      <c r="H280" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E280,'Project Tracker'!$F280)&lt;&gt;2,"",DAYS360('Project Tracker'!$E280,'Project Tracker'!$F280,FALSE))</f>
+        <v/>
+      </c>
       <c r="I280" s="17"/>
     </row>
     <row r="281" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4488,7 +5685,10 @@
       <c r="E281" s="24"/>
       <c r="F281" s="24"/>
       <c r="G281" s="17"/>
-      <c r="H281" s="20"/>
+      <c r="H281" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E281,'Project Tracker'!$F281)&lt;&gt;2,"",DAYS360('Project Tracker'!$E281,'Project Tracker'!$F281,FALSE))</f>
+        <v/>
+      </c>
       <c r="I281" s="17"/>
     </row>
     <row r="282" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4498,7 +5698,10 @@
       <c r="E282" s="24"/>
       <c r="F282" s="24"/>
       <c r="G282" s="17"/>
-      <c r="H282" s="20"/>
+      <c r="H282" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E282,'Project Tracker'!$F282)&lt;&gt;2,"",DAYS360('Project Tracker'!$E282,'Project Tracker'!$F282,FALSE))</f>
+        <v/>
+      </c>
       <c r="I282" s="17"/>
     </row>
     <row r="283" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4508,7 +5711,10 @@
       <c r="E283" s="24"/>
       <c r="F283" s="24"/>
       <c r="G283" s="17"/>
-      <c r="H283" s="20"/>
+      <c r="H283" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E283,'Project Tracker'!$F283)&lt;&gt;2,"",DAYS360('Project Tracker'!$E283,'Project Tracker'!$F283,FALSE))</f>
+        <v/>
+      </c>
       <c r="I283" s="17"/>
     </row>
     <row r="284" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4518,7 +5724,10 @@
       <c r="E284" s="24"/>
       <c r="F284" s="24"/>
       <c r="G284" s="17"/>
-      <c r="H284" s="20"/>
+      <c r="H284" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E284,'Project Tracker'!$F284)&lt;&gt;2,"",DAYS360('Project Tracker'!$E284,'Project Tracker'!$F284,FALSE))</f>
+        <v/>
+      </c>
       <c r="I284" s="17"/>
     </row>
     <row r="285" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4528,7 +5737,10 @@
       <c r="E285" s="24"/>
       <c r="F285" s="24"/>
       <c r="G285" s="17"/>
-      <c r="H285" s="20"/>
+      <c r="H285" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E285,'Project Tracker'!$F285)&lt;&gt;2,"",DAYS360('Project Tracker'!$E285,'Project Tracker'!$F285,FALSE))</f>
+        <v/>
+      </c>
       <c r="I285" s="17"/>
     </row>
     <row r="286" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4538,7 +5750,10 @@
       <c r="E286" s="24"/>
       <c r="F286" s="24"/>
       <c r="G286" s="17"/>
-      <c r="H286" s="20"/>
+      <c r="H286" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E286,'Project Tracker'!$F286)&lt;&gt;2,"",DAYS360('Project Tracker'!$E286,'Project Tracker'!$F286,FALSE))</f>
+        <v/>
+      </c>
       <c r="I286" s="17"/>
     </row>
     <row r="287" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4548,7 +5763,10 @@
       <c r="E287" s="24"/>
       <c r="F287" s="24"/>
       <c r="G287" s="17"/>
-      <c r="H287" s="20"/>
+      <c r="H287" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E287,'Project Tracker'!$F287)&lt;&gt;2,"",DAYS360('Project Tracker'!$E287,'Project Tracker'!$F287,FALSE))</f>
+        <v/>
+      </c>
       <c r="I287" s="17"/>
     </row>
     <row r="288" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4558,7 +5776,10 @@
       <c r="E288" s="24"/>
       <c r="F288" s="24"/>
       <c r="G288" s="17"/>
-      <c r="H288" s="20"/>
+      <c r="H288" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E288,'Project Tracker'!$F288)&lt;&gt;2,"",DAYS360('Project Tracker'!$E288,'Project Tracker'!$F288,FALSE))</f>
+        <v/>
+      </c>
       <c r="I288" s="17"/>
     </row>
     <row r="289" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4568,7 +5789,10 @@
       <c r="E289" s="24"/>
       <c r="F289" s="24"/>
       <c r="G289" s="17"/>
-      <c r="H289" s="20"/>
+      <c r="H289" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E289,'Project Tracker'!$F289)&lt;&gt;2,"",DAYS360('Project Tracker'!$E289,'Project Tracker'!$F289,FALSE))</f>
+        <v/>
+      </c>
       <c r="I289" s="17"/>
     </row>
     <row r="290" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4578,7 +5802,10 @@
       <c r="E290" s="24"/>
       <c r="F290" s="24"/>
       <c r="G290" s="17"/>
-      <c r="H290" s="20"/>
+      <c r="H290" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E290,'Project Tracker'!$F290)&lt;&gt;2,"",DAYS360('Project Tracker'!$E290,'Project Tracker'!$F290,FALSE))</f>
+        <v/>
+      </c>
       <c r="I290" s="17"/>
     </row>
     <row r="291" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4588,7 +5815,10 @@
       <c r="E291" s="24"/>
       <c r="F291" s="24"/>
       <c r="G291" s="17"/>
-      <c r="H291" s="20"/>
+      <c r="H291" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E291,'Project Tracker'!$F291)&lt;&gt;2,"",DAYS360('Project Tracker'!$E291,'Project Tracker'!$F291,FALSE))</f>
+        <v/>
+      </c>
       <c r="I291" s="17"/>
     </row>
     <row r="292" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4598,7 +5828,10 @@
       <c r="E292" s="24"/>
       <c r="F292" s="24"/>
       <c r="G292" s="17"/>
-      <c r="H292" s="20"/>
+      <c r="H292" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E292,'Project Tracker'!$F292)&lt;&gt;2,"",DAYS360('Project Tracker'!$E292,'Project Tracker'!$F292,FALSE))</f>
+        <v/>
+      </c>
       <c r="I292" s="17"/>
     </row>
     <row r="293" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4608,7 +5841,10 @@
       <c r="E293" s="24"/>
       <c r="F293" s="24"/>
       <c r="G293" s="17"/>
-      <c r="H293" s="20"/>
+      <c r="H293" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E293,'Project Tracker'!$F293)&lt;&gt;2,"",DAYS360('Project Tracker'!$E293,'Project Tracker'!$F293,FALSE))</f>
+        <v/>
+      </c>
       <c r="I293" s="17"/>
     </row>
     <row r="294" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4618,7 +5854,10 @@
       <c r="E294" s="24"/>
       <c r="F294" s="24"/>
       <c r="G294" s="17"/>
-      <c r="H294" s="20"/>
+      <c r="H294" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E294,'Project Tracker'!$F294)&lt;&gt;2,"",DAYS360('Project Tracker'!$E294,'Project Tracker'!$F294,FALSE))</f>
+        <v/>
+      </c>
       <c r="I294" s="17"/>
     </row>
     <row r="295" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4628,7 +5867,10 @@
       <c r="E295" s="24"/>
       <c r="F295" s="24"/>
       <c r="G295" s="17"/>
-      <c r="H295" s="20"/>
+      <c r="H295" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E295,'Project Tracker'!$F295)&lt;&gt;2,"",DAYS360('Project Tracker'!$E295,'Project Tracker'!$F295,FALSE))</f>
+        <v/>
+      </c>
       <c r="I295" s="17"/>
     </row>
     <row r="296" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4638,7 +5880,10 @@
       <c r="E296" s="24"/>
       <c r="F296" s="24"/>
       <c r="G296" s="17"/>
-      <c r="H296" s="20"/>
+      <c r="H296" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E296,'Project Tracker'!$F296)&lt;&gt;2,"",DAYS360('Project Tracker'!$E296,'Project Tracker'!$F296,FALSE))</f>
+        <v/>
+      </c>
       <c r="I296" s="17"/>
     </row>
     <row r="297" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4648,7 +5893,10 @@
       <c r="E297" s="24"/>
       <c r="F297" s="24"/>
       <c r="G297" s="17"/>
-      <c r="H297" s="20"/>
+      <c r="H297" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E297,'Project Tracker'!$F297)&lt;&gt;2,"",DAYS360('Project Tracker'!$E297,'Project Tracker'!$F297,FALSE))</f>
+        <v/>
+      </c>
       <c r="I297" s="17"/>
     </row>
     <row r="298" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4658,7 +5906,10 @@
       <c r="E298" s="24"/>
       <c r="F298" s="24"/>
       <c r="G298" s="17"/>
-      <c r="H298" s="20"/>
+      <c r="H298" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E298,'Project Tracker'!$F298)&lt;&gt;2,"",DAYS360('Project Tracker'!$E298,'Project Tracker'!$F298,FALSE))</f>
+        <v/>
+      </c>
       <c r="I298" s="17"/>
     </row>
     <row r="299" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4668,7 +5919,10 @@
       <c r="E299" s="24"/>
       <c r="F299" s="24"/>
       <c r="G299" s="17"/>
-      <c r="H299" s="20"/>
+      <c r="H299" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E299,'Project Tracker'!$F299)&lt;&gt;2,"",DAYS360('Project Tracker'!$E299,'Project Tracker'!$F299,FALSE))</f>
+        <v/>
+      </c>
       <c r="I299" s="17"/>
     </row>
     <row r="300" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4678,7 +5932,10 @@
       <c r="E300" s="24"/>
       <c r="F300" s="24"/>
       <c r="G300" s="17"/>
-      <c r="H300" s="20"/>
+      <c r="H300" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E300,'Project Tracker'!$F300)&lt;&gt;2,"",DAYS360('Project Tracker'!$E300,'Project Tracker'!$F300,FALSE))</f>
+        <v/>
+      </c>
       <c r="I300" s="17"/>
     </row>
     <row r="301" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4688,7 +5945,10 @@
       <c r="E301" s="24"/>
       <c r="F301" s="24"/>
       <c r="G301" s="17"/>
-      <c r="H301" s="20"/>
+      <c r="H301" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E301,'Project Tracker'!$F301)&lt;&gt;2,"",DAYS360('Project Tracker'!$E301,'Project Tracker'!$F301,FALSE))</f>
+        <v/>
+      </c>
       <c r="I301" s="17"/>
     </row>
     <row r="302" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4698,7 +5958,10 @@
       <c r="E302" s="24"/>
       <c r="F302" s="24"/>
       <c r="G302" s="17"/>
-      <c r="H302" s="20"/>
+      <c r="H302" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E302,'Project Tracker'!$F302)&lt;&gt;2,"",DAYS360('Project Tracker'!$E302,'Project Tracker'!$F302,FALSE))</f>
+        <v/>
+      </c>
       <c r="I302" s="17"/>
     </row>
     <row r="303" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4708,7 +5971,10 @@
       <c r="E303" s="24"/>
       <c r="F303" s="24"/>
       <c r="G303" s="17"/>
-      <c r="H303" s="20"/>
+      <c r="H303" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E303,'Project Tracker'!$F303)&lt;&gt;2,"",DAYS360('Project Tracker'!$E303,'Project Tracker'!$F303,FALSE))</f>
+        <v/>
+      </c>
       <c r="I303" s="17"/>
     </row>
     <row r="304" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4718,7 +5984,10 @@
       <c r="E304" s="24"/>
       <c r="F304" s="24"/>
       <c r="G304" s="17"/>
-      <c r="H304" s="20"/>
+      <c r="H304" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E304,'Project Tracker'!$F304)&lt;&gt;2,"",DAYS360('Project Tracker'!$E304,'Project Tracker'!$F304,FALSE))</f>
+        <v/>
+      </c>
       <c r="I304" s="17"/>
     </row>
     <row r="305" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4728,7 +5997,10 @@
       <c r="E305" s="24"/>
       <c r="F305" s="24"/>
       <c r="G305" s="17"/>
-      <c r="H305" s="20"/>
+      <c r="H305" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E305,'Project Tracker'!$F305)&lt;&gt;2,"",DAYS360('Project Tracker'!$E305,'Project Tracker'!$F305,FALSE))</f>
+        <v/>
+      </c>
       <c r="I305" s="17"/>
     </row>
     <row r="306" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4738,7 +6010,10 @@
       <c r="E306" s="24"/>
       <c r="F306" s="24"/>
       <c r="G306" s="17"/>
-      <c r="H306" s="20"/>
+      <c r="H306" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E306,'Project Tracker'!$F306)&lt;&gt;2,"",DAYS360('Project Tracker'!$E306,'Project Tracker'!$F306,FALSE))</f>
+        <v/>
+      </c>
       <c r="I306" s="17"/>
     </row>
     <row r="307" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4748,7 +6023,10 @@
       <c r="E307" s="24"/>
       <c r="F307" s="24"/>
       <c r="G307" s="17"/>
-      <c r="H307" s="20"/>
+      <c r="H307" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E307,'Project Tracker'!$F307)&lt;&gt;2,"",DAYS360('Project Tracker'!$E307,'Project Tracker'!$F307,FALSE))</f>
+        <v/>
+      </c>
       <c r="I307" s="17"/>
     </row>
     <row r="308" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4758,7 +6036,10 @@
       <c r="E308" s="24"/>
       <c r="F308" s="24"/>
       <c r="G308" s="17"/>
-      <c r="H308" s="20"/>
+      <c r="H308" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E308,'Project Tracker'!$F308)&lt;&gt;2,"",DAYS360('Project Tracker'!$E308,'Project Tracker'!$F308,FALSE))</f>
+        <v/>
+      </c>
       <c r="I308" s="17"/>
     </row>
     <row r="309" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4768,7 +6049,10 @@
       <c r="E309" s="24"/>
       <c r="F309" s="24"/>
       <c r="G309" s="17"/>
-      <c r="H309" s="20"/>
+      <c r="H309" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E309,'Project Tracker'!$F309)&lt;&gt;2,"",DAYS360('Project Tracker'!$E309,'Project Tracker'!$F309,FALSE))</f>
+        <v/>
+      </c>
       <c r="I309" s="17"/>
     </row>
     <row r="310" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4778,7 +6062,10 @@
       <c r="E310" s="24"/>
       <c r="F310" s="24"/>
       <c r="G310" s="17"/>
-      <c r="H310" s="20"/>
+      <c r="H310" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E310,'Project Tracker'!$F310)&lt;&gt;2,"",DAYS360('Project Tracker'!$E310,'Project Tracker'!$F310,FALSE))</f>
+        <v/>
+      </c>
       <c r="I310" s="17"/>
     </row>
     <row r="311" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4788,7 +6075,10 @@
       <c r="E311" s="24"/>
       <c r="F311" s="24"/>
       <c r="G311" s="17"/>
-      <c r="H311" s="20"/>
+      <c r="H311" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E311,'Project Tracker'!$F311)&lt;&gt;2,"",DAYS360('Project Tracker'!$E311,'Project Tracker'!$F311,FALSE))</f>
+        <v/>
+      </c>
       <c r="I311" s="17"/>
     </row>
     <row r="312" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4798,7 +6088,10 @@
       <c r="E312" s="24"/>
       <c r="F312" s="24"/>
       <c r="G312" s="17"/>
-      <c r="H312" s="20"/>
+      <c r="H312" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E312,'Project Tracker'!$F312)&lt;&gt;2,"",DAYS360('Project Tracker'!$E312,'Project Tracker'!$F312,FALSE))</f>
+        <v/>
+      </c>
       <c r="I312" s="17"/>
     </row>
     <row r="313" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4808,7 +6101,10 @@
       <c r="E313" s="24"/>
       <c r="F313" s="24"/>
       <c r="G313" s="17"/>
-      <c r="H313" s="20"/>
+      <c r="H313" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E313,'Project Tracker'!$F313)&lt;&gt;2,"",DAYS360('Project Tracker'!$E313,'Project Tracker'!$F313,FALSE))</f>
+        <v/>
+      </c>
       <c r="I313" s="17"/>
     </row>
     <row r="314" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4818,7 +6114,10 @@
       <c r="E314" s="24"/>
       <c r="F314" s="24"/>
       <c r="G314" s="17"/>
-      <c r="H314" s="20"/>
+      <c r="H314" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E314,'Project Tracker'!$F314)&lt;&gt;2,"",DAYS360('Project Tracker'!$E314,'Project Tracker'!$F314,FALSE))</f>
+        <v/>
+      </c>
       <c r="I314" s="17"/>
     </row>
     <row r="315" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4828,7 +6127,10 @@
       <c r="E315" s="24"/>
       <c r="F315" s="24"/>
       <c r="G315" s="17"/>
-      <c r="H315" s="20"/>
+      <c r="H315" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E315,'Project Tracker'!$F315)&lt;&gt;2,"",DAYS360('Project Tracker'!$E315,'Project Tracker'!$F315,FALSE))</f>
+        <v/>
+      </c>
       <c r="I315" s="17"/>
     </row>
     <row r="316" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4838,7 +6140,10 @@
       <c r="E316" s="24"/>
       <c r="F316" s="24"/>
       <c r="G316" s="17"/>
-      <c r="H316" s="20"/>
+      <c r="H316" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E316,'Project Tracker'!$F316)&lt;&gt;2,"",DAYS360('Project Tracker'!$E316,'Project Tracker'!$F316,FALSE))</f>
+        <v/>
+      </c>
       <c r="I316" s="17"/>
     </row>
     <row r="317" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4848,7 +6153,10 @@
       <c r="E317" s="24"/>
       <c r="F317" s="24"/>
       <c r="G317" s="17"/>
-      <c r="H317" s="20"/>
+      <c r="H317" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E317,'Project Tracker'!$F317)&lt;&gt;2,"",DAYS360('Project Tracker'!$E317,'Project Tracker'!$F317,FALSE))</f>
+        <v/>
+      </c>
       <c r="I317" s="17"/>
     </row>
     <row r="318" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4858,7 +6166,10 @@
       <c r="E318" s="24"/>
       <c r="F318" s="24"/>
       <c r="G318" s="17"/>
-      <c r="H318" s="20"/>
+      <c r="H318" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E318,'Project Tracker'!$F318)&lt;&gt;2,"",DAYS360('Project Tracker'!$E318,'Project Tracker'!$F318,FALSE))</f>
+        <v/>
+      </c>
       <c r="I318" s="17"/>
     </row>
     <row r="319" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4868,7 +6179,10 @@
       <c r="E319" s="24"/>
       <c r="F319" s="24"/>
       <c r="G319" s="17"/>
-      <c r="H319" s="20"/>
+      <c r="H319" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E319,'Project Tracker'!$F319)&lt;&gt;2,"",DAYS360('Project Tracker'!$E319,'Project Tracker'!$F319,FALSE))</f>
+        <v/>
+      </c>
       <c r="I319" s="17"/>
     </row>
     <row r="320" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4878,7 +6192,10 @@
       <c r="E320" s="24"/>
       <c r="F320" s="24"/>
       <c r="G320" s="17"/>
-      <c r="H320" s="20"/>
+      <c r="H320" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E320,'Project Tracker'!$F320)&lt;&gt;2,"",DAYS360('Project Tracker'!$E320,'Project Tracker'!$F320,FALSE))</f>
+        <v/>
+      </c>
       <c r="I320" s="17"/>
     </row>
     <row r="321" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4888,7 +6205,10 @@
       <c r="E321" s="24"/>
       <c r="F321" s="24"/>
       <c r="G321" s="17"/>
-      <c r="H321" s="20"/>
+      <c r="H321" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E321,'Project Tracker'!$F321)&lt;&gt;2,"",DAYS360('Project Tracker'!$E321,'Project Tracker'!$F321,FALSE))</f>
+        <v/>
+      </c>
       <c r="I321" s="17"/>
     </row>
     <row r="322" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4898,7 +6218,10 @@
       <c r="E322" s="24"/>
       <c r="F322" s="24"/>
       <c r="G322" s="17"/>
-      <c r="H322" s="20"/>
+      <c r="H322" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E322,'Project Tracker'!$F322)&lt;&gt;2,"",DAYS360('Project Tracker'!$E322,'Project Tracker'!$F322,FALSE))</f>
+        <v/>
+      </c>
       <c r="I322" s="17"/>
     </row>
     <row r="323" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4908,7 +6231,10 @@
       <c r="E323" s="24"/>
       <c r="F323" s="24"/>
       <c r="G323" s="17"/>
-      <c r="H323" s="20"/>
+      <c r="H323" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E323,'Project Tracker'!$F323)&lt;&gt;2,"",DAYS360('Project Tracker'!$E323,'Project Tracker'!$F323,FALSE))</f>
+        <v/>
+      </c>
       <c r="I323" s="17"/>
     </row>
     <row r="324" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4918,7 +6244,10 @@
       <c r="E324" s="24"/>
       <c r="F324" s="24"/>
       <c r="G324" s="17"/>
-      <c r="H324" s="20"/>
+      <c r="H324" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E324,'Project Tracker'!$F324)&lt;&gt;2,"",DAYS360('Project Tracker'!$E324,'Project Tracker'!$F324,FALSE))</f>
+        <v/>
+      </c>
       <c r="I324" s="17"/>
     </row>
     <row r="325" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4928,7 +6257,10 @@
       <c r="E325" s="24"/>
       <c r="F325" s="24"/>
       <c r="G325" s="17"/>
-      <c r="H325" s="20"/>
+      <c r="H325" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E325,'Project Tracker'!$F325)&lt;&gt;2,"",DAYS360('Project Tracker'!$E325,'Project Tracker'!$F325,FALSE))</f>
+        <v/>
+      </c>
       <c r="I325" s="17"/>
     </row>
     <row r="326" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4938,7 +6270,10 @@
       <c r="E326" s="24"/>
       <c r="F326" s="24"/>
       <c r="G326" s="17"/>
-      <c r="H326" s="20"/>
+      <c r="H326" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E326,'Project Tracker'!$F326)&lt;&gt;2,"",DAYS360('Project Tracker'!$E326,'Project Tracker'!$F326,FALSE))</f>
+        <v/>
+      </c>
       <c r="I326" s="17"/>
     </row>
     <row r="327" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4948,7 +6283,10 @@
       <c r="E327" s="24"/>
       <c r="F327" s="24"/>
       <c r="G327" s="17"/>
-      <c r="H327" s="20"/>
+      <c r="H327" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E327,'Project Tracker'!$F327)&lt;&gt;2,"",DAYS360('Project Tracker'!$E327,'Project Tracker'!$F327,FALSE))</f>
+        <v/>
+      </c>
       <c r="I327" s="17"/>
     </row>
     <row r="328" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4958,7 +6296,10 @@
       <c r="E328" s="24"/>
       <c r="F328" s="24"/>
       <c r="G328" s="17"/>
-      <c r="H328" s="20"/>
+      <c r="H328" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E328,'Project Tracker'!$F328)&lt;&gt;2,"",DAYS360('Project Tracker'!$E328,'Project Tracker'!$F328,FALSE))</f>
+        <v/>
+      </c>
       <c r="I328" s="17"/>
     </row>
     <row r="329" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4968,7 +6309,10 @@
       <c r="E329" s="24"/>
       <c r="F329" s="24"/>
       <c r="G329" s="17"/>
-      <c r="H329" s="20"/>
+      <c r="H329" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E329,'Project Tracker'!$F329)&lt;&gt;2,"",DAYS360('Project Tracker'!$E329,'Project Tracker'!$F329,FALSE))</f>
+        <v/>
+      </c>
       <c r="I329" s="17"/>
     </row>
     <row r="330" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4978,7 +6322,10 @@
       <c r="E330" s="24"/>
       <c r="F330" s="24"/>
       <c r="G330" s="17"/>
-      <c r="H330" s="20"/>
+      <c r="H330" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E330,'Project Tracker'!$F330)&lt;&gt;2,"",DAYS360('Project Tracker'!$E330,'Project Tracker'!$F330,FALSE))</f>
+        <v/>
+      </c>
       <c r="I330" s="17"/>
     </row>
     <row r="331" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4988,7 +6335,10 @@
       <c r="E331" s="24"/>
       <c r="F331" s="24"/>
       <c r="G331" s="17"/>
-      <c r="H331" s="20"/>
+      <c r="H331" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E331,'Project Tracker'!$F331)&lt;&gt;2,"",DAYS360('Project Tracker'!$E331,'Project Tracker'!$F331,FALSE))</f>
+        <v/>
+      </c>
       <c r="I331" s="17"/>
     </row>
     <row r="332" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4998,7 +6348,10 @@
       <c r="E332" s="24"/>
       <c r="F332" s="24"/>
       <c r="G332" s="17"/>
-      <c r="H332" s="20"/>
+      <c r="H332" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E332,'Project Tracker'!$F332)&lt;&gt;2,"",DAYS360('Project Tracker'!$E332,'Project Tracker'!$F332,FALSE))</f>
+        <v/>
+      </c>
       <c r="I332" s="17"/>
     </row>
     <row r="333" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5008,7 +6361,10 @@
       <c r="E333" s="24"/>
       <c r="F333" s="24"/>
       <c r="G333" s="17"/>
-      <c r="H333" s="20"/>
+      <c r="H333" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E333,'Project Tracker'!$F333)&lt;&gt;2,"",DAYS360('Project Tracker'!$E333,'Project Tracker'!$F333,FALSE))</f>
+        <v/>
+      </c>
       <c r="I333" s="17"/>
     </row>
     <row r="334" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5018,7 +6374,10 @@
       <c r="E334" s="24"/>
       <c r="F334" s="24"/>
       <c r="G334" s="17"/>
-      <c r="H334" s="20"/>
+      <c r="H334" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E334,'Project Tracker'!$F334)&lt;&gt;2,"",DAYS360('Project Tracker'!$E334,'Project Tracker'!$F334,FALSE))</f>
+        <v/>
+      </c>
       <c r="I334" s="17"/>
     </row>
     <row r="335" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5028,7 +6387,10 @@
       <c r="E335" s="24"/>
       <c r="F335" s="24"/>
       <c r="G335" s="17"/>
-      <c r="H335" s="20"/>
+      <c r="H335" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E335,'Project Tracker'!$F335)&lt;&gt;2,"",DAYS360('Project Tracker'!$E335,'Project Tracker'!$F335,FALSE))</f>
+        <v/>
+      </c>
       <c r="I335" s="17"/>
     </row>
     <row r="336" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5038,7 +6400,10 @@
       <c r="E336" s="24"/>
       <c r="F336" s="24"/>
       <c r="G336" s="17"/>
-      <c r="H336" s="20"/>
+      <c r="H336" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E336,'Project Tracker'!$F336)&lt;&gt;2,"",DAYS360('Project Tracker'!$E336,'Project Tracker'!$F336,FALSE))</f>
+        <v/>
+      </c>
       <c r="I336" s="17"/>
     </row>
     <row r="337" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5048,7 +6413,10 @@
       <c r="E337" s="24"/>
       <c r="F337" s="24"/>
       <c r="G337" s="17"/>
-      <c r="H337" s="20"/>
+      <c r="H337" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E337,'Project Tracker'!$F337)&lt;&gt;2,"",DAYS360('Project Tracker'!$E337,'Project Tracker'!$F337,FALSE))</f>
+        <v/>
+      </c>
       <c r="I337" s="17"/>
     </row>
     <row r="338" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5058,7 +6426,10 @@
       <c r="E338" s="24"/>
       <c r="F338" s="24"/>
       <c r="G338" s="17"/>
-      <c r="H338" s="20"/>
+      <c r="H338" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E338,'Project Tracker'!$F338)&lt;&gt;2,"",DAYS360('Project Tracker'!$E338,'Project Tracker'!$F338,FALSE))</f>
+        <v/>
+      </c>
       <c r="I338" s="17"/>
     </row>
     <row r="339" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5068,7 +6439,10 @@
       <c r="E339" s="24"/>
       <c r="F339" s="24"/>
       <c r="G339" s="17"/>
-      <c r="H339" s="20"/>
+      <c r="H339" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E339,'Project Tracker'!$F339)&lt;&gt;2,"",DAYS360('Project Tracker'!$E339,'Project Tracker'!$F339,FALSE))</f>
+        <v/>
+      </c>
       <c r="I339" s="17"/>
     </row>
     <row r="340" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5078,7 +6452,10 @@
       <c r="E340" s="24"/>
       <c r="F340" s="24"/>
       <c r="G340" s="17"/>
-      <c r="H340" s="20"/>
+      <c r="H340" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E340,'Project Tracker'!$F340)&lt;&gt;2,"",DAYS360('Project Tracker'!$E340,'Project Tracker'!$F340,FALSE))</f>
+        <v/>
+      </c>
       <c r="I340" s="17"/>
     </row>
     <row r="341" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5088,7 +6465,10 @@
       <c r="E341" s="24"/>
       <c r="F341" s="24"/>
       <c r="G341" s="17"/>
-      <c r="H341" s="20"/>
+      <c r="H341" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E341,'Project Tracker'!$F341)&lt;&gt;2,"",DAYS360('Project Tracker'!$E341,'Project Tracker'!$F341,FALSE))</f>
+        <v/>
+      </c>
       <c r="I341" s="17"/>
     </row>
     <row r="342" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5098,7 +6478,10 @@
       <c r="E342" s="24"/>
       <c r="F342" s="24"/>
       <c r="G342" s="17"/>
-      <c r="H342" s="20"/>
+      <c r="H342" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E342,'Project Tracker'!$F342)&lt;&gt;2,"",DAYS360('Project Tracker'!$E342,'Project Tracker'!$F342,FALSE))</f>
+        <v/>
+      </c>
       <c r="I342" s="17"/>
     </row>
     <row r="343" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5108,7 +6491,10 @@
       <c r="E343" s="24"/>
       <c r="F343" s="24"/>
       <c r="G343" s="17"/>
-      <c r="H343" s="20"/>
+      <c r="H343" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E343,'Project Tracker'!$F343)&lt;&gt;2,"",DAYS360('Project Tracker'!$E343,'Project Tracker'!$F343,FALSE))</f>
+        <v/>
+      </c>
       <c r="I343" s="17"/>
     </row>
     <row r="344" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5118,7 +6504,10 @@
       <c r="E344" s="24"/>
       <c r="F344" s="24"/>
       <c r="G344" s="17"/>
-      <c r="H344" s="20"/>
+      <c r="H344" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E344,'Project Tracker'!$F344)&lt;&gt;2,"",DAYS360('Project Tracker'!$E344,'Project Tracker'!$F344,FALSE))</f>
+        <v/>
+      </c>
       <c r="I344" s="17"/>
     </row>
     <row r="345" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5128,7 +6517,10 @@
       <c r="E345" s="24"/>
       <c r="F345" s="24"/>
       <c r="G345" s="17"/>
-      <c r="H345" s="20"/>
+      <c r="H345" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E345,'Project Tracker'!$F345)&lt;&gt;2,"",DAYS360('Project Tracker'!$E345,'Project Tracker'!$F345,FALSE))</f>
+        <v/>
+      </c>
       <c r="I345" s="17"/>
     </row>
     <row r="346" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5138,7 +6530,10 @@
       <c r="E346" s="24"/>
       <c r="F346" s="24"/>
       <c r="G346" s="17"/>
-      <c r="H346" s="20"/>
+      <c r="H346" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E346,'Project Tracker'!$F346)&lt;&gt;2,"",DAYS360('Project Tracker'!$E346,'Project Tracker'!$F346,FALSE))</f>
+        <v/>
+      </c>
       <c r="I346" s="17"/>
     </row>
     <row r="347" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5148,7 +6543,10 @@
       <c r="E347" s="24"/>
       <c r="F347" s="24"/>
       <c r="G347" s="17"/>
-      <c r="H347" s="20"/>
+      <c r="H347" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E347,'Project Tracker'!$F347)&lt;&gt;2,"",DAYS360('Project Tracker'!$E347,'Project Tracker'!$F347,FALSE))</f>
+        <v/>
+      </c>
       <c r="I347" s="17"/>
     </row>
     <row r="348" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5158,7 +6556,10 @@
       <c r="E348" s="24"/>
       <c r="F348" s="24"/>
       <c r="G348" s="17"/>
-      <c r="H348" s="20"/>
+      <c r="H348" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E348,'Project Tracker'!$F348)&lt;&gt;2,"",DAYS360('Project Tracker'!$E348,'Project Tracker'!$F348,FALSE))</f>
+        <v/>
+      </c>
       <c r="I348" s="17"/>
     </row>
     <row r="349" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5168,7 +6569,10 @@
       <c r="E349" s="24"/>
       <c r="F349" s="24"/>
       <c r="G349" s="17"/>
-      <c r="H349" s="20"/>
+      <c r="H349" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E349,'Project Tracker'!$F349)&lt;&gt;2,"",DAYS360('Project Tracker'!$E349,'Project Tracker'!$F349,FALSE))</f>
+        <v/>
+      </c>
       <c r="I349" s="17"/>
     </row>
     <row r="350" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5178,7 +6582,10 @@
       <c r="E350" s="24"/>
       <c r="F350" s="24"/>
       <c r="G350" s="17"/>
-      <c r="H350" s="20"/>
+      <c r="H350" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E350,'Project Tracker'!$F350)&lt;&gt;2,"",DAYS360('Project Tracker'!$E350,'Project Tracker'!$F350,FALSE))</f>
+        <v/>
+      </c>
       <c r="I350" s="17"/>
     </row>
     <row r="351" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5188,7 +6595,10 @@
       <c r="E351" s="24"/>
       <c r="F351" s="24"/>
       <c r="G351" s="17"/>
-      <c r="H351" s="20"/>
+      <c r="H351" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E351,'Project Tracker'!$F351)&lt;&gt;2,"",DAYS360('Project Tracker'!$E351,'Project Tracker'!$F351,FALSE))</f>
+        <v/>
+      </c>
       <c r="I351" s="17"/>
     </row>
     <row r="352" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5198,7 +6608,10 @@
       <c r="E352" s="24"/>
       <c r="F352" s="24"/>
       <c r="G352" s="17"/>
-      <c r="H352" s="20"/>
+      <c r="H352" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E352,'Project Tracker'!$F352)&lt;&gt;2,"",DAYS360('Project Tracker'!$E352,'Project Tracker'!$F352,FALSE))</f>
+        <v/>
+      </c>
       <c r="I352" s="17"/>
     </row>
     <row r="353" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5208,7 +6621,10 @@
       <c r="E353" s="24"/>
       <c r="F353" s="24"/>
       <c r="G353" s="17"/>
-      <c r="H353" s="20"/>
+      <c r="H353" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E353,'Project Tracker'!$F353)&lt;&gt;2,"",DAYS360('Project Tracker'!$E353,'Project Tracker'!$F353,FALSE))</f>
+        <v/>
+      </c>
       <c r="I353" s="17"/>
     </row>
     <row r="354" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5218,7 +6634,10 @@
       <c r="E354" s="24"/>
       <c r="F354" s="24"/>
       <c r="G354" s="17"/>
-      <c r="H354" s="20"/>
+      <c r="H354" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E354,'Project Tracker'!$F354)&lt;&gt;2,"",DAYS360('Project Tracker'!$E354,'Project Tracker'!$F354,FALSE))</f>
+        <v/>
+      </c>
       <c r="I354" s="17"/>
     </row>
     <row r="355" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5228,7 +6647,10 @@
       <c r="E355" s="24"/>
       <c r="F355" s="24"/>
       <c r="G355" s="17"/>
-      <c r="H355" s="20"/>
+      <c r="H355" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E355,'Project Tracker'!$F355)&lt;&gt;2,"",DAYS360('Project Tracker'!$E355,'Project Tracker'!$F355,FALSE))</f>
+        <v/>
+      </c>
       <c r="I355" s="17"/>
     </row>
     <row r="356" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5238,7 +6660,10 @@
       <c r="E356" s="24"/>
       <c r="F356" s="24"/>
       <c r="G356" s="17"/>
-      <c r="H356" s="20"/>
+      <c r="H356" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E356,'Project Tracker'!$F356)&lt;&gt;2,"",DAYS360('Project Tracker'!$E356,'Project Tracker'!$F356,FALSE))</f>
+        <v/>
+      </c>
       <c r="I356" s="17"/>
     </row>
     <row r="357" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5248,7 +6673,10 @@
       <c r="E357" s="24"/>
       <c r="F357" s="24"/>
       <c r="G357" s="17"/>
-      <c r="H357" s="20"/>
+      <c r="H357" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E357,'Project Tracker'!$F357)&lt;&gt;2,"",DAYS360('Project Tracker'!$E357,'Project Tracker'!$F357,FALSE))</f>
+        <v/>
+      </c>
       <c r="I357" s="17"/>
     </row>
     <row r="358" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5258,7 +6686,10 @@
       <c r="E358" s="24"/>
       <c r="F358" s="24"/>
       <c r="G358" s="17"/>
-      <c r="H358" s="20"/>
+      <c r="H358" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E358,'Project Tracker'!$F358)&lt;&gt;2,"",DAYS360('Project Tracker'!$E358,'Project Tracker'!$F358,FALSE))</f>
+        <v/>
+      </c>
       <c r="I358" s="17"/>
     </row>
     <row r="359" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5268,7 +6699,10 @@
       <c r="E359" s="24"/>
       <c r="F359" s="24"/>
       <c r="G359" s="17"/>
-      <c r="H359" s="20"/>
+      <c r="H359" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E359,'Project Tracker'!$F359)&lt;&gt;2,"",DAYS360('Project Tracker'!$E359,'Project Tracker'!$F359,FALSE))</f>
+        <v/>
+      </c>
       <c r="I359" s="17"/>
     </row>
     <row r="360" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5278,7 +6712,10 @@
       <c r="E360" s="24"/>
       <c r="F360" s="24"/>
       <c r="G360" s="17"/>
-      <c r="H360" s="20"/>
+      <c r="H360" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E360,'Project Tracker'!$F360)&lt;&gt;2,"",DAYS360('Project Tracker'!$E360,'Project Tracker'!$F360,FALSE))</f>
+        <v/>
+      </c>
       <c r="I360" s="17"/>
     </row>
     <row r="361" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5288,7 +6725,10 @@
       <c r="E361" s="24"/>
       <c r="F361" s="24"/>
       <c r="G361" s="17"/>
-      <c r="H361" s="20"/>
+      <c r="H361" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E361,'Project Tracker'!$F361)&lt;&gt;2,"",DAYS360('Project Tracker'!$E361,'Project Tracker'!$F361,FALSE))</f>
+        <v/>
+      </c>
       <c r="I361" s="17"/>
     </row>
     <row r="362" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5298,7 +6738,10 @@
       <c r="E362" s="24"/>
       <c r="F362" s="24"/>
       <c r="G362" s="17"/>
-      <c r="H362" s="20"/>
+      <c r="H362" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E362,'Project Tracker'!$F362)&lt;&gt;2,"",DAYS360('Project Tracker'!$E362,'Project Tracker'!$F362,FALSE))</f>
+        <v/>
+      </c>
       <c r="I362" s="17"/>
     </row>
     <row r="363" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5308,7 +6751,10 @@
       <c r="E363" s="24"/>
       <c r="F363" s="24"/>
       <c r="G363" s="17"/>
-      <c r="H363" s="20"/>
+      <c r="H363" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E363,'Project Tracker'!$F363)&lt;&gt;2,"",DAYS360('Project Tracker'!$E363,'Project Tracker'!$F363,FALSE))</f>
+        <v/>
+      </c>
       <c r="I363" s="17"/>
     </row>
     <row r="364" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5318,7 +6764,10 @@
       <c r="E364" s="24"/>
       <c r="F364" s="24"/>
       <c r="G364" s="17"/>
-      <c r="H364" s="20"/>
+      <c r="H364" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E364,'Project Tracker'!$F364)&lt;&gt;2,"",DAYS360('Project Tracker'!$E364,'Project Tracker'!$F364,FALSE))</f>
+        <v/>
+      </c>
       <c r="I364" s="17"/>
     </row>
     <row r="365" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5328,7 +6777,10 @@
       <c r="E365" s="24"/>
       <c r="F365" s="24"/>
       <c r="G365" s="17"/>
-      <c r="H365" s="20"/>
+      <c r="H365" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E365,'Project Tracker'!$F365)&lt;&gt;2,"",DAYS360('Project Tracker'!$E365,'Project Tracker'!$F365,FALSE))</f>
+        <v/>
+      </c>
       <c r="I365" s="17"/>
     </row>
     <row r="366" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5338,7 +6790,10 @@
       <c r="E366" s="24"/>
       <c r="F366" s="24"/>
       <c r="G366" s="17"/>
-      <c r="H366" s="20"/>
+      <c r="H366" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E366,'Project Tracker'!$F366)&lt;&gt;2,"",DAYS360('Project Tracker'!$E366,'Project Tracker'!$F366,FALSE))</f>
+        <v/>
+      </c>
       <c r="I366" s="17"/>
     </row>
     <row r="367" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5348,7 +6803,10 @@
       <c r="E367" s="24"/>
       <c r="F367" s="24"/>
       <c r="G367" s="17"/>
-      <c r="H367" s="20"/>
+      <c r="H367" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E367,'Project Tracker'!$F367)&lt;&gt;2,"",DAYS360('Project Tracker'!$E367,'Project Tracker'!$F367,FALSE))</f>
+        <v/>
+      </c>
       <c r="I367" s="17"/>
     </row>
     <row r="368" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5358,7 +6816,10 @@
       <c r="E368" s="24"/>
       <c r="F368" s="24"/>
       <c r="G368" s="17"/>
-      <c r="H368" s="20"/>
+      <c r="H368" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E368,'Project Tracker'!$F368)&lt;&gt;2,"",DAYS360('Project Tracker'!$E368,'Project Tracker'!$F368,FALSE))</f>
+        <v/>
+      </c>
       <c r="I368" s="17"/>
     </row>
     <row r="369" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5368,7 +6829,10 @@
       <c r="E369" s="24"/>
       <c r="F369" s="24"/>
       <c r="G369" s="17"/>
-      <c r="H369" s="20"/>
+      <c r="H369" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E369,'Project Tracker'!$F369)&lt;&gt;2,"",DAYS360('Project Tracker'!$E369,'Project Tracker'!$F369,FALSE))</f>
+        <v/>
+      </c>
       <c r="I369" s="17"/>
     </row>
     <row r="370" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5378,7 +6842,10 @@
       <c r="E370" s="24"/>
       <c r="F370" s="24"/>
       <c r="G370" s="17"/>
-      <c r="H370" s="20"/>
+      <c r="H370" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E370,'Project Tracker'!$F370)&lt;&gt;2,"",DAYS360('Project Tracker'!$E370,'Project Tracker'!$F370,FALSE))</f>
+        <v/>
+      </c>
       <c r="I370" s="17"/>
     </row>
     <row r="371" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5388,7 +6855,10 @@
       <c r="E371" s="24"/>
       <c r="F371" s="24"/>
       <c r="G371" s="17"/>
-      <c r="H371" s="20"/>
+      <c r="H371" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E371,'Project Tracker'!$F371)&lt;&gt;2,"",DAYS360('Project Tracker'!$E371,'Project Tracker'!$F371,FALSE))</f>
+        <v/>
+      </c>
       <c r="I371" s="17"/>
     </row>
     <row r="372" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5398,7 +6868,10 @@
       <c r="E372" s="24"/>
       <c r="F372" s="24"/>
       <c r="G372" s="17"/>
-      <c r="H372" s="20"/>
+      <c r="H372" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E372,'Project Tracker'!$F372)&lt;&gt;2,"",DAYS360('Project Tracker'!$E372,'Project Tracker'!$F372,FALSE))</f>
+        <v/>
+      </c>
       <c r="I372" s="17"/>
     </row>
     <row r="373" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5408,7 +6881,10 @@
       <c r="E373" s="24"/>
       <c r="F373" s="24"/>
       <c r="G373" s="17"/>
-      <c r="H373" s="20"/>
+      <c r="H373" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E373,'Project Tracker'!$F373)&lt;&gt;2,"",DAYS360('Project Tracker'!$E373,'Project Tracker'!$F373,FALSE))</f>
+        <v/>
+      </c>
       <c r="I373" s="17"/>
     </row>
     <row r="374" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5418,7 +6894,10 @@
       <c r="E374" s="24"/>
       <c r="F374" s="24"/>
       <c r="G374" s="17"/>
-      <c r="H374" s="20"/>
+      <c r="H374" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E374,'Project Tracker'!$F374)&lt;&gt;2,"",DAYS360('Project Tracker'!$E374,'Project Tracker'!$F374,FALSE))</f>
+        <v/>
+      </c>
       <c r="I374" s="17"/>
     </row>
     <row r="375" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5428,7 +6907,10 @@
       <c r="E375" s="24"/>
       <c r="F375" s="24"/>
       <c r="G375" s="17"/>
-      <c r="H375" s="20"/>
+      <c r="H375" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E375,'Project Tracker'!$F375)&lt;&gt;2,"",DAYS360('Project Tracker'!$E375,'Project Tracker'!$F375,FALSE))</f>
+        <v/>
+      </c>
       <c r="I375" s="17"/>
     </row>
     <row r="376" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5438,7 +6920,10 @@
       <c r="E376" s="24"/>
       <c r="F376" s="24"/>
       <c r="G376" s="17"/>
-      <c r="H376" s="20"/>
+      <c r="H376" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E376,'Project Tracker'!$F376)&lt;&gt;2,"",DAYS360('Project Tracker'!$E376,'Project Tracker'!$F376,FALSE))</f>
+        <v/>
+      </c>
       <c r="I376" s="17"/>
     </row>
     <row r="377" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5448,7 +6933,10 @@
       <c r="E377" s="24"/>
       <c r="F377" s="24"/>
       <c r="G377" s="17"/>
-      <c r="H377" s="20"/>
+      <c r="H377" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E377,'Project Tracker'!$F377)&lt;&gt;2,"",DAYS360('Project Tracker'!$E377,'Project Tracker'!$F377,FALSE))</f>
+        <v/>
+      </c>
       <c r="I377" s="17"/>
     </row>
     <row r="378" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5458,7 +6946,10 @@
       <c r="E378" s="24"/>
       <c r="F378" s="24"/>
       <c r="G378" s="17"/>
-      <c r="H378" s="20"/>
+      <c r="H378" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E378,'Project Tracker'!$F378)&lt;&gt;2,"",DAYS360('Project Tracker'!$E378,'Project Tracker'!$F378,FALSE))</f>
+        <v/>
+      </c>
       <c r="I378" s="17"/>
     </row>
     <row r="379" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5468,7 +6959,10 @@
       <c r="E379" s="24"/>
       <c r="F379" s="24"/>
       <c r="G379" s="17"/>
-      <c r="H379" s="20"/>
+      <c r="H379" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E379,'Project Tracker'!$F379)&lt;&gt;2,"",DAYS360('Project Tracker'!$E379,'Project Tracker'!$F379,FALSE))</f>
+        <v/>
+      </c>
       <c r="I379" s="17"/>
     </row>
     <row r="380" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5478,7 +6972,10 @@
       <c r="E380" s="24"/>
       <c r="F380" s="24"/>
       <c r="G380" s="17"/>
-      <c r="H380" s="20"/>
+      <c r="H380" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E380,'Project Tracker'!$F380)&lt;&gt;2,"",DAYS360('Project Tracker'!$E380,'Project Tracker'!$F380,FALSE))</f>
+        <v/>
+      </c>
       <c r="I380" s="17"/>
     </row>
     <row r="381" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5488,7 +6985,10 @@
       <c r="E381" s="24"/>
       <c r="F381" s="24"/>
       <c r="G381" s="17"/>
-      <c r="H381" s="20"/>
+      <c r="H381" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E381,'Project Tracker'!$F381)&lt;&gt;2,"",DAYS360('Project Tracker'!$E381,'Project Tracker'!$F381,FALSE))</f>
+        <v/>
+      </c>
       <c r="I381" s="17"/>
     </row>
     <row r="382" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5498,7 +6998,10 @@
       <c r="E382" s="24"/>
       <c r="F382" s="24"/>
       <c r="G382" s="17"/>
-      <c r="H382" s="20"/>
+      <c r="H382" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E382,'Project Tracker'!$F382)&lt;&gt;2,"",DAYS360('Project Tracker'!$E382,'Project Tracker'!$F382,FALSE))</f>
+        <v/>
+      </c>
       <c r="I382" s="17"/>
     </row>
     <row r="383" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5508,7 +7011,10 @@
       <c r="E383" s="24"/>
       <c r="F383" s="24"/>
       <c r="G383" s="17"/>
-      <c r="H383" s="20"/>
+      <c r="H383" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E383,'Project Tracker'!$F383)&lt;&gt;2,"",DAYS360('Project Tracker'!$E383,'Project Tracker'!$F383,FALSE))</f>
+        <v/>
+      </c>
       <c r="I383" s="17"/>
     </row>
     <row r="384" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5518,7 +7024,10 @@
       <c r="E384" s="24"/>
       <c r="F384" s="24"/>
       <c r="G384" s="17"/>
-      <c r="H384" s="20"/>
+      <c r="H384" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E384,'Project Tracker'!$F384)&lt;&gt;2,"",DAYS360('Project Tracker'!$E384,'Project Tracker'!$F384,FALSE))</f>
+        <v/>
+      </c>
       <c r="I384" s="17"/>
     </row>
     <row r="385" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5528,7 +7037,10 @@
       <c r="E385" s="24"/>
       <c r="F385" s="24"/>
       <c r="G385" s="17"/>
-      <c r="H385" s="20"/>
+      <c r="H385" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E385,'Project Tracker'!$F385)&lt;&gt;2,"",DAYS360('Project Tracker'!$E385,'Project Tracker'!$F385,FALSE))</f>
+        <v/>
+      </c>
       <c r="I385" s="17"/>
     </row>
     <row r="386" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5538,7 +7050,10 @@
       <c r="E386" s="24"/>
       <c r="F386" s="24"/>
       <c r="G386" s="17"/>
-      <c r="H386" s="20"/>
+      <c r="H386" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E386,'Project Tracker'!$F386)&lt;&gt;2,"",DAYS360('Project Tracker'!$E386,'Project Tracker'!$F386,FALSE))</f>
+        <v/>
+      </c>
       <c r="I386" s="17"/>
     </row>
     <row r="387" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5548,7 +7063,10 @@
       <c r="E387" s="24"/>
       <c r="F387" s="24"/>
       <c r="G387" s="17"/>
-      <c r="H387" s="20"/>
+      <c r="H387" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E387,'Project Tracker'!$F387)&lt;&gt;2,"",DAYS360('Project Tracker'!$E387,'Project Tracker'!$F387,FALSE))</f>
+        <v/>
+      </c>
       <c r="I387" s="17"/>
     </row>
     <row r="388" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5558,7 +7076,10 @@
       <c r="E388" s="24"/>
       <c r="F388" s="24"/>
       <c r="G388" s="17"/>
-      <c r="H388" s="20"/>
+      <c r="H388" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E388,'Project Tracker'!$F388)&lt;&gt;2,"",DAYS360('Project Tracker'!$E388,'Project Tracker'!$F388,FALSE))</f>
+        <v/>
+      </c>
       <c r="I388" s="17"/>
     </row>
     <row r="389" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5568,7 +7089,10 @@
       <c r="E389" s="24"/>
       <c r="F389" s="24"/>
       <c r="G389" s="17"/>
-      <c r="H389" s="20"/>
+      <c r="H389" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E389,'Project Tracker'!$F389)&lt;&gt;2,"",DAYS360('Project Tracker'!$E389,'Project Tracker'!$F389,FALSE))</f>
+        <v/>
+      </c>
       <c r="I389" s="17"/>
     </row>
     <row r="390" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5578,7 +7102,10 @@
       <c r="E390" s="24"/>
       <c r="F390" s="24"/>
       <c r="G390" s="17"/>
-      <c r="H390" s="20"/>
+      <c r="H390" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E390,'Project Tracker'!$F390)&lt;&gt;2,"",DAYS360('Project Tracker'!$E390,'Project Tracker'!$F390,FALSE))</f>
+        <v/>
+      </c>
       <c r="I390" s="17"/>
     </row>
     <row r="391" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5588,7 +7115,10 @@
       <c r="E391" s="24"/>
       <c r="F391" s="24"/>
       <c r="G391" s="17"/>
-      <c r="H391" s="20"/>
+      <c r="H391" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E391,'Project Tracker'!$F391)&lt;&gt;2,"",DAYS360('Project Tracker'!$E391,'Project Tracker'!$F391,FALSE))</f>
+        <v/>
+      </c>
       <c r="I391" s="17"/>
     </row>
     <row r="392" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5598,7 +7128,10 @@
       <c r="E392" s="24"/>
       <c r="F392" s="24"/>
       <c r="G392" s="17"/>
-      <c r="H392" s="20"/>
+      <c r="H392" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E392,'Project Tracker'!$F392)&lt;&gt;2,"",DAYS360('Project Tracker'!$E392,'Project Tracker'!$F392,FALSE))</f>
+        <v/>
+      </c>
       <c r="I392" s="17"/>
     </row>
     <row r="393" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5608,7 +7141,10 @@
       <c r="E393" s="24"/>
       <c r="F393" s="24"/>
       <c r="G393" s="17"/>
-      <c r="H393" s="20"/>
+      <c r="H393" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E393,'Project Tracker'!$F393)&lt;&gt;2,"",DAYS360('Project Tracker'!$E393,'Project Tracker'!$F393,FALSE))</f>
+        <v/>
+      </c>
       <c r="I393" s="17"/>
     </row>
     <row r="394" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5618,7 +7154,10 @@
       <c r="E394" s="24"/>
       <c r="F394" s="24"/>
       <c r="G394" s="17"/>
-      <c r="H394" s="20"/>
+      <c r="H394" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E394,'Project Tracker'!$F394)&lt;&gt;2,"",DAYS360('Project Tracker'!$E394,'Project Tracker'!$F394,FALSE))</f>
+        <v/>
+      </c>
       <c r="I394" s="17"/>
     </row>
     <row r="395" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5628,7 +7167,10 @@
       <c r="E395" s="24"/>
       <c r="F395" s="24"/>
       <c r="G395" s="17"/>
-      <c r="H395" s="20"/>
+      <c r="H395" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E395,'Project Tracker'!$F395)&lt;&gt;2,"",DAYS360('Project Tracker'!$E395,'Project Tracker'!$F395,FALSE))</f>
+        <v/>
+      </c>
       <c r="I395" s="17"/>
     </row>
     <row r="396" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5638,7 +7180,10 @@
       <c r="E396" s="24"/>
       <c r="F396" s="24"/>
       <c r="G396" s="17"/>
-      <c r="H396" s="20"/>
+      <c r="H396" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E396,'Project Tracker'!$F396)&lt;&gt;2,"",DAYS360('Project Tracker'!$E396,'Project Tracker'!$F396,FALSE))</f>
+        <v/>
+      </c>
       <c r="I396" s="17"/>
     </row>
     <row r="397" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5648,7 +7193,10 @@
       <c r="E397" s="24"/>
       <c r="F397" s="24"/>
       <c r="G397" s="17"/>
-      <c r="H397" s="20"/>
+      <c r="H397" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E397,'Project Tracker'!$F397)&lt;&gt;2,"",DAYS360('Project Tracker'!$E397,'Project Tracker'!$F397,FALSE))</f>
+        <v/>
+      </c>
       <c r="I397" s="17"/>
     </row>
     <row r="398" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5658,7 +7206,10 @@
       <c r="E398" s="24"/>
       <c r="F398" s="24"/>
       <c r="G398" s="17"/>
-      <c r="H398" s="20"/>
+      <c r="H398" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E398,'Project Tracker'!$F398)&lt;&gt;2,"",DAYS360('Project Tracker'!$E398,'Project Tracker'!$F398,FALSE))</f>
+        <v/>
+      </c>
       <c r="I398" s="17"/>
     </row>
     <row r="399" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5668,7 +7219,10 @@
       <c r="E399" s="24"/>
       <c r="F399" s="24"/>
       <c r="G399" s="17"/>
-      <c r="H399" s="20"/>
+      <c r="H399" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E399,'Project Tracker'!$F399)&lt;&gt;2,"",DAYS360('Project Tracker'!$E399,'Project Tracker'!$F399,FALSE))</f>
+        <v/>
+      </c>
       <c r="I399" s="17"/>
     </row>
     <row r="400" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5678,7 +7232,10 @@
       <c r="E400" s="24"/>
       <c r="F400" s="24"/>
       <c r="G400" s="17"/>
-      <c r="H400" s="20"/>
+      <c r="H400" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E400,'Project Tracker'!$F400)&lt;&gt;2,"",DAYS360('Project Tracker'!$E400,'Project Tracker'!$F400,FALSE))</f>
+        <v/>
+      </c>
       <c r="I400" s="17"/>
     </row>
     <row r="401" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5688,7 +7245,10 @@
       <c r="E401" s="24"/>
       <c r="F401" s="24"/>
       <c r="G401" s="17"/>
-      <c r="H401" s="20"/>
+      <c r="H401" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E401,'Project Tracker'!$F401)&lt;&gt;2,"",DAYS360('Project Tracker'!$E401,'Project Tracker'!$F401,FALSE))</f>
+        <v/>
+      </c>
       <c r="I401" s="17"/>
     </row>
     <row r="402" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5698,7 +7258,10 @@
       <c r="E402" s="24"/>
       <c r="F402" s="24"/>
       <c r="G402" s="17"/>
-      <c r="H402" s="20"/>
+      <c r="H402" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E402,'Project Tracker'!$F402)&lt;&gt;2,"",DAYS360('Project Tracker'!$E402,'Project Tracker'!$F402,FALSE))</f>
+        <v/>
+      </c>
       <c r="I402" s="17"/>
     </row>
     <row r="403" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5708,7 +7271,10 @@
       <c r="E403" s="24"/>
       <c r="F403" s="24"/>
       <c r="G403" s="17"/>
-      <c r="H403" s="20"/>
+      <c r="H403" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E403,'Project Tracker'!$F403)&lt;&gt;2,"",DAYS360('Project Tracker'!$E403,'Project Tracker'!$F403,FALSE))</f>
+        <v/>
+      </c>
       <c r="I403" s="17"/>
     </row>
     <row r="404" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5718,7 +7284,10 @@
       <c r="E404" s="24"/>
       <c r="F404" s="24"/>
       <c r="G404" s="17"/>
-      <c r="H404" s="20"/>
+      <c r="H404" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E404,'Project Tracker'!$F404)&lt;&gt;2,"",DAYS360('Project Tracker'!$E404,'Project Tracker'!$F404,FALSE))</f>
+        <v/>
+      </c>
       <c r="I404" s="17"/>
     </row>
     <row r="405" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5728,7 +7297,10 @@
       <c r="E405" s="24"/>
       <c r="F405" s="24"/>
       <c r="G405" s="17"/>
-      <c r="H405" s="20"/>
+      <c r="H405" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E405,'Project Tracker'!$F405)&lt;&gt;2,"",DAYS360('Project Tracker'!$E405,'Project Tracker'!$F405,FALSE))</f>
+        <v/>
+      </c>
       <c r="I405" s="17"/>
     </row>
     <row r="406" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5738,7 +7310,10 @@
       <c r="E406" s="24"/>
       <c r="F406" s="24"/>
       <c r="G406" s="17"/>
-      <c r="H406" s="20"/>
+      <c r="H406" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E406,'Project Tracker'!$F406)&lt;&gt;2,"",DAYS360('Project Tracker'!$E406,'Project Tracker'!$F406,FALSE))</f>
+        <v/>
+      </c>
       <c r="I406" s="17"/>
     </row>
     <row r="407" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5748,7 +7323,10 @@
       <c r="E407" s="24"/>
       <c r="F407" s="24"/>
       <c r="G407" s="17"/>
-      <c r="H407" s="20"/>
+      <c r="H407" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E407,'Project Tracker'!$F407)&lt;&gt;2,"",DAYS360('Project Tracker'!$E407,'Project Tracker'!$F407,FALSE))</f>
+        <v/>
+      </c>
       <c r="I407" s="17"/>
     </row>
     <row r="408" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5758,7 +7336,10 @@
       <c r="E408" s="24"/>
       <c r="F408" s="24"/>
       <c r="G408" s="17"/>
-      <c r="H408" s="20"/>
+      <c r="H408" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E408,'Project Tracker'!$F408)&lt;&gt;2,"",DAYS360('Project Tracker'!$E408,'Project Tracker'!$F408,FALSE))</f>
+        <v/>
+      </c>
       <c r="I408" s="17"/>
     </row>
     <row r="409" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5768,7 +7349,10 @@
       <c r="E409" s="24"/>
       <c r="F409" s="24"/>
       <c r="G409" s="17"/>
-      <c r="H409" s="20"/>
+      <c r="H409" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E409,'Project Tracker'!$F409)&lt;&gt;2,"",DAYS360('Project Tracker'!$E409,'Project Tracker'!$F409,FALSE))</f>
+        <v/>
+      </c>
       <c r="I409" s="17"/>
     </row>
     <row r="410" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5778,7 +7362,10 @@
       <c r="E410" s="24"/>
       <c r="F410" s="24"/>
       <c r="G410" s="17"/>
-      <c r="H410" s="20"/>
+      <c r="H410" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E410,'Project Tracker'!$F410)&lt;&gt;2,"",DAYS360('Project Tracker'!$E410,'Project Tracker'!$F410,FALSE))</f>
+        <v/>
+      </c>
       <c r="I410" s="17"/>
     </row>
     <row r="411" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5788,7 +7375,10 @@
       <c r="E411" s="24"/>
       <c r="F411" s="24"/>
       <c r="G411" s="17"/>
-      <c r="H411" s="20"/>
+      <c r="H411" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E411,'Project Tracker'!$F411)&lt;&gt;2,"",DAYS360('Project Tracker'!$E411,'Project Tracker'!$F411,FALSE))</f>
+        <v/>
+      </c>
       <c r="I411" s="17"/>
     </row>
     <row r="412" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5798,7 +7388,10 @@
       <c r="E412" s="24"/>
       <c r="F412" s="24"/>
       <c r="G412" s="17"/>
-      <c r="H412" s="20"/>
+      <c r="H412" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E412,'Project Tracker'!$F412)&lt;&gt;2,"",DAYS360('Project Tracker'!$E412,'Project Tracker'!$F412,FALSE))</f>
+        <v/>
+      </c>
       <c r="I412" s="17"/>
     </row>
     <row r="413" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5808,7 +7401,10 @@
       <c r="E413" s="24"/>
       <c r="F413" s="24"/>
       <c r="G413" s="17"/>
-      <c r="H413" s="20"/>
+      <c r="H413" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E413,'Project Tracker'!$F413)&lt;&gt;2,"",DAYS360('Project Tracker'!$E413,'Project Tracker'!$F413,FALSE))</f>
+        <v/>
+      </c>
       <c r="I413" s="17"/>
     </row>
     <row r="414" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5818,7 +7414,10 @@
       <c r="E414" s="24"/>
       <c r="F414" s="24"/>
       <c r="G414" s="17"/>
-      <c r="H414" s="20"/>
+      <c r="H414" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E414,'Project Tracker'!$F414)&lt;&gt;2,"",DAYS360('Project Tracker'!$E414,'Project Tracker'!$F414,FALSE))</f>
+        <v/>
+      </c>
       <c r="I414" s="17"/>
     </row>
     <row r="415" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5828,7 +7427,10 @@
       <c r="E415" s="24"/>
       <c r="F415" s="24"/>
       <c r="G415" s="17"/>
-      <c r="H415" s="20"/>
+      <c r="H415" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E415,'Project Tracker'!$F415)&lt;&gt;2,"",DAYS360('Project Tracker'!$E415,'Project Tracker'!$F415,FALSE))</f>
+        <v/>
+      </c>
       <c r="I415" s="17"/>
     </row>
     <row r="416" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5838,7 +7440,10 @@
       <c r="E416" s="24"/>
       <c r="F416" s="24"/>
       <c r="G416" s="17"/>
-      <c r="H416" s="20"/>
+      <c r="H416" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E416,'Project Tracker'!$F416)&lt;&gt;2,"",DAYS360('Project Tracker'!$E416,'Project Tracker'!$F416,FALSE))</f>
+        <v/>
+      </c>
       <c r="I416" s="17"/>
     </row>
     <row r="417" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5848,7 +7453,10 @@
       <c r="E417" s="24"/>
       <c r="F417" s="24"/>
       <c r="G417" s="17"/>
-      <c r="H417" s="20"/>
+      <c r="H417" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E417,'Project Tracker'!$F417)&lt;&gt;2,"",DAYS360('Project Tracker'!$E417,'Project Tracker'!$F417,FALSE))</f>
+        <v/>
+      </c>
       <c r="I417" s="17"/>
     </row>
     <row r="418" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5858,7 +7466,10 @@
       <c r="E418" s="24"/>
       <c r="F418" s="24"/>
       <c r="G418" s="17"/>
-      <c r="H418" s="20"/>
+      <c r="H418" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E418,'Project Tracker'!$F418)&lt;&gt;2,"",DAYS360('Project Tracker'!$E418,'Project Tracker'!$F418,FALSE))</f>
+        <v/>
+      </c>
       <c r="I418" s="17"/>
     </row>
     <row r="419" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5868,7 +7479,10 @@
       <c r="E419" s="24"/>
       <c r="F419" s="24"/>
       <c r="G419" s="17"/>
-      <c r="H419" s="20"/>
+      <c r="H419" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E419,'Project Tracker'!$F419)&lt;&gt;2,"",DAYS360('Project Tracker'!$E419,'Project Tracker'!$F419,FALSE))</f>
+        <v/>
+      </c>
       <c r="I419" s="17"/>
     </row>
     <row r="420" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5878,7 +7492,10 @@
       <c r="E420" s="24"/>
       <c r="F420" s="24"/>
       <c r="G420" s="17"/>
-      <c r="H420" s="20"/>
+      <c r="H420" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E420,'Project Tracker'!$F420)&lt;&gt;2,"",DAYS360('Project Tracker'!$E420,'Project Tracker'!$F420,FALSE))</f>
+        <v/>
+      </c>
       <c r="I420" s="17"/>
     </row>
     <row r="421" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5888,7 +7505,10 @@
       <c r="E421" s="24"/>
       <c r="F421" s="24"/>
       <c r="G421" s="17"/>
-      <c r="H421" s="20"/>
+      <c r="H421" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E421,'Project Tracker'!$F421)&lt;&gt;2,"",DAYS360('Project Tracker'!$E421,'Project Tracker'!$F421,FALSE))</f>
+        <v/>
+      </c>
       <c r="I421" s="17"/>
     </row>
     <row r="422" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5898,7 +7518,10 @@
       <c r="E422" s="24"/>
       <c r="F422" s="24"/>
       <c r="G422" s="17"/>
-      <c r="H422" s="20"/>
+      <c r="H422" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E422,'Project Tracker'!$F422)&lt;&gt;2,"",DAYS360('Project Tracker'!$E422,'Project Tracker'!$F422,FALSE))</f>
+        <v/>
+      </c>
       <c r="I422" s="17"/>
     </row>
     <row r="423" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5908,7 +7531,10 @@
       <c r="E423" s="24"/>
       <c r="F423" s="24"/>
       <c r="G423" s="17"/>
-      <c r="H423" s="20"/>
+      <c r="H423" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E423,'Project Tracker'!$F423)&lt;&gt;2,"",DAYS360('Project Tracker'!$E423,'Project Tracker'!$F423,FALSE))</f>
+        <v/>
+      </c>
       <c r="I423" s="17"/>
     </row>
     <row r="424" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5918,7 +7544,10 @@
       <c r="E424" s="24"/>
       <c r="F424" s="24"/>
       <c r="G424" s="17"/>
-      <c r="H424" s="20"/>
+      <c r="H424" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E424,'Project Tracker'!$F424)&lt;&gt;2,"",DAYS360('Project Tracker'!$E424,'Project Tracker'!$F424,FALSE))</f>
+        <v/>
+      </c>
       <c r="I424" s="17"/>
     </row>
     <row r="425" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5928,7 +7557,10 @@
       <c r="E425" s="24"/>
       <c r="F425" s="24"/>
       <c r="G425" s="17"/>
-      <c r="H425" s="20"/>
+      <c r="H425" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E425,'Project Tracker'!$F425)&lt;&gt;2,"",DAYS360('Project Tracker'!$E425,'Project Tracker'!$F425,FALSE))</f>
+        <v/>
+      </c>
       <c r="I425" s="17"/>
     </row>
     <row r="426" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5938,7 +7570,10 @@
       <c r="E426" s="24"/>
       <c r="F426" s="24"/>
       <c r="G426" s="17"/>
-      <c r="H426" s="20"/>
+      <c r="H426" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E426,'Project Tracker'!$F426)&lt;&gt;2,"",DAYS360('Project Tracker'!$E426,'Project Tracker'!$F426,FALSE))</f>
+        <v/>
+      </c>
       <c r="I426" s="17"/>
     </row>
     <row r="427" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5948,7 +7583,10 @@
       <c r="E427" s="24"/>
       <c r="F427" s="24"/>
       <c r="G427" s="17"/>
-      <c r="H427" s="20"/>
+      <c r="H427" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E427,'Project Tracker'!$F427)&lt;&gt;2,"",DAYS360('Project Tracker'!$E427,'Project Tracker'!$F427,FALSE))</f>
+        <v/>
+      </c>
       <c r="I427" s="17"/>
     </row>
     <row r="428" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5958,7 +7596,10 @@
       <c r="E428" s="24"/>
       <c r="F428" s="24"/>
       <c r="G428" s="17"/>
-      <c r="H428" s="20"/>
+      <c r="H428" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E428,'Project Tracker'!$F428)&lt;&gt;2,"",DAYS360('Project Tracker'!$E428,'Project Tracker'!$F428,FALSE))</f>
+        <v/>
+      </c>
       <c r="I428" s="17"/>
     </row>
     <row r="429" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5968,7 +7609,10 @@
       <c r="E429" s="24"/>
       <c r="F429" s="24"/>
       <c r="G429" s="17"/>
-      <c r="H429" s="20"/>
+      <c r="H429" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E429,'Project Tracker'!$F429)&lt;&gt;2,"",DAYS360('Project Tracker'!$E429,'Project Tracker'!$F429,FALSE))</f>
+        <v/>
+      </c>
       <c r="I429" s="17"/>
     </row>
     <row r="430" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5978,7 +7622,10 @@
       <c r="E430" s="24"/>
       <c r="F430" s="24"/>
       <c r="G430" s="17"/>
-      <c r="H430" s="20"/>
+      <c r="H430" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E430,'Project Tracker'!$F430)&lt;&gt;2,"",DAYS360('Project Tracker'!$E430,'Project Tracker'!$F430,FALSE))</f>
+        <v/>
+      </c>
       <c r="I430" s="17"/>
     </row>
     <row r="431" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5988,7 +7635,10 @@
       <c r="E431" s="24"/>
       <c r="F431" s="24"/>
       <c r="G431" s="17"/>
-      <c r="H431" s="20"/>
+      <c r="H431" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E431,'Project Tracker'!$F431)&lt;&gt;2,"",DAYS360('Project Tracker'!$E431,'Project Tracker'!$F431,FALSE))</f>
+        <v/>
+      </c>
       <c r="I431" s="17"/>
     </row>
     <row r="432" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5998,7 +7648,10 @@
       <c r="E432" s="24"/>
       <c r="F432" s="24"/>
       <c r="G432" s="17"/>
-      <c r="H432" s="20"/>
+      <c r="H432" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E432,'Project Tracker'!$F432)&lt;&gt;2,"",DAYS360('Project Tracker'!$E432,'Project Tracker'!$F432,FALSE))</f>
+        <v/>
+      </c>
       <c r="I432" s="17"/>
     </row>
     <row r="433" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6008,7 +7661,10 @@
       <c r="E433" s="24"/>
       <c r="F433" s="24"/>
       <c r="G433" s="17"/>
-      <c r="H433" s="20"/>
+      <c r="H433" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E433,'Project Tracker'!$F433)&lt;&gt;2,"",DAYS360('Project Tracker'!$E433,'Project Tracker'!$F433,FALSE))</f>
+        <v/>
+      </c>
       <c r="I433" s="17"/>
     </row>
     <row r="434" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6018,7 +7674,10 @@
       <c r="E434" s="24"/>
       <c r="F434" s="24"/>
       <c r="G434" s="17"/>
-      <c r="H434" s="20"/>
+      <c r="H434" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E434,'Project Tracker'!$F434)&lt;&gt;2,"",DAYS360('Project Tracker'!$E434,'Project Tracker'!$F434,FALSE))</f>
+        <v/>
+      </c>
       <c r="I434" s="17"/>
     </row>
     <row r="435" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6028,7 +7687,10 @@
       <c r="E435" s="24"/>
       <c r="F435" s="24"/>
       <c r="G435" s="17"/>
-      <c r="H435" s="20"/>
+      <c r="H435" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E435,'Project Tracker'!$F435)&lt;&gt;2,"",DAYS360('Project Tracker'!$E435,'Project Tracker'!$F435,FALSE))</f>
+        <v/>
+      </c>
       <c r="I435" s="17"/>
     </row>
     <row r="436" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6038,7 +7700,10 @@
       <c r="E436" s="24"/>
       <c r="F436" s="24"/>
       <c r="G436" s="17"/>
-      <c r="H436" s="20"/>
+      <c r="H436" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E436,'Project Tracker'!$F436)&lt;&gt;2,"",DAYS360('Project Tracker'!$E436,'Project Tracker'!$F436,FALSE))</f>
+        <v/>
+      </c>
       <c r="I436" s="17"/>
     </row>
     <row r="437" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6048,7 +7713,10 @@
       <c r="E437" s="24"/>
       <c r="F437" s="24"/>
       <c r="G437" s="17"/>
-      <c r="H437" s="20"/>
+      <c r="H437" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E437,'Project Tracker'!$F437)&lt;&gt;2,"",DAYS360('Project Tracker'!$E437,'Project Tracker'!$F437,FALSE))</f>
+        <v/>
+      </c>
       <c r="I437" s="17"/>
     </row>
     <row r="438" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6058,7 +7726,10 @@
       <c r="E438" s="24"/>
       <c r="F438" s="24"/>
       <c r="G438" s="17"/>
-      <c r="H438" s="20"/>
+      <c r="H438" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E438,'Project Tracker'!$F438)&lt;&gt;2,"",DAYS360('Project Tracker'!$E438,'Project Tracker'!$F438,FALSE))</f>
+        <v/>
+      </c>
       <c r="I438" s="17"/>
     </row>
     <row r="439" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6068,7 +7739,10 @@
       <c r="E439" s="24"/>
       <c r="F439" s="24"/>
       <c r="G439" s="17"/>
-      <c r="H439" s="20"/>
+      <c r="H439" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E439,'Project Tracker'!$F439)&lt;&gt;2,"",DAYS360('Project Tracker'!$E439,'Project Tracker'!$F439,FALSE))</f>
+        <v/>
+      </c>
       <c r="I439" s="17"/>
     </row>
     <row r="440" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6078,7 +7752,10 @@
       <c r="E440" s="24"/>
       <c r="F440" s="24"/>
       <c r="G440" s="17"/>
-      <c r="H440" s="20"/>
+      <c r="H440" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E440,'Project Tracker'!$F440)&lt;&gt;2,"",DAYS360('Project Tracker'!$E440,'Project Tracker'!$F440,FALSE))</f>
+        <v/>
+      </c>
       <c r="I440" s="17"/>
     </row>
     <row r="441" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6088,7 +7765,10 @@
       <c r="E441" s="24"/>
       <c r="F441" s="24"/>
       <c r="G441" s="17"/>
-      <c r="H441" s="20"/>
+      <c r="H441" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E441,'Project Tracker'!$F441)&lt;&gt;2,"",DAYS360('Project Tracker'!$E441,'Project Tracker'!$F441,FALSE))</f>
+        <v/>
+      </c>
       <c r="I441" s="17"/>
     </row>
     <row r="442" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6098,7 +7778,10 @@
       <c r="E442" s="24"/>
       <c r="F442" s="24"/>
       <c r="G442" s="17"/>
-      <c r="H442" s="20"/>
+      <c r="H442" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E442,'Project Tracker'!$F442)&lt;&gt;2,"",DAYS360('Project Tracker'!$E442,'Project Tracker'!$F442,FALSE))</f>
+        <v/>
+      </c>
       <c r="I442" s="17"/>
     </row>
     <row r="443" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6108,7 +7791,10 @@
       <c r="E443" s="24"/>
       <c r="F443" s="24"/>
       <c r="G443" s="17"/>
-      <c r="H443" s="20"/>
+      <c r="H443" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E443,'Project Tracker'!$F443)&lt;&gt;2,"",DAYS360('Project Tracker'!$E443,'Project Tracker'!$F443,FALSE))</f>
+        <v/>
+      </c>
       <c r="I443" s="17"/>
     </row>
     <row r="444" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6118,7 +7804,10 @@
       <c r="E444" s="24"/>
       <c r="F444" s="24"/>
       <c r="G444" s="17"/>
-      <c r="H444" s="20"/>
+      <c r="H444" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E444,'Project Tracker'!$F444)&lt;&gt;2,"",DAYS360('Project Tracker'!$E444,'Project Tracker'!$F444,FALSE))</f>
+        <v/>
+      </c>
       <c r="I444" s="17"/>
     </row>
     <row r="445" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6128,7 +7817,10 @@
       <c r="E445" s="24"/>
       <c r="F445" s="24"/>
       <c r="G445" s="17"/>
-      <c r="H445" s="20"/>
+      <c r="H445" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E445,'Project Tracker'!$F445)&lt;&gt;2,"",DAYS360('Project Tracker'!$E445,'Project Tracker'!$F445,FALSE))</f>
+        <v/>
+      </c>
       <c r="I445" s="17"/>
     </row>
     <row r="446" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6138,7 +7830,10 @@
       <c r="E446" s="24"/>
       <c r="F446" s="24"/>
       <c r="G446" s="17"/>
-      <c r="H446" s="20"/>
+      <c r="H446" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E446,'Project Tracker'!$F446)&lt;&gt;2,"",DAYS360('Project Tracker'!$E446,'Project Tracker'!$F446,FALSE))</f>
+        <v/>
+      </c>
       <c r="I446" s="17"/>
     </row>
     <row r="447" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6148,7 +7843,10 @@
       <c r="E447" s="24"/>
       <c r="F447" s="24"/>
       <c r="G447" s="17"/>
-      <c r="H447" s="20"/>
+      <c r="H447" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E447,'Project Tracker'!$F447)&lt;&gt;2,"",DAYS360('Project Tracker'!$E447,'Project Tracker'!$F447,FALSE))</f>
+        <v/>
+      </c>
       <c r="I447" s="17"/>
     </row>
     <row r="448" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6158,7 +7856,10 @@
       <c r="E448" s="24"/>
       <c r="F448" s="24"/>
       <c r="G448" s="17"/>
-      <c r="H448" s="20"/>
+      <c r="H448" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E448,'Project Tracker'!$F448)&lt;&gt;2,"",DAYS360('Project Tracker'!$E448,'Project Tracker'!$F448,FALSE))</f>
+        <v/>
+      </c>
       <c r="I448" s="17"/>
     </row>
     <row r="449" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6168,7 +7869,10 @@
       <c r="E449" s="24"/>
       <c r="F449" s="24"/>
       <c r="G449" s="17"/>
-      <c r="H449" s="20"/>
+      <c r="H449" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E449,'Project Tracker'!$F449)&lt;&gt;2,"",DAYS360('Project Tracker'!$E449,'Project Tracker'!$F449,FALSE))</f>
+        <v/>
+      </c>
       <c r="I449" s="17"/>
     </row>
     <row r="450" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6178,7 +7882,10 @@
       <c r="E450" s="24"/>
       <c r="F450" s="24"/>
       <c r="G450" s="17"/>
-      <c r="H450" s="20"/>
+      <c r="H450" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E450,'Project Tracker'!$F450)&lt;&gt;2,"",DAYS360('Project Tracker'!$E450,'Project Tracker'!$F450,FALSE))</f>
+        <v/>
+      </c>
       <c r="I450" s="17"/>
     </row>
     <row r="451" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6188,7 +7895,10 @@
       <c r="E451" s="24"/>
       <c r="F451" s="24"/>
       <c r="G451" s="17"/>
-      <c r="H451" s="20"/>
+      <c r="H451" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E451,'Project Tracker'!$F451)&lt;&gt;2,"",DAYS360('Project Tracker'!$E451,'Project Tracker'!$F451,FALSE))</f>
+        <v/>
+      </c>
       <c r="I451" s="17"/>
     </row>
     <row r="452" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6198,7 +7908,10 @@
       <c r="E452" s="24"/>
       <c r="F452" s="24"/>
       <c r="G452" s="17"/>
-      <c r="H452" s="20"/>
+      <c r="H452" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E452,'Project Tracker'!$F452)&lt;&gt;2,"",DAYS360('Project Tracker'!$E452,'Project Tracker'!$F452,FALSE))</f>
+        <v/>
+      </c>
       <c r="I452" s="17"/>
     </row>
     <row r="453" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6208,7 +7921,10 @@
       <c r="E453" s="24"/>
       <c r="F453" s="24"/>
       <c r="G453" s="17"/>
-      <c r="H453" s="20"/>
+      <c r="H453" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E453,'Project Tracker'!$F453)&lt;&gt;2,"",DAYS360('Project Tracker'!$E453,'Project Tracker'!$F453,FALSE))</f>
+        <v/>
+      </c>
       <c r="I453" s="17"/>
     </row>
     <row r="454" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6218,7 +7934,10 @@
       <c r="E454" s="24"/>
       <c r="F454" s="24"/>
       <c r="G454" s="17"/>
-      <c r="H454" s="20"/>
+      <c r="H454" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E454,'Project Tracker'!$F454)&lt;&gt;2,"",DAYS360('Project Tracker'!$E454,'Project Tracker'!$F454,FALSE))</f>
+        <v/>
+      </c>
       <c r="I454" s="17"/>
     </row>
     <row r="455" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6228,7 +7947,10 @@
       <c r="E455" s="24"/>
       <c r="F455" s="24"/>
       <c r="G455" s="17"/>
-      <c r="H455" s="20"/>
+      <c r="H455" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E455,'Project Tracker'!$F455)&lt;&gt;2,"",DAYS360('Project Tracker'!$E455,'Project Tracker'!$F455,FALSE))</f>
+        <v/>
+      </c>
       <c r="I455" s="17"/>
     </row>
     <row r="456" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6238,7 +7960,10 @@
       <c r="E456" s="24"/>
       <c r="F456" s="24"/>
       <c r="G456" s="17"/>
-      <c r="H456" s="20"/>
+      <c r="H456" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E456,'Project Tracker'!$F456)&lt;&gt;2,"",DAYS360('Project Tracker'!$E456,'Project Tracker'!$F456,FALSE))</f>
+        <v/>
+      </c>
       <c r="I456" s="17"/>
     </row>
     <row r="457" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6248,7 +7973,10 @@
       <c r="E457" s="24"/>
       <c r="F457" s="24"/>
       <c r="G457" s="17"/>
-      <c r="H457" s="20"/>
+      <c r="H457" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E457,'Project Tracker'!$F457)&lt;&gt;2,"",DAYS360('Project Tracker'!$E457,'Project Tracker'!$F457,FALSE))</f>
+        <v/>
+      </c>
       <c r="I457" s="17"/>
     </row>
     <row r="458" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6258,7 +7986,10 @@
       <c r="E458" s="24"/>
       <c r="F458" s="24"/>
       <c r="G458" s="17"/>
-      <c r="H458" s="20"/>
+      <c r="H458" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E458,'Project Tracker'!$F458)&lt;&gt;2,"",DAYS360('Project Tracker'!$E458,'Project Tracker'!$F458,FALSE))</f>
+        <v/>
+      </c>
       <c r="I458" s="17"/>
     </row>
     <row r="459" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6268,7 +7999,10 @@
       <c r="E459" s="24"/>
       <c r="F459" s="24"/>
       <c r="G459" s="17"/>
-      <c r="H459" s="20"/>
+      <c r="H459" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E459,'Project Tracker'!$F459)&lt;&gt;2,"",DAYS360('Project Tracker'!$E459,'Project Tracker'!$F459,FALSE))</f>
+        <v/>
+      </c>
       <c r="I459" s="17"/>
     </row>
     <row r="460" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6278,7 +8012,10 @@
       <c r="E460" s="24"/>
       <c r="F460" s="24"/>
       <c r="G460" s="17"/>
-      <c r="H460" s="20"/>
+      <c r="H460" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E460,'Project Tracker'!$F460)&lt;&gt;2,"",DAYS360('Project Tracker'!$E460,'Project Tracker'!$F460,FALSE))</f>
+        <v/>
+      </c>
       <c r="I460" s="17"/>
     </row>
     <row r="461" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6288,7 +8025,10 @@
       <c r="E461" s="24"/>
       <c r="F461" s="24"/>
       <c r="G461" s="17"/>
-      <c r="H461" s="20"/>
+      <c r="H461" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E461,'Project Tracker'!$F461)&lt;&gt;2,"",DAYS360('Project Tracker'!$E461,'Project Tracker'!$F461,FALSE))</f>
+        <v/>
+      </c>
       <c r="I461" s="17"/>
     </row>
     <row r="462" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6298,7 +8038,10 @@
       <c r="E462" s="24"/>
       <c r="F462" s="24"/>
       <c r="G462" s="17"/>
-      <c r="H462" s="20"/>
+      <c r="H462" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E462,'Project Tracker'!$F462)&lt;&gt;2,"",DAYS360('Project Tracker'!$E462,'Project Tracker'!$F462,FALSE))</f>
+        <v/>
+      </c>
       <c r="I462" s="17"/>
     </row>
     <row r="463" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6308,7 +8051,10 @@
       <c r="E463" s="24"/>
       <c r="F463" s="24"/>
       <c r="G463" s="17"/>
-      <c r="H463" s="20"/>
+      <c r="H463" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E463,'Project Tracker'!$F463)&lt;&gt;2,"",DAYS360('Project Tracker'!$E463,'Project Tracker'!$F463,FALSE))</f>
+        <v/>
+      </c>
       <c r="I463" s="17"/>
     </row>
     <row r="464" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6318,7 +8064,10 @@
       <c r="E464" s="24"/>
       <c r="F464" s="24"/>
       <c r="G464" s="17"/>
-      <c r="H464" s="20"/>
+      <c r="H464" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E464,'Project Tracker'!$F464)&lt;&gt;2,"",DAYS360('Project Tracker'!$E464,'Project Tracker'!$F464,FALSE))</f>
+        <v/>
+      </c>
       <c r="I464" s="17"/>
     </row>
     <row r="465" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6328,7 +8077,10 @@
       <c r="E465" s="24"/>
       <c r="F465" s="24"/>
       <c r="G465" s="17"/>
-      <c r="H465" s="20"/>
+      <c r="H465" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E465,'Project Tracker'!$F465)&lt;&gt;2,"",DAYS360('Project Tracker'!$E465,'Project Tracker'!$F465,FALSE))</f>
+        <v/>
+      </c>
       <c r="I465" s="17"/>
     </row>
     <row r="466" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6338,7 +8090,10 @@
       <c r="E466" s="24"/>
       <c r="F466" s="24"/>
       <c r="G466" s="17"/>
-      <c r="H466" s="20"/>
+      <c r="H466" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E466,'Project Tracker'!$F466)&lt;&gt;2,"",DAYS360('Project Tracker'!$E466,'Project Tracker'!$F466,FALSE))</f>
+        <v/>
+      </c>
       <c r="I466" s="17"/>
     </row>
     <row r="467" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6348,7 +8103,10 @@
       <c r="E467" s="24"/>
       <c r="F467" s="24"/>
       <c r="G467" s="17"/>
-      <c r="H467" s="20"/>
+      <c r="H467" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E467,'Project Tracker'!$F467)&lt;&gt;2,"",DAYS360('Project Tracker'!$E467,'Project Tracker'!$F467,FALSE))</f>
+        <v/>
+      </c>
       <c r="I467" s="17"/>
     </row>
     <row r="468" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6358,7 +8116,10 @@
       <c r="E468" s="24"/>
       <c r="F468" s="24"/>
       <c r="G468" s="17"/>
-      <c r="H468" s="20"/>
+      <c r="H468" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E468,'Project Tracker'!$F468)&lt;&gt;2,"",DAYS360('Project Tracker'!$E468,'Project Tracker'!$F468,FALSE))</f>
+        <v/>
+      </c>
       <c r="I468" s="17"/>
     </row>
     <row r="469" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6368,7 +8129,10 @@
       <c r="E469" s="24"/>
       <c r="F469" s="24"/>
       <c r="G469" s="17"/>
-      <c r="H469" s="20"/>
+      <c r="H469" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E469,'Project Tracker'!$F469)&lt;&gt;2,"",DAYS360('Project Tracker'!$E469,'Project Tracker'!$F469,FALSE))</f>
+        <v/>
+      </c>
       <c r="I469" s="17"/>
     </row>
     <row r="470" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6378,7 +8142,10 @@
       <c r="E470" s="24"/>
       <c r="F470" s="24"/>
       <c r="G470" s="17"/>
-      <c r="H470" s="20"/>
+      <c r="H470" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E470,'Project Tracker'!$F470)&lt;&gt;2,"",DAYS360('Project Tracker'!$E470,'Project Tracker'!$F470,FALSE))</f>
+        <v/>
+      </c>
       <c r="I470" s="17"/>
     </row>
     <row r="471" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6388,7 +8155,10 @@
       <c r="E471" s="24"/>
       <c r="F471" s="24"/>
       <c r="G471" s="17"/>
-      <c r="H471" s="20"/>
+      <c r="H471" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E471,'Project Tracker'!$F471)&lt;&gt;2,"",DAYS360('Project Tracker'!$E471,'Project Tracker'!$F471,FALSE))</f>
+        <v/>
+      </c>
       <c r="I471" s="17"/>
     </row>
     <row r="472" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6398,7 +8168,10 @@
       <c r="E472" s="24"/>
       <c r="F472" s="24"/>
       <c r="G472" s="17"/>
-      <c r="H472" s="20"/>
+      <c r="H472" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E472,'Project Tracker'!$F472)&lt;&gt;2,"",DAYS360('Project Tracker'!$E472,'Project Tracker'!$F472,FALSE))</f>
+        <v/>
+      </c>
       <c r="I472" s="17"/>
     </row>
     <row r="473" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6408,7 +8181,10 @@
       <c r="E473" s="24"/>
       <c r="F473" s="24"/>
       <c r="G473" s="17"/>
-      <c r="H473" s="20"/>
+      <c r="H473" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E473,'Project Tracker'!$F473)&lt;&gt;2,"",DAYS360('Project Tracker'!$E473,'Project Tracker'!$F473,FALSE))</f>
+        <v/>
+      </c>
       <c r="I473" s="17"/>
     </row>
     <row r="474" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6418,7 +8194,10 @@
       <c r="E474" s="24"/>
       <c r="F474" s="24"/>
       <c r="G474" s="17"/>
-      <c r="H474" s="20"/>
+      <c r="H474" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E474,'Project Tracker'!$F474)&lt;&gt;2,"",DAYS360('Project Tracker'!$E474,'Project Tracker'!$F474,FALSE))</f>
+        <v/>
+      </c>
       <c r="I474" s="17"/>
     </row>
     <row r="475" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6428,7 +8207,10 @@
       <c r="E475" s="24"/>
       <c r="F475" s="24"/>
       <c r="G475" s="17"/>
-      <c r="H475" s="20"/>
+      <c r="H475" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E475,'Project Tracker'!$F475)&lt;&gt;2,"",DAYS360('Project Tracker'!$E475,'Project Tracker'!$F475,FALSE))</f>
+        <v/>
+      </c>
       <c r="I475" s="17"/>
     </row>
     <row r="476" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6438,7 +8220,10 @@
       <c r="E476" s="24"/>
       <c r="F476" s="24"/>
       <c r="G476" s="17"/>
-      <c r="H476" s="20"/>
+      <c r="H476" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E476,'Project Tracker'!$F476)&lt;&gt;2,"",DAYS360('Project Tracker'!$E476,'Project Tracker'!$F476,FALSE))</f>
+        <v/>
+      </c>
       <c r="I476" s="17"/>
     </row>
     <row r="477" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6448,7 +8233,10 @@
       <c r="E477" s="24"/>
       <c r="F477" s="24"/>
       <c r="G477" s="17"/>
-      <c r="H477" s="20"/>
+      <c r="H477" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E477,'Project Tracker'!$F477)&lt;&gt;2,"",DAYS360('Project Tracker'!$E477,'Project Tracker'!$F477,FALSE))</f>
+        <v/>
+      </c>
       <c r="I477" s="17"/>
     </row>
     <row r="478" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6458,7 +8246,10 @@
       <c r="E478" s="24"/>
       <c r="F478" s="24"/>
       <c r="G478" s="17"/>
-      <c r="H478" s="20"/>
+      <c r="H478" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E478,'Project Tracker'!$F478)&lt;&gt;2,"",DAYS360('Project Tracker'!$E478,'Project Tracker'!$F478,FALSE))</f>
+        <v/>
+      </c>
       <c r="I478" s="17"/>
     </row>
     <row r="479" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6468,7 +8259,10 @@
       <c r="E479" s="24"/>
       <c r="F479" s="24"/>
       <c r="G479" s="17"/>
-      <c r="H479" s="20"/>
+      <c r="H479" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E479,'Project Tracker'!$F479)&lt;&gt;2,"",DAYS360('Project Tracker'!$E479,'Project Tracker'!$F479,FALSE))</f>
+        <v/>
+      </c>
       <c r="I479" s="17"/>
     </row>
     <row r="480" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6478,7 +8272,10 @@
       <c r="E480" s="24"/>
       <c r="F480" s="24"/>
       <c r="G480" s="17"/>
-      <c r="H480" s="20"/>
+      <c r="H480" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E480,'Project Tracker'!$F480)&lt;&gt;2,"",DAYS360('Project Tracker'!$E480,'Project Tracker'!$F480,FALSE))</f>
+        <v/>
+      </c>
       <c r="I480" s="17"/>
     </row>
     <row r="481" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6488,7 +8285,10 @@
       <c r="E481" s="24"/>
       <c r="F481" s="24"/>
       <c r="G481" s="17"/>
-      <c r="H481" s="20"/>
+      <c r="H481" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E481,'Project Tracker'!$F481)&lt;&gt;2,"",DAYS360('Project Tracker'!$E481,'Project Tracker'!$F481,FALSE))</f>
+        <v/>
+      </c>
       <c r="I481" s="17"/>
     </row>
     <row r="482" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6498,7 +8298,10 @@
       <c r="E482" s="24"/>
       <c r="F482" s="24"/>
       <c r="G482" s="17"/>
-      <c r="H482" s="20"/>
+      <c r="H482" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E482,'Project Tracker'!$F482)&lt;&gt;2,"",DAYS360('Project Tracker'!$E482,'Project Tracker'!$F482,FALSE))</f>
+        <v/>
+      </c>
       <c r="I482" s="17"/>
     </row>
     <row r="483" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6508,7 +8311,10 @@
       <c r="E483" s="24"/>
       <c r="F483" s="24"/>
       <c r="G483" s="17"/>
-      <c r="H483" s="20"/>
+      <c r="H483" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E483,'Project Tracker'!$F483)&lt;&gt;2,"",DAYS360('Project Tracker'!$E483,'Project Tracker'!$F483,FALSE))</f>
+        <v/>
+      </c>
       <c r="I483" s="17"/>
     </row>
     <row r="484" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6518,7 +8324,10 @@
       <c r="E484" s="24"/>
       <c r="F484" s="24"/>
       <c r="G484" s="17"/>
-      <c r="H484" s="20"/>
+      <c r="H484" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E484,'Project Tracker'!$F484)&lt;&gt;2,"",DAYS360('Project Tracker'!$E484,'Project Tracker'!$F484,FALSE))</f>
+        <v/>
+      </c>
       <c r="I484" s="17"/>
     </row>
     <row r="485" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6528,7 +8337,10 @@
       <c r="E485" s="24"/>
       <c r="F485" s="24"/>
       <c r="G485" s="17"/>
-      <c r="H485" s="20"/>
+      <c r="H485" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E485,'Project Tracker'!$F485)&lt;&gt;2,"",DAYS360('Project Tracker'!$E485,'Project Tracker'!$F485,FALSE))</f>
+        <v/>
+      </c>
       <c r="I485" s="17"/>
     </row>
     <row r="486" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6538,7 +8350,10 @@
       <c r="E486" s="24"/>
       <c r="F486" s="24"/>
       <c r="G486" s="17"/>
-      <c r="H486" s="20"/>
+      <c r="H486" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E486,'Project Tracker'!$F486)&lt;&gt;2,"",DAYS360('Project Tracker'!$E486,'Project Tracker'!$F486,FALSE))</f>
+        <v/>
+      </c>
       <c r="I486" s="17"/>
     </row>
     <row r="487" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6548,7 +8363,10 @@
       <c r="E487" s="24"/>
       <c r="F487" s="24"/>
       <c r="G487" s="17"/>
-      <c r="H487" s="20"/>
+      <c r="H487" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E487,'Project Tracker'!$F487)&lt;&gt;2,"",DAYS360('Project Tracker'!$E487,'Project Tracker'!$F487,FALSE))</f>
+        <v/>
+      </c>
       <c r="I487" s="17"/>
     </row>
     <row r="488" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6558,7 +8376,10 @@
       <c r="E488" s="24"/>
       <c r="F488" s="24"/>
       <c r="G488" s="17"/>
-      <c r="H488" s="20"/>
+      <c r="H488" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E488,'Project Tracker'!$F488)&lt;&gt;2,"",DAYS360('Project Tracker'!$E488,'Project Tracker'!$F488,FALSE))</f>
+        <v/>
+      </c>
       <c r="I488" s="17"/>
     </row>
     <row r="489" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6568,7 +8389,10 @@
       <c r="E489" s="24"/>
       <c r="F489" s="24"/>
       <c r="G489" s="17"/>
-      <c r="H489" s="20"/>
+      <c r="H489" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E489,'Project Tracker'!$F489)&lt;&gt;2,"",DAYS360('Project Tracker'!$E489,'Project Tracker'!$F489,FALSE))</f>
+        <v/>
+      </c>
       <c r="I489" s="17"/>
     </row>
     <row r="490" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6578,7 +8402,10 @@
       <c r="E490" s="24"/>
       <c r="F490" s="24"/>
       <c r="G490" s="17"/>
-      <c r="H490" s="20"/>
+      <c r="H490" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E490,'Project Tracker'!$F490)&lt;&gt;2,"",DAYS360('Project Tracker'!$E490,'Project Tracker'!$F490,FALSE))</f>
+        <v/>
+      </c>
       <c r="I490" s="17"/>
     </row>
     <row r="491" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6588,7 +8415,10 @@
       <c r="E491" s="24"/>
       <c r="F491" s="24"/>
       <c r="G491" s="17"/>
-      <c r="H491" s="20"/>
+      <c r="H491" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E491,'Project Tracker'!$F491)&lt;&gt;2,"",DAYS360('Project Tracker'!$E491,'Project Tracker'!$F491,FALSE))</f>
+        <v/>
+      </c>
       <c r="I491" s="17"/>
     </row>
     <row r="492" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6598,7 +8428,10 @@
       <c r="E492" s="24"/>
       <c r="F492" s="24"/>
       <c r="G492" s="17"/>
-      <c r="H492" s="20"/>
+      <c r="H492" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E492,'Project Tracker'!$F492)&lt;&gt;2,"",DAYS360('Project Tracker'!$E492,'Project Tracker'!$F492,FALSE))</f>
+        <v/>
+      </c>
       <c r="I492" s="17"/>
     </row>
     <row r="493" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6608,7 +8441,10 @@
       <c r="E493" s="24"/>
       <c r="F493" s="24"/>
       <c r="G493" s="17"/>
-      <c r="H493" s="20"/>
+      <c r="H493" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E493,'Project Tracker'!$F493)&lt;&gt;2,"",DAYS360('Project Tracker'!$E493,'Project Tracker'!$F493,FALSE))</f>
+        <v/>
+      </c>
       <c r="I493" s="17"/>
     </row>
     <row r="494" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6618,7 +8454,10 @@
       <c r="E494" s="24"/>
       <c r="F494" s="24"/>
       <c r="G494" s="17"/>
-      <c r="H494" s="20"/>
+      <c r="H494" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E494,'Project Tracker'!$F494)&lt;&gt;2,"",DAYS360('Project Tracker'!$E494,'Project Tracker'!$F494,FALSE))</f>
+        <v/>
+      </c>
       <c r="I494" s="17"/>
     </row>
     <row r="495" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6628,7 +8467,10 @@
       <c r="E495" s="24"/>
       <c r="F495" s="24"/>
       <c r="G495" s="17"/>
-      <c r="H495" s="20"/>
+      <c r="H495" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E495,'Project Tracker'!$F495)&lt;&gt;2,"",DAYS360('Project Tracker'!$E495,'Project Tracker'!$F495,FALSE))</f>
+        <v/>
+      </c>
       <c r="I495" s="17"/>
     </row>
     <row r="496" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6638,7 +8480,10 @@
       <c r="E496" s="24"/>
       <c r="F496" s="24"/>
       <c r="G496" s="17"/>
-      <c r="H496" s="20"/>
+      <c r="H496" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E496,'Project Tracker'!$F496)&lt;&gt;2,"",DAYS360('Project Tracker'!$E496,'Project Tracker'!$F496,FALSE))</f>
+        <v/>
+      </c>
       <c r="I496" s="17"/>
     </row>
     <row r="497" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6648,7 +8493,10 @@
       <c r="E497" s="24"/>
       <c r="F497" s="24"/>
       <c r="G497" s="17"/>
-      <c r="H497" s="20"/>
+      <c r="H497" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E497,'Project Tracker'!$F497)&lt;&gt;2,"",DAYS360('Project Tracker'!$E497,'Project Tracker'!$F497,FALSE))</f>
+        <v/>
+      </c>
       <c r="I497" s="17"/>
     </row>
     <row r="498" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6658,7 +8506,10 @@
       <c r="E498" s="24"/>
       <c r="F498" s="24"/>
       <c r="G498" s="17"/>
-      <c r="H498" s="20"/>
+      <c r="H498" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E498,'Project Tracker'!$F498)&lt;&gt;2,"",DAYS360('Project Tracker'!$E498,'Project Tracker'!$F498,FALSE))</f>
+        <v/>
+      </c>
       <c r="I498" s="17"/>
     </row>
     <row r="499" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6668,7 +8519,10 @@
       <c r="E499" s="24"/>
       <c r="F499" s="24"/>
       <c r="G499" s="17"/>
-      <c r="H499" s="20"/>
+      <c r="H499" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E499,'Project Tracker'!$F499)&lt;&gt;2,"",DAYS360('Project Tracker'!$E499,'Project Tracker'!$F499,FALSE))</f>
+        <v/>
+      </c>
       <c r="I499" s="17"/>
     </row>
     <row r="500" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6678,7 +8532,10 @@
       <c r="E500" s="24"/>
       <c r="F500" s="24"/>
       <c r="G500" s="17"/>
-      <c r="H500" s="20"/>
+      <c r="H500" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E500,'Project Tracker'!$F500)&lt;&gt;2,"",DAYS360('Project Tracker'!$E500,'Project Tracker'!$F500,FALSE))</f>
+        <v/>
+      </c>
       <c r="I500" s="17"/>
     </row>
     <row r="501" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6688,7 +8545,10 @@
       <c r="E501" s="24"/>
       <c r="F501" s="24"/>
       <c r="G501" s="17"/>
-      <c r="H501" s="20"/>
+      <c r="H501" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E501,'Project Tracker'!$F501)&lt;&gt;2,"",DAYS360('Project Tracker'!$E501,'Project Tracker'!$F501,FALSE))</f>
+        <v/>
+      </c>
       <c r="I501" s="17"/>
     </row>
     <row r="502" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6698,7 +8558,10 @@
       <c r="E502" s="24"/>
       <c r="F502" s="24"/>
       <c r="G502" s="17"/>
-      <c r="H502" s="20"/>
+      <c r="H502" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E502,'Project Tracker'!$F502)&lt;&gt;2,"",DAYS360('Project Tracker'!$E502,'Project Tracker'!$F502,FALSE))</f>
+        <v/>
+      </c>
       <c r="I502" s="17"/>
     </row>
     <row r="503" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6708,7 +8571,10 @@
       <c r="E503" s="24"/>
       <c r="F503" s="24"/>
       <c r="G503" s="17"/>
-      <c r="H503" s="20"/>
+      <c r="H503" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E503,'Project Tracker'!$F503)&lt;&gt;2,"",DAYS360('Project Tracker'!$E503,'Project Tracker'!$F503,FALSE))</f>
+        <v/>
+      </c>
       <c r="I503" s="17"/>
     </row>
     <row r="504" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6718,7 +8584,10 @@
       <c r="E504" s="24"/>
       <c r="F504" s="24"/>
       <c r="G504" s="17"/>
-      <c r="H504" s="20"/>
+      <c r="H504" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E504,'Project Tracker'!$F504)&lt;&gt;2,"",DAYS360('Project Tracker'!$E504,'Project Tracker'!$F504,FALSE))</f>
+        <v/>
+      </c>
       <c r="I504" s="17"/>
     </row>
     <row r="505" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6728,7 +8597,10 @@
       <c r="E505" s="24"/>
       <c r="F505" s="24"/>
       <c r="G505" s="17"/>
-      <c r="H505" s="20"/>
+      <c r="H505" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E505,'Project Tracker'!$F505)&lt;&gt;2,"",DAYS360('Project Tracker'!$E505,'Project Tracker'!$F505,FALSE))</f>
+        <v/>
+      </c>
       <c r="I505" s="17"/>
     </row>
     <row r="506" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6738,7 +8610,10 @@
       <c r="E506" s="24"/>
       <c r="F506" s="24"/>
       <c r="G506" s="17"/>
-      <c r="H506" s="20"/>
+      <c r="H506" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E506,'Project Tracker'!$F506)&lt;&gt;2,"",DAYS360('Project Tracker'!$E506,'Project Tracker'!$F506,FALSE))</f>
+        <v/>
+      </c>
       <c r="I506" s="17"/>
     </row>
     <row r="507" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6748,7 +8623,10 @@
       <c r="E507" s="24"/>
       <c r="F507" s="24"/>
       <c r="G507" s="17"/>
-      <c r="H507" s="20"/>
+      <c r="H507" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E507,'Project Tracker'!$F507)&lt;&gt;2,"",DAYS360('Project Tracker'!$E507,'Project Tracker'!$F507,FALSE))</f>
+        <v/>
+      </c>
       <c r="I507" s="17"/>
     </row>
     <row r="508" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6758,7 +8636,10 @@
       <c r="E508" s="24"/>
       <c r="F508" s="24"/>
       <c r="G508" s="17"/>
-      <c r="H508" s="20"/>
+      <c r="H508" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E508,'Project Tracker'!$F508)&lt;&gt;2,"",DAYS360('Project Tracker'!$E508,'Project Tracker'!$F508,FALSE))</f>
+        <v/>
+      </c>
       <c r="I508" s="17"/>
     </row>
     <row r="509" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6768,7 +8649,10 @@
       <c r="E509" s="24"/>
       <c r="F509" s="24"/>
       <c r="G509" s="17"/>
-      <c r="H509" s="20"/>
+      <c r="H509" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E509,'Project Tracker'!$F509)&lt;&gt;2,"",DAYS360('Project Tracker'!$E509,'Project Tracker'!$F509,FALSE))</f>
+        <v/>
+      </c>
       <c r="I509" s="17"/>
     </row>
     <row r="510" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6778,7 +8662,10 @@
       <c r="E510" s="24"/>
       <c r="F510" s="24"/>
       <c r="G510" s="17"/>
-      <c r="H510" s="20"/>
+      <c r="H510" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E510,'Project Tracker'!$F510)&lt;&gt;2,"",DAYS360('Project Tracker'!$E510,'Project Tracker'!$F510,FALSE))</f>
+        <v/>
+      </c>
       <c r="I510" s="17"/>
     </row>
     <row r="511" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6788,7 +8675,10 @@
       <c r="E511" s="24"/>
       <c r="F511" s="24"/>
       <c r="G511" s="17"/>
-      <c r="H511" s="20"/>
+      <c r="H511" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E511,'Project Tracker'!$F511)&lt;&gt;2,"",DAYS360('Project Tracker'!$E511,'Project Tracker'!$F511,FALSE))</f>
+        <v/>
+      </c>
       <c r="I511" s="17"/>
     </row>
     <row r="512" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6798,7 +8688,10 @@
       <c r="E512" s="24"/>
       <c r="F512" s="24"/>
       <c r="G512" s="17"/>
-      <c r="H512" s="20"/>
+      <c r="H512" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E512,'Project Tracker'!$F512)&lt;&gt;2,"",DAYS360('Project Tracker'!$E512,'Project Tracker'!$F512,FALSE))</f>
+        <v/>
+      </c>
       <c r="I512" s="17"/>
     </row>
     <row r="513" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6808,7 +8701,10 @@
       <c r="E513" s="24"/>
       <c r="F513" s="24"/>
       <c r="G513" s="17"/>
-      <c r="H513" s="20"/>
+      <c r="H513" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E513,'Project Tracker'!$F513)&lt;&gt;2,"",DAYS360('Project Tracker'!$E513,'Project Tracker'!$F513,FALSE))</f>
+        <v/>
+      </c>
       <c r="I513" s="17"/>
     </row>
     <row r="514" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6818,7 +8714,10 @@
       <c r="E514" s="24"/>
       <c r="F514" s="24"/>
       <c r="G514" s="17"/>
-      <c r="H514" s="20"/>
+      <c r="H514" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E514,'Project Tracker'!$F514)&lt;&gt;2,"",DAYS360('Project Tracker'!$E514,'Project Tracker'!$F514,FALSE))</f>
+        <v/>
+      </c>
       <c r="I514" s="17"/>
     </row>
     <row r="515" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6828,7 +8727,10 @@
       <c r="E515" s="24"/>
       <c r="F515" s="24"/>
       <c r="G515" s="17"/>
-      <c r="H515" s="20"/>
+      <c r="H515" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E515,'Project Tracker'!$F515)&lt;&gt;2,"",DAYS360('Project Tracker'!$E515,'Project Tracker'!$F515,FALSE))</f>
+        <v/>
+      </c>
       <c r="I515" s="17"/>
     </row>
     <row r="516" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6838,7 +8740,10 @@
       <c r="E516" s="24"/>
       <c r="F516" s="24"/>
       <c r="G516" s="17"/>
-      <c r="H516" s="20"/>
+      <c r="H516" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E516,'Project Tracker'!$F516)&lt;&gt;2,"",DAYS360('Project Tracker'!$E516,'Project Tracker'!$F516,FALSE))</f>
+        <v/>
+      </c>
       <c r="I516" s="17"/>
     </row>
     <row r="517" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6848,7 +8753,10 @@
       <c r="E517" s="24"/>
       <c r="F517" s="24"/>
       <c r="G517" s="17"/>
-      <c r="H517" s="20"/>
+      <c r="H517" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E517,'Project Tracker'!$F517)&lt;&gt;2,"",DAYS360('Project Tracker'!$E517,'Project Tracker'!$F517,FALSE))</f>
+        <v/>
+      </c>
       <c r="I517" s="17"/>
     </row>
     <row r="518" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6858,7 +8766,10 @@
       <c r="E518" s="24"/>
       <c r="F518" s="24"/>
       <c r="G518" s="17"/>
-      <c r="H518" s="20"/>
+      <c r="H518" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E518,'Project Tracker'!$F518)&lt;&gt;2,"",DAYS360('Project Tracker'!$E518,'Project Tracker'!$F518,FALSE))</f>
+        <v/>
+      </c>
       <c r="I518" s="17"/>
     </row>
     <row r="519" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6868,7 +8779,10 @@
       <c r="E519" s="24"/>
       <c r="F519" s="24"/>
       <c r="G519" s="17"/>
-      <c r="H519" s="20"/>
+      <c r="H519" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E519,'Project Tracker'!$F519)&lt;&gt;2,"",DAYS360('Project Tracker'!$E519,'Project Tracker'!$F519,FALSE))</f>
+        <v/>
+      </c>
       <c r="I519" s="17"/>
     </row>
     <row r="520" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6878,7 +8792,10 @@
       <c r="E520" s="24"/>
       <c r="F520" s="24"/>
       <c r="G520" s="17"/>
-      <c r="H520" s="20"/>
+      <c r="H520" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E520,'Project Tracker'!$F520)&lt;&gt;2,"",DAYS360('Project Tracker'!$E520,'Project Tracker'!$F520,FALSE))</f>
+        <v/>
+      </c>
       <c r="I520" s="17"/>
     </row>
     <row r="521" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6888,7 +8805,10 @@
       <c r="E521" s="24"/>
       <c r="F521" s="24"/>
       <c r="G521" s="17"/>
-      <c r="H521" s="20"/>
+      <c r="H521" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E521,'Project Tracker'!$F521)&lt;&gt;2,"",DAYS360('Project Tracker'!$E521,'Project Tracker'!$F521,FALSE))</f>
+        <v/>
+      </c>
       <c r="I521" s="17"/>
     </row>
     <row r="522" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6898,7 +8818,10 @@
       <c r="E522" s="24"/>
       <c r="F522" s="24"/>
       <c r="G522" s="17"/>
-      <c r="H522" s="20"/>
+      <c r="H522" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E522,'Project Tracker'!$F522)&lt;&gt;2,"",DAYS360('Project Tracker'!$E522,'Project Tracker'!$F522,FALSE))</f>
+        <v/>
+      </c>
       <c r="I522" s="17"/>
     </row>
     <row r="523" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6908,7 +8831,10 @@
       <c r="E523" s="24"/>
       <c r="F523" s="24"/>
       <c r="G523" s="17"/>
-      <c r="H523" s="20"/>
+      <c r="H523" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E523,'Project Tracker'!$F523)&lt;&gt;2,"",DAYS360('Project Tracker'!$E523,'Project Tracker'!$F523,FALSE))</f>
+        <v/>
+      </c>
       <c r="I523" s="17"/>
     </row>
     <row r="524" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6918,7 +8844,10 @@
       <c r="E524" s="24"/>
       <c r="F524" s="24"/>
       <c r="G524" s="17"/>
-      <c r="H524" s="20"/>
+      <c r="H524" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E524,'Project Tracker'!$F524)&lt;&gt;2,"",DAYS360('Project Tracker'!$E524,'Project Tracker'!$F524,FALSE))</f>
+        <v/>
+      </c>
       <c r="I524" s="17"/>
     </row>
     <row r="525" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6928,7 +8857,10 @@
       <c r="E525" s="24"/>
       <c r="F525" s="24"/>
       <c r="G525" s="17"/>
-      <c r="H525" s="20"/>
+      <c r="H525" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E525,'Project Tracker'!$F525)&lt;&gt;2,"",DAYS360('Project Tracker'!$E525,'Project Tracker'!$F525,FALSE))</f>
+        <v/>
+      </c>
       <c r="I525" s="17"/>
     </row>
     <row r="526" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6938,7 +8870,10 @@
       <c r="E526" s="24"/>
       <c r="F526" s="24"/>
       <c r="G526" s="17"/>
-      <c r="H526" s="20"/>
+      <c r="H526" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E526,'Project Tracker'!$F526)&lt;&gt;2,"",DAYS360('Project Tracker'!$E526,'Project Tracker'!$F526,FALSE))</f>
+        <v/>
+      </c>
       <c r="I526" s="17"/>
     </row>
     <row r="527" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6948,7 +8883,10 @@
       <c r="E527" s="24"/>
       <c r="F527" s="24"/>
       <c r="G527" s="17"/>
-      <c r="H527" s="20"/>
+      <c r="H527" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E527,'Project Tracker'!$F527)&lt;&gt;2,"",DAYS360('Project Tracker'!$E527,'Project Tracker'!$F527,FALSE))</f>
+        <v/>
+      </c>
       <c r="I527" s="17"/>
     </row>
     <row r="528" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6958,7 +8896,10 @@
       <c r="E528" s="24"/>
       <c r="F528" s="24"/>
       <c r="G528" s="17"/>
-      <c r="H528" s="20"/>
+      <c r="H528" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E528,'Project Tracker'!$F528)&lt;&gt;2,"",DAYS360('Project Tracker'!$E528,'Project Tracker'!$F528,FALSE))</f>
+        <v/>
+      </c>
       <c r="I528" s="17"/>
     </row>
     <row r="529" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6968,7 +8909,10 @@
       <c r="E529" s="24"/>
       <c r="F529" s="24"/>
       <c r="G529" s="17"/>
-      <c r="H529" s="20"/>
+      <c r="H529" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E529,'Project Tracker'!$F529)&lt;&gt;2,"",DAYS360('Project Tracker'!$E529,'Project Tracker'!$F529,FALSE))</f>
+        <v/>
+      </c>
       <c r="I529" s="17"/>
     </row>
     <row r="530" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6978,7 +8922,10 @@
       <c r="E530" s="24"/>
       <c r="F530" s="24"/>
       <c r="G530" s="17"/>
-      <c r="H530" s="20"/>
+      <c r="H530" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E530,'Project Tracker'!$F530)&lt;&gt;2,"",DAYS360('Project Tracker'!$E530,'Project Tracker'!$F530,FALSE))</f>
+        <v/>
+      </c>
       <c r="I530" s="17"/>
     </row>
     <row r="531" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6988,7 +8935,10 @@
       <c r="E531" s="24"/>
       <c r="F531" s="24"/>
       <c r="G531" s="17"/>
-      <c r="H531" s="20"/>
+      <c r="H531" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E531,'Project Tracker'!$F531)&lt;&gt;2,"",DAYS360('Project Tracker'!$E531,'Project Tracker'!$F531,FALSE))</f>
+        <v/>
+      </c>
       <c r="I531" s="17"/>
     </row>
     <row r="532" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6998,7 +8948,10 @@
       <c r="E532" s="24"/>
       <c r="F532" s="24"/>
       <c r="G532" s="17"/>
-      <c r="H532" s="20"/>
+      <c r="H532" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E532,'Project Tracker'!$F532)&lt;&gt;2,"",DAYS360('Project Tracker'!$E532,'Project Tracker'!$F532,FALSE))</f>
+        <v/>
+      </c>
       <c r="I532" s="17"/>
     </row>
     <row r="533" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7008,7 +8961,10 @@
       <c r="E533" s="24"/>
       <c r="F533" s="24"/>
       <c r="G533" s="17"/>
-      <c r="H533" s="20"/>
+      <c r="H533" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E533,'Project Tracker'!$F533)&lt;&gt;2,"",DAYS360('Project Tracker'!$E533,'Project Tracker'!$F533,FALSE))</f>
+        <v/>
+      </c>
       <c r="I533" s="17"/>
     </row>
     <row r="534" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7018,7 +8974,10 @@
       <c r="E534" s="24"/>
       <c r="F534" s="24"/>
       <c r="G534" s="17"/>
-      <c r="H534" s="20"/>
+      <c r="H534" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E534,'Project Tracker'!$F534)&lt;&gt;2,"",DAYS360('Project Tracker'!$E534,'Project Tracker'!$F534,FALSE))</f>
+        <v/>
+      </c>
       <c r="I534" s="17"/>
     </row>
     <row r="535" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7028,7 +8987,10 @@
       <c r="E535" s="24"/>
       <c r="F535" s="24"/>
       <c r="G535" s="17"/>
-      <c r="H535" s="20"/>
+      <c r="H535" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E535,'Project Tracker'!$F535)&lt;&gt;2,"",DAYS360('Project Tracker'!$E535,'Project Tracker'!$F535,FALSE))</f>
+        <v/>
+      </c>
       <c r="I535" s="17"/>
     </row>
     <row r="536" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7038,7 +9000,10 @@
       <c r="E536" s="24"/>
       <c r="F536" s="24"/>
       <c r="G536" s="17"/>
-      <c r="H536" s="20"/>
+      <c r="H536" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E536,'Project Tracker'!$F536)&lt;&gt;2,"",DAYS360('Project Tracker'!$E536,'Project Tracker'!$F536,FALSE))</f>
+        <v/>
+      </c>
       <c r="I536" s="17"/>
     </row>
     <row r="537" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7048,7 +9013,10 @@
       <c r="E537" s="24"/>
       <c r="F537" s="24"/>
       <c r="G537" s="17"/>
-      <c r="H537" s="20"/>
+      <c r="H537" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E537,'Project Tracker'!$F537)&lt;&gt;2,"",DAYS360('Project Tracker'!$E537,'Project Tracker'!$F537,FALSE))</f>
+        <v/>
+      </c>
       <c r="I537" s="17"/>
     </row>
     <row r="538" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7058,7 +9026,10 @@
       <c r="E538" s="24"/>
       <c r="F538" s="24"/>
       <c r="G538" s="17"/>
-      <c r="H538" s="20"/>
+      <c r="H538" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E538,'Project Tracker'!$F538)&lt;&gt;2,"",DAYS360('Project Tracker'!$E538,'Project Tracker'!$F538,FALSE))</f>
+        <v/>
+      </c>
       <c r="I538" s="17"/>
     </row>
     <row r="539" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7068,7 +9039,10 @@
       <c r="E539" s="24"/>
       <c r="F539" s="24"/>
       <c r="G539" s="17"/>
-      <c r="H539" s="20"/>
+      <c r="H539" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E539,'Project Tracker'!$F539)&lt;&gt;2,"",DAYS360('Project Tracker'!$E539,'Project Tracker'!$F539,FALSE))</f>
+        <v/>
+      </c>
       <c r="I539" s="17"/>
     </row>
     <row r="540" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7078,7 +9052,10 @@
       <c r="E540" s="24"/>
       <c r="F540" s="24"/>
       <c r="G540" s="17"/>
-      <c r="H540" s="20"/>
+      <c r="H540" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E540,'Project Tracker'!$F540)&lt;&gt;2,"",DAYS360('Project Tracker'!$E540,'Project Tracker'!$F540,FALSE))</f>
+        <v/>
+      </c>
       <c r="I540" s="17"/>
     </row>
     <row r="541" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7088,7 +9065,10 @@
       <c r="E541" s="24"/>
       <c r="F541" s="24"/>
       <c r="G541" s="17"/>
-      <c r="H541" s="20"/>
+      <c r="H541" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E541,'Project Tracker'!$F541)&lt;&gt;2,"",DAYS360('Project Tracker'!$E541,'Project Tracker'!$F541,FALSE))</f>
+        <v/>
+      </c>
       <c r="I541" s="17"/>
     </row>
     <row r="542" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7098,7 +9078,10 @@
       <c r="E542" s="24"/>
       <c r="F542" s="24"/>
       <c r="G542" s="17"/>
-      <c r="H542" s="20"/>
+      <c r="H542" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E542,'Project Tracker'!$F542)&lt;&gt;2,"",DAYS360('Project Tracker'!$E542,'Project Tracker'!$F542,FALSE))</f>
+        <v/>
+      </c>
       <c r="I542" s="17"/>
     </row>
     <row r="543" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7108,7 +9091,10 @@
       <c r="E543" s="24"/>
       <c r="F543" s="24"/>
       <c r="G543" s="17"/>
-      <c r="H543" s="20"/>
+      <c r="H543" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E543,'Project Tracker'!$F543)&lt;&gt;2,"",DAYS360('Project Tracker'!$E543,'Project Tracker'!$F543,FALSE))</f>
+        <v/>
+      </c>
       <c r="I543" s="17"/>
     </row>
     <row r="544" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7118,7 +9104,10 @@
       <c r="E544" s="24"/>
       <c r="F544" s="24"/>
       <c r="G544" s="17"/>
-      <c r="H544" s="20"/>
+      <c r="H544" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E544,'Project Tracker'!$F544)&lt;&gt;2,"",DAYS360('Project Tracker'!$E544,'Project Tracker'!$F544,FALSE))</f>
+        <v/>
+      </c>
       <c r="I544" s="17"/>
     </row>
     <row r="545" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7128,7 +9117,10 @@
       <c r="E545" s="24"/>
       <c r="F545" s="24"/>
       <c r="G545" s="17"/>
-      <c r="H545" s="20"/>
+      <c r="H545" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E545,'Project Tracker'!$F545)&lt;&gt;2,"",DAYS360('Project Tracker'!$E545,'Project Tracker'!$F545,FALSE))</f>
+        <v/>
+      </c>
       <c r="I545" s="17"/>
     </row>
     <row r="546" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7138,7 +9130,10 @@
       <c r="E546" s="24"/>
       <c r="F546" s="24"/>
       <c r="G546" s="17"/>
-      <c r="H546" s="20"/>
+      <c r="H546" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E546,'Project Tracker'!$F546)&lt;&gt;2,"",DAYS360('Project Tracker'!$E546,'Project Tracker'!$F546,FALSE))</f>
+        <v/>
+      </c>
       <c r="I546" s="17"/>
     </row>
     <row r="547" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7148,7 +9143,10 @@
       <c r="E547" s="24"/>
       <c r="F547" s="24"/>
       <c r="G547" s="17"/>
-      <c r="H547" s="20"/>
+      <c r="H547" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E547,'Project Tracker'!$F547)&lt;&gt;2,"",DAYS360('Project Tracker'!$E547,'Project Tracker'!$F547,FALSE))</f>
+        <v/>
+      </c>
       <c r="I547" s="17"/>
     </row>
     <row r="548" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7158,7 +9156,10 @@
       <c r="E548" s="24"/>
       <c r="F548" s="24"/>
       <c r="G548" s="17"/>
-      <c r="H548" s="20"/>
+      <c r="H548" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E548,'Project Tracker'!$F548)&lt;&gt;2,"",DAYS360('Project Tracker'!$E548,'Project Tracker'!$F548,FALSE))</f>
+        <v/>
+      </c>
       <c r="I548" s="17"/>
     </row>
     <row r="549" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7168,7 +9169,10 @@
       <c r="E549" s="24"/>
       <c r="F549" s="24"/>
       <c r="G549" s="17"/>
-      <c r="H549" s="20"/>
+      <c r="H549" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E549,'Project Tracker'!$F549)&lt;&gt;2,"",DAYS360('Project Tracker'!$E549,'Project Tracker'!$F549,FALSE))</f>
+        <v/>
+      </c>
       <c r="I549" s="17"/>
     </row>
     <row r="550" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7178,7 +9182,10 @@
       <c r="E550" s="24"/>
       <c r="F550" s="24"/>
       <c r="G550" s="17"/>
-      <c r="H550" s="20"/>
+      <c r="H550" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E550,'Project Tracker'!$F550)&lt;&gt;2,"",DAYS360('Project Tracker'!$E550,'Project Tracker'!$F550,FALSE))</f>
+        <v/>
+      </c>
       <c r="I550" s="17"/>
     </row>
     <row r="551" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7188,7 +9195,10 @@
       <c r="E551" s="24"/>
       <c r="F551" s="24"/>
       <c r="G551" s="17"/>
-      <c r="H551" s="20"/>
+      <c r="H551" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E551,'Project Tracker'!$F551)&lt;&gt;2,"",DAYS360('Project Tracker'!$E551,'Project Tracker'!$F551,FALSE))</f>
+        <v/>
+      </c>
       <c r="I551" s="17"/>
     </row>
     <row r="552" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7198,7 +9208,10 @@
       <c r="E552" s="24"/>
       <c r="F552" s="24"/>
       <c r="G552" s="17"/>
-      <c r="H552" s="20"/>
+      <c r="H552" s="20" t="str">
+        <f>IF(COUNTA('Project Tracker'!$E552,'Project Tracker'!$F552)&lt;&gt;2,"",DAYS360('Project Tracker'!$E552,'Project Tracker'!$F552,FALSE))</f>
+        <v/>
+      </c>
       <c r="I552" s="17"/>
     </row>
     <row r="553" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7352,36 +9365,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C52F64F2-A0CB-432E-B537-8AB164D6506B}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.81640625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="27.54296875" style="26" customWidth="1"/>
-    <col min="3" max="3" width="18.54296875" style="26" customWidth="1"/>
-    <col min="4" max="4" width="27.54296875" style="26" customWidth="1"/>
+    <col min="2" max="2" width="18.08984375" style="26" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="25.26953125" style="26" customWidth="1"/>
     <col min="5" max="16384" width="8.7265625" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C2" s="28">
         <v>45593</v>
@@ -7392,10 +9405,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C3" s="28">
         <v>45594</v>
@@ -7406,10 +9419,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C4" s="28">
         <v>45594</v>
@@ -7420,10 +9433,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C5" s="28">
         <v>45594</v>
@@ -7434,10 +9447,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C6" s="28">
         <v>45596</v>
@@ -7448,15 +9461,57 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C7" s="28">
         <v>45596</v>
       </c>
       <c r="D7" s="29">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45598</v>
+      </c>
+      <c r="D8" s="29">
+        <v>2.0833333333333332E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45599</v>
+      </c>
+      <c r="D9" s="29">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45599</v>
+      </c>
+      <c r="D10" s="29">
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -7490,7 +9545,7 @@
     <row r="2" spans="1:4" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11"/>
       <c r="B2" s="15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -7504,70 +9559,70 @@
     <row r="4" spans="1:4" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>3</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>4</v>
       </c>
       <c r="D4" s="14"/>
     </row>
     <row r="5" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="12"/>
     </row>
     <row r="6" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="12"/>
     </row>
     <row r="8" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
       <c r="B8" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="12"/>
     </row>
     <row r="9" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="B10" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="12"/>
     </row>
@@ -7575,116 +9630,116 @@
       <c r="A11" s="11"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="12"/>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="21"/>
       <c r="C12" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="21"/>
       <c r="C13" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="21"/>
       <c r="C14" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="21"/>
       <c r="C15" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="21"/>
       <c r="C16" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="21"/>
       <c r="C17" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="21"/>
       <c r="C18" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="21"/>
       <c r="C19" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="21"/>
       <c r="C20" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="21"/>
       <c r="C21" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="21"/>
       <c r="C22" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="21"/>
       <c r="C23" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="21"/>
       <c r="C24" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="21"/>
       <c r="C25" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="21"/>
       <c r="C26" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="21"/>
       <c r="C27" s="21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="21"/>
       <c r="C28" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="21"/>
       <c r="C29" s="21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -7704,23 +9759,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8036,22 +10080,29 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066C173-72E5-4455-ACFB-9A7596D30A2B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8078,9 +10129,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066C173-72E5-4455-ACFB-9A7596D30A2B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
